--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,46 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>nama_tempat</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>teks_ulasan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>cleaning</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tokenizing</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>stopword</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>stemming</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>predicted</t>
         </is>
@@ -473,40 +466,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Pantai Batu Bintang</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>lumayan bagusaman untuk anak main dipantainya</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>lumayan bagusaman anak main pantai</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -515,40 +513,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Pantai Citepus</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -557,40 +560,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -599,40 +607,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>ALUN ALUN GADOBANGKONG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luas,mudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>ECON</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luasmudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>['tempat', 'di', 'pelabuhan', 'ratu', 'buat', 'main', 'keluarga', 'cuma', 'jarang', 'tempat', 'untuk', 'berteduh', 'suasana', 'pantai', 'indah', 'banyak', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'lebih', 'di', 'pelihara', 'dan', 'di', 'perindah', 'supaya', 'tempat', 'nya', 'makin', 'bagus']</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>['pelabuhan', 'ratu', 'main', 'keluarga', 'jarang', 'berteduh', 'suasana', 'pantai', 'indah', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'pelihara', 'perindah', 'nya', 'bagus']</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>labuh ratu main keluarga jarang teduh suasana pantai indah tukang dagang parkir luasmudah mudah pelihara indah nya bagus</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>ECON</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>NEUT</t>
         </is>
@@ -641,40 +654,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Tempat nya nongkrong anak plara,keren pokonya tmpat nya asik...bnyk hiburn dan permainan anak</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>tempat nya nongkrong anak plarakeren pokonya tmpat nya asikbnyk hiburn dan permainan anak</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>['tempat', 'nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'dan', 'permainan', 'anak']</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>['nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'permainan', 'anak']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>nya nongkrong anak plarakeren poko tmpat nya asikbnyk hiburn main anak</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -683,40 +701,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Jangilus Monument</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -725,40 +748,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>bagus,,enak buat liburan bersama keluarga</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>bagusenak buat liburan bersama keluarga</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>['bagusenak', 'liburan', 'keluarga']</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>bagusenak libur keluarga</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -767,40 +795,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>PANTAI CIBANGBAN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Life guard nya siaga slalu...toiletnya bersih</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>life guard nya siaga slalutoiletnya bersih</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>['life', 'guard', 'nya', 'siaga', 'slalutoiletnya', 'bersih']</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>['life', 'guard', 'nya', 'siaga', 'slalutoiletnya', 'bersih']</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>life guard nya siaga slalutoiletnya bersih</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -809,40 +842,45 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Lokasi yg nyaman, bangunannya salah satu yg tahan gempa dengan rujukan dari BNPB. Mudah di akses dari jalan raya. Bisa menginap dengan harga yg terjangkau. Menjadi pusat penelitian ketahanan gempa.</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>lokasi yg nyaman bangunannya salah satu yg tahan gempa dengan rujukan dari bnpb mudah di akses dari jalan raya bisa menginap dengan harga yg terjangkau menjadi pusat penelitian ketahanan gempa</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'satu', 'yg', 'tahan', 'gempa', 'dengan', 'rujukan', 'dari', 'bnpb', 'mudah', 'di', 'akses', 'dari', 'jalan', 'raya', 'bisa', 'menginap', 'dengan', 'harga', 'yg', 'terjangkau', 'menjadi', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'yg', 'tahan', 'gempa', 'rujukan', 'bnpb', 'mudah', 'akses', 'jalan', 'raya', 'menginap', 'harga', 'yg', 'terjangkau', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>lokasi yg nyaman bangun salah yg tahan gempa rujuk bnpb mudah akses jalan raya inap harga yg jangkau pusat teliti tahan gempa</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -851,40 +889,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -893,40 +936,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Pantai Citepus</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Keindahan senja yang hangat di bibir pantai dan sajian seafood yang cuma enak dan enak bangeud, plus sahabat-sahabat terbaik sebagai teman makan, bikin timbangan naik deh, dijamin! ððð â¦</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>keindahan senja yang hangat di bibir pantai dan sajian seafood yang cuma enak dan enak bangeud plus sahabatsahabat terbaik sebagai teman makan bikin timbangan naik deh dijamin ððð â</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>['keindahan', 'senja', 'yang', 'hangat', 'di', 'bibir', 'pantai', 'dan', 'sajian', 'seafood', 'yang', 'cuma', 'enak', 'dan', 'enak', 'bangeud', 'plus', 'sahabatsahabat', 'terbaik', 'sebagai', 'teman', 'makan', 'bikin', 'timbangan', 'naik', 'deh', 'dijamin', 'ððð', 'â']</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>['keindahan', 'senja', 'hangat', 'bibir', 'pantai', 'sajian', 'seafood', 'enak', 'enak', 'bangeud', 'plus', 'sahabatsahabat', 'terbaik', 'teman', 'makan', 'bikin', 'timbangan', 'deh', 'dijamin', 'ððð', 'â']</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>indah senja hangat bibir pantai saji seafood enak enak bangeud plus sahabatsahabat baik teman makan bikin timbang deh jamin</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -935,40 +983,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Pantai Karang Sari</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>Pemandangannya bagus, cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>pemandangannya bagus cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>['pemandangannya', 'bagus', 'cuma', 'sekarang', 'pantai', 'nya', 'rusak', 'cuma', 'ada', 'bebatuan', 'doang']</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>['pemandangannya', 'bagus', 'pantai', 'nya', 'rusak', 'bebatuan', 'doang']</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>pandang bagus pantai nya rusak bebatuan doang</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>NEUT</t>
         </is>
@@ -977,40 +1030,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Pantai Karang Sari</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1019,40 +1077,45 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1061,40 +1124,45 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>PANTAI CIBANGBAN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Susah wf.sama signal.,..</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>DIGI</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>susah wfsama signal</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>susah wfsama signal</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>DIGI</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1103,40 +1171,45 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Jangilus Monument</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>Simpang tiga baru sapi jalan raya menuju RSUD plara polres sukabumi DPRD dan perkantoran pemerintah lainya</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>simpang tiga baru sapi jalan raya menuju rsud plara polres sukabumi dprd dan perkantoran pemerintah lainya</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>['simpang', 'tiga', 'baru', 'sapi', 'jalan', 'raya', 'menuju', 'rsud', 'plara', 'polres', 'sukabumi', 'dprd', 'dan', 'perkantoran', 'pemerintah', 'lainya']</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>['simpang', 'sapi', 'jalan', 'raya', 'rsud', 'plara', 'polres', 'sukabumi', 'dprd', 'perkantoran', 'pemerintah', 'lainya']</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>simpang sapi jalan raya rsud plara polres sukabumi dprd kantor perintah lai</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1145,40 +1218,45 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1187,40 +1265,45 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Pantai Batu Bintang</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>CONF</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>CONF</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1229,40 +1312,45 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Pantai Citepus Sukabumi</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1271,40 +1359,45 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>NEUT</t>
         </is>
@@ -1313,40 +1406,45 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>LAND</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>LAND</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1355,40 +1453,45 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>Sayang stay dekat pasar ikan jadi agak macet n bau ikan</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>sayang stay dekat pasar ikan jadi agak macet n bau ikan</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>['sayang', 'stay', 'dekat', 'pasar', 'ikan', 'jadi', 'agak', 'macet', 'n', 'bau', 'ikan']</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>['sayang', 'stay', 'pasar', 'ikan', 'macet', 'n', 'bau', 'ikan']</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>sayang stay pasar ikan macet n bau ikan</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1397,40 +1500,45 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Pantai Citepus Sukabumi</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1439,40 +1547,45 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>Tempat bagus buat olahraga ð Komplit dari mulai lapangan basket, lapangan sepakbola, lintasan atletik,cuma harus dijaga kebersihannya nya ya gaessss+toilet nyað â¦</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>tempat bagus buat olahraga ð komplit dari mulai lapangan basket lapangan sepakbola lintasan atletikcuma harus dijaga kebersihannya nya ya gaesssstoilet nyað â</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>['tempat', 'bagus', 'buat', 'olahraga', 'ð', 'komplit', 'dari', 'mulai', 'lapangan', 'basket', 'lapangan', 'sepakbola', 'lintasan', 'atletikcuma', 'harus', 'dijaga', 'kebersihannya', 'nya', 'ya', 'gaesssstoilet', 'nyað', 'â']</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>['bagus', 'olahraga', 'ð', 'komplit', 'lapangan', 'basket', 'lapangan', 'sepakbola', 'lintasan', 'atletikcuma', 'dijaga', 'kebersihannya', 'nya', 'ya', 'gaesssstoilet', 'nyað', 'â']</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>bagus olahraga komplit lapang basket lapang sepakbola lintas atletikcuma jaga bersih nya ya gaesssstoilet nya</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1481,40 +1594,45 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H26" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1523,40 +1641,45 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>jalannya agak rame.. ya namanya juga jalur padat.. oke.. dekat dengan pelelangan ikan.. kesini buat istirahat.. sambil nyari kuliner khas.. katanya sih ada bakso ikan.. tapi dicari gak dapat.. sempat beli ikan juga.. pokoknya disini surga ikan laut kalau buat oleh2 ke rumah.</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>jalannya agak rame ya namanya juga jalur padat oke dekat dengan pelelangan ikan kesini buat istirahat sambil nyari kuliner khas katanya sih ada bakso ikan tapi dicari gak dapat sempat beli ikan juga pokoknya disini surga ikan laut kalau buat oleh ke rumah</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>['jalannya', 'agak', 'rame', 'ya', 'namanya', 'juga', 'jalur', 'padat', 'oke', 'dekat', 'dengan', 'pelelangan', 'ikan', 'kesini', 'buat', 'istirahat', 'sambil', 'nyari', 'kuliner', 'khas', 'katanya', 'sih', 'ada', 'bakso', 'ikan', 'tapi', 'dicari', 'gak', 'dapat', 'sempat', 'beli', 'ikan', 'juga', 'pokoknya', 'disini', 'surga', 'ikan', 'laut', 'kalau', 'buat', 'oleh', 'ke', 'rumah']</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>['jalannya', 'rame', 'ya', 'namanya', 'jalur', 'padat', 'oke', 'pelelangan', 'ikan', 'kesini', 'istirahat', 'nyari', 'kuliner', 'khas', 'sih', 'bakso', 'ikan', 'dicari', 'gak', 'beli', 'ikan', 'pokoknya', 'surga', 'ikan', 'laut', 'rumah']</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>jalan rame ya nama jalur padat oke lelang ikan kesini istirahat nyari kuliner khas sih bakso ikan cari gak beli ikan pokok surga ikan laut rumah</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H27" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1565,40 +1688,45 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Wisata Alam Pantai Sukawayana</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Di kelola oleh oknum</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>CONF</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>di kelola oleh oknum</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>['di', 'kelola', 'oleh', 'oknum']</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>['kelola', 'oknum']</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>kelola oknum</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>CONF</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1607,40 +1735,45 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Pantai Citepus Sukabumi</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>kamar mandinya gelap</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>kamar mandinya gelap</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>kamar mandi gelap</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H29" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1649,40 +1782,45 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>CONF</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>['skarang', 'lebih', 'sepi', 'dan', 'kebanyakan', 'di', 'pakai', 'oknum', 'pemuda', 'pemudi', 'buat', 'pacaran', 'kadang', 'suka', 'ada', 'yg', 'mabuk', 'atau', 'tawuran', 'anak', 'sekolah']</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>['skarang', 'sepi', 'kebanyakan', 'pakai', 'oknum', 'pemuda', 'pemudi', 'pacaran', 'kadang', 'suka', 'yg', 'mabuk', 'tawuran', 'anak', 'sekolah']</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>skarang sepi banyak pakai oknum pemuda pemudi pacar kadang suka yg mabuk tawur anak sekolah</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>CONF</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1691,40 +1829,45 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Pantai Twenty Cipatuguran</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>ECON</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>ECON</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>INFRA</t>
         </is>
@@ -1733,40 +1876,45 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Taman Bappeda</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>Yuk bisa kali Pemda, dinas atau instansi terkait di rawat fasilitas umumnya.  Hasil pantauan msh banyak yg rusak dan ada pihak2 yg gak bertanggung jawab â¦</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>yuk bisa kali pemda dinas atau instansi terkait di rawat fasilitas umumnya hasil pantauan msh banyak yg rusak dan ada pihak yg gak bertanggung jawab â</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>['yuk', 'bisa', 'kali', 'pemda', 'dinas', 'atau', 'instansi', 'terkait', 'di', 'rawat', 'fasilitas', 'umumnya', 'hasil', 'pantauan', 'msh', 'banyak', 'yg', 'rusak', 'dan', 'ada', 'pihak', 'yg', 'gak', 'bertanggung', 'jawab', 'â']</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>['yuk', 'kali', 'pemda', 'dinas', 'instansi', 'terkait', 'rawat', 'fasilitas', 'hasil', 'pantauan', 'msh', 'yg', 'rusak', 'yg', 'gak', 'bertanggung', 'â']</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>yuk kali pemda dinas instansi kait rawat fasilitas hasil pantau msh yg rusak yg gak tanggung</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H32" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1775,40 +1923,45 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Waterpark Citepus Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>Mantappppp</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>mantappppp</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>['mantappppp']</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>['mantappppp']</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>mantappppp</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="H33" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1817,40 +1970,45 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Wisata Alam Pantai Sukawayana</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>LAND</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>LAND</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1859,40 +2017,45 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Jangilus Monument</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>Tugu jangilus memjadi ikon masuk kota palabuhanratu..kalau seandainya dikasih hiasan kaya lampu akan lebih indah dan menarik...i love palabuhanratu kota kelahiranku.</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>tugu jangilus memjadi ikon masuk kota palabuhanratukalau seandainya dikasih hiasan kaya lampu akan lebih indah dan menariki love palabuhanratu kota kelahiranku</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>['tugu', 'jangilus', 'memjadi', 'ikon', 'masuk', 'kota', 'palabuhanratukalau', 'seandainya', 'dikasih', 'hiasan', 'kaya', 'lampu', 'akan', 'lebih', 'indah', 'dan', 'menariki', 'love', 'palabuhanratu', 'kota', 'kelahiranku']</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>['tugu', 'jangilus', 'memjadi', 'ikon', 'masuk', 'kota', 'palabuhanratukalau', 'seandainya', 'dikasih', 'hiasan', 'kaya', 'lampu', 'indah', 'menariki', 'love', 'palabuhanratu', 'kota', 'kelahiranku']</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>tugu jangilus memjadi ikon masuk kota palabuhanratukalau anda kasih hias kaya lampu indah tarik love palabuhanratu kota lahir</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="H35" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1901,40 +2064,45 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>Jajahannya banyak pilihan dan enak ð Tahu crispy juara, sate padang juga mantul, cilok lumayan, cilor enak, pisang keju enak, sate2 an enak, waduh kalap pokoknya â¦</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>jajahannya banyak pilihan dan enak ð tahu crispy juara sate padang juga mantul cilok lumayan cilor enak pisang keju enak sate an enak waduh kalap pokoknya â</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>['jajahannya', 'banyak', 'pilihan', 'dan', 'enak', 'ð', 'tahu', 'crispy', 'juara', 'sate', 'padang', 'juga', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'waduh', 'kalap', 'pokoknya', 'â']</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>['jajahannya', 'pilihan', 'enak', 'ð', 'crispy', 'juara', 'sate', 'padang', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'kalap', 'pokoknya', 'â']</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>jajah pilih enak crispy juara sate padang mantul cilok lumayan cilor enak pisang keju enak sate an enak kalap pokok</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="H36" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1943,40 +2111,45 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Smile hill Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -1985,40 +2158,45 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Pantai Citepus</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>Pantainya sudah mulai tertata rapi &amp; parkir udah lumayan tertib. Tinggal kesadaran pengunjungnga aja untuk g buang sampah sembarangan. Untuk pengelola mungkin bisa diberbanyak tempat sampah supaya pantai Citepus bisa tetap bersih &amp; nyaman.</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>ECON</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>pantainya sudah mulai tertata rapi parkir udah lumayan tertib tinggal kesadaran pengunjungnga aja untuk g buang sampah sembarangan untuk pengelola mungkin bisa diberbanyak tempat sampah supaya pantai citepus bisa tetap bersih nyaman</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>['pantainya', 'sudah', 'mulai', 'tertata', 'rapi', 'parkir', 'udah', 'lumayan', 'tertib', 'tinggal', 'kesadaran', 'pengunjungnga', 'aja', 'untuk', 'g', 'buang', 'sampah', 'sembarangan', 'untuk', 'pengelola', 'mungkin', 'bisa', 'diberbanyak', 'tempat', 'sampah', 'supaya', 'pantai', 'citepus', 'bisa', 'tetap', 'bersih', 'nyaman']</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>['pantainya', 'tertata', 'rapi', 'parkir', 'udah', 'lumayan', 'tertib', 'tinggal', 'kesadaran', 'pengunjungnga', 'aja', 'g', 'buang', 'sampah', 'sembarangan', 'pengelola', 'diberbanyak', 'sampah', 'pantai', 'citepus', 'bersih', 'nyaman']</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>pantai tata rapi parkir udah lumayan tertib tinggal sadar pengunjungnga aja g buang sampah sembarang kelola banyak sampah pantai citepus bersih nyaman</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>ECON</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>INFRA</t>
         </is>
@@ -2027,40 +2205,45 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>Tempat nongkrong asik,banyak juga berbagai kuliner - kuliner di alun - alun pelabuhan ratu,tidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>CONF</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>tempat nongkrong asikbanyak juga berbagai kuliner kuliner di alun alun pelabuhan ratutidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>['tempat', 'nongkrong', 'asikbanyak', 'juga', 'berbagai', 'kuliner', 'kuliner', 'di', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'ada', 'tiket', 'masuk', 'untuk', 'main', 'ke', 'dalam', 'nya', 'tapi', 'untuk', 'sekarang', 'diabatasi', 'karena', 'pandemi', 'wajib', 'pakai', 'masker', 'dan', 'dilarang', 'berkerumun']</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>['nongkrong', 'asikbanyak', 'kuliner', 'kuliner', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'tiket', 'masuk', 'main', 'nya', 'diabatasi', 'pandemi', 'wajib', 'pakai', 'masker', 'dilarang', 'berkerumun']</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>nongkrong asikbanyak kuliner kuliner alun alun labuh ratutidak tiket masuk main nya diabatasi pandemi wajib pakai masker larang kerumun</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>CONF</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -2069,40 +2252,45 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya. Detail bajunya bagus banget</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>LAND</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya detail bajunya bagus banget</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>['baju', 'baju', 'yg', 'tetsedia', 'untuk', 'di', 'sewakan', 'sangat', 'bagus', 'dan', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'dengan', 'ke', 'inginan', 'saya', 'detail', 'bajunya', 'bagus', 'banget']</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>['baju', 'baju', 'yg', 'tetsedia', 'sewakan', 'bagus', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'inginan', 'detail', 'bajunya', 'bagus', 'banget']</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>baju baju yg tetsedia sewa bagus riquesan buat baju nya sesuai banget ingin detail baju bagus banget</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>LAND</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>NEUT</t>
         </is>
@@ -2111,40 +2299,45 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>Pantai nyaman, tapi mohon pihak pengelola mohon dengan sangat, sediakan tempat sampah atau Peraturan Dilarang Buang Sampah</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>CONF</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>pantai nyaman tapi mohon pihak pengelola mohon dengan sangat sediakan tempat sampah atau peraturan dilarang buang sampah</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>['pantai', 'nyaman', 'tapi', 'mohon', 'pihak', 'pengelola', 'mohon', 'dengan', 'sangat', 'sediakan', 'tempat', 'sampah', 'atau', 'peraturan', 'dilarang', 'buang', 'sampah']</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>['pantai', 'nyaman', 'mohon', 'pengelola', 'mohon', 'sediakan', 'sampah', 'peraturan', 'dilarang', 'buang', 'sampah']</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>pantai nyaman mohon kelola mohon sedia sampah atur larang buang sampah</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>CONF</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>INFRA</t>
         </is>
@@ -2153,40 +2346,45 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Pantai Batu Bintang</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>Pertama ngecamp pinggir pantai tuu rasanya,MasyaAllah.. Pantai ini tu,deket ke warung,deket ke mushola,air untuk mandi lancar.tapi,kalau mau cam di tarif lagi untuk biaya kebersihan 1 tenda 20-25k untuk yang mau ikut â¦</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>ECON</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>pertama ngecamp pinggir pantai tuu rasanyamasyaallah pantai ini tudeket ke warungdeket ke musholaair untuk mandi lancartapikalau mau cam di tarif lagi untuk biaya kebersihan tenda k untuk yang mau ikut â</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>['pertama', 'ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'ini', 'tudeket', 'ke', 'warungdeket', 'ke', 'musholaair', 'untuk', 'mandi', 'lancartapikalau', 'mau', 'cam', 'di', 'tarif', 'lagi', 'untuk', 'biaya', 'kebersihan', 'tenda', 'k', 'untuk', 'yang', 'mau', 'ikut', 'â']</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>['ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'tudeket', 'warungdeket', 'musholaair', 'mandi', 'lancartapikalau', 'cam', 'tarif', 'biaya', 'kebersihan', 'tenda', 'k', 'â']</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>ngecamp pinggir pantai tuu rasanyamasyaallah pantai tudeket warungdeket musholaair mandi lancartapikalau cam tarif biaya bersih tenda k</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>ECON</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -2195,40 +2393,45 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>CONF</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>CONF</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>
@@ -2237,40 +2440,45 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>Keren nih tempatnya, sambil istirahat trus pesen kelapa muda , duh di seruput, alamak hati senang , ingat kerjaan nya setelah di jakarta aja ya, â¦</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>keren nih tempatnya sambil istirahat trus pesen kelapa muda duh di seruput alamak hati senang ingat kerjaan nya setelah di jakarta aja ya â</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>['keren', 'nih', 'tempatnya', 'sambil', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'di', 'seruput', 'alamak', 'hati', 'senang', 'ingat', 'kerjaan', 'nya', 'setelah', 'di', 'jakarta', 'aja', 'ya', 'â']</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>['keren', 'nih', 'tempatnya', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'seruput', 'alamak', 'hati', 'senang', 'kerjaan', 'nya', 'jakarta', 'aja', 'ya', 'â']</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>keren nih tempat istirahat trus sen kelapa muda duh seruput alamak hati senang kerja nya jakarta aja ya</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
       <c r="H44" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
+          <t>Pasir pantai tidak tajam, lumayan bersih, banyak toilet, kamar mandi dan musola. Harga makanan dan minuman sesuai kantong.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lumayan bagusaman untuk anak main dipantainya</t>
+          <t>pasir pantai tidak tajam lumayan bersih banyak toilet kamar mandi dan musola harga makanan dan minuman sesuai kantong</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
+          <t>['pasir', 'pantai', 'tidak', 'tajam', 'lumayan', 'bersih', 'banyak', 'toilet', 'kamar', 'mandi', 'dan', 'musola', 'harga', 'makanan', 'dan', 'minuman', 'sesuai', 'kantong']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
+          <t>['pasir', 'pantai', 'tajam', 'lumayan', 'bersih', 'toilet', 'kamar', 'mandi', 'musola', 'harga', 'makanan', 'minuman', 'sesuai', 'kantong']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>lumayan bagusaman anak main pantai</t>
+          <t>pasir pantai tajam lumayan bersih toilet kamar mandi musola harga makan minum sesuai kantong</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -513,42 +513,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -560,42 +560,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
+          <t>Untuk tgl 16 mei 2025 strukturnya untuk sebagian masih sedang dalam perbaikan. Toilet yg tersedia di dekat alun2 untuk yang perempuan sudah tidak ada kunci nya. Dan kebetulan juga waktu saya berkunjung stand pedagang dan pameran sudah siap â¦</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
+          <t>untuk tgl mei strukturnya untuk sebagian masih sedang dalam perbaikan toilet yg tersedia di dekat alun untuk yang perempuan sudah tidak ada kunci nya dan kebetulan juga waktu saya berkunjung stand pedagang dan pameran sudah siap â</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
+          <t>['untuk', 'tgl', 'mei', 'strukturnya', 'untuk', 'sebagian', 'masih', 'sedang', 'dalam', 'perbaikan', 'toilet', 'yg', 'tersedia', 'di', 'dekat', 'alun', 'untuk', 'yang', 'perempuan', 'sudah', 'tidak', 'ada', 'kunci', 'nya', 'dan', 'kebetulan', 'juga', 'waktu', 'saya', 'berkunjung', 'stand', 'pedagang', 'dan', 'pameran', 'sudah', 'siap', 'â']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
+          <t>['tgl', 'mei', 'strukturnya', 'perbaikan', 'toilet', 'yg', 'tersedia', 'alun', 'perempuan', 'kunci', 'nya', 'berkunjung', 'stand', 'pedagang', 'pameran', 'â']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
+          <t>tgl mei struktur baik toilet yg sedia alun perempuan kunci nya kunjung stand dagang pamer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -607,200 +607,200 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luas,mudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+          <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luasmudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+          <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['tempat', 'di', 'pelabuhan', 'ratu', 'buat', 'main', 'keluarga', 'cuma', 'jarang', 'tempat', 'untuk', 'berteduh', 'suasana', 'pantai', 'indah', 'banyak', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'lebih', 'di', 'pelihara', 'dan', 'di', 'perindah', 'supaya', 'tempat', 'nya', 'makin', 'bagus']</t>
+          <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['pelabuhan', 'ratu', 'main', 'keluarga', 'jarang', 'berteduh', 'suasana', 'pantai', 'indah', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'pelihara', 'perindah', 'nya', 'bagus']</t>
+          <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>labuh ratu main keluarga jarang teduh suasana pantai indah tukang dagang parkir luasmudah mudah pelihara indah nya bagus</t>
+          <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tempat nya nongkrong anak plara,keren pokonya tmpat nya asik...bnyk hiburn dan permainan anak</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>tempat nya nongkrong anak plarakeren pokonya tmpat nya asikbnyk hiburn dan permainan anak</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'dan', 'permainan', 'anak']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'permainan', 'anak']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nya nongkrong anak plarakeren poko tmpat nya asikbnyk hiburn main anak</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
+          <t>Bagus cm tmpat smpah sedikit.. ama pedagang julid ge bnyk Parkir liar bnyk View lumayan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
+          <t>bagus cm tmpat smpah sedikit ama pedagang julid ge bnyk parkir liar bnyk view lumayan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
+          <t>['bagus', 'cm', 'tmpat', 'smpah', 'sedikit', 'ama', 'pedagang', 'julid', 'ge', 'bnyk', 'parkir', 'liar', 'bnyk', 'view', 'lumayan']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
+          <t>['bagus', 'cm', 'tmpat', 'smpah', 'ama', 'pedagang', 'julid', 'ge', 'bnyk', 'parkir', 'liar', 'bnyk', 'view', 'lumayan']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
+          <t>bagus cm tmpat smpah ama dagang julid ge bnyk parkir liar bnyk view lumayan</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bagus,,enak buat liburan bersama keluarga</t>
+          <t>Pemandangannya bagus, cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>bagusenak buat liburan bersama keluarga</t>
+          <t>pemandangannya bagus cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
+          <t>['pemandangannya', 'bagus', 'cuma', 'sekarang', 'pantai', 'nya', 'rusak', 'cuma', 'ada', 'bebatuan', 'doang']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['bagusenak', 'liburan', 'keluarga']</t>
+          <t>['pemandangannya', 'bagus', 'pantai', 'nya', 'rusak', 'bebatuan', 'doang']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>bagusenak libur keluarga</t>
+          <t>pandang bagus pantai nya rusak bebatuan doang</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Life guard nya siaga slalu...toiletnya bersih</t>
+          <t>A comfortable square for resting and chatting with family. The place is very spacious, you can also enjoy culinary activities. There is a mosque that is very comfortable for worship, clean toilets, many separate ablution areas for brothers â¦</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -810,22 +810,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>life guard nya siaga slalutoiletnya bersih</t>
+          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers â</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['life', 'guard', 'nya', 'siaga', 'slalutoiletnya', 'bersih']</t>
+          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['life', 'guard', 'nya', 'siaga', 'slalutoiletnya', 'bersih']</t>
+          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>life guard nya siaga slalutoiletnya bersih</t>
+          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -842,42 +842,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lokasi yg nyaman, bangunannya salah satu yg tahan gempa dengan rujukan dari BNPB. Mudah di akses dari jalan raya. Bisa menginap dengan harga yg terjangkau. Menjadi pusat penelitian ketahanan gempa.</t>
+          <t>Di kelola oleh oknum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>lokasi yg nyaman bangunannya salah satu yg tahan gempa dengan rujukan dari bnpb mudah di akses dari jalan raya bisa menginap dengan harga yg terjangkau menjadi pusat penelitian ketahanan gempa</t>
+          <t>di kelola oleh oknum</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'satu', 'yg', 'tahan', 'gempa', 'dengan', 'rujukan', 'dari', 'bnpb', 'mudah', 'di', 'akses', 'dari', 'jalan', 'raya', 'bisa', 'menginap', 'dengan', 'harga', 'yg', 'terjangkau', 'menjadi', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
+          <t>['di', 'kelola', 'oleh', 'oknum']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'yg', 'tahan', 'gempa', 'rujukan', 'bnpb', 'mudah', 'akses', 'jalan', 'raya', 'menginap', 'harga', 'yg', 'terjangkau', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
+          <t>['kelola', 'oknum']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lokasi yg nyaman bangun salah yg tahan gempa rujuk bnpb mudah akses jalan raya inap harga yg jangkau pusat teliti tahan gempa</t>
+          <t>kelola oknum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -889,47 +889,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Menikmati</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>menikmati</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['menikmati']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['menikmati']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>nikmat</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
@@ -941,37 +941,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Keindahan senja yang hangat di bibir pantai dan sajian seafood yang cuma enak dan enak bangeud, plus sahabat-sahabat terbaik sebagai teman makan, bikin timbangan naik deh, dijamin! ððð â¦</t>
+          <t>Pantainya bersih, yang terpenting harga makanan dan minuman super murah,parkir jg normal..</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>keindahan senja yang hangat di bibir pantai dan sajian seafood yang cuma enak dan enak bangeud plus sahabatsahabat terbaik sebagai teman makan bikin timbangan naik deh dijamin ððð â</t>
+          <t>pantainya bersih yang terpenting harga makanan dan minuman super murahparkir jg normal</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['keindahan', 'senja', 'yang', 'hangat', 'di', 'bibir', 'pantai', 'dan', 'sajian', 'seafood', 'yang', 'cuma', 'enak', 'dan', 'enak', 'bangeud', 'plus', 'sahabatsahabat', 'terbaik', 'sebagai', 'teman', 'makan', 'bikin', 'timbangan', 'naik', 'deh', 'dijamin', 'ððð', 'â']</t>
+          <t>['pantainya', 'bersih', 'yang', 'terpenting', 'harga', 'makanan', 'dan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['keindahan', 'senja', 'hangat', 'bibir', 'pantai', 'sajian', 'seafood', 'enak', 'enak', 'bangeud', 'plus', 'sahabatsahabat', 'terbaik', 'teman', 'makan', 'bikin', 'timbangan', 'deh', 'dijamin', 'ððð', 'â']</t>
+          <t>['pantainya', 'bersih', 'terpenting', 'harga', 'makanan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>indah senja hangat bibir pantai saji seafood enak enak bangeud plus sahabatsahabat baik teman makan bikin timbang deh jamin</t>
+          <t>pantai bersih penting harga makan minum super murahparkir jg normal</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -983,59 +983,59 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pemandangannya bagus, cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>pemandangannya bagus cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['pemandangannya', 'bagus', 'cuma', 'sekarang', 'pantai', 'nya', 'rusak', 'cuma', 'ada', 'bebatuan', 'doang']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['pemandangannya', 'bagus', 'pantai', 'nya', 'rusak', 'bebatuan', 'doang']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>pandang bagus pantai nya rusak bebatuan doang</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+          <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+          <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+          <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1077,42 +1077,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1124,42 +1124,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Susah wf.sama signal.,..</t>
+          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1171,59 +1171,59 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Simpang tiga baru sapi jalan raya menuju RSUD plara polres sukabumi DPRD dan perkantoran pemerintah lainya</t>
+          <t>Kapan kapan ke sini dah</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>simpang tiga baru sapi jalan raya menuju rsud plara polres sukabumi dprd dan perkantoran pemerintah lainya</t>
+          <t>kapan kapan ke sini dah</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['simpang', 'tiga', 'baru', 'sapi', 'jalan', 'raya', 'menuju', 'rsud', 'plara', 'polres', 'sukabumi', 'dprd', 'dan', 'perkantoran', 'pemerintah', 'lainya']</t>
+          <t>['kapan', 'kapan', 'ke', 'sini', 'dah']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['simpang', 'sapi', 'jalan', 'raya', 'rsud', 'plara', 'polres', 'sukabumi', 'dprd', 'perkantoran', 'pemerintah', 'lainya']</t>
+          <t>['dah']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>simpang sapi jalan raya rsud plara polres sukabumi dprd kantor perintah lai</t>
+          <t>dah</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>Jajahannya banyak pilihan dan enak ð Tahu crispy juara, sate padang juga mantul, cilok lumayan, cilor enak, pisang keju enak, sate2 an enak, waduh kalap pokoknya â¦</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1233,22 +1233,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>jajahannya banyak pilihan dan enak ð tahu crispy juara sate padang juga mantul cilok lumayan cilor enak pisang keju enak sate an enak waduh kalap pokoknya â</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+          <t>['jajahannya', 'banyak', 'pilihan', 'dan', 'enak', 'ð', 'tahu', 'crispy', 'juara', 'sate', 'padang', 'juga', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'waduh', 'kalap', 'pokoknya', 'â']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+          <t>['jajahannya', 'pilihan', 'enak', 'ð', 'crispy', 'juara', 'sate', 'padang', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'kalap', 'pokoknya', 'â']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+          <t>jajah pilih enak crispy juara sate padang mantul cilok lumayan cilor enak pisang keju enak sate an enak kalap pokok</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1265,89 +1265,89 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>nongki chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1374,22 +1374,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
+          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1399,49 +1399,49 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>Pantai ci letuh Sukabumi Jabar yang indah,,nyaman dan ramah..</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>pantai ci letuh sukabumi jabar yang indahnyaman dan ramah</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
+          <t>['pantai', 'ci', 'letuh', 'sukabumi', 'jabar', 'yang', 'indahnyaman', 'dan', 'ramah']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
+          <t>['pantai', 'ci', 'letuh', 'sukabumi', 'jabar', 'indahnyaman', 'ramah']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
+          <t>pantai ci letuh sukabumi jabar indahnyaman ramah</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1453,42 +1453,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sayang stay dekat pasar ikan jadi agak macet n bau ikan</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>sayang stay dekat pasar ikan jadi agak macet n bau ikan</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['sayang', 'stay', 'dekat', 'pasar', 'ikan', 'jadi', 'agak', 'macet', 'n', 'bau', 'ikan']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['sayang', 'stay', 'pasar', 'ikan', 'macet', 'n', 'bau', 'ikan']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>sayang stay pasar ikan macet n bau ikan</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1500,42 +1500,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tempat bagus buat olahraga ð Komplit dari mulai lapangan basket, lapangan sepakbola, lintasan atletik,cuma harus dijaga kebersihannya nya ya gaessss+toilet nyað â¦</t>
+          <t>Sampai masih pagi Nama pantai baru tau dikasih tau google ð¤­ Warung tutup bulan puasa. Toilet blm buka mesti minta tolong buat dibuka. Airnya â¦</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tempat bagus buat olahraga ð komplit dari mulai lapangan basket lapangan sepakbola lintasan atletikcuma harus dijaga kebersihannya nya ya gaesssstoilet nyað â</t>
+          <t>sampai masih pagi nama pantai baru tau dikasih tau google ð warung tutup bulan puasa toilet blm buka mesti minta tolong buat dibuka airnya â</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['tempat', 'bagus', 'buat', 'olahraga', 'ð', 'komplit', 'dari', 'mulai', 'lapangan', 'basket', 'lapangan', 'sepakbola', 'lintasan', 'atletikcuma', 'harus', 'dijaga', 'kebersihannya', 'nya', 'ya', 'gaesssstoilet', 'nyað', 'â']</t>
+          <t>['sampai', 'masih', 'pagi', 'nama', 'pantai', 'baru', 'tau', 'dikasih', 'tau', 'google', 'ð', 'warung', 'tutup', 'bulan', 'puasa', 'toilet', 'blm', 'buka', 'mesti', 'minta', 'tolong', 'buat', 'dibuka', 'airnya', 'â']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['bagus', 'olahraga', 'ð', 'komplit', 'lapangan', 'basket', 'lapangan', 'sepakbola', 'lintasan', 'atletikcuma', 'dijaga', 'kebersihannya', 'nya', 'ya', 'gaesssstoilet', 'nyað', 'â']</t>
+          <t>['pagi', 'nama', 'pantai', 'tau', 'dikasih', 'tau', 'google', 'ð', 'warung', 'tutup', 'puasa', 'toilet', 'blm', 'buka', 'mesti', 'tolong', 'dibuka', 'airnya', 'â']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>bagus olahraga komplit lapang basket lapang sepakbola lintas atletikcuma jaga bersih nya ya gaesssstoilet nya</t>
+          <t>pagi nama pantai tau kasih tau google warung tutup puasa toilet blm buka mesti tolong buka air</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1594,12 +1594,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
+          <t>Kotor alun alunnya banyak sampah...mampir ke masjid di alun2 bersih dan nyaman</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1609,22 +1609,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
+          <t>kotor alun alunnya banyak sampahmampir ke masjid di alun bersih dan nyaman</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
+          <t>['kotor', 'alun', 'alunnya', 'banyak', 'sampahmampir', 'ke', 'masjid', 'di', 'alun', 'bersih', 'dan', 'nyaman']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
+          <t>['kotor', 'alun', 'alunnya', 'sampahmampir', 'masjid', 'alun', 'bersih', 'nyaman']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
+          <t>kotor alun alun sampahmampir masjid alun bersih nyaman</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1641,12 +1641,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jalannya agak rame.. ya namanya juga jalur padat.. oke.. dekat dengan pelelangan ikan.. kesini buat istirahat.. sambil nyari kuliner khas.. katanya sih ada bakso ikan.. tapi dicari gak dapat.. sempat beli ikan juga.. pokoknya disini surga ikan laut kalau buat oleh2 ke rumah.</t>
+          <t>Air terlihat agak kotor, pasirnya hitam.. Mungkin bagi yang terbiasa ke pantai wilayah Jawa bagian timur akan merasa kurang nyaman</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jalannya agak rame ya namanya juga jalur padat oke dekat dengan pelelangan ikan kesini buat istirahat sambil nyari kuliner khas katanya sih ada bakso ikan tapi dicari gak dapat sempat beli ikan juga pokoknya disini surga ikan laut kalau buat oleh ke rumah</t>
+          <t>air terlihat agak kotor pasirnya hitam mungkin bagi yang terbiasa ke pantai wilayah jawa bagian timur akan merasa kurang nyaman</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['jalannya', 'agak', 'rame', 'ya', 'namanya', 'juga', 'jalur', 'padat', 'oke', 'dekat', 'dengan', 'pelelangan', 'ikan', 'kesini', 'buat', 'istirahat', 'sambil', 'nyari', 'kuliner', 'khas', 'katanya', 'sih', 'ada', 'bakso', 'ikan', 'tapi', 'dicari', 'gak', 'dapat', 'sempat', 'beli', 'ikan', 'juga', 'pokoknya', 'disini', 'surga', 'ikan', 'laut', 'kalau', 'buat', 'oleh', 'ke', 'rumah']</t>
+          <t>['air', 'terlihat', 'agak', 'kotor', 'pasirnya', 'hitam', 'mungkin', 'bagi', 'yang', 'terbiasa', 'ke', 'pantai', 'wilayah', 'jawa', 'bagian', 'timur', 'akan', 'merasa', 'kurang', 'nyaman']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['jalannya', 'rame', 'ya', 'namanya', 'jalur', 'padat', 'oke', 'pelelangan', 'ikan', 'kesini', 'istirahat', 'nyari', 'kuliner', 'khas', 'sih', 'bakso', 'ikan', 'dicari', 'gak', 'beli', 'ikan', 'pokoknya', 'surga', 'ikan', 'laut', 'rumah']</t>
+          <t>['air', 'kotor', 'pasirnya', 'hitam', 'terbiasa', 'pantai', 'wilayah', 'jawa', 'timur', 'nyaman']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>jalan rame ya nama jalur padat oke lelang ikan kesini istirahat nyari kuliner khas sih bakso ikan cari gak beli ikan pokok surga ikan laut rumah</t>
+          <t>air kotor pasir hitam biasa pantai wilayah jawa timur nyaman</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1688,42 +1688,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Di kelola oleh oknum</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>di kelola oleh oknum</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['di', 'kelola', 'oleh', 'oknum']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['kelola', 'oknum']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>kelola oknum</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1735,12 +1735,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Taman Bappeda</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Tempat nyaman tapi patung kura kura banyak di rusak oleh orang yang tidak bertanggung jawab.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1750,22 +1750,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>tempat nyaman tapi patung kura kura banyak di rusak oleh orang yang tidak bertanggung jawab</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['tempat', 'nyaman', 'tapi', 'patung', 'kura', 'kura', 'banyak', 'di', 'rusak', 'oleh', 'orang', 'yang', 'tidak', 'bertanggung', 'jawab']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['nyaman', 'patung', 'kura', 'kura', 'rusak', 'orang', 'bertanggung']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>nyaman patung kura kura rusak orang tanggung</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1829,89 +1829,89 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>bagus,,enak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>bagusenak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['bagusenak', 'liburan', 'keluarga']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>bagusenak libur keluarga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Taman Bappeda</t>
+          <t>Smile hill Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Yuk bisa kali Pemda, dinas atau instansi terkait di rawat fasilitas umumnya.  Hasil pantauan msh banyak yg rusak dan ada pihak2 yg gak bertanggung jawab â¦</t>
+          <t>Bagus tempatnya, apa lagi kalau naik ke atas bukitnyaa,. Kreen..  Tpi klau sdah jam 16.30 gak bisa lagi buat naik ke bukitnya, karna pagar sdah ditutup..</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>yuk bisa kali pemda dinas atau instansi terkait di rawat fasilitas umumnya hasil pantauan msh banyak yg rusak dan ada pihak yg gak bertanggung jawab â</t>
+          <t>bagus tempatnya apa lagi kalau naik ke atas bukitnyaa kreen tpi klau sdah jam gak bisa lagi buat naik ke bukitnya karna pagar sdah ditutup</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['yuk', 'bisa', 'kali', 'pemda', 'dinas', 'atau', 'instansi', 'terkait', 'di', 'rawat', 'fasilitas', 'umumnya', 'hasil', 'pantauan', 'msh', 'banyak', 'yg', 'rusak', 'dan', 'ada', 'pihak', 'yg', 'gak', 'bertanggung', 'jawab', 'â']</t>
+          <t>['bagus', 'tempatnya', 'apa', 'lagi', 'kalau', 'naik', 'ke', 'atas', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bisa', 'lagi', 'buat', 'naik', 'ke', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['yuk', 'kali', 'pemda', 'dinas', 'instansi', 'terkait', 'rawat', 'fasilitas', 'hasil', 'pantauan', 'msh', 'yg', 'rusak', 'yg', 'gak', 'bertanggung', 'â']</t>
+          <t>['bagus', 'tempatnya', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>yuk kali pemda dinas instansi kait rawat fasilitas hasil pantau msh yg rusak yg gak tanggung</t>
+          <t>bagus tempat bukitnyaa kreen tpi klau sdah jam gak bukit karna pagar sdah tutup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mantappppp</t>
+          <t>Tempatnya ramai, pemandangannya bagus, tempat yang tepat untuk mengajak anak-anak bermain. Tempat yang sempurna untuk berfoto, meskipun tidak terlalu bersih dan agak sulit â¦</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1938,22 +1938,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>mantappppp</t>
+          <t>tempatnya ramai pemandangannya bagus tempat yang tepat untuk mengajak anakanak bermain tempat yang sempurna untuk berfoto meskipun tidak terlalu bersih dan agak sulit â</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['mantappppp']</t>
+          <t>['tempatnya', 'ramai', 'pemandangannya', 'bagus', 'tempat', 'yang', 'tepat', 'untuk', 'mengajak', 'anakanak', 'bermain', 'tempat', 'yang', 'sempurna', 'untuk', 'berfoto', 'meskipun', 'tidak', 'terlalu', 'bersih', 'dan', 'agak', 'sulit', 'â']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['mantappppp']</t>
+          <t>['tempatnya', 'ramai', 'pemandangannya', 'bagus', 'mengajak', 'anakanak', 'bermain', 'sempurna', 'berfoto', 'bersih', 'sulit', 'â']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>mantappppp</t>
+          <t>tempat ramai pandang bagus ajak anakanak main sempurna foto bersih sulit</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1970,12 +1970,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pas main kesini lge tidk terlalu rame padahal hari libur. Ampe di lokasi kita d tawarin ibu2 yg punya punya  saung untuk sewa saungnya. Krn gak terlalu rame kami dapat harga Rp 50.000,- (bisa sharian di pakenya). â¦</t>
+          <t>Buka setiap hari, tiket masuk kisaran 20 ribu. Tempat nyaman,luas ,kolam cukup banyak ,  kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia. â¦</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1985,22 +1985,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk terlalu rame padahal hari libur ampe di lokasi kita d tawarin ibu yg punya punya saung untuk sewa saungnya krn gak terlalu rame kami dapat harga rp bisa sharian di pakenya â</t>
+          <t>buka setiap hari tiket masuk kisaran ribu tempat nyamanluas kolam cukup banyak kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia â</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'terlalu', 'rame', 'padahal', 'hari', 'libur', 'ampe', 'di', 'lokasi', 'kita', 'd', 'tawarin', 'ibu', 'yg', 'punya', 'punya', 'saung', 'untuk', 'sewa', 'saungnya', 'krn', 'gak', 'terlalu', 'rame', 'kami', 'dapat', 'harga', 'rp', 'bisa', 'sharian', 'di', 'pakenya', 'â']</t>
+          <t>['buka', 'setiap', 'hari', 'tiket', 'masuk', 'kisaran', 'ribu', 'tempat', 'nyamanluas', 'kolam', 'cukup', 'banyak', 'kantin', 'dan', 'tempat', 'sewa', 'ban', 'juga', 'ada', 'tempat', 'berteduh', 'atau', 'bale', 'juga', 'tersedia', 'â']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['pas', 'main', 'kesini', 'lge', 'tidk', 'rame', 'libur', 'ampe', 'lokasi', 'd', 'tawarin', 'yg', 'saung', 'sewa', 'saungnya', 'krn', 'gak', 'rame', 'harga', 'rp', 'sharian', 'pakenya', 'â']</t>
+          <t>['buka', 'tiket', 'masuk', 'kisaran', 'ribu', 'nyamanluas', 'kolam', 'kantin', 'sewa', 'ban', 'berteduh', 'bale', 'tersedia', 'â']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>pas main kesini lge tidk rame libur ampe lokasi d tawarin yg saung sewa saung krn gak rame harga rp sharian pakenya</t>
+          <t>buka tiket masuk kisar ribu nyamanluas kolam kantin sewa ban teduh bale sedia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2017,12 +2017,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tugu jangilus memjadi ikon masuk kota palabuhanratu..kalau seandainya dikasih hiasan kaya lampu akan lebih indah dan menarik...i love palabuhanratu kota kelahiranku.</t>
+          <t>Kerennn</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2032,22 +2032,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tugu jangilus memjadi ikon masuk kota palabuhanratukalau seandainya dikasih hiasan kaya lampu akan lebih indah dan menariki love palabuhanratu kota kelahiranku</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'memjadi', 'ikon', 'masuk', 'kota', 'palabuhanratukalau', 'seandainya', 'dikasih', 'hiasan', 'kaya', 'lampu', 'akan', 'lebih', 'indah', 'dan', 'menariki', 'love', 'palabuhanratu', 'kota', 'kelahiranku']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'memjadi', 'ikon', 'masuk', 'kota', 'palabuhanratukalau', 'seandainya', 'dikasih', 'hiasan', 'kaya', 'lampu', 'indah', 'menariki', 'love', 'palabuhanratu', 'kota', 'kelahiranku']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>tugu jangilus memjadi ikon masuk kota palabuhanratukalau anda kasih hias kaya lampu indah tarik love palabuhanratu kota lahir</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2064,42 +2064,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jajahannya banyak pilihan dan enak ð Tahu crispy juara, sate padang juga mantul, cilok lumayan, cilor enak, pisang keju enak, sate2 an enak, waduh kalap pokoknya â¦</t>
+          <t>Enak sih pantai nya ngga kotor cuma pasir nya aja yg warna coklat ngga kaya Sawarna yg pasir nya masi putih ðð â¦</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jajahannya banyak pilihan dan enak ð tahu crispy juara sate padang juga mantul cilok lumayan cilor enak pisang keju enak sate an enak waduh kalap pokoknya â</t>
+          <t>enak sih pantai nya ngga kotor cuma pasir nya aja yg warna coklat ngga kaya sawarna yg pasir nya masi putih ðð â</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['jajahannya', 'banyak', 'pilihan', 'dan', 'enak', 'ð', 'tahu', 'crispy', 'juara', 'sate', 'padang', 'juga', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'waduh', 'kalap', 'pokoknya', 'â']</t>
+          <t>['enak', 'sih', 'pantai', 'nya', 'ngga', 'kotor', 'cuma', 'pasir', 'nya', 'aja', 'yg', 'warna', 'coklat', 'ngga', 'kaya', 'sawarna', 'yg', 'pasir', 'nya', 'masi', 'putih', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['jajahannya', 'pilihan', 'enak', 'ð', 'crispy', 'juara', 'sate', 'padang', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'kalap', 'pokoknya', 'â']</t>
+          <t>['enak', 'sih', 'pantai', 'nya', 'ngga', 'kotor', 'pasir', 'nya', 'aja', 'yg', 'warna', 'coklat', 'ngga', 'kaya', 'sawarna', 'yg', 'pasir', 'nya', 'masi', 'putih', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>jajah pilih enak crispy juara sate padang mantul cilok lumayan cilor enak pisang keju enak sate an enak kalap pokok</t>
+          <t>enak sih pantai nya ngga kotor pasir nya aja yg warna coklat ngga kaya sawarna yg pasir nya mas putih</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2111,42 +2111,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
+          <t>rekomendasi untuk nongkrong buat kaula muda,cocok untuk semua umur.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
+          <t>rekomendasi untuk nongkrong buat kaula mudacocok untuk semua umur</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
+          <t>['rekomendasi', 'untuk', 'nongkrong', 'buat', 'kaula', 'mudacocok', 'untuk', 'semua', 'umur']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
+          <t>['rekomendasi', 'nongkrong', 'kaula', 'mudacocok', 'umur']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
+          <t>rekomendasi nongkrong kaula mudacocok umur</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2158,89 +2158,89 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pantainya sudah mulai tertata rapi &amp; parkir udah lumayan tertib. Tinggal kesadaran pengunjungnga aja untuk g buang sampah sembarangan. Untuk pengelola mungkin bisa diberbanyak tempat sampah supaya pantai Citepus bisa tetap bersih &amp; nyaman.</t>
+          <t>The place is comfortable, cool, the toilet is always clean. The prayer clothes in the mosque are fragrant and clean. There are many vendors selling unique and cheap snacks, and the taste is also delicious.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>pantainya sudah mulai tertata rapi parkir udah lumayan tertib tinggal kesadaran pengunjungnga aja untuk g buang sampah sembarangan untuk pengelola mungkin bisa diberbanyak tempat sampah supaya pantai citepus bisa tetap bersih nyaman</t>
+          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['pantainya', 'sudah', 'mulai', 'tertata', 'rapi', 'parkir', 'udah', 'lumayan', 'tertib', 'tinggal', 'kesadaran', 'pengunjungnga', 'aja', 'untuk', 'g', 'buang', 'sampah', 'sembarangan', 'untuk', 'pengelola', 'mungkin', 'bisa', 'diberbanyak', 'tempat', 'sampah', 'supaya', 'pantai', 'citepus', 'bisa', 'tetap', 'bersih', 'nyaman']</t>
+          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['pantainya', 'tertata', 'rapi', 'parkir', 'udah', 'lumayan', 'tertib', 'tinggal', 'kesadaran', 'pengunjungnga', 'aja', 'g', 'buang', 'sampah', 'sembarangan', 'pengelola', 'diberbanyak', 'sampah', 'pantai', 'citepus', 'bersih', 'nyaman']</t>
+          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>pantai tata rapi parkir udah lumayan tertib tinggal sadar pengunjungnga aja g buang sampah sembarang kelola banyak sampah pantai citepus bersih nyaman</t>
+          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tempat nongkrong asik,banyak juga berbagai kuliner - kuliner di alun - alun pelabuhan ratu,tidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tempat nongkrong asikbanyak juga berbagai kuliner kuliner di alun alun pelabuhan ratutidak ada tiket masuk untuk main ke dalam nya tapi untuk sekarang diabatasi karena pandemi wajib pakai masker dan dilarang berkerumun</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['tempat', 'nongkrong', 'asikbanyak', 'juga', 'berbagai', 'kuliner', 'kuliner', 'di', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'ada', 'tiket', 'masuk', 'untuk', 'main', 'ke', 'dalam', 'nya', 'tapi', 'untuk', 'sekarang', 'diabatasi', 'karena', 'pandemi', 'wajib', 'pakai', 'masker', 'dan', 'dilarang', 'berkerumun']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['nongkrong', 'asikbanyak', 'kuliner', 'kuliner', 'alun', 'alun', 'pelabuhan', 'ratutidak', 'tiket', 'masuk', 'main', 'nya', 'diabatasi', 'pandemi', 'wajib', 'pakai', 'masker', 'dilarang', 'berkerumun']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>nongkrong asikbanyak kuliner kuliner alun alun labuh ratutidak tiket masuk main nya diabatasi pandemi wajib pakai masker larang kerumun</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2257,131 +2257,131 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya. Detail bajunya bagus banget</t>
+          <t>Alun-alun palabuhanratu tempat yang nyaman untuk beristirahat ataupun sekedar nongkrong,karena disana tempatnya luas bisa area bermain anak,banyak pedagang yg menjual aneka jajanan,disampingnya ada mesjid agung yang luas dan nyaman untuk melaksanakan sholat juga tersedia wc/toilet</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya detail bajunya bagus banget</t>
+          <t>alunalun palabuhanratu tempat yang nyaman untuk beristirahat ataupun sekedar nongkrongkarena disana tempatnya luas bisa area bermain anakbanyak pedagang yg menjual aneka jajanandisampingnya ada mesjid agung yang luas dan nyaman untuk melaksanakan sholat juga tersedia wctoilet</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['baju', 'baju', 'yg', 'tetsedia', 'untuk', 'di', 'sewakan', 'sangat', 'bagus', 'dan', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'dengan', 'ke', 'inginan', 'saya', 'detail', 'bajunya', 'bagus', 'banget']</t>
+          <t>['alunalun', 'palabuhanratu', 'tempat', 'yang', 'nyaman', 'untuk', 'beristirahat', 'ataupun', 'sekedar', 'nongkrongkarena', 'disana', 'tempatnya', 'luas', 'bisa', 'area', 'bermain', 'anakbanyak', 'pedagang', 'yg', 'menjual', 'aneka', 'jajanandisampingnya', 'ada', 'mesjid', 'agung', 'yang', 'luas', 'dan', 'nyaman', 'untuk', 'melaksanakan', 'sholat', 'juga', 'tersedia', 'wctoilet']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['baju', 'baju', 'yg', 'tetsedia', 'sewakan', 'bagus', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'inginan', 'detail', 'bajunya', 'bagus', 'banget']</t>
+          <t>['alunalun', 'palabuhanratu', 'nyaman', 'beristirahat', 'sekedar', 'nongkrongkarena', 'disana', 'tempatnya', 'luas', 'area', 'bermain', 'anakbanyak', 'pedagang', 'yg', 'menjual', 'aneka', 'jajanandisampingnya', 'mesjid', 'agung', 'luas', 'nyaman', 'melaksanakan', 'sholat', 'tersedia', 'wctoilet']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>baju baju yg tetsedia sewa bagus riquesan buat baju nya sesuai banget ingin detail baju bagus banget</t>
+          <t>alunalun palabuhanratu nyaman istirahat dar nongkrongkarena sana tempat luas area main anakbanyak dagang yg jual aneka jajanandisampingnya mesjid agung luas nyaman laksana sholat sedia wctoilet</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pantai nyaman, tapi mohon pihak pengelola mohon dengan sangat, sediakan tempat sampah atau Peraturan Dilarang Buang Sampah</t>
+          <t>Bagus tempatnya, asik, cukup tenang kalau di hari weekday, santai banget, warung banyak, dan pemandangannya cantik</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>pantai nyaman tapi mohon pihak pengelola mohon dengan sangat sediakan tempat sampah atau peraturan dilarang buang sampah</t>
+          <t>bagus tempatnya asik cukup tenang kalau di hari weekday santai banget warung banyak dan pemandangannya cantik</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['pantai', 'nyaman', 'tapi', 'mohon', 'pihak', 'pengelola', 'mohon', 'dengan', 'sangat', 'sediakan', 'tempat', 'sampah', 'atau', 'peraturan', 'dilarang', 'buang', 'sampah']</t>
+          <t>['bagus', 'tempatnya', 'asik', 'cukup', 'tenang', 'kalau', 'di', 'hari', 'weekday', 'santai', 'banget', 'warung', 'banyak', 'dan', 'pemandangannya', 'cantik']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['pantai', 'nyaman', 'mohon', 'pengelola', 'mohon', 'sediakan', 'sampah', 'peraturan', 'dilarang', 'buang', 'sampah']</t>
+          <t>['bagus', 'tempatnya', 'asik', 'tenang', 'weekday', 'santai', 'banget', 'warung', 'pemandangannya', 'cantik']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>pantai nyaman mohon kelola mohon sedia sampah atur larang buang sampah</t>
+          <t>bagus tempat asik tenang weekday santai banget warung pandang cantik</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pertama ngecamp pinggir pantai tuu rasanya,MasyaAllah.. Pantai ini tu,deket ke warung,deket ke mushola,air untuk mandi lancar.tapi,kalau mau cam di tarif lagi untuk biaya kebersihan 1 tenda 20-25k untuk yang mau ikut â¦</t>
+          <t>Pantai selatan nan indah.perlu penataan.dan pembenahan dengan ke seriusan pemda setempat.agar bisa menjadi obyek wisata andalan.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>pertama ngecamp pinggir pantai tuu rasanyamasyaallah pantai ini tudeket ke warungdeket ke musholaair untuk mandi lancartapikalau mau cam di tarif lagi untuk biaya kebersihan tenda k untuk yang mau ikut â</t>
+          <t>pantai selatan nan indahperlu penataandan pembenahan dengan ke seriusan pemda setempatagar bisa menjadi obyek wisata andalan</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['pertama', 'ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'ini', 'tudeket', 'ke', 'warungdeket', 'ke', 'musholaair', 'untuk', 'mandi', 'lancartapikalau', 'mau', 'cam', 'di', 'tarif', 'lagi', 'untuk', 'biaya', 'kebersihan', 'tenda', 'k', 'untuk', 'yang', 'mau', 'ikut', 'â']</t>
+          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'dengan', 'ke', 'seriusan', 'pemda', 'setempatagar', 'bisa', 'menjadi', 'obyek', 'wisata', 'andalan']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'tudeket', 'warungdeket', 'musholaair', 'mandi', 'lancartapikalau', 'cam', 'tarif', 'biaya', 'kebersihan', 'tenda', 'k', 'â']</t>
+          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'seriusan', 'pemda', 'setempatagar', 'obyek', 'wisata', 'andalan']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ngecamp pinggir pantai tuu rasanyamasyaallah pantai tudeket warungdeket musholaair mandi lancartapikalau cam tarif biaya bersih tenda k</t>
+          <t>pantai selatan nan indahperlu penataandan benah serius pemda setempatagar obyek wisata andal</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2393,42 +2393,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>Pemandangan baik,bagus,hanya saja tempat ganti pakaian/mandi agak kurang rapih saja</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>pemandangan baikbagushanya saja tempat ganti pakaianmandi agak kurang rapih saja</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['pemandangan', 'baikbagushanya', 'saja', 'tempat', 'ganti', 'pakaianmandi', 'agak', 'kurang', 'rapih', 'saja']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['pemandangan', 'baikbagushanya', 'ganti', 'pakaianmandi', 'rapih']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>pandang baikbagushanya ganti pakaianmandi rapih</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2440,12 +2440,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Keren nih tempatnya, sambil istirahat trus pesen kelapa muda , duh di seruput, alamak hati senang , ingat kerjaan nya setelah di jakarta aja ya, â¦</t>
+          <t>Lapangannya luas,rapih, bersih,di tata dengan sangat bagus,penyuluh sosial masyarakat kab sukabumi,mengikuti upacara hari jadi Sukabumi</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2455,22 +2455,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>keren nih tempatnya sambil istirahat trus pesen kelapa muda duh di seruput alamak hati senang ingat kerjaan nya setelah di jakarta aja ya â</t>
+          <t>lapangannya luasrapih bersihdi tata dengan sangat baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara hari jadi sukabumi</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['keren', 'nih', 'tempatnya', 'sambil', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'di', 'seruput', 'alamak', 'hati', 'senang', 'ingat', 'kerjaan', 'nya', 'setelah', 'di', 'jakarta', 'aja', 'ya', 'â']</t>
+          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'dengan', 'sangat', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'hari', 'jadi', 'sukabumi']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['keren', 'nih', 'tempatnya', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'seruput', 'alamak', 'hati', 'senang', 'kerjaan', 'nya', 'jakarta', 'aja', 'ya', 'â']</t>
+          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'sukabumi']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>keren nih tempat istirahat trus sen kelapa muda duh seruput alamak hati senang kerja nya jakarta aja ya</t>
+          <t>lapang luasrapih bersihdi tata baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara sukabumi</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2481,6 +2481,335 @@
       <c r="I44" t="inlineStr">
         <is>
           <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Parkir bayar, tapi ada barang yg hilang. Pas dicek di pantai barang bwaan berkurang. Krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>parkir bayar tapi ada barang yg hilang pas dicek di pantai barang bwaan berkurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>['parkir', 'bayar', 'tapi', 'ada', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'di', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>['parkir', 'bayar', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>parkir bayar barang yg hilang pas cek pantai barang bwaan kurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Lokasi strategis. Cocok untuk santai cocok untuk anak-anak, cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan, cocok untuk yg tua muda semuanya.. tinggal d jaga bersama sama.. jangan vandalisme dan mengotorinya dgn sampah..okkkk</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>lokasi strategis cocok untuk santai cocok untuk anakanak cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan cocok untuk yg tua muda semuanya tinggal d jaga bersama sama jangan vandalisme dan mengotorinya dgn sampahokkkk</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>['lokasi', 'strategis', 'cocok', 'untuk', 'santai', 'cocok', 'untuk', 'anakanak', 'cocok', 'untuk', 'olahraga', 'subuh', 'dengan', 'udara', 'yg', 'segar', 'dekat', 'pegunungan', 'cocok', 'untuk', 'yg', 'tua', 'muda', 'semuanya', 'tinggal', 'd', 'jaga', 'bersama', 'sama', 'jangan', 'vandalisme', 'dan', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>['lokasi', 'strategis', 'cocok', 'santai', 'cocok', 'anakanak', 'cocok', 'olahraga', 'subuh', 'udara', 'yg', 'segar', 'pegunungan', 'cocok', 'yg', 'tua', 'muda', 'tinggal', 'd', 'jaga', 'vandalisme', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>lokasi strategis cocok santai cocok anakanak cocok olahraga subuh udara yg segar gunung cocok yg tua muda tinggal d jaga vandalisme kotor dgn sampahokkkk</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Waterpark Citepus Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>mudik dari bandung, ga berani berenang d pantai, jd k kolam renang aja. kolam udah bagus, cuma perlu penegasan d saung2 u/ pngunjung. sewa jg gppa u/ saung, drpd ga jelas nongkrong dmna.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>LAND</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>mudik dari bandung ga berani berenang d pantai jd k kolam renang aja kolam udah bagus cuma perlu penegasan d saung u pngunjung sewa jg gppa u saung drpd ga jelas nongkrong dmna</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>['mudik', 'dari', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'cuma', 'perlu', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'jelas', 'nongkrong', 'dmna']</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>['mudik', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'nongkrong', 'dmna']</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>mudik bandung ga berani renang d pantai jd k kolam renang aja kolam udah bagus tegas d saung u pngunjung sewa jg gppa u saung drpd ga nongkrong dmna</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>LAND</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sdh mulai banyak kerusakan. Terutama pada area olahraga. Kurang terawat tidak seperti awal awal</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>sdh mulai banyak kerusakan terutama pada area olahraga kurang terawat tidak seperti awal awal</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>['sdh', 'mulai', 'banyak', 'kerusakan', 'terutama', 'pada', 'area', 'olahraga', 'kurang', 'terawat', 'tidak', 'seperti', 'awal', 'awal']</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>['sdh', 'kerusakan', 'area', 'olahraga', 'terawat']</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>sdh rusa area olahraga awat</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ALUN ALUN GADOBANGKONG</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>tempat yg indah,penataan yg bagus,tetap jaga kebersihan....</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>tempat yg indahpenataan yg bagustetap jaga kebersihan</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>['tempat', 'yg', 'indahpenataan', 'yg', 'bagustetap', 'jaga', 'kebersihan']</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>['yg', 'indahpenataan', 'yg', 'bagustetap', 'jaga', 'kebersihan']</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>yg indahpenataan yg bagustetap jaga bersih</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Pantai Batu Bintang</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pertama ngecamp pinggir pantai tuu rasanya,MasyaAllah.. Pantai ini tu,deket ke warung,deket ke mushola,air untuk mandi lancar.tapi,kalau mau cam di tarif lagi untuk biaya kebersihan 1 tenda 20-25k untuk yang mau ikut â¦</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>pertama ngecamp pinggir pantai tuu rasanyamasyaallah pantai ini tudeket ke warungdeket ke musholaair untuk mandi lancartapikalau mau cam di tarif lagi untuk biaya kebersihan tenda k untuk yang mau ikut â</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>['pertama', 'ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'ini', 'tudeket', 'ke', 'warungdeket', 'ke', 'musholaair', 'untuk', 'mandi', 'lancartapikalau', 'mau', 'cam', 'di', 'tarif', 'lagi', 'untuk', 'biaya', 'kebersihan', 'tenda', 'k', 'untuk', 'yang', 'mau', 'ikut', 'â']</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>['ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'tudeket', 'warungdeket', 'musholaair', 'mandi', 'lancartapikalau', 'cam', 'tarif', 'biaya', 'kebersihan', 'tenda', 'k', 'â']</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ngecamp pinggir pantai tuu rasanyamasyaallah pantai tudeket warungdeket musholaair mandi lancartapikalau cam tarif biaya bersih tenda k</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Pantai Citepus Sukabumi</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>ECON</t>
         </is>
       </c>
     </row>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pasir pantai tidak tajam, lumayan bersih, banyak toilet, kamar mandi dan musola. Harga makanan dan minuman sesuai kantong.</t>
+          <t>Ikon kota palabuhanratu......bagus</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pasir pantai tidak tajam lumayan bersih banyak toilet kamar mandi dan musola harga makanan dan minuman sesuai kantong</t>
+          <t>ikon kota palabuhanratubagus</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['pasir', 'pantai', 'tidak', 'tajam', 'lumayan', 'bersih', 'banyak', 'toilet', 'kamar', 'mandi', 'dan', 'musola', 'harga', 'makanan', 'dan', 'minuman', 'sesuai', 'kantong']</t>
+          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['pasir', 'pantai', 'tajam', 'lumayan', 'bersih', 'toilet', 'kamar', 'mandi', 'musola', 'harga', 'makanan', 'minuman', 'sesuai', 'kantong']</t>
+          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>pasir pantai tajam lumayan bersih toilet kamar mandi musola harga makan minum sesuai kantong</t>
+          <t>ikon kota palabuhanratubagus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -513,12 +513,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -553,19 +553,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Untuk tgl 16 mei 2025 strukturnya untuk sebagian masih sedang dalam perbaikan. Toilet yg tersedia di dekat alun2 untuk yang perempuan sudah tidak ada kunci nya. Dan kebetulan juga waktu saya berkunjung stand pedagang dan pameran sudah siap â¦</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -575,22 +575,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>untuk tgl mei strukturnya untuk sebagian masih sedang dalam perbaikan toilet yg tersedia di dekat alun untuk yang perempuan sudah tidak ada kunci nya dan kebetulan juga waktu saya berkunjung stand pedagang dan pameran sudah siap â</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['untuk', 'tgl', 'mei', 'strukturnya', 'untuk', 'sebagian', 'masih', 'sedang', 'dalam', 'perbaikan', 'toilet', 'yg', 'tersedia', 'di', 'dekat', 'alun', 'untuk', 'yang', 'perempuan', 'sudah', 'tidak', 'ada', 'kunci', 'nya', 'dan', 'kebetulan', 'juga', 'waktu', 'saya', 'berkunjung', 'stand', 'pedagang', 'dan', 'pameran', 'sudah', 'siap', 'â']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['tgl', 'mei', 'strukturnya', 'perbaikan', 'toilet', 'yg', 'tersedia', 'alun', 'perempuan', 'kunci', 'nya', 'berkunjung', 'stand', 'pedagang', 'pameran', 'â']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>tgl mei struktur baik toilet yg sedia alun perempuan kunci nya kunjung stand dagang pamer</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -607,106 +607,106 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
+          <t>Akses masuk dengan mobil relatif mudah hingga ke bibir pantai</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
+          <t>akses masuk dengan mobil relatif mudah hingga ke bibir pantai</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
+          <t>['akses', 'masuk', 'dengan', 'mobil', 'relatif', 'mudah', 'hingga', 'ke', 'bibir', 'pantai']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
+          <t>['akses', 'masuk', 'mobil', 'relatif', 'mudah', 'bibir', 'pantai']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
+          <t>akses masuk mobil relatif mudah bibir pantai</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>ECON</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>Alhamdulillahasih bersih, indah apalagi di malam hari, tepat nya di depan majid agung palabuahan ratu, banyak tersedia jajanan juga, ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>alhamdulillahasih bersih indah apalagi di malam hari tepat nya di depan majid agung palabuahan ratu banyak tersedia jajanan juga ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['alhamdulillahasih', 'bersih', 'indah', 'apalagi', 'di', 'malam', 'hari', 'tepat', 'nya', 'di', 'depan', 'majid', 'agung', 'palabuahan', 'ratu', 'banyak', 'tersedia', 'jajanan', 'juga', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended', 'lah']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['alhamdulillahasih', 'bersih', 'indah', 'malam', 'nya', 'majid', 'agung', 'palabuahan', 'ratu', 'tersedia', 'jajanan', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>alhamdulillahasih bersih indah malam nya majid agung palabuahan ratu sedia jajan ubtuk dar santa denfan keluarga rekomended</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bagus cm tmpat smpah sedikit.. ama pedagang julid ge bnyk Parkir liar bnyk View lumayan</t>
+          <t>Di kelola oleh oknum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>bagus cm tmpat smpah sedikit ama pedagang julid ge bnyk parkir liar bnyk view lumayan</t>
+          <t>di kelola oleh oknum</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['bagus', 'cm', 'tmpat', 'smpah', 'sedikit', 'ama', 'pedagang', 'julid', 'ge', 'bnyk', 'parkir', 'liar', 'bnyk', 'view', 'lumayan']</t>
+          <t>['di', 'kelola', 'oleh', 'oknum']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['bagus', 'cm', 'tmpat', 'smpah', 'ama', 'pedagang', 'julid', 'ge', 'bnyk', 'parkir', 'liar', 'bnyk', 'view', 'lumayan']</t>
+          <t>['kelola', 'oknum']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>bagus cm tmpat smpah ama dagang julid ge bnyk parkir liar bnyk view lumayan</t>
+          <t>kelola oknum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -741,66 +741,66 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pemandangannya bagus, cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
+          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>pemandangannya bagus cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
+          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['pemandangannya', 'bagus', 'cuma', 'sekarang', 'pantai', 'nya', 'rusak', 'cuma', 'ada', 'bebatuan', 'doang']</t>
+          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['pemandangannya', 'bagus', 'pantai', 'nya', 'rusak', 'bebatuan', 'doang']</t>
+          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>pandang bagus pantai nya rusak bebatuan doang</t>
+          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A comfortable square for resting and chatting with family. The place is very spacious, you can also enjoy culinary activities. There is a mosque that is very comfortable for worship, clean toilets, many separate ablution areas for brothers â¦</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -810,22 +810,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers â</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -842,136 +842,136 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Di kelola oleh oknum</t>
+          <t>untuk  harga masuk motor 10k, mobil 20k, mobil travel 30k bis kecil 50k, bis besar 100k menurutku dengan harga segini udah worth it banget sih karna pantai dan pemandangannya ga mainmain bener2 sekeren itu bikin betah seharian</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>di kelola oleh oknum</t>
+          <t>untuk harga masuk motor k mobil k mobil travel k bis kecil k bis besar k menurutku dengan harga segini udah worth it banget sih karna pantai dan pemandangannya ga mainmain bener sekeren itu bikin betah seharian</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['di', 'kelola', 'oleh', 'oknum']</t>
+          <t>['untuk', 'harga', 'masuk', 'motor', 'k', 'mobil', 'k', 'mobil', 'travel', 'k', 'bis', 'kecil', 'k', 'bis', 'besar', 'k', 'menurutku', 'dengan', 'harga', 'segini', 'udah', 'worth', 'it', 'banget', 'sih', 'karna', 'pantai', 'dan', 'pemandangannya', 'ga', 'mainmain', 'bener', 'sekeren', 'itu', 'bikin', 'betah', 'seharian']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['kelola', 'oknum']</t>
+          <t>['harga', 'masuk', 'motor', 'k', 'mobil', 'k', 'mobil', 'travel', 'k', 'bis', 'k', 'bis', 'k', 'menurutku', 'harga', 'segini', 'udah', 'worth', 'it', 'banget', 'sih', 'karna', 'pantai', 'pemandangannya', 'ga', 'mainmain', 'bener', 'sekeren', 'bikin', 'betah', 'seharian']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>kelola oknum</t>
+          <t>harga masuk motor k mobil k mobil travel k bis k bis k turut harga gin udah worth it banget sih karna pantai pandang ga mainmain bener keren bikin betah hari</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>ECON</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Menikmati</t>
+          <t>mudik dari bandung, ga berani berenang d pantai, jd k kolam renang aja. kolam udah bagus, cuma perlu penegasan d saung2 u/ pngunjung. sewa jg gppa u/ saung, drpd ga jelas nongkrong dmna.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>menikmati</t>
+          <t>mudik dari bandung ga berani berenang d pantai jd k kolam renang aja kolam udah bagus cuma perlu penegasan d saung u pngunjung sewa jg gppa u saung drpd ga jelas nongkrong dmna</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['menikmati']</t>
+          <t>['mudik', 'dari', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'cuma', 'perlu', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'jelas', 'nongkrong', 'dmna']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['menikmati']</t>
+          <t>['mudik', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'nongkrong', 'dmna']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>nikmat</t>
+          <t>mudik bandung ga berani renang d pantai jd k kolam renang aja kolam udah bagus tegas d saung u pngunjung sewa jg gppa u saung drpd ga nongkrong dmna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pantainya bersih, yang terpenting harga makanan dan minuman super murah,parkir jg normal..</t>
+          <t>bagus,,enak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>pantainya bersih yang terpenting harga makanan dan minuman super murahparkir jg normal</t>
+          <t>bagusenak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersih', 'yang', 'terpenting', 'harga', 'makanan', 'dan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
+          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersih', 'terpenting', 'harga', 'makanan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
+          <t>['bagusenak', 'liburan', 'keluarga']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>pantai bersih penting harga makan minum super murahparkir jg normal</t>
+          <t>bagusenak libur keluarga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -983,12 +983,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -998,22 +998,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>asik pantai hibur anak anakmantap</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1030,42 +1030,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
+          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
+          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
+          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
+          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
+          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,141 +1077,141 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kapan kapan ke sini dah</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>kapan kapan ke sini dah</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['kapan', 'kapan', 'ke', 'sini', 'dah']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['dah']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>dah</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jajahannya banyak pilihan dan enak ð Tahu crispy juara, sate padang juga mantul, cilok lumayan, cilor enak, pisang keju enak, sate2 an enak, waduh kalap pokoknya â¦</t>
+          <t>Tampil nasyid tingkat provinsi..mantap cah2 Lanang ð¥°ð¥° â¦</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1233,22 +1233,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jajahannya banyak pilihan dan enak ð tahu crispy juara sate padang juga mantul cilok lumayan cilor enak pisang keju enak sate an enak waduh kalap pokoknya â</t>
+          <t>tampil nasyid tingkat provinsimantap cah lanang ðð â</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['jajahannya', 'banyak', 'pilihan', 'dan', 'enak', 'ð', 'tahu', 'crispy', 'juara', 'sate', 'padang', 'juga', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'waduh', 'kalap', 'pokoknya', 'â']</t>
+          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['jajahannya', 'pilihan', 'enak', 'ð', 'crispy', 'juara', 'sate', 'padang', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'kalap', 'pokoknya', 'â']</t>
+          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jajah pilih enak crispy juara sate padang mantul cilok lumayan cilor enak pisang keju enak sate an enak kalap pokok</t>
+          <t>tampil nasyid tingkat provinsimantap cah lanang</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1312,12 +1312,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
+          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1327,22 +1327,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
+          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>nongki chill and cheap yg cocok pas sunsetan</t>
+          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1359,42 +1359,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
+          <t>Pantai ci letuh Sukabumi Jabar yang indah,,nyaman dan ramah..</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
+          <t>pantai ci letuh sukabumi jabar yang indahnyaman dan ramah</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['pantai', 'ci', 'letuh', 'sukabumi', 'jabar', 'yang', 'indahnyaman', 'dan', 'ramah']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['pantai', 'ci', 'letuh', 'sukabumi', 'jabar', 'indahnyaman', 'ramah']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
+          <t>pantai ci letuh sukabumi jabar indahnyaman ramah</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1406,59 +1406,59 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pantai ci letuh Sukabumi Jabar yang indah,,nyaman dan ramah..</t>
+          <t>Pemandangannya bagus, cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>pantai ci letuh sukabumi jabar yang indahnyaman dan ramah</t>
+          <t>pemandangannya bagus cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['pantai', 'ci', 'letuh', 'sukabumi', 'jabar', 'yang', 'indahnyaman', 'dan', 'ramah']</t>
+          <t>['pemandangannya', 'bagus', 'cuma', 'sekarang', 'pantai', 'nya', 'rusak', 'cuma', 'ada', 'bebatuan', 'doang']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['pantai', 'ci', 'letuh', 'sukabumi', 'jabar', 'indahnyaman', 'ramah']</t>
+          <t>['pemandangannya', 'bagus', 'pantai', 'nya', 'rusak', 'bebatuan', 'doang']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>pantai ci letuh sukabumi jabar indahnyaman ramah</t>
+          <t>pandang bagus pantai nya rusak bebatuan doang</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1468,22 +1468,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1500,12 +1500,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>Jalanya mantap</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1515,22 +1515,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>jalanya mantap</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+          <t>jala mantap</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1540,96 +1540,96 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sampai masih pagi Nama pantai baru tau dikasih tau google ð¤­ Warung tutup bulan puasa. Toilet blm buka mesti minta tolong buat dibuka. Airnya â¦</t>
+          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>sampai masih pagi nama pantai baru tau dikasih tau google ð warung tutup bulan puasa toilet blm buka mesti minta tolong buat dibuka airnya â</t>
+          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['sampai', 'masih', 'pagi', 'nama', 'pantai', 'baru', 'tau', 'dikasih', 'tau', 'google', 'ð', 'warung', 'tutup', 'bulan', 'puasa', 'toilet', 'blm', 'buka', 'mesti', 'minta', 'tolong', 'buat', 'dibuka', 'airnya', 'â']</t>
+          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['pagi', 'nama', 'pantai', 'tau', 'dikasih', 'tau', 'google', 'ð', 'warung', 'tutup', 'puasa', 'toilet', 'blm', 'buka', 'mesti', 'tolong', 'dibuka', 'airnya', 'â']</t>
+          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>pagi nama pantai tau kasih tau google warung tutup puasa toilet blm buka mesti tolong buka air</t>
+          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kotor alun alunnya banyak sampah...mampir ke masjid di alun2 bersih dan nyaman</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>kotor alun alunnya banyak sampahmampir ke masjid di alun bersih dan nyaman</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['kotor', 'alun', 'alunnya', 'banyak', 'sampahmampir', 'ke', 'masjid', 'di', 'alun', 'bersih', 'dan', 'nyaman']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['kotor', 'alun', 'alunnya', 'sampahmampir', 'masjid', 'alun', 'bersih', 'nyaman']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>kotor alun alun sampahmampir masjid alun bersih nyaman</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1641,12 +1641,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Air terlihat agak kotor, pasirnya hitam.. Mungkin bagi yang terbiasa ke pantai wilayah Jawa bagian timur akan merasa kurang nyaman</t>
+          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>air terlihat agak kotor pasirnya hitam mungkin bagi yang terbiasa ke pantai wilayah jawa bagian timur akan merasa kurang nyaman</t>
+          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['air', 'terlihat', 'agak', 'kotor', 'pasirnya', 'hitam', 'mungkin', 'bagi', 'yang', 'terbiasa', 'ke', 'pantai', 'wilayah', 'jawa', 'bagian', 'timur', 'akan', 'merasa', 'kurang', 'nyaman']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['air', 'kotor', 'pasirnya', 'hitam', 'terbiasa', 'pantai', 'wilayah', 'jawa', 'timur', 'nyaman']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>air kotor pasir hitam biasa pantai wilayah jawa timur nyaman</t>
+          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1688,42 +1688,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Keren nih tempatnya, sambil istirahat trus pesen kelapa muda , duh di seruput, alamak hati senang , ingat kerjaan nya setelah di jakarta aja ya, â¦</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>keren nih tempatnya sambil istirahat trus pesen kelapa muda duh di seruput alamak hati senang ingat kerjaan nya setelah di jakarta aja ya â</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['keren', 'nih', 'tempatnya', 'sambil', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'di', 'seruput', 'alamak', 'hati', 'senang', 'ingat', 'kerjaan', 'nya', 'setelah', 'di', 'jakarta', 'aja', 'ya', 'â']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['keren', 'nih', 'tempatnya', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'seruput', 'alamak', 'hati', 'senang', 'kerjaan', 'nya', 'jakarta', 'aja', 'ya', 'â']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>keren nih tempat istirahat trus sen kelapa muda duh seruput alamak hati senang kerja nya jakarta aja ya</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1735,42 +1735,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Taman Bappeda</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tempat nyaman tapi patung kura kura banyak di rusak oleh orang yang tidak bertanggung jawab.</t>
+          <t>Liburan murmer ,,sewa rumah di pinggir pantai murah cuma sayang banyak yg ngamen.. Repot juga tiap 5 menit mah dikira liburan banyak duit...bilang maaf ga pergi2.. Saran siapin receh yg banyak</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tempat nyaman tapi patung kura kura banyak di rusak oleh orang yang tidak bertanggung jawab</t>
+          <t>liburan murmer sewa rumah di pinggir pantai murah cuma sayang banyak yg ngamen repot juga tiap menit mah dikira liburan banyak duitbilang maaf ga pergi saran siapin receh yg banyak</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['tempat', 'nyaman', 'tapi', 'patung', 'kura', 'kura', 'banyak', 'di', 'rusak', 'oleh', 'orang', 'yang', 'tidak', 'bertanggung', 'jawab']</t>
+          <t>['liburan', 'murmer', 'sewa', 'rumah', 'di', 'pinggir', 'pantai', 'murah', 'cuma', 'sayang', 'banyak', 'yg', 'ngamen', 'repot', 'juga', 'tiap', 'menit', 'mah', 'dikira', 'liburan', 'banyak', 'duitbilang', 'maaf', 'ga', 'pergi', 'saran', 'siapin', 'receh', 'yg', 'banyak']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['nyaman', 'patung', 'kura', 'kura', 'rusak', 'orang', 'bertanggung']</t>
+          <t>['liburan', 'murmer', 'sewa', 'rumah', 'pinggir', 'pantai', 'murah', 'sayang', 'yg', 'ngamen', 'repot', 'menit', 'mah', 'liburan', 'duitbilang', 'maaf', 'ga', 'pergi', 'saran', 'siapin', 'receh', 'yg']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>nyaman patung kura kura rusak orang tanggung</t>
+          <t>libur murmer sewa rumah pinggir pantai murah sayang yg ngamen repot menit mah libur duitbilang maaf ga pergi saran siapin receh yg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1782,12 +1782,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1797,22 +1797,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['skarang', 'lebih', 'sepi', 'dan', 'kebanyakan', 'di', 'pakai', 'oknum', 'pemuda', 'pemudi', 'buat', 'pacaran', 'kadang', 'suka', 'ada', 'yg', 'mabuk', 'atau', 'tawuran', 'anak', 'sekolah']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['skarang', 'sepi', 'kebanyakan', 'pakai', 'oknum', 'pemuda', 'pemudi', 'pacaran', 'kadang', 'suka', 'yg', 'mabuk', 'tawuran', 'anak', 'sekolah']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>skarang sepi banyak pakai oknum pemuda pemudi pacar kadang suka yg mabuk tawur anak sekolah</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1829,42 +1829,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Smile hill Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>bagus,,enak buat liburan bersama keluarga</t>
+          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>bagusenak buat liburan bersama keluarga</t>
+          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
+          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['bagusenak', 'liburan', 'keluarga']</t>
+          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>bagusenak libur keluarga</t>
+          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1876,940 +1876,141 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bagus tempatnya, apa lagi kalau naik ke atas bukitnyaa,. Kreen..  Tpi klau sdah jam 16.30 gak bisa lagi buat naik ke bukitnya, karna pagar sdah ditutup..</t>
+          <t>Pantainya kurang bagus kotor terus parkiranya gaboleh didepan warung sama yg punya warung</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>bagus tempatnya apa lagi kalau naik ke atas bukitnyaa kreen tpi klau sdah jam gak bisa lagi buat naik ke bukitnya karna pagar sdah ditutup</t>
+          <t>pantainya kurang bagus kotor terus parkiranya gaboleh didepan warung sama yg punya warung</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'apa', 'lagi', 'kalau', 'naik', 'ke', 'atas', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bisa', 'lagi', 'buat', 'naik', 'ke', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
+          <t>['pantainya', 'kurang', 'bagus', 'kotor', 'terus', 'parkiranya', 'gaboleh', 'didepan', 'warung', 'sama', 'yg', 'punya', 'warung']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'bukitnyaa', 'kreen', 'tpi', 'klau', 'sdah', 'jam', 'gak', 'bukitnya', 'karna', 'pagar', 'sdah', 'ditutup']</t>
+          <t>['pantainya', 'bagus', 'kotor', 'parkiranya', 'gaboleh', 'didepan', 'warung', 'yg', 'warung']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>bagus tempat bukitnyaa kreen tpi klau sdah jam gak bukit karna pagar sdah tutup</t>
+          <t>pantai bagus kotor parkiranya gaboleh depan warung yg warung</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tempatnya ramai, pemandangannya bagus, tempat yang tepat untuk mengajak anak-anak bermain. Tempat yang sempurna untuk berfoto, meskipun tidak terlalu bersih dan agak sulit â¦</t>
+          <t>Pas banget buat nongki akses enak dan strategis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tempatnya ramai pemandangannya bagus tempat yang tepat untuk mengajak anakanak bermain tempat yang sempurna untuk berfoto meskipun tidak terlalu bersih dan agak sulit â</t>
+          <t>pas banget buat nongki akses enak dan strategis</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['tempatnya', 'ramai', 'pemandangannya', 'bagus', 'tempat', 'yang', 'tepat', 'untuk', 'mengajak', 'anakanak', 'bermain', 'tempat', 'yang', 'sempurna', 'untuk', 'berfoto', 'meskipun', 'tidak', 'terlalu', 'bersih', 'dan', 'agak', 'sulit', 'â']</t>
+          <t>['pas', 'banget', 'buat', 'nongki', 'akses', 'enak', 'dan', 'strategis']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['tempatnya', 'ramai', 'pemandangannya', 'bagus', 'mengajak', 'anakanak', 'bermain', 'sempurna', 'berfoto', 'bersih', 'sulit', 'â']</t>
+          <t>['pas', 'banget', 'nongki', 'akses', 'enak', 'strategis']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>tempat ramai pandang bagus ajak anakanak main sempurna foto bersih sulit</t>
+          <t>pas banget nongki akses enak strategis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Buka setiap hari, tiket masuk kisaran 20 ribu. Tempat nyaman,luas ,kolam cukup banyak ,  kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia. â¦</t>
+          <t>Pertama ngecamp pinggir pantai tuu rasanya,MasyaAllah.. Pantai ini tu,deket ke warung,deket ke mushola,air untuk mandi lancar.tapi,kalau mau cam di tarif lagi untuk biaya kebersihan 1 tenda 20-25k untuk yang mau ikut â¦</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>buka setiap hari tiket masuk kisaran ribu tempat nyamanluas kolam cukup banyak kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia â</t>
+          <t>pertama ngecamp pinggir pantai tuu rasanyamasyaallah pantai ini tudeket ke warungdeket ke musholaair untuk mandi lancartapikalau mau cam di tarif lagi untuk biaya kebersihan tenda k untuk yang mau ikut â</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['buka', 'setiap', 'hari', 'tiket', 'masuk', 'kisaran', 'ribu', 'tempat', 'nyamanluas', 'kolam', 'cukup', 'banyak', 'kantin', 'dan', 'tempat', 'sewa', 'ban', 'juga', 'ada', 'tempat', 'berteduh', 'atau', 'bale', 'juga', 'tersedia', 'â']</t>
+          <t>['pertama', 'ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'ini', 'tudeket', 'ke', 'warungdeket', 'ke', 'musholaair', 'untuk', 'mandi', 'lancartapikalau', 'mau', 'cam', 'di', 'tarif', 'lagi', 'untuk', 'biaya', 'kebersihan', 'tenda', 'k', 'untuk', 'yang', 'mau', 'ikut', 'â']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['buka', 'tiket', 'masuk', 'kisaran', 'ribu', 'nyamanluas', 'kolam', 'kantin', 'sewa', 'ban', 'berteduh', 'bale', 'tersedia', 'â']</t>
+          <t>['ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'tudeket', 'warungdeket', 'musholaair', 'mandi', 'lancartapikalau', 'cam', 'tarif', 'biaya', 'kebersihan', 'tenda', 'k', 'â']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>buka tiket masuk kisar ribu nyamanluas kolam kantin sewa ban teduh bale sedia</t>
+          <t>ngecamp pinggir pantai tuu rasanyamasyaallah pantai tudeket warungdeket musholaair mandi lancartapikalau cam tarif biaya bersih tenda k</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>PANTAI CIBANGBAN</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Kerennn</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>kerennn</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>['kerennn']</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>['kerennn']</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>kerennn</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Pantai Citepus</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Enak sih pantai nya ngga kotor cuma pasir nya aja yg warna coklat ngga kaya Sawarna yg pasir nya masi putih ðð â¦</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>enak sih pantai nya ngga kotor cuma pasir nya aja yg warna coklat ngga kaya sawarna yg pasir nya masi putih ðð â</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>['enak', 'sih', 'pantai', 'nya', 'ngga', 'kotor', 'cuma', 'pasir', 'nya', 'aja', 'yg', 'warna', 'coklat', 'ngga', 'kaya', 'sawarna', 'yg', 'pasir', 'nya', 'masi', 'putih', 'ðð', 'â']</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>['enak', 'sih', 'pantai', 'nya', 'ngga', 'kotor', 'pasir', 'nya', 'aja', 'yg', 'warna', 'coklat', 'ngga', 'kaya', 'sawarna', 'yg', 'pasir', 'nya', 'masi', 'putih', 'ðð', 'â']</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>enak sih pantai nya ngga kotor pasir nya aja yg warna coklat ngga kaya sawarna yg pasir nya mas putih</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Alun - Alun Palabuhanratu</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>rekomendasi untuk nongkrong buat kaula muda,cocok untuk semua umur.</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>rekomendasi untuk nongkrong buat kaula mudacocok untuk semua umur</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>['rekomendasi', 'untuk', 'nongkrong', 'buat', 'kaula', 'mudacocok', 'untuk', 'semua', 'umur']</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>['rekomendasi', 'nongkrong', 'kaula', 'mudacocok', 'umur']</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>rekomendasi nongkrong kaula mudacocok umur</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Alun - Alun Palabuhanratu</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>The place is comfortable, cool, the toilet is always clean. The prayer clothes in the mosque are fragrant and clean. There are many vendors selling unique and cheap snacks, and the taste is also delicious.</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Pantai Citepus Sukabumi</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Alun - Alun Palabuhanratu</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Alun-alun palabuhanratu tempat yang nyaman untuk beristirahat ataupun sekedar nongkrong,karena disana tempatnya luas bisa area bermain anak,banyak pedagang yg menjual aneka jajanan,disampingnya ada mesjid agung yang luas dan nyaman untuk melaksanakan sholat juga tersedia wc/toilet</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>alunalun palabuhanratu tempat yang nyaman untuk beristirahat ataupun sekedar nongkrongkarena disana tempatnya luas bisa area bermain anakbanyak pedagang yg menjual aneka jajanandisampingnya ada mesjid agung yang luas dan nyaman untuk melaksanakan sholat juga tersedia wctoilet</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>['alunalun', 'palabuhanratu', 'tempat', 'yang', 'nyaman', 'untuk', 'beristirahat', 'ataupun', 'sekedar', 'nongkrongkarena', 'disana', 'tempatnya', 'luas', 'bisa', 'area', 'bermain', 'anakbanyak', 'pedagang', 'yg', 'menjual', 'aneka', 'jajanandisampingnya', 'ada', 'mesjid', 'agung', 'yang', 'luas', 'dan', 'nyaman', 'untuk', 'melaksanakan', 'sholat', 'juga', 'tersedia', 'wctoilet']</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>['alunalun', 'palabuhanratu', 'nyaman', 'beristirahat', 'sekedar', 'nongkrongkarena', 'disana', 'tempatnya', 'luas', 'area', 'bermain', 'anakbanyak', 'pedagang', 'yg', 'menjual', 'aneka', 'jajanandisampingnya', 'mesjid', 'agung', 'luas', 'nyaman', 'melaksanakan', 'sholat', 'tersedia', 'wctoilet']</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>alunalun palabuhanratu nyaman istirahat dar nongkrongkarena sana tempat luas area main anakbanyak dagang yg jual aneka jajanandisampingnya mesjid agung luas nyaman laksana sholat sedia wctoilet</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Bagus tempatnya, asik, cukup tenang kalau di hari weekday, santai banget, warung banyak, dan pemandangannya cantik</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>bagus tempatnya asik cukup tenang kalau di hari weekday santai banget warung banyak dan pemandangannya cantik</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>['bagus', 'tempatnya', 'asik', 'cukup', 'tenang', 'kalau', 'di', 'hari', 'weekday', 'santai', 'banget', 'warung', 'banyak', 'dan', 'pemandangannya', 'cantik']</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>['bagus', 'tempatnya', 'asik', 'tenang', 'weekday', 'santai', 'banget', 'warung', 'pemandangannya', 'cantik']</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>bagus tempat asik tenang weekday santai banget warung pandang cantik</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Alun - Alun Palabuhanratu</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Pantai selatan nan indah.perlu penataan.dan pembenahan dengan ke seriusan pemda setempat.agar bisa menjadi obyek wisata andalan.</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>pantai selatan nan indahperlu penataandan pembenahan dengan ke seriusan pemda setempatagar bisa menjadi obyek wisata andalan</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'dengan', 'ke', 'seriusan', 'pemda', 'setempatagar', 'bisa', 'menjadi', 'obyek', 'wisata', 'andalan']</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'seriusan', 'pemda', 'setempatagar', 'obyek', 'wisata', 'andalan']</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>pantai selatan nan indahperlu penataandan benah serius pemda setempatagar obyek wisata andal</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>PANTAI CIBANGBAN</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Pemandangan baik,bagus,hanya saja tempat ganti pakaian/mandi agak kurang rapih saja</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>pemandangan baikbagushanya saja tempat ganti pakaianmandi agak kurang rapih saja</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>['pemandangan', 'baikbagushanya', 'saja', 'tempat', 'ganti', 'pakaianmandi', 'agak', 'kurang', 'rapih', 'saja']</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>['pemandangan', 'baikbagushanya', 'ganti', 'pakaianmandi', 'rapih']</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>pandang baikbagushanya ganti pakaianmandi rapih</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Lapangannya luas,rapih, bersih,di tata dengan sangat bagus,penyuluh sosial masyarakat kab sukabumi,mengikuti upacara hari jadi Sukabumi</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>lapangannya luasrapih bersihdi tata dengan sangat baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara hari jadi sukabumi</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'dengan', 'sangat', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'hari', 'jadi', 'sukabumi']</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'sukabumi']</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>lapang luasrapih bersihdi tata baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara sukabumi</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Alun - Alun Palabuhanratu</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Parkir bayar, tapi ada barang yg hilang. Pas dicek di pantai barang bwaan berkurang. Krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>parkir bayar tapi ada barang yg hilang pas dicek di pantai barang bwaan berkurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>['parkir', 'bayar', 'tapi', 'ada', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'di', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>['parkir', 'bayar', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>parkir bayar barang yg hilang pas cek pantai barang bwaan kurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Lokasi strategis. Cocok untuk santai cocok untuk anak-anak, cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan, cocok untuk yg tua muda semuanya.. tinggal d jaga bersama sama.. jangan vandalisme dan mengotorinya dgn sampah..okkkk</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>lokasi strategis cocok untuk santai cocok untuk anakanak cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan cocok untuk yg tua muda semuanya tinggal d jaga bersama sama jangan vandalisme dan mengotorinya dgn sampahokkkk</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>['lokasi', 'strategis', 'cocok', 'untuk', 'santai', 'cocok', 'untuk', 'anakanak', 'cocok', 'untuk', 'olahraga', 'subuh', 'dengan', 'udara', 'yg', 'segar', 'dekat', 'pegunungan', 'cocok', 'untuk', 'yg', 'tua', 'muda', 'semuanya', 'tinggal', 'd', 'jaga', 'bersama', 'sama', 'jangan', 'vandalisme', 'dan', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>['lokasi', 'strategis', 'cocok', 'santai', 'cocok', 'anakanak', 'cocok', 'olahraga', 'subuh', 'udara', 'yg', 'segar', 'pegunungan', 'cocok', 'yg', 'tua', 'muda', 'tinggal', 'd', 'jaga', 'vandalisme', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>lokasi strategis cocok santai cocok anakanak cocok olahraga subuh udara yg segar gunung cocok yg tua muda tinggal d jaga vandalisme kotor dgn sampahokkkk</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>mudik dari bandung, ga berani berenang d pantai, jd k kolam renang aja. kolam udah bagus, cuma perlu penegasan d saung2 u/ pngunjung. sewa jg gppa u/ saung, drpd ga jelas nongkrong dmna.</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>LAND</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>mudik dari bandung ga berani berenang d pantai jd k kolam renang aja kolam udah bagus cuma perlu penegasan d saung u pngunjung sewa jg gppa u saung drpd ga jelas nongkrong dmna</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>['mudik', 'dari', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'cuma', 'perlu', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'jelas', 'nongkrong', 'dmna']</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>['mudik', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'nongkrong', 'dmna']</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>mudik bandung ga berani renang d pantai jd k kolam renang aja kolam udah bagus tegas d saung u pngunjung sewa jg gppa u saung drpd ga nongkrong dmna</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>LAND</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Sdh mulai banyak kerusakan. Terutama pada area olahraga. Kurang terawat tidak seperti awal awal</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>sdh mulai banyak kerusakan terutama pada area olahraga kurang terawat tidak seperti awal awal</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>['sdh', 'mulai', 'banyak', 'kerusakan', 'terutama', 'pada', 'area', 'olahraga', 'kurang', 'terawat', 'tidak', 'seperti', 'awal', 'awal']</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>['sdh', 'kerusakan', 'area', 'olahraga', 'terawat']</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>sdh rusa area olahraga awat</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>tempat yg indah,penataan yg bagus,tetap jaga kebersihan....</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>tempat yg indahpenataan yg bagustetap jaga kebersihan</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>['tempat', 'yg', 'indahpenataan', 'yg', 'bagustetap', 'jaga', 'kebersihan']</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>['yg', 'indahpenataan', 'yg', 'bagustetap', 'jaga', 'kebersihan']</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>yg indahpenataan yg bagustetap jaga bersih</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Pantai Batu Bintang</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Pertama ngecamp pinggir pantai tuu rasanya,MasyaAllah.. Pantai ini tu,deket ke warung,deket ke mushola,air untuk mandi lancar.tapi,kalau mau cam di tarif lagi untuk biaya kebersihan 1 tenda 20-25k untuk yang mau ikut â¦</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>pertama ngecamp pinggir pantai tuu rasanyamasyaallah pantai ini tudeket ke warungdeket ke musholaair untuk mandi lancartapikalau mau cam di tarif lagi untuk biaya kebersihan tenda k untuk yang mau ikut â</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>['pertama', 'ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'ini', 'tudeket', 'ke', 'warungdeket', 'ke', 'musholaair', 'untuk', 'mandi', 'lancartapikalau', 'mau', 'cam', 'di', 'tarif', 'lagi', 'untuk', 'biaya', 'kebersihan', 'tenda', 'k', 'untuk', 'yang', 'mau', 'ikut', 'â']</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>['ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'tudeket', 'warungdeket', 'musholaair', 'mandi', 'lancartapikalau', 'cam', 'tarif', 'biaya', 'kebersihan', 'tenda', 'k', 'â']</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>ngecamp pinggir pantai tuu rasanyamasyaallah pantai tudeket warungdeket musholaair mandi lancartapikalau cam tarif biaya bersih tenda k</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Pantai Citepus Sukabumi</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Tempat cukup nyaman untuk sekadar beristirahat melepas penat. Banyak jajanan, area parkir cukup luas. Ombak cukup besar. Banyak pengamen.</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>CONF</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>tempat cukup nyaman untuk sekadar beristirahat melepas penat banyak jajanan area parkir cukup luas ombak cukup besar banyak pengamen</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>['tempat', 'cukup', 'nyaman', 'untuk', 'sekadar', 'beristirahat', 'melepas', 'penat', 'banyak', 'jajanan', 'area', 'parkir', 'cukup', 'luas', 'ombak', 'cukup', 'besar', 'banyak', 'pengamen']</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>['nyaman', 'beristirahat', 'melepas', 'penat', 'jajanan', 'area', 'parkir', 'luas', 'ombak', 'pengamen']</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>nyaman istirahat lepas penat jajan area parkir luas ombak amen</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>CONF</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>ECON</t>
         </is>
       </c>
     </row>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,59 +466,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ikon kota palabuhanratu......bagus</t>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ikon kota palabuhanratubagus</t>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ikon kota palabuhanratubagus</t>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
+          <t>Lokasi strategis. Cocok untuk santai cocok untuk anak-anak, cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan, cocok untuk yg tua muda semuanya.. tinggal d jaga bersama sama.. jangan vandalisme dan mengotorinya dgn sampah..okkkk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
+          <t>lokasi strategis cocok untuk santai cocok untuk anakanak cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan cocok untuk yg tua muda semuanya tinggal d jaga bersama sama jangan vandalisme dan mengotorinya dgn sampahokkkk</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
+          <t>['lokasi', 'strategis', 'cocok', 'untuk', 'santai', 'cocok', 'untuk', 'anakanak', 'cocok', 'untuk', 'olahraga', 'subuh', 'dengan', 'udara', 'yg', 'segar', 'dekat', 'pegunungan', 'cocok', 'untuk', 'yg', 'tua', 'muda', 'semuanya', 'tinggal', 'd', 'jaga', 'bersama', 'sama', 'jangan', 'vandalisme', 'dan', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
+          <t>['lokasi', 'strategis', 'cocok', 'santai', 'cocok', 'anakanak', 'cocok', 'olahraga', 'subuh', 'udara', 'yg', 'segar', 'pegunungan', 'cocok', 'yg', 'tua', 'muda', 'tinggal', 'd', 'jaga', 'vandalisme', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
+          <t>lokasi strategis cocok santai cocok anakanak cocok olahraga subuh udara yg segar gunung cocok yg tua muda tinggal d jaga vandalisme kotor dgn sampahokkkk</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -553,19 +553,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>SDH tidak terlalu bagus...kalau malam sangat gelap..bnyk lampu yg mati dan tak diperbaiki..Pedagang Kaki lima nya sih lumayan tertata rapi...</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -575,22 +575,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>sdh tidak terlalu baguskalau malam sangat gelapbnyk lampu yg mati dan tak diperbaikipedagang kaki lima nya sih lumayan tertata rapi</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['sdh', 'tidak', 'terlalu', 'baguskalau', 'malam', 'sangat', 'gelapbnyk', 'lampu', 'yg', 'mati', 'dan', 'tak', 'diperbaikipedagang', 'kaki', 'lima', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['sdh', 'baguskalau', 'malam', 'gelapbnyk', 'lampu', 'yg', 'mati', 'diperbaikipedagang', 'kaki', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>sdh baguskalau malam gelapbnyk lampu yg mati diperbaikipedagang kaki nya sih lumayan tata rapi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -607,59 +607,59 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Akses masuk dengan mobil relatif mudah hingga ke bibir pantai</t>
+          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>akses masuk dengan mobil relatif mudah hingga ke bibir pantai</t>
+          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['akses', 'masuk', 'dengan', 'mobil', 'relatif', 'mudah', 'hingga', 'ke', 'bibir', 'pantai']</t>
+          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['akses', 'masuk', 'mobil', 'relatif', 'mudah', 'bibir', 'pantai']</t>
+          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>akses masuk mobil relatif mudah bibir pantai</t>
+          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alhamdulillahasih bersih, indah apalagi di malam hari, tepat nya di depan majid agung palabuahan ratu, banyak tersedia jajanan juga, ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
+          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -669,22 +669,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>alhamdulillahasih bersih indah apalagi di malam hari tepat nya di depan majid agung palabuahan ratu banyak tersedia jajanan juga ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
+          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['alhamdulillahasih', 'bersih', 'indah', 'apalagi', 'di', 'malam', 'hari', 'tepat', 'nya', 'di', 'depan', 'majid', 'agung', 'palabuahan', 'ratu', 'banyak', 'tersedia', 'jajanan', 'juga', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended', 'lah']</t>
+          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['alhamdulillahasih', 'bersih', 'indah', 'malam', 'nya', 'majid', 'agung', 'palabuahan', 'ratu', 'tersedia', 'jajanan', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended']</t>
+          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>alhamdulillahasih bersih indah malam nya majid agung palabuahan ratu sedia jajan ubtuk dar santa denfan keluarga rekomended</t>
+          <t>kali lapang cangehgarbagus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -701,42 +701,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Di kelola oleh oknum</t>
+          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>di kelola oleh oknum</t>
+          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['di', 'kelola', 'oleh', 'oknum']</t>
+          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['kelola', 'oknum']</t>
+          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>kelola oknum</t>
+          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -748,42 +748,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
+          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
+          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
+          <t>cocok jalanjalan santai ramai sejuk</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -795,42 +795,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>ga ada pungli tapi kalo mau mesen makanan alangkah baiknya tanya harga dulu soalnya main getok harga</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>ga ada pungli tapi kalo mau mesen makanan alangkah baiknya tanya harga dulu soalnya main getok harga</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['ga', 'ada', 'pungli', 'tapi', 'kalo', 'mau', 'mesen', 'makanan', 'alangkah', 'baiknya', 'tanya', 'harga', 'dulu', 'soalnya', 'main', 'getok', 'harga']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['ga', 'pungli', 'kalo', 'mesen', 'makanan', 'alangkah', 'baiknya', 'harga', 'main', 'getok', 'harga']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>ga pungli kalo mesen makan alangkah baik harga main getok harga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -842,12 +842,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>untuk  harga masuk motor 10k, mobil 20k, mobil travel 30k bis kecil 50k, bis besar 100k menurutku dengan harga segini udah worth it banget sih karna pantai dan pemandangannya ga mainmain bener2 sekeren itu bikin betah seharian</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -857,22 +857,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>untuk harga masuk motor k mobil k mobil travel k bis kecil k bis besar k menurutku dengan harga segini udah worth it banget sih karna pantai dan pemandangannya ga mainmain bener sekeren itu bikin betah seharian</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['untuk', 'harga', 'masuk', 'motor', 'k', 'mobil', 'k', 'mobil', 'travel', 'k', 'bis', 'kecil', 'k', 'bis', 'besar', 'k', 'menurutku', 'dengan', 'harga', 'segini', 'udah', 'worth', 'it', 'banget', 'sih', 'karna', 'pantai', 'dan', 'pemandangannya', 'ga', 'mainmain', 'bener', 'sekeren', 'itu', 'bikin', 'betah', 'seharian']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['harga', 'masuk', 'motor', 'k', 'mobil', 'k', 'mobil', 'travel', 'k', 'bis', 'k', 'bis', 'k', 'menurutku', 'harga', 'segini', 'udah', 'worth', 'it', 'banget', 'sih', 'karna', 'pantai', 'pemandangannya', 'ga', 'mainmain', 'bener', 'sekeren', 'bikin', 'betah', 'seharian']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>harga masuk motor k mobil k mobil travel k bis k bis k turut harga gin udah worth it banget sih karna pantai pandang ga mainmain bener keren bikin betah hari</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -882,49 +882,49 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>mudik dari bandung, ga berani berenang d pantai, jd k kolam renang aja. kolam udah bagus, cuma perlu penegasan d saung2 u/ pngunjung. sewa jg gppa u/ saung, drpd ga jelas nongkrong dmna.</t>
+          <t>Pagi,siang mlm ramai pedagang smua murah meriah. Buat nongkrong smua usia jgn lupa silakan berkunjung, anda pasti suka....</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>mudik dari bandung ga berani berenang d pantai jd k kolam renang aja kolam udah bagus cuma perlu penegasan d saung u pngunjung sewa jg gppa u saung drpd ga jelas nongkrong dmna</t>
+          <t>pagisiang mlm ramai pedagang smua murah meriah buat nongkrong smua usia jgn lupa silakan berkunjung anda pasti suka</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['mudik', 'dari', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'cuma', 'perlu', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'jelas', 'nongkrong', 'dmna']</t>
+          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'buat', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'anda', 'pasti', 'suka']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['mudik', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'nongkrong', 'dmna']</t>
+          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'suka']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>mudik bandung ga berani renang d pantai jd k kolam renang aja kolam udah bagus tegas d saung u pngunjung sewa jg gppa u saung drpd ga nongkrong dmna</t>
+          <t>pagisiang mlm ramai dagang smua murah riah nongkrong smua usia jgn lupa sila kunjung suka</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -936,12 +936,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bagus,,enak buat liburan bersama keluarga</t>
+          <t>Pantai selatan nan indah.perlu penataan.dan pembenahan dengan ke seriusan pemda setempat.agar bisa menjadi obyek wisata andalan.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -951,22 +951,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>bagusenak buat liburan bersama keluarga</t>
+          <t>pantai selatan nan indahperlu penataandan pembenahan dengan ke seriusan pemda setempatagar bisa menjadi obyek wisata andalan</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
+          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'dengan', 'ke', 'seriusan', 'pemda', 'setempatagar', 'bisa', 'menjadi', 'obyek', 'wisata', 'andalan']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['bagusenak', 'liburan', 'keluarga']</t>
+          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'seriusan', 'pemda', 'setempatagar', 'obyek', 'wisata', 'andalan']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>bagusenak libur keluarga</t>
+          <t>pantai selatan nan indahperlu penataandan benah serius pemda setempatagar obyek wisata andal</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -983,42 +983,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Asik pantainya banyak hiburan buat anak anak,mantap</t>
+          <t>Sdh mulai banyak kerusakan. Terutama pada area olahraga. Kurang terawat tidak seperti awal awal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>asik pantainya banyak hiburan buat anak anakmantap</t>
+          <t>sdh mulai banyak kerusakan terutama pada area olahraga kurang terawat tidak seperti awal awal</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'banyak', 'hiburan', 'buat', 'anak', 'anakmantap']</t>
+          <t>['sdh', 'mulai', 'banyak', 'kerusakan', 'terutama', 'pada', 'area', 'olahraga', 'kurang', 'terawat', 'tidak', 'seperti', 'awal', 'awal']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['asik', 'pantainya', 'hiburan', 'anak', 'anakmantap']</t>
+          <t>['sdh', 'kerusakan', 'area', 'olahraga', 'terawat']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>asik pantai hibur anak anakmantap</t>
+          <t>sdh rusa area olahraga awat</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1030,42 +1030,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>Kerennn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
+          <t>['kerennn']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
+          <t>kerennn</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,136 +1077,136 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Smile hill Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1218,42 +1218,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tampil nasyid tingkat provinsi..mantap cah2 Lanang ð¥°ð¥° â¦</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>tampil nasyid tingkat provinsimantap cah lanang ðð â</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tampil nasyid tingkat provinsimantap cah lanang</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1265,12 +1265,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tiket masuk free. View bagus banget terutama pas sunset. Makanan disini harganya standar. Mocinya enak 5k-an doang. Ada penginapan terdekat juga, indomaret tinggal jalan 5 menitan. Bisa naik kuda, itu 30k sekali naik Pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>Kondisi lapang lumayan baik. Track lari sedikit rusak. Lari pagi di hari minggu tidak terlalu padat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1280,22 +1280,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget terutama pas sunset makanan disini harganya standar mocinya enak kan doang ada penginapan terdekat juga indomaret tinggal jalan menitan bisa naik kuda itu k sekali naik pantainya bersih dan ngga terlalu panas walaupun siang</t>
+          <t>kondisi lapang lumayan baik track lari sedikit rusak lari pagi di hari minggu tidak terlalu padat</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'terutama', 'pas', 'sunset', 'makanan', 'disini', 'harganya', 'standar', 'mocinya', 'enak', 'kan', 'doang', 'ada', 'penginapan', 'terdekat', 'juga', 'indomaret', 'tinggal', 'jalan', 'menitan', 'bisa', 'naik', 'kuda', 'itu', 'k', 'sekali', 'naik', 'pantainya', 'bersih', 'dan', 'ngga', 'terlalu', 'panas', 'walaupun', 'siang']</t>
+          <t>['kondisi', 'lapang', 'lumayan', 'baik', 'track', 'lari', 'sedikit', 'rusak', 'lari', 'pagi', 'di', 'hari', 'minggu', 'tidak', 'terlalu', 'padat']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['tiket', 'masuk', 'free', 'view', 'bagus', 'banget', 'pas', 'sunset', 'makanan', 'harganya', 'standar', 'mocinya', 'enak', 'doang', 'penginapan', 'terdekat', 'indomaret', 'tinggal', 'jalan', 'menitan', 'kuda', 'k', 'pantainya', 'bersih', 'ngga', 'panas', 'siang']</t>
+          <t>['kondisi', 'lapang', 'lumayan', 'track', 'lari', 'rusak', 'lari', 'pagi', 'minggu', 'padat']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiket masuk free view bagus banget pas sunset makan harga standar mocinya enak doang inap dekat indomaret tinggal jalan menit kuda k pantai bersih ngga panas siang</t>
+          <t>kondisi lapang lumayan track lari rusak lari pagi minggu padat</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1305,49 +1305,49 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pantai ci letuh Sukabumi Jabar yang indah,,nyaman dan ramah..</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1374,22 +1374,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>pantai ci letuh sukabumi jabar yang indahnyaman dan ramah</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['pantai', 'ci', 'letuh', 'sukabumi', 'jabar', 'yang', 'indahnyaman', 'dan', 'ramah']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['pantai', 'ci', 'letuh', 'sukabumi', 'jabar', 'indahnyaman', 'ramah']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>pantai ci letuh sukabumi jabar indahnyaman ramah</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pemandangannya bagus, cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1421,22 +1421,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>pemandangannya bagus cuma sekarang pantai nya rusak cuma ada bebatuan doang</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['pemandangannya', 'bagus', 'cuma', 'sekarang', 'pantai', 'nya', 'rusak', 'cuma', 'ada', 'bebatuan', 'doang']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['pemandangannya', 'bagus', 'pantai', 'nya', 'rusak', 'bebatuan', 'doang']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>pandang bagus pantai nya rusak bebatuan doang</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1446,49 +1446,49 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>The place is comfortable, cool, the toilet is always clean. The prayer clothes in the mosque are fragrant and clean. There are many vendors selling unique and cheap snacks, and the taste is also delicious.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1500,12 +1500,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jalanya mantap</t>
+          <t>Palabuhanratu square is a comfortable place to rest or just hang out, because the place is spacious and can be a children's play area, there are many traders selling various snacks, next to it there is a large and comfortable grand mosque for praying, there are also toilets available.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1515,22 +1515,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jalanya mantap</t>
+          <t>palabuhanratu square is a comfortable place to rest or just hang out because the place is spacious and can be a childrens play area there are many traders selling various snacks next to it there is a large and comfortable grand mosque for praying there are also toilets available</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['palabuhanratu', 'square', 'is', 'a', 'comfortable', 'place', 'to', 'rest', 'or', 'just', 'hang', 'out', 'because', 'the', 'place', 'is', 'spacious', 'and', 'can', 'be', 'a', 'childrens', 'play', 'area', 'there', 'are', 'many', 'traders', 'selling', 'various', 'snacks', 'next', 'to', 'it', 'there', 'is', 'a', 'large', 'and', 'comfortable', 'grand', 'mosque', 'for', 'praying', 'there', 'are', 'also', 'toilets', 'available']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['palabuhanratu', 'square', 'is', 'a', 'comfortable', 'place', 'to', 'rest', 'or', 'just', 'hang', 'out', 'because', 'the', 'place', 'is', 'spacious', 'and', 'can', 'be', 'a', 'childrens', 'play', 'area', 'there', 'are', 'many', 'traders', 'selling', 'various', 'snacks', 'next', 'to', 'it', 'there', 'is', 'a', 'large', 'and', 'comfortable', 'grand', 'mosque', 'for', 'praying', 'there', 'are', 'also', 'toilets', 'available']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jala mantap</t>
+          <t>palabuhanratu square is a comfortable place to rest or just hang out because the place is spacious and can be a childrens play area there are many traders selling various snacks next to it there is a large and comfortable grand mosque for praying there are also toilets available</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
@@ -1552,89 +1552,89 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
+          <t>Palabuhanratu Square is the center of Palabuhanratu City. It is characterized by a large plot of land. Surrounding it are functional buildings. This square is located in Palabuhanratu Village, Palabuhanratu City District, precisely on Jalan Siliwangi Palabuhanratu, to the east of the Great Mosque of Palabuhanratu.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
+          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
+          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
+          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
+          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Pemandangannya indah dan akses jalan ke arah pantai cibanban lumayan bagus dan cukup menantang. Kalau dari Cianjur jaraknya gak terlalu jauh, jadi bisa berangkat pagi pulang lagi sore.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>pemandangannya indah dan akses jalan ke arah pantai cibanban lumayan bagus dan cukup menantang kalau dari cianjur jaraknya gak terlalu jauh jadi bisa berangkat pagi pulang lagi sore</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['pemandangannya', 'indah', 'dan', 'akses', 'jalan', 'ke', 'arah', 'pantai', 'cibanban', 'lumayan', 'bagus', 'dan', 'cukup', 'menantang', 'kalau', 'dari', 'cianjur', 'jaraknya', 'gak', 'terlalu', 'jauh', 'jadi', 'bisa', 'berangkat', 'pagi', 'pulang', 'lagi', 'sore']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['pemandangannya', 'indah', 'akses', 'jalan', 'arah', 'pantai', 'cibanban', 'lumayan', 'bagus', 'menantang', 'cianjur', 'jaraknya', 'gak', 'berangkat', 'pagi', 'pulang', 'sore']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>pandang indah akses jalan arah pantai cibanban lumayan bagus tantang cianjur jarak gak berangkat pagi pulang sore</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
@@ -1688,12 +1688,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Keren nih tempatnya, sambil istirahat trus pesen kelapa muda , duh di seruput, alamak hati senang , ingat kerjaan nya setelah di jakarta aja ya, â¦</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1703,22 +1703,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>keren nih tempatnya sambil istirahat trus pesen kelapa muda duh di seruput alamak hati senang ingat kerjaan nya setelah di jakarta aja ya â</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['keren', 'nih', 'tempatnya', 'sambil', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'di', 'seruput', 'alamak', 'hati', 'senang', 'ingat', 'kerjaan', 'nya', 'setelah', 'di', 'jakarta', 'aja', 'ya', 'â']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['keren', 'nih', 'tempatnya', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'seruput', 'alamak', 'hati', 'senang', 'kerjaan', 'nya', 'jakarta', 'aja', 'ya', 'â']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>keren nih tempat istirahat trus sen kelapa muda duh seruput alamak hati senang kerja nya jakarta aja ya</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1735,42 +1735,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Liburan murmer ,,sewa rumah di pinggir pantai murah cuma sayang banyak yg ngamen.. Repot juga tiap 5 menit mah dikira liburan banyak duit...bilang maaf ga pergi2.. Saran siapin receh yg banyak</t>
+          <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>liburan murmer sewa rumah di pinggir pantai murah cuma sayang banyak yg ngamen repot juga tiap menit mah dikira liburan banyak duitbilang maaf ga pergi saran siapin receh yg banyak</t>
+          <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['liburan', 'murmer', 'sewa', 'rumah', 'di', 'pinggir', 'pantai', 'murah', 'cuma', 'sayang', 'banyak', 'yg', 'ngamen', 'repot', 'juga', 'tiap', 'menit', 'mah', 'dikira', 'liburan', 'banyak', 'duitbilang', 'maaf', 'ga', 'pergi', 'saran', 'siapin', 'receh', 'yg', 'banyak']</t>
+          <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['liburan', 'murmer', 'sewa', 'rumah', 'pinggir', 'pantai', 'murah', 'sayang', 'yg', 'ngamen', 'repot', 'menit', 'mah', 'liburan', 'duitbilang', 'maaf', 'ga', 'pergi', 'saran', 'siapin', 'receh', 'yg']</t>
+          <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>libur murmer sewa rumah pinggir pantai murah sayang yg ngamen repot menit mah libur duitbilang maaf ga pergi saran siapin receh yg</t>
+          <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1782,42 +1782,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Keren nih tempatnya, sambil istirahat trus pesen kelapa muda , duh di seruput, alamak hati senang , ingat kerjaan nya setelah di jakarta aja ya, â¦</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>keren nih tempatnya sambil istirahat trus pesen kelapa muda duh di seruput alamak hati senang ingat kerjaan nya setelah di jakarta aja ya â</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['keren', 'nih', 'tempatnya', 'sambil', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'di', 'seruput', 'alamak', 'hati', 'senang', 'ingat', 'kerjaan', 'nya', 'setelah', 'di', 'jakarta', 'aja', 'ya', 'â']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['keren', 'nih', 'tempatnya', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'seruput', 'alamak', 'hati', 'senang', 'kerjaan', 'nya', 'jakarta', 'aja', 'ya', 'â']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>keren nih tempat istirahat trus sen kelapa muda duh seruput alamak hati senang kerja nya jakarta aja ya</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1829,42 +1829,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
+          <t>Di kelola oleh oknum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
+          <t>di kelola oleh oknum</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
+          <t>['di', 'kelola', 'oleh', 'oknum']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
+          <t>['kelola', 'oknum']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
+          <t>kelola oknum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1876,139 +1876,1314 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pantainya kurang bagus kotor terus parkiranya gaboleh didepan warung sama yg punya warung</t>
+          <t>The 77th HAB ceremony at the Sukabumi Regency Ministry of Religious Affairs Office. Atmosphere in traditional attire.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>pantainya kurang bagus kotor terus parkiranya gaboleh didepan warung sama yg punya warung</t>
+          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['pantainya', 'kurang', 'bagus', 'kotor', 'terus', 'parkiranya', 'gaboleh', 'didepan', 'warung', 'sama', 'yg', 'punya', 'warung']</t>
+          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'kotor', 'parkiranya', 'gaboleh', 'didepan', 'warung', 'yg', 'warung']</t>
+          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>pantai bagus kotor parkiranya gaboleh depan warung yg warung</t>
+          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pas banget buat nongki akses enak dan strategis</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>pas banget buat nongki akses enak dan strategis</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['pas', 'banget', 'buat', 'nongki', 'akses', 'enak', 'dan', 'strategis']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['pas', 'banget', 'nongki', 'akses', 'enak', 'strategis']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>pas banget nongki akses enak strategis</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>The atmosphere is comfortable and pleasant. You can play in the sand on the beach, making it perfect for family outings.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DIGI</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>DIGI</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Wisata Alam Pantai Sukawayana</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Pantai Karang Sari</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ALUN ALUN GADOBANGKONG</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luas,mudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luasmudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>['tempat', 'di', 'pelabuhan', 'ratu', 'buat', 'main', 'keluarga', 'cuma', 'jarang', 'tempat', 'untuk', 'berteduh', 'suasana', 'pantai', 'indah', 'banyak', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'lebih', 'di', 'pelihara', 'dan', 'di', 'perindah', 'supaya', 'tempat', 'nya', 'makin', 'bagus']</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>['pelabuhan', 'ratu', 'main', 'keluarga', 'jarang', 'berteduh', 'suasana', 'pantai', 'indah', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'pelihara', 'perindah', 'nya', 'bagus']</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>labuh ratu main keluarga jarang teduh suasana pantai indah tukang dagang parkir luasmudah mudah pelihara indah nya bagus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Pantai Karang Sari</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Banyak sampah, kayanya kalo mlm sring dipake buat hal-hal yg tdk sharusnya. Tlg Bapak satpol PP dan Polisi mengawal tempat tsb. Trmksh.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>banyak sampah kayanya kalo mlm sring dipake buat halhal yg tdk sharusnya tlg bapak satpol pp dan polisi mengawal tempat tsb trmksh</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>['banyak', 'sampah', 'kayanya', 'kalo', 'mlm', 'sring', 'dipake', 'buat', 'halhal', 'yg', 'tdk', 'sharusnya', 'tlg', 'bapak', 'satpol', 'pp', 'dan', 'polisi', 'mengawal', 'tempat', 'tsb', 'trmksh']</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>['sampah', 'kayanya', 'kalo', 'mlm', 'sring', 'dipake', 'halhal', 'yg', 'tdk', 'sharusnya', 'tlg', 'satpol', 'pp', 'polisi', 'mengawal', 'tsb', 'trmksh']</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>sampah kaya kalo mlm sring dipake halhal yg tdk sharusnya tlg satpol pp polisi awal tsb trmksh</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ALUN ALUN GADOBANGKONG</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>A place in Pelabuhan Ratu for families to play, but there are rarely any places to take shelter, a beautiful beach atmosphere, lots of traders, spacious parking, hopefully it will be better maintained and beautified so that the place will be even better.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DIGI</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>a place in pelabuhan ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>a place in labuh ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>DIGI</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Pantai Citepus</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Liburan murmer ,,sewa rumah di pinggir pantai murah cuma sayang banyak yg ngamen.. Repot juga tiap 5 menit mah dikira liburan banyak duit...bilang maaf ga pergi2.. Saran siapin receh yg banyak</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>liburan murmer sewa rumah di pinggir pantai murah cuma sayang banyak yg ngamen repot juga tiap menit mah dikira liburan banyak duitbilang maaf ga pergi saran siapin receh yg banyak</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>['liburan', 'murmer', 'sewa', 'rumah', 'di', 'pinggir', 'pantai', 'murah', 'cuma', 'sayang', 'banyak', 'yg', 'ngamen', 'repot', 'juga', 'tiap', 'menit', 'mah', 'dikira', 'liburan', 'banyak', 'duitbilang', 'maaf', 'ga', 'pergi', 'saran', 'siapin', 'receh', 'yg', 'banyak']</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>['liburan', 'murmer', 'sewa', 'rumah', 'pinggir', 'pantai', 'murah', 'sayang', 'yg', 'ngamen', 'repot', 'menit', 'mah', 'liburan', 'duitbilang', 'maaf', 'ga', 'pergi', 'saran', 'siapin', 'receh', 'yg']</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>libur murmer sewa rumah pinggir pantai murah sayang yg ngamen repot menit mah libur duitbilang maaf ga pergi saran siapin receh yg</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Pantai Citepus</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Enak sih pantai nya ngga kotor cuma pasir nya aja yg warna coklat ngga kaya Sawarna yg pasir nya masi putih ðð â¦</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>enak sih pantai nya ngga kotor cuma pasir nya aja yg warna coklat ngga kaya sawarna yg pasir nya masi putih ðð â</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>['enak', 'sih', 'pantai', 'nya', 'ngga', 'kotor', 'cuma', 'pasir', 'nya', 'aja', 'yg', 'warna', 'coklat', 'ngga', 'kaya', 'sawarna', 'yg', 'pasir', 'nya', 'masi', 'putih', 'ðð', 'â']</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>['enak', 'sih', 'pantai', 'nya', 'ngga', 'kotor', 'pasir', 'nya', 'aja', 'yg', 'warna', 'coklat', 'ngga', 'kaya', 'sawarna', 'yg', 'pasir', 'nya', 'masi', 'putih', 'ðð', 'â']</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>enak sih pantai nya ngga kotor pasir nya aja yg warna coklat ngga kaya sawarna yg pasir nya mas putih</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Accommodating thousands of people, with a nice park and toilet facilities...</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>accommodating thousands of people with a nice park and toilet facilities</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>accommodating thousands of people with a nice park and toilet facilities</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>The mosque is large and quite clean. The ablution area and toilets are also clean. There are many vendors around the square.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>the mosque is large and quite clean the ablution area and toilets are also clean there are many vendors around the square</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>['the', 'mosque', 'is', 'large', 'and', 'quite', 'clean', 'the', 'ablution', 'area', 'and', 'toilets', 'are', 'also', 'clean', 'there', 'are', 'many', 'vendors', 'around', 'the', 'square']</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>['the', 'mosque', 'is', 'large', 'and', 'quite', 'clean', 'the', 'ablution', 'area', 'and', 'toilets', 'are', 'also', 'clean', 'there', 'are', 'many', 'vendors', 'around', 'the', 'square']</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>the mosque is large and quite clean the ablution area and toilets are also clean there are many vendors around the square</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PANTAI CIBANGBAN</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Untuk pantainya seperti pantai kebanyakan, dengan ombak besarnya. Sarana di dipantai tersebut kurang nyaman, lesehan buat nginap terbilang mahal, kurang aman buat anak2 bermain air karena minimnya pengawasan petugas.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>untuk pantainya seperti pantai kebanyakan dengan ombak besarnya sarana di dipantai tersebut kurang nyaman lesehan buat nginap terbilang mahal kurang aman buat anak bermain air karena minimnya pengawasan petugas</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>['untuk', 'pantainya', 'seperti', 'pantai', 'kebanyakan', 'dengan', 'ombak', 'besarnya', 'sarana', 'di', 'dipantai', 'tersebut', 'kurang', 'nyaman', 'lesehan', 'buat', 'nginap', 'terbilang', 'mahal', 'kurang', 'aman', 'buat', 'anak', 'bermain', 'air', 'karena', 'minimnya', 'pengawasan', 'petugas']</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>['pantainya', 'pantai', 'kebanyakan', 'ombak', 'besarnya', 'sarana', 'dipantai', 'nyaman', 'lesehan', 'nginap', 'terbilang', 'mahal', 'aman', 'anak', 'bermain', 'air', 'minimnya', 'pengawasan', 'petugas']</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>pantai pantai banyak ombak besar sarana pantai nyaman leseh nginap bilang mahal aman anak main air minim awas tugas</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Pantai Citepus</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Jangilus Monument</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ikon kota palabuhanratu......bagus</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ikon kota palabuhanratubagus</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ikon kota palabuhanratubagus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Waterpark Citepus Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mantappppp</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>mantappppp</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>['mantappppp']</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>['mantappppp']</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>mantappppp</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Pantai Batu Bintang</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Pantai Batu Bintang merupakan salah satu pantai yang terletak di Pelabuhan Ratu, Kabupaten Sukabumi, Jawa Barat. Pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik. â¦</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>pantai batu bintang merupakan salah satu pantai yang terletak di pelabuhan ratu kabupaten sukabumi jawa barat pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik â</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>['pantai', 'batu', 'bintang', 'merupakan', 'salah', 'satu', 'pantai', 'yang', 'terletak', 'di', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'ini', 'terkenal', 'dengan', 'keindahan', 'pantainya', 'yang', 'masih', 'alami', 'dan', 'dihiasi', 'dengan', 'bebatuan', 'yang', 'unik', 'dan', 'menarik', 'â']</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>['pantai', 'batu', 'bintang', 'salah', 'pantai', 'terletak', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'terkenal', 'keindahan', 'pantainya', 'alami', 'dihiasi', 'bebatuan', 'unik', 'menarik', 'â']</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>pantai batu bintang salah pantai letak labuh ratu kabupaten sukabumi jawa barat pantai kenal indah pantai alami hias bebatuan unik tarik</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ALUN ALUN GADOBANGKONG</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Bagus cm tmpat smpah sedikit.. ama pedagang julid ge bnyk Parkir liar bnyk View lumayan</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>bagus cm tmpat smpah sedikit ama pedagang julid ge bnyk parkir liar bnyk view lumayan</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>['bagus', 'cm', 'tmpat', 'smpah', 'sedikit', 'ama', 'pedagang', 'julid', 'ge', 'bnyk', 'parkir', 'liar', 'bnyk', 'view', 'lumayan']</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>['bagus', 'cm', 'tmpat', 'smpah', 'ama', 'pedagang', 'julid', 'ge', 'bnyk', 'parkir', 'liar', 'bnyk', 'view', 'lumayan']</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>bagus cm tmpat smpah ama dagang julid ge bnyk parkir liar bnyk view lumayan</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>bagus,,enak buat liburan bersama keluarga</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>bagusenak buat liburan bersama keluarga</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>['bagusenak', 'liburan', 'keluarga']</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>bagusenak libur keluarga</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Pantai Batu Bintang</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Pantai Citepus</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Pantai Twenty Cipatuguran</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Pantai Batu Bintang</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>lumayan bagusaman untuk anak main dipantainya</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>lumayan bagusaman anak main pantai</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Pantai Batu Bintang</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>Pertama ngecamp pinggir pantai tuu rasanya,MasyaAllah.. Pantai ini tu,deket ke warung,deket ke mushola,air untuk mandi lancar.tapi,kalau mau cam di tarif lagi untuk biaya kebersihan 1 tenda 20-25k untuk yang mau ikut â¦</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>ECON</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>pertama ngecamp pinggir pantai tuu rasanyamasyaallah pantai ini tudeket ke warungdeket ke musholaair untuk mandi lancartapikalau mau cam di tarif lagi untuk biaya kebersihan tenda k untuk yang mau ikut â</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>['pertama', 'ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'ini', 'tudeket', 'ke', 'warungdeket', 'ke', 'musholaair', 'untuk', 'mandi', 'lancartapikalau', 'mau', 'cam', 'di', 'tarif', 'lagi', 'untuk', 'biaya', 'kebersihan', 'tenda', 'k', 'untuk', 'yang', 'mau', 'ikut', 'â']</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>['ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'tudeket', 'warungdeket', 'musholaair', 'mandi', 'lancartapikalau', 'cam', 'tarif', 'biaya', 'kebersihan', 'tenda', 'k', 'â']</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>ngecamp pinggir pantai tuu rasanyamasyaallah pantai tudeket warungdeket musholaair mandi lancartapikalau cam tarif biaya bersih tenda k</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>ECON</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Tempat nya strategis untuk istrahat. Setelah solat d mesjid, bisa jajan dan mknan dlu, bnyak tempat jajannya, dekat dgn KFC, ATM dan toserba juga...ð â¦</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DIGI</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>tempat nya strategis untuk istrahat setelah solat d mesjid bisa jajan dan mknan dlu bnyak tempat jajannya dekat dgn kfc atm dan toserba jugað â</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>['tempat', 'nya', 'strategis', 'untuk', 'istrahat', 'setelah', 'solat', 'd', 'mesjid', 'bisa', 'jajan', 'dan', 'mknan', 'dlu', 'bnyak', 'tempat', 'jajannya', 'dekat', 'dgn', 'kfc', 'atm', 'dan', 'toserba', 'jugað', 'â']</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>['nya', 'strategis', 'istrahat', 'solat', 'd', 'mesjid', 'jajan', 'mknan', 'dlu', 'bnyak', 'jajannya', 'dgn', 'kfc', 'atm', 'toserba', 'jugað', 'â']</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>nya strategis istrahat solat d mesjid jajan mknan dlu bnyak jajan dgn kfc atm toserba juga</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>DIGI</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -466,89 +466,89 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
+          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
+          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
+          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
+          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
+          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lokasi strategis. Cocok untuk santai cocok untuk anak-anak, cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan, cocok untuk yg tua muda semuanya.. tinggal d jaga bersama sama.. jangan vandalisme dan mengotorinya dgn sampah..okkkk</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>lokasi strategis cocok untuk santai cocok untuk anakanak cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan cocok untuk yg tua muda semuanya tinggal d jaga bersama sama jangan vandalisme dan mengotorinya dgn sampahokkkk</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['lokasi', 'strategis', 'cocok', 'untuk', 'santai', 'cocok', 'untuk', 'anakanak', 'cocok', 'untuk', 'olahraga', 'subuh', 'dengan', 'udara', 'yg', 'segar', 'dekat', 'pegunungan', 'cocok', 'untuk', 'yg', 'tua', 'muda', 'semuanya', 'tinggal', 'd', 'jaga', 'bersama', 'sama', 'jangan', 'vandalisme', 'dan', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['lokasi', 'strategis', 'cocok', 'santai', 'cocok', 'anakanak', 'cocok', 'olahraga', 'subuh', 'udara', 'yg', 'segar', 'pegunungan', 'cocok', 'yg', 'tua', 'muda', 'tinggal', 'd', 'jaga', 'vandalisme', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>lokasi strategis cocok santai cocok anakanak cocok olahraga subuh udara yg segar gunung cocok yg tua muda tinggal d jaga vandalisme kotor dgn sampahokkkk</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -560,12 +560,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SDH tidak terlalu bagus...kalau malam sangat gelap..bnyk lampu yg mati dan tak diperbaiki..Pedagang Kaki lima nya sih lumayan tertata rapi...</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -575,22 +575,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sdh tidak terlalu baguskalau malam sangat gelapbnyk lampu yg mati dan tak diperbaikipedagang kaki lima nya sih lumayan tertata rapi</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['sdh', 'tidak', 'terlalu', 'baguskalau', 'malam', 'sangat', 'gelapbnyk', 'lampu', 'yg', 'mati', 'dan', 'tak', 'diperbaikipedagang', 'kaki', 'lima', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['sdh', 'baguskalau', 'malam', 'gelapbnyk', 'lampu', 'yg', 'mati', 'diperbaikipedagang', 'kaki', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>sdh baguskalau malam gelapbnyk lampu yg mati diperbaikipedagang kaki nya sih lumayan tata rapi</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -607,59 +607,59 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
+          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
+          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
+          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
+          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
+          <t>nongki chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
+          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -669,22 +669,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
+          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>kali lapang cangehgarbagus</t>
+          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -701,42 +701,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -748,12 +748,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+          <t>Air nya hijau ga terurus banyak bentuknya, gazebo udah pada rusak</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -763,22 +763,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+          <t>air nya hijau ga terurus banyak bentuknya gazebo udah pada rusak</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'banyak', 'bentuknya', 'gazebo', 'udah', 'pada', 'rusak']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'bentuknya', 'gazebo', 'udah', 'rusak']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>cocok jalanjalan santai ramai sejuk</t>
+          <t>air nya hijau ga urus bentuk gazebo udah rusak</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -795,42 +795,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Smile hill Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ga ada pungli tapi kalo mau mesen makanan alangkah baiknya tanya harga dulu soalnya main getok harga</t>
+          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ga ada pungli tapi kalo mau mesen makanan alangkah baiknya tanya harga dulu soalnya main getok harga</t>
+          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['ga', 'ada', 'pungli', 'tapi', 'kalo', 'mau', 'mesen', 'makanan', 'alangkah', 'baiknya', 'tanya', 'harga', 'dulu', 'soalnya', 'main', 'getok', 'harga']</t>
+          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['ga', 'pungli', 'kalo', 'mesen', 'makanan', 'alangkah', 'baiknya', 'harga', 'main', 'getok', 'harga']</t>
+          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ga pungli kalo mesen makan alangkah baik harga main getok harga</t>
+          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -842,42 +842,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Untuk pantainya seperti pantai kebanyakan, dengan ombak besarnya. Sarana di dipantai tersebut kurang nyaman, lesehan buat nginap terbilang mahal, kurang aman buat anak2 bermain air karena minimnya pengawasan petugas.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>untuk pantainya seperti pantai kebanyakan dengan ombak besarnya sarana di dipantai tersebut kurang nyaman lesehan buat nginap terbilang mahal kurang aman buat anak bermain air karena minimnya pengawasan petugas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['untuk', 'pantainya', 'seperti', 'pantai', 'kebanyakan', 'dengan', 'ombak', 'besarnya', 'sarana', 'di', 'dipantai', 'tersebut', 'kurang', 'nyaman', 'lesehan', 'buat', 'nginap', 'terbilang', 'mahal', 'kurang', 'aman', 'buat', 'anak', 'bermain', 'air', 'karena', 'minimnya', 'pengawasan', 'petugas']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['pantainya', 'pantai', 'kebanyakan', 'ombak', 'besarnya', 'sarana', 'dipantai', 'nyaman', 'lesehan', 'nginap', 'terbilang', 'mahal', 'aman', 'anak', 'bermain', 'air', 'minimnya', 'pengawasan', 'petugas']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>pantai pantai banyak ombak besar sarana pantai nyaman leseh nginap bilang mahal aman anak main air minim awas tugas</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -889,42 +889,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pagi,siang mlm ramai pedagang smua murah meriah. Buat nongkrong smua usia jgn lupa silakan berkunjung, anda pasti suka....</t>
+          <t>The 77th HAB ceremony at the Sukabumi Regency Ministry of Religious Affairs Office. Atmosphere in traditional attire.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>pagisiang mlm ramai pedagang smua murah meriah buat nongkrong smua usia jgn lupa silakan berkunjung anda pasti suka</t>
+          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'buat', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'anda', 'pasti', 'suka']</t>
+          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'suka']</t>
+          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>pagisiang mlm ramai dagang smua murah riah nongkrong smua usia jgn lupa sila kunjung suka</t>
+          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -936,12 +936,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pantai selatan nan indah.perlu penataan.dan pembenahan dengan ke seriusan pemda setempat.agar bisa menjadi obyek wisata andalan.</t>
+          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -951,22 +951,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>pantai selatan nan indahperlu penataandan pembenahan dengan ke seriusan pemda setempatagar bisa menjadi obyek wisata andalan</t>
+          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'dengan', 'ke', 'seriusan', 'pemda', 'setempatagar', 'bisa', 'menjadi', 'obyek', 'wisata', 'andalan']</t>
+          <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'seriusan', 'pemda', 'setempatagar', 'obyek', 'wisata', 'andalan']</t>
+          <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>pantai selatan nan indahperlu penataandan benah serius pemda setempatagar obyek wisata andal</t>
+          <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -983,42 +983,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sdh mulai banyak kerusakan. Terutama pada area olahraga. Kurang terawat tidak seperti awal awal</t>
+          <t>Ikon kota palabuhanratu......bagus</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>sdh mulai banyak kerusakan terutama pada area olahraga kurang terawat tidak seperti awal awal</t>
+          <t>ikon kota palabuhanratubagus</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['sdh', 'mulai', 'banyak', 'kerusakan', 'terutama', 'pada', 'area', 'olahraga', 'kurang', 'terawat', 'tidak', 'seperti', 'awal', 'awal']</t>
+          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['sdh', 'kerusakan', 'area', 'olahraga', 'terawat']</t>
+          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>sdh rusa area olahraga awat</t>
+          <t>ikon kota palabuhanratubagus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1030,12 +1030,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kerennn</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>kerennn</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['kerennn']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['kerennn']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>kerennn</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1077,12 +1077,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1092,22 +1092,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['skarang', 'lebih', 'sepi', 'dan', 'kebanyakan', 'di', 'pakai', 'oknum', 'pemuda', 'pemudi', 'buat', 'pacaran', 'kadang', 'suka', 'ada', 'yg', 'mabuk', 'atau', 'tawuran', 'anak', 'sekolah']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['skarang', 'sepi', 'kebanyakan', 'pakai', 'oknum', 'pemuda', 'pemudi', 'pacaran', 'kadang', 'suka', 'yg', 'mabuk', 'tawuran', 'anak', 'sekolah']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>skarang sepi banyak pakai oknum pemuda pemudi pacar kadang suka yg mabuk tawur anak sekolah</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1124,42 +1124,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
+          <t>Jajahannya banyak pilihan dan enak ð Tahu crispy juara, sate padang juga mantul, cilok lumayan, cilor enak, pisang keju enak, sate2 an enak, waduh kalap pokoknya â¦</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
+          <t>jajahannya banyak pilihan dan enak ð tahu crispy juara sate padang juga mantul cilok lumayan cilor enak pisang keju enak sate an enak waduh kalap pokoknya â</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
+          <t>['jajahannya', 'banyak', 'pilihan', 'dan', 'enak', 'ð', 'tahu', 'crispy', 'juara', 'sate', 'padang', 'juga', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'waduh', 'kalap', 'pokoknya', 'â']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
+          <t>['jajahannya', 'pilihan', 'enak', 'ð', 'crispy', 'juara', 'sate', 'padang', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'kalap', 'pokoknya', 'â']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
+          <t>jajah pilih enak crispy juara sate padang mantul cilok lumayan cilor enak pisang keju enak sate an enak kalap pokok</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1171,42 +1171,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
+          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
+          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
+          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1218,42 +1218,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1265,42 +1265,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kondisi lapang lumayan baik. Track lari sedikit rusak. Lari pagi di hari minggu tidak terlalu padat</t>
+          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>kondisi lapang lumayan baik track lari sedikit rusak lari pagi di hari minggu tidak terlalu padat</t>
+          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['kondisi', 'lapang', 'lumayan', 'baik', 'track', 'lari', 'sedikit', 'rusak', 'lari', 'pagi', 'di', 'hari', 'minggu', 'tidak', 'terlalu', 'padat']</t>
+          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['kondisi', 'lapang', 'lumayan', 'track', 'lari', 'rusak', 'lari', 'pagi', 'minggu', 'padat']</t>
+          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>kondisi lapang lumayan track lari rusak lari pagi minggu padat</t>
+          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1312,42 +1312,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1359,89 +1359,89 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>pake produck gk kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1453,42 +1453,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The place is comfortable, cool, the toilet is always clean. The prayer clothes in the mosque are fragrant and clean. There are many vendors selling unique and cheap snacks, and the taste is also delicious.</t>
+          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
+          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
+          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
+          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
+          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1500,12 +1500,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Palabuhanratu square is a comfortable place to rest or just hang out, because the place is spacious and can be a children's play area, there are many traders selling various snacks, next to it there is a large and comfortable grand mosque for praying, there are also toilets available.</t>
+          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1515,22 +1515,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>palabuhanratu square is a comfortable place to rest or just hang out because the place is spacious and can be a childrens play area there are many traders selling various snacks next to it there is a large and comfortable grand mosque for praying there are also toilets available</t>
+          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'a', 'comfortable', 'place', 'to', 'rest', 'or', 'just', 'hang', 'out', 'because', 'the', 'place', 'is', 'spacious', 'and', 'can', 'be', 'a', 'childrens', 'play', 'area', 'there', 'are', 'many', 'traders', 'selling', 'various', 'snacks', 'next', 'to', 'it', 'there', 'is', 'a', 'large', 'and', 'comfortable', 'grand', 'mosque', 'for', 'praying', 'there', 'are', 'also', 'toilets', 'available']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'a', 'comfortable', 'place', 'to', 'rest', 'or', 'just', 'hang', 'out', 'because', 'the', 'place', 'is', 'spacious', 'and', 'can', 'be', 'a', 'childrens', 'play', 'area', 'there', 'are', 'many', 'traders', 'selling', 'various', 'snacks', 'next', 'to', 'it', 'there', 'is', 'a', 'large', 'and', 'comfortable', 'grand', 'mosque', 'for', 'praying', 'there', 'are', 'also', 'toilets', 'available']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>palabuhanratu square is a comfortable place to rest or just hang out because the place is spacious and can be a childrens play area there are many traders selling various snacks next to it there is a large and comfortable grand mosque for praying there are also toilets available</t>
+          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Palabuhanratu Square is the center of Palabuhanratu City. It is characterized by a large plot of land. Surrounding it are functional buildings. This square is located in Palabuhanratu Village, Palabuhanratu City District, precisely on Jalan Siliwangi Palabuhanratu, to the east of the Great Mosque of Palabuhanratu.</t>
+          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
+          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
+          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1587,96 +1587,96 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pemandangannya indah dan akses jalan ke arah pantai cibanban lumayan bagus dan cukup menantang. Kalau dari Cianjur jaraknya gak terlalu jauh, jadi bisa berangkat pagi pulang lagi sore.</t>
+          <t>Beautiful, neat and clean. Suitable for taking photos for sunset hunters</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>pemandangannya indah dan akses jalan ke arah pantai cibanban lumayan bagus dan cukup menantang kalau dari cianjur jaraknya gak terlalu jauh jadi bisa berangkat pagi pulang lagi sore</t>
+          <t>beautiful neat and clean suitable for taking photos for sunset hunters</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['pemandangannya', 'indah', 'dan', 'akses', 'jalan', 'ke', 'arah', 'pantai', 'cibanban', 'lumayan', 'bagus', 'dan', 'cukup', 'menantang', 'kalau', 'dari', 'cianjur', 'jaraknya', 'gak', 'terlalu', 'jauh', 'jadi', 'bisa', 'berangkat', 'pagi', 'pulang', 'lagi', 'sore']</t>
+          <t>['beautiful', 'neat', 'and', 'clean', 'suitable', 'for', 'taking', 'photos', 'for', 'sunset', 'hunters']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['pemandangannya', 'indah', 'akses', 'jalan', 'arah', 'pantai', 'cibanban', 'lumayan', 'bagus', 'menantang', 'cianjur', 'jaraknya', 'gak', 'berangkat', 'pagi', 'pulang', 'sore']</t>
+          <t>['beautiful', 'neat', 'and', 'clean', 'suitable', 'for', 'taking', 'photos', 'for', 'sunset', 'hunters']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>pandang indah akses jalan arah pantai cibanban lumayan bagus tantang cianjur jarak gak berangkat pagi pulang sore</t>
+          <t>beautiful neat and clean suitable for taking photos for sunset hunters</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
+          <t>Alun Alun Pelabuhan Ratu Sukabumi adalah tempat yang menawan dengan pesona alamnya. Keindahan alun-alun dan pemandangan laut yang menakjubkan membuatnya menjadi tempat yang pas untuk bersantai. Suasana tenang dan sejuk di sekitar area ini â¦</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
+          <t>alun alun pelabuhan ratu sukabumi adalah tempat yang menawan dengan pesona alamnya keindahan alunalun dan pemandangan laut yang menakjubkan membuatnya menjadi tempat yang pas untuk bersantai suasana tenang dan sejuk di sekitar area ini â</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['alun', 'alun', 'pelabuhan', 'ratu', 'sukabumi', 'adalah', 'tempat', 'yang', 'menawan', 'dengan', 'pesona', 'alamnya', 'keindahan', 'alunalun', 'dan', 'pemandangan', 'laut', 'yang', 'menakjubkan', 'membuatnya', 'menjadi', 'tempat', 'yang', 'pas', 'untuk', 'bersantai', 'suasana', 'tenang', 'dan', 'sejuk', 'di', 'sekitar', 'area', 'ini', 'â']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['alun', 'alun', 'pelabuhan', 'ratu', 'sukabumi', 'menawan', 'pesona', 'alamnya', 'keindahan', 'alunalun', 'pemandangan', 'laut', 'menakjubkan', 'membuatnya', 'pas', 'bersantai', 'suasana', 'tenang', 'sejuk', 'area', 'â']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
+          <t>alun alun labuh ratu sukabumi tawan pesona alam indah alunalun pandang laut takjub buat pas santa suasana tenang sejuk area</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1688,42 +1688,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>Di kelola oleh oknum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>di kelola oleh oknum</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['di', 'kelola', 'oleh', 'oknum']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['kelola', 'oknum']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>kelola oknum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1735,42 +1735,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
+          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
+          <t>mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
+          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
+          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
+          <t>mantaps dah olahraga ringan keluarga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1782,12 +1782,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Keren nih tempatnya, sambil istirahat trus pesen kelapa muda , duh di seruput, alamak hati senang , ingat kerjaan nya setelah di jakarta aja ya, â¦</t>
+          <t>Pemandangan baik,bagus,hanya saja tempat ganti pakaian/mandi agak kurang rapih saja</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1797,22 +1797,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>keren nih tempatnya sambil istirahat trus pesen kelapa muda duh di seruput alamak hati senang ingat kerjaan nya setelah di jakarta aja ya â</t>
+          <t>pemandangan baikbagushanya saja tempat ganti pakaianmandi agak kurang rapih saja</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['keren', 'nih', 'tempatnya', 'sambil', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'di', 'seruput', 'alamak', 'hati', 'senang', 'ingat', 'kerjaan', 'nya', 'setelah', 'di', 'jakarta', 'aja', 'ya', 'â']</t>
+          <t>['pemandangan', 'baikbagushanya', 'saja', 'tempat', 'ganti', 'pakaianmandi', 'agak', 'kurang', 'rapih', 'saja']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['keren', 'nih', 'tempatnya', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'seruput', 'alamak', 'hati', 'senang', 'kerjaan', 'nya', 'jakarta', 'aja', 'ya', 'â']</t>
+          <t>['pemandangan', 'baikbagushanya', 'ganti', 'pakaianmandi', 'rapih']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>keren nih tempat istirahat trus sen kelapa muda duh seruput alamak hati senang kerja nya jakarta aja ya</t>
+          <t>pandang baikbagushanya ganti pakaianmandi rapih</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1829,42 +1829,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Di kelola oleh oknum</t>
+          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>di kelola oleh oknum</t>
+          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['di', 'kelola', 'oleh', 'oknum']</t>
+          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['kelola', 'oknum']</t>
+          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>kelola oknum</t>
+          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1876,42 +1876,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The 77th HAB ceremony at the Sukabumi Regency Ministry of Religious Affairs Office. Atmosphere in traditional attire.</t>
+          <t>Tidak nyaman oleh orngÂ² yg menyewakan tempat untuk istirahat/baleÂ² Krn mahal Dan sangat perhitungan...di sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d Carikan tmpt istrht Krn mrk welcome dan baikÂ².</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
+          <t>tidak nyaman oleh orngâ² yg menyewakan tempat untuk istirahatbaleâ² krn mahal dan sangat perhitungandi sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d carikan tmpt istrht krn mrk welcome dan baikâ²</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
+          <t>['tidak', 'nyaman', 'oleh', 'orngâ²', 'yg', 'menyewakan', 'tempat', 'untuk', 'istirahatbaleâ²', 'krn', 'mahal', 'dan', 'sangat', 'perhitungandi', 'sarankan', 'jika', 'berwisata', 'ke', 'sana', 'bisa', 'meminta', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'untuk', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'dan', 'baikâ²']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
+          <t>['nyaman', 'orngâ²', 'yg', 'menyewakan', 'istirahatbaleâ²', 'krn', 'mahal', 'perhitungandi', 'sarankan', 'berwisata', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'baikâ²']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
+          <t>nyaman orng yg sewa istirahatbale krn mahal perhitungandi saran wisata bantu jasa kpd jaga pintu masuk utama d cari tmpt istrht krn mrk welcome baik</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1923,42 +1923,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>A place in Pelabuhan Ratu for families to play, but there are rarely any places to take shelter, a beautiful beach atmosphere, lots of traders, spacious parking, hopefully it will be better maintained and beautified so that the place will be even better.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>a place in pelabuhan ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>a place in labuh ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1970,42 +1970,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The atmosphere is comfortable and pleasant. You can play in the sand on the beach, making it perfect for family outings.</t>
+          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
+          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
+          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
+          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
+          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2017,59 +2017,59 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+          <t>Bagus ada masjidnya ada lapangannya dan jualannya juga cuman Memang karena sekarang lagi Corona jadi agak sepi cuman sekarang udah lumayan mulai kembali banyak orang sih ke alun-alun ini tempat pusatnya pelabuhanratu gitu selain pantainya â¦</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+          <t>bagus ada masjidnya ada lapangannya dan jualannya juga cuman memang karena sekarang lagi corona jadi agak sepi cuman sekarang udah lumayan mulai kembali banyak orang sih ke alunalun ini tempat pusatnya pelabuhanratu gitu selain pantainya â</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
+          <t>['bagus', 'ada', 'masjidnya', 'ada', 'lapangannya', 'dan', 'jualannya', 'juga', 'cuman', 'memang', 'karena', 'sekarang', 'lagi', 'corona', 'jadi', 'agak', 'sepi', 'cuman', 'sekarang', 'udah', 'lumayan', 'mulai', 'kembali', 'banyak', 'orang', 'sih', 'ke', 'alunalun', 'ini', 'tempat', 'pusatnya', 'pelabuhanratu', 'gitu', 'selain', 'pantainya', 'â']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
+          <t>['bagus', 'masjidnya', 'lapangannya', 'jualannya', 'cuman', 'corona', 'sepi', 'cuman', 'udah', 'lumayan', 'orang', 'sih', 'alunalun', 'pusatnya', 'pelabuhanratu', 'gitu', 'pantainya', 'â']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
+          <t>bagus masjid lapang jual cuman corona sepi cuman udah lumayan orang sih alunalun pusat pelabuhanratu gitu pantai</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2111,12 +2111,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luas,mudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luasmudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['tempat', 'di', 'pelabuhan', 'ratu', 'buat', 'main', 'keluarga', 'cuma', 'jarang', 'tempat', 'untuk', 'berteduh', 'suasana', 'pantai', 'indah', 'banyak', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'lebih', 'di', 'pelihara', 'dan', 'di', 'perindah', 'supaya', 'tempat', 'nya', 'makin', 'bagus']</t>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['pelabuhan', 'ratu', 'main', 'keluarga', 'jarang', 'berteduh', 'suasana', 'pantai', 'indah', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'pelihara', 'perindah', 'nya', 'bagus']</t>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>labuh ratu main keluarga jarang teduh suasana pantai indah tukang dagang parkir luasmudah mudah pelihara indah nya bagus</t>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2151,49 +2151,49 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Banyak sampah, kayanya kalo mlm sring dipake buat hal-hal yg tdk sharusnya. Tlg Bapak satpol PP dan Polisi mengawal tempat tsb. Trmksh.</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>banyak sampah kayanya kalo mlm sring dipake buat halhal yg tdk sharusnya tlg bapak satpol pp dan polisi mengawal tempat tsb trmksh</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['banyak', 'sampah', 'kayanya', 'kalo', 'mlm', 'sring', 'dipake', 'buat', 'halhal', 'yg', 'tdk', 'sharusnya', 'tlg', 'bapak', 'satpol', 'pp', 'dan', 'polisi', 'mengawal', 'tempat', 'tsb', 'trmksh']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['sampah', 'kayanya', 'kalo', 'mlm', 'sring', 'dipake', 'halhal', 'yg', 'tdk', 'sharusnya', 'tlg', 'satpol', 'pp', 'polisi', 'mengawal', 'tsb', 'trmksh']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>sampah kaya kalo mlm sring dipake halhal yg tdk sharusnya tlg satpol pp polisi awal tsb trmksh</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2205,42 +2205,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A place in Pelabuhan Ratu for families to play, but there are rarely any places to take shelter, a beautiful beach atmosphere, lots of traders, spacious parking, hopefully it will be better maintained and beautified so that the place will be even better.</t>
+          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>a place in pelabuhan ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>a place in labuh ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2252,42 +2252,42 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Liburan murmer ,,sewa rumah di pinggir pantai murah cuma sayang banyak yg ngamen.. Repot juga tiap 5 menit mah dikira liburan banyak duit...bilang maaf ga pergi2.. Saran siapin receh yg banyak</t>
+          <t>It's free, with no entrance fee. The sand is fine and coral-free. Toilet and changing room facilities need to be expanded and their cleanliness monitored.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>liburan murmer sewa rumah di pinggir pantai murah cuma sayang banyak yg ngamen repot juga tiap menit mah dikira liburan banyak duitbilang maaf ga pergi saran siapin receh yg banyak</t>
+          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['liburan', 'murmer', 'sewa', 'rumah', 'di', 'pinggir', 'pantai', 'murah', 'cuma', 'sayang', 'banyak', 'yg', 'ngamen', 'repot', 'juga', 'tiap', 'menit', 'mah', 'dikira', 'liburan', 'banyak', 'duitbilang', 'maaf', 'ga', 'pergi', 'saran', 'siapin', 'receh', 'yg', 'banyak']</t>
+          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['liburan', 'murmer', 'sewa', 'rumah', 'pinggir', 'pantai', 'murah', 'sayang', 'yg', 'ngamen', 'repot', 'menit', 'mah', 'liburan', 'duitbilang', 'maaf', 'ga', 'pergi', 'saran', 'siapin', 'receh', 'yg']</t>
+          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>libur murmer sewa rumah pinggir pantai murah sayang yg ngamen repot menit mah libur duitbilang maaf ga pergi saran siapin receh yg</t>
+          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Enak sih pantai nya ngga kotor cuma pasir nya aja yg warna coklat ngga kaya Sawarna yg pasir nya masi putih ðð â¦</t>
+          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2314,22 +2314,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>enak sih pantai nya ngga kotor cuma pasir nya aja yg warna coklat ngga kaya sawarna yg pasir nya masi putih ðð â</t>
+          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['enak', 'sih', 'pantai', 'nya', 'ngga', 'kotor', 'cuma', 'pasir', 'nya', 'aja', 'yg', 'warna', 'coklat', 'ngga', 'kaya', 'sawarna', 'yg', 'pasir', 'nya', 'masi', 'putih', 'ðð', 'â']</t>
+          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['enak', 'sih', 'pantai', 'nya', 'ngga', 'kotor', 'pasir', 'nya', 'aja', 'yg', 'warna', 'coklat', 'ngga', 'kaya', 'sawarna', 'yg', 'pasir', 'nya', 'masi', 'putih', 'ðð', 'â']</t>
+          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>enak sih pantai nya ngga kotor pasir nya aja yg warna coklat ngga kaya sawarna yg pasir nya mas putih</t>
+          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2339,19 +2339,19 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Accommodating thousands of people, with a nice park and toilet facilities...</t>
+          <t>SDH tidak terlalu bagus...kalau malam sangat gelap..bnyk lampu yg mati dan tak diperbaiki..Pedagang Kaki lima nya sih lumayan tertata rapi...</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2361,22 +2361,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>accommodating thousands of people with a nice park and toilet facilities</t>
+          <t>sdh tidak terlalu baguskalau malam sangat gelapbnyk lampu yg mati dan tak diperbaikipedagang kaki lima nya sih lumayan tertata rapi</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
+          <t>['sdh', 'tidak', 'terlalu', 'baguskalau', 'malam', 'sangat', 'gelapbnyk', 'lampu', 'yg', 'mati', 'dan', 'tak', 'diperbaikipedagang', 'kaki', 'lima', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
+          <t>['sdh', 'baguskalau', 'malam', 'gelapbnyk', 'lampu', 'yg', 'mati', 'diperbaikipedagang', 'kaki', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>accommodating thousands of people with a nice park and toilet facilities</t>
+          <t>sdh baguskalau malam gelapbnyk lampu yg mati diperbaikipedagang kaki nya sih lumayan tata rapi</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2393,42 +2393,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The mosque is large and quite clean. The ablution area and toilets are also clean. There are many vendors around the square.</t>
+          <t>Tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>the mosque is large and quite clean the ablution area and toilets are also clean there are many vendors around the square</t>
+          <t>tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['the', 'mosque', 'is', 'large', 'and', 'quite', 'clean', 'the', 'ablution', 'area', 'and', 'toilets', 'are', 'also', 'clean', 'there', 'are', 'many', 'vendors', 'around', 'the', 'square']</t>
+          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['the', 'mosque', 'is', 'large', 'and', 'quite', 'clean', 'the', 'ablution', 'area', 'and', 'toilets', 'are', 'also', 'clean', 'there', 'are', 'many', 'vendors', 'around', 'the', 'square']</t>
+          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>the mosque is large and quite clean the ablution area and toilets are also clean there are many vendors around the square</t>
+          <t>tugu nyah udah pindahin</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2440,59 +2440,59 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Untuk pantainya seperti pantai kebanyakan, dengan ombak besarnya. Sarana di dipantai tersebut kurang nyaman, lesehan buat nginap terbilang mahal, kurang aman buat anak2 bermain air karena minimnya pengawasan petugas.</t>
+          <t>Buka setiap hari, tiket masuk kisaran 20 ribu. Tempat nyaman,luas ,kolam cukup banyak ,  kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia. â¦</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>LAND</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>buka setiap hari tiket masuk kisaran ribu tempat nyamanluas kolam cukup banyak kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia â</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>['buka', 'setiap', 'hari', 'tiket', 'masuk', 'kisaran', 'ribu', 'tempat', 'nyamanluas', 'kolam', 'cukup', 'banyak', 'kantin', 'dan', 'tempat', 'sewa', 'ban', 'juga', 'ada', 'tempat', 'berteduh', 'atau', 'bale', 'juga', 'tersedia', 'â']</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>['buka', 'tiket', 'masuk', 'kisaran', 'ribu', 'nyamanluas', 'kolam', 'kantin', 'sewa', 'ban', 'berteduh', 'bale', 'tersedia', 'â']</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>buka tiket masuk kisar ribu nyamanluas kolam kantin sewa ban teduh bale sedia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>LAND</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
           <t>ECON</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>untuk pantainya seperti pantai kebanyakan dengan ombak besarnya sarana di dipantai tersebut kurang nyaman lesehan buat nginap terbilang mahal kurang aman buat anak bermain air karena minimnya pengawasan petugas</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>['untuk', 'pantainya', 'seperti', 'pantai', 'kebanyakan', 'dengan', 'ombak', 'besarnya', 'sarana', 'di', 'dipantai', 'tersebut', 'kurang', 'nyaman', 'lesehan', 'buat', 'nginap', 'terbilang', 'mahal', 'kurang', 'aman', 'buat', 'anak', 'bermain', 'air', 'karena', 'minimnya', 'pengawasan', 'petugas']</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>['pantainya', 'pantai', 'kebanyakan', 'ombak', 'besarnya', 'sarana', 'dipantai', 'nyaman', 'lesehan', 'nginap', 'terbilang', 'mahal', 'aman', 'anak', 'bermain', 'air', 'minimnya', 'pengawasan', 'petugas']</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>pantai pantai banyak ombak besar sarana pantai nyaman leseh nginap bilang mahal aman anak main air minim awas tugas</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
+          <t>A comfortable square for resting and chatting with family. The place is very spacious, you can also enjoy culinary activities. There is a mosque that is very comfortable for worship, clean toilets, many separate ablution areas for brothers â¦</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2502,22 +2502,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
+          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers â</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
+          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
+          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
+          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2527,49 +2527,49 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ikon kota palabuhanratu......bagus</t>
+          <t>The staff are friendly, the beach is nice, but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower... try to take a shower in the toilet near the beach, the toilet near the floor is not suitable â¦</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ikon kota palabuhanratubagus</t>
+          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable â</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ikon kota palabuhanratubagus</t>
+          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2581,12 +2581,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mantappppp</t>
+          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>mantappppp</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['mantappppp']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['mantappppp']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>mantappppp</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2628,42 +2628,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang merupakan salah satu pantai yang terletak di Pelabuhan Ratu, Kabupaten Sukabumi, Jawa Barat. Pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik. â¦</t>
+          <t>Karang Sari Beach. Located before Citepus Beach from the market. The atmosphere is quite nice for photos, and swimming is also possible, but be â¦</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>pantai batu bintang merupakan salah satu pantai yang terletak di pelabuhan ratu kabupaten sukabumi jawa barat pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik â</t>
+          <t>karang sari beach located before citepus beach from the market the atmosphere is quite nice for photos and swimming is also possible but be â</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['pantai', 'batu', 'bintang', 'merupakan', 'salah', 'satu', 'pantai', 'yang', 'terletak', 'di', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'ini', 'terkenal', 'dengan', 'keindahan', 'pantainya', 'yang', 'masih', 'alami', 'dan', 'dihiasi', 'dengan', 'bebatuan', 'yang', 'unik', 'dan', 'menarik', 'â']</t>
+          <t>['karang', 'sari', 'beach', 'located', 'before', 'citepus', 'beach', 'from', 'the', 'market', 'the', 'atmosphere', 'is', 'quite', 'nice', 'for', 'photos', 'and', 'swimming', 'is', 'also', 'possible', 'but', 'be', 'â']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['pantai', 'batu', 'bintang', 'salah', 'pantai', 'terletak', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'terkenal', 'keindahan', 'pantainya', 'alami', 'dihiasi', 'bebatuan', 'unik', 'menarik', 'â']</t>
+          <t>['karang', 'sari', 'beach', 'located', 'before', 'citepus', 'beach', 'from', 'the', 'market', 'the', 'atmosphere', 'is', 'quite', 'nice', 'for', 'photos', 'and', 'swimming', 'is', 'also', 'possible', 'but', 'be', 'â']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>pantai batu bintang salah pantai letak labuh ratu kabupaten sukabumi jawa barat pantai kenal indah pantai alami hias bebatuan unik tarik</t>
+          <t>karang sari beach located before citepus beach from the market the atmosphere is quite nice for photos and swimming is also possible but be</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2675,59 +2675,59 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bagus cm tmpat smpah sedikit.. ama pedagang julid ge bnyk Parkir liar bnyk View lumayan</t>
+          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>bagus cm tmpat smpah sedikit ama pedagang julid ge bnyk parkir liar bnyk view lumayan</t>
+          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>['bagus', 'cm', 'tmpat', 'smpah', 'sedikit', 'ama', 'pedagang', 'julid', 'ge', 'bnyk', 'parkir', 'liar', 'bnyk', 'view', 'lumayan']</t>
+          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['bagus', 'cm', 'tmpat', 'smpah', 'ama', 'pedagang', 'julid', 'ge', 'bnyk', 'parkir', 'liar', 'bnyk', 'view', 'lumayan']</t>
+          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>bagus cm tmpat smpah ama dagang julid ge bnyk parkir liar bnyk view lumayan</t>
+          <t>kali lapang cangehgarbagus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>bagus,,enak buat liburan bersama keluarga</t>
+          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2737,22 +2737,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>bagusenak buat liburan bersama keluarga</t>
+          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
+          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['bagusenak', 'liburan', 'keluarga']</t>
+          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>bagusenak libur keluarga</t>
+          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2769,42 +2769,42 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2816,12 +2816,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
+          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2831,22 +2831,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
+          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
+          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2863,59 +2863,59 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
+          <t>Nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak  mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang  sebab ada oknum pedagang terutama pedagang  gorengan ada bapa bapa yang menjual /mencampur gorengan sisa hari kemarinnya,yang diangetin lagi hingga  terasa keras dan basi.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
+          <t>nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang sebab ada oknum pedagang terutama pedagang gorengan ada bapa bapa yang menjual mencampur gorengan sisa hari kemarinnyayang diangetin lagi hingga terasa keras dan basi</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
+          <t>['nyaman', 'untuk', 'nyari', 'kuliner', 'cuma', 'tolong', 'ditertibkan', 'para', 'pedagangnya', 'supaya', 'tidak', 'mengganggu', 'lalu', 'lintas', 'juga', 'rasanya', 'harus', 'ada', 'pembinaan', 'pada', 'para', 'pedagang', 'sebab', 'ada', 'oknum', 'pedagang', 'terutama', 'pedagang', 'gorengan', 'ada', 'bapa', 'bapa', 'yang', 'menjual', 'mencampur', 'gorengan', 'sisa', 'hari', 'kemarinnyayang', 'diangetin', 'lagi', 'hingga', 'terasa', 'keras', 'dan', 'basi']</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
+          <t>['nyaman', 'nyari', 'kuliner', 'tolong', 'ditertibkan', 'pedagangnya', 'mengganggu', 'lintas', 'pembinaan', 'pedagang', 'oknum', 'pedagang', 'pedagang', 'gorengan', 'bapa', 'bapa', 'menjual', 'mencampur', 'gorengan', 'sisa', 'kemarinnyayang', 'diangetin', 'keras', 'basi']</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
+          <t>nyaman nyari kuliner tolong tertib dagang ganggu lintas bina dagang oknum dagang dagang goreng bapa bapa jual campur goreng sisa kemarinnyayang diangetin keras basi</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>bagus,,enak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2925,22 +2925,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>bagusenak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+          <t>['bagusenak', 'liburan', 'keluarga']</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+          <t>bagusenak libur keluarga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2957,47 +2957,47 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
@@ -3051,42 +3051,42 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3098,42 +3098,42 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pertama ngecamp pinggir pantai tuu rasanya,MasyaAllah.. Pantai ini tu,deket ke warung,deket ke mushola,air untuk mandi lancar.tapi,kalau mau cam di tarif lagi untuk biaya kebersihan 1 tenda 20-25k untuk yang mau ikut â¦</t>
+          <t>Kondisi lapang lumayan baik. Track lari sedikit rusak. Lari pagi di hari minggu tidak terlalu padat</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>pertama ngecamp pinggir pantai tuu rasanyamasyaallah pantai ini tudeket ke warungdeket ke musholaair untuk mandi lancartapikalau mau cam di tarif lagi untuk biaya kebersihan tenda k untuk yang mau ikut â</t>
+          <t>kondisi lapang lumayan baik track lari sedikit rusak lari pagi di hari minggu tidak terlalu padat</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>['pertama', 'ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'ini', 'tudeket', 'ke', 'warungdeket', 'ke', 'musholaair', 'untuk', 'mandi', 'lancartapikalau', 'mau', 'cam', 'di', 'tarif', 'lagi', 'untuk', 'biaya', 'kebersihan', 'tenda', 'k', 'untuk', 'yang', 'mau', 'ikut', 'â']</t>
+          <t>['kondisi', 'lapang', 'lumayan', 'baik', 'track', 'lari', 'sedikit', 'rusak', 'lari', 'pagi', 'di', 'hari', 'minggu', 'tidak', 'terlalu', 'padat']</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>['ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'tudeket', 'warungdeket', 'musholaair', 'mandi', 'lancartapikalau', 'cam', 'tarif', 'biaya', 'kebersihan', 'tenda', 'k', 'â']</t>
+          <t>['kondisi', 'lapang', 'lumayan', 'track', 'lari', 'rusak', 'lari', 'pagi', 'minggu', 'padat']</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ngecamp pinggir pantai tuu rasanyamasyaallah pantai tudeket warungdeket musholaair mandi lancartapikalau cam tarif biaya bersih tenda k</t>
+          <t>kondisi lapang lumayan track lari rusak lari pagi minggu padat</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3145,42 +3145,42 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tempat nya strategis untuk istrahat. Setelah solat d mesjid, bisa jajan dan mknan dlu, bnyak tempat jajannya, dekat dgn KFC, ATM dan toserba juga...ð â¦</t>
+          <t>Pertama ngecamp pinggir pantai tuu rasanya,MasyaAllah.. Pantai ini tu,deket ke warung,deket ke mushola,air untuk mandi lancar.tapi,kalau mau cam di tarif lagi untuk biaya kebersihan 1 tenda 20-25k untuk yang mau ikut â¦</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tempat nya strategis untuk istrahat setelah solat d mesjid bisa jajan dan mknan dlu bnyak tempat jajannya dekat dgn kfc atm dan toserba jugað â</t>
+          <t>pertama ngecamp pinggir pantai tuu rasanyamasyaallah pantai ini tudeket ke warungdeket ke musholaair untuk mandi lancartapikalau mau cam di tarif lagi untuk biaya kebersihan tenda k untuk yang mau ikut â</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'strategis', 'untuk', 'istrahat', 'setelah', 'solat', 'd', 'mesjid', 'bisa', 'jajan', 'dan', 'mknan', 'dlu', 'bnyak', 'tempat', 'jajannya', 'dekat', 'dgn', 'kfc', 'atm', 'dan', 'toserba', 'jugað', 'â']</t>
+          <t>['pertama', 'ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'ini', 'tudeket', 'ke', 'warungdeket', 'ke', 'musholaair', 'untuk', 'mandi', 'lancartapikalau', 'mau', 'cam', 'di', 'tarif', 'lagi', 'untuk', 'biaya', 'kebersihan', 'tenda', 'k', 'untuk', 'yang', 'mau', 'ikut', 'â']</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>['nya', 'strategis', 'istrahat', 'solat', 'd', 'mesjid', 'jajan', 'mknan', 'dlu', 'bnyak', 'jajannya', 'dgn', 'kfc', 'atm', 'toserba', 'jugað', 'â']</t>
+          <t>['ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'tudeket', 'warungdeket', 'musholaair', 'mandi', 'lancartapikalau', 'cam', 'tarif', 'biaya', 'kebersihan', 'tenda', 'k', 'â']</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>nya strategis istrahat solat d mesjid jajan mknan dlu bnyak jajan dgn kfc atm toserba juga</t>
+          <t>ngecamp pinggir pantai tuu rasanyamasyaallah pantai tudeket warungdeket musholaair mandi lancartapikalau cam tarif biaya bersih tenda k</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
+          <t>Alhamdulillahasih bersih, indah apalagi di malam hari, tepat nya di depan majid agung palabuahan ratu, banyak tersedia jajanan juga, ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
+          <t>alhamdulillahasih bersih indah apalagi di malam hari tepat nya di depan majid agung palabuahan ratu banyak tersedia jajanan juga ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
+          <t>['alhamdulillahasih', 'bersih', 'indah', 'apalagi', 'di', 'malam', 'hari', 'tepat', 'nya', 'di', 'depan', 'majid', 'agung', 'palabuahan', 'ratu', 'banyak', 'tersedia', 'jajanan', 'juga', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended', 'lah']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
+          <t>['alhamdulillahasih', 'bersih', 'indah', 'malam', 'nya', 'majid', 'agung', 'palabuahan', 'ratu', 'tersedia', 'jajanan', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
+          <t>alhamdulillahasih bersih indah malam nya majid agung palabuahan ratu sedia jajan ubtuk dar santa denfan keluarga rekomended</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -513,12 +513,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>kali lapang cangehgarbagus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -560,59 +560,59 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
+          <t>bagus,,enak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -622,22 +622,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
+          <t>bagusenak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['bagusenak', 'liburan', 'keluarga']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nongki chill and cheap yg cocok pas sunsetan</t>
+          <t>bagusenak libur keluarga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -654,42 +654,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -706,37 +706,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -748,12 +748,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Air nya hijau ga terurus banyak bentuknya, gazebo udah pada rusak</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -763,22 +763,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>air nya hijau ga terurus banyak bentuknya gazebo udah pada rusak</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'banyak', 'bentuknya', 'gazebo', 'udah', 'pada', 'rusak']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'bentuknya', 'gazebo', 'udah', 'rusak']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>air nya hijau ga urus bentuk gazebo udah rusak</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -795,12 +795,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
+          <t>It's best to come here in the late afternoon, the view is beautiful. It's a shame the toilets are dirty.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -810,22 +810,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
+          <t>its best to come here in the late afternoon the view is beautiful its a shame the toilets are dirty</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
+          <t>['its', 'best', 'to', 'come', 'here', 'in', 'the', 'late', 'afternoon', 'the', 'view', 'is', 'beautiful', 'its', 'a', 'shame', 'the', 'toilets', 'are', 'dirty']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
+          <t>['its', 'best', 'to', 'come', 'here', 'in', 'the', 'late', 'afternoon', 'the', 'view', 'is', 'beautiful', 'its', 'a', 'shame', 'the', 'toilets', 'are', 'dirty']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
+          <t>its best to come here in the late afternoon the view is beautiful its a shame the toilets are dirty</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -842,12 +842,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Untuk pantainya seperti pantai kebanyakan, dengan ombak besarnya. Sarana di dipantai tersebut kurang nyaman, lesehan buat nginap terbilang mahal, kurang aman buat anak2 bermain air karena minimnya pengawasan petugas.</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -857,22 +857,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>untuk pantainya seperti pantai kebanyakan dengan ombak besarnya sarana di dipantai tersebut kurang nyaman lesehan buat nginap terbilang mahal kurang aman buat anak bermain air karena minimnya pengawasan petugas</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['untuk', 'pantainya', 'seperti', 'pantai', 'kebanyakan', 'dengan', 'ombak', 'besarnya', 'sarana', 'di', 'dipantai', 'tersebut', 'kurang', 'nyaman', 'lesehan', 'buat', 'nginap', 'terbilang', 'mahal', 'kurang', 'aman', 'buat', 'anak', 'bermain', 'air', 'karena', 'minimnya', 'pengawasan', 'petugas']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['pantainya', 'pantai', 'kebanyakan', 'ombak', 'besarnya', 'sarana', 'dipantai', 'nyaman', 'lesehan', 'nginap', 'terbilang', 'mahal', 'aman', 'anak', 'bermain', 'air', 'minimnya', 'pengawasan', 'petugas']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>pantai pantai banyak ombak besar sarana pantai nyaman leseh nginap bilang mahal aman anak main air minim awas tugas</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -882,49 +882,49 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The 77th HAB ceremony at the Sukabumi Regency Ministry of Religious Affairs Office. Atmosphere in traditional attire.</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -936,42 +936,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -983,12 +983,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ikon kota palabuhanratu......bagus</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -998,22 +998,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ikon kota palabuhanratubagus</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ikon kota palabuhanratubagus</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1030,42 +1030,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Sangat buruk. Pasilitas hampir semua ruksak. Tempat bermain anak, tempatmain skate. Bangunan banyak yang sudah hancur</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>sangat buruk pasilitas hampir semua ruksak tempat bermain anak tempatmain skate bangunan banyak yang sudah hancur</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['sangat', 'buruk', 'pasilitas', 'hampir', 'semua', 'ruksak', 'tempat', 'bermain', 'anak', 'tempatmain', 'skate', 'bangunan', 'banyak', 'yang', 'sudah', 'hancur']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['buruk', 'pasilitas', 'ruksak', 'bermain', 'anak', 'tempatmain', 'skate', 'bangunan', 'hancur']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>buruk pasilitas ruksak main anak tempatmain skate bangun hancur</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,42 +1077,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
+          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
+          <t>mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['skarang', 'lebih', 'sepi', 'dan', 'kebanyakan', 'di', 'pakai', 'oknum', 'pemuda', 'pemudi', 'buat', 'pacaran', 'kadang', 'suka', 'ada', 'yg', 'mabuk', 'atau', 'tawuran', 'anak', 'sekolah']</t>
+          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['skarang', 'sepi', 'kebanyakan', 'pakai', 'oknum', 'pemuda', 'pemudi', 'pacaran', 'kadang', 'suka', 'yg', 'mabuk', 'tawuran', 'anak', 'sekolah']</t>
+          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>skarang sepi banyak pakai oknum pemuda pemudi pacar kadang suka yg mabuk tawur anak sekolah</t>
+          <t>mantaps dah olahraga ringan keluarga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1129,37 +1129,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jajahannya banyak pilihan dan enak ð Tahu crispy juara, sate padang juga mantul, cilok lumayan, cilor enak, pisang keju enak, sate2 an enak, waduh kalap pokoknya â¦</t>
+          <t>Kotor alun alunnya banyak sampah...mampir ke masjid di alun2 bersih dan nyaman</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jajahannya banyak pilihan dan enak ð tahu crispy juara sate padang juga mantul cilok lumayan cilor enak pisang keju enak sate an enak waduh kalap pokoknya â</t>
+          <t>kotor alun alunnya banyak sampahmampir ke masjid di alun bersih dan nyaman</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['jajahannya', 'banyak', 'pilihan', 'dan', 'enak', 'ð', 'tahu', 'crispy', 'juara', 'sate', 'padang', 'juga', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'waduh', 'kalap', 'pokoknya', 'â']</t>
+          <t>['kotor', 'alun', 'alunnya', 'banyak', 'sampahmampir', 'ke', 'masjid', 'di', 'alun', 'bersih', 'dan', 'nyaman']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['jajahannya', 'pilihan', 'enak', 'ð', 'crispy', 'juara', 'sate', 'padang', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'kalap', 'pokoknya', 'â']</t>
+          <t>['kotor', 'alun', 'alunnya', 'sampahmampir', 'masjid', 'alun', 'bersih', 'nyaman']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jajah pilih enak crispy juara sate padang mantul cilok lumayan cilor enak pisang keju enak sate an enak kalap pokok</t>
+          <t>kotor alun alun sampahmampir masjid alun bersih nyaman</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1171,42 +1171,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
+          <t>Pasir pantai tidak tajam, lumayan bersih, banyak toilet, kamar mandi dan musola. Harga makanan dan minuman sesuai kantong.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
+          <t>pasir pantai tidak tajam lumayan bersih banyak toilet kamar mandi dan musola harga makanan dan minuman sesuai kantong</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['pasir', 'pantai', 'tidak', 'tajam', 'lumayan', 'bersih', 'banyak', 'toilet', 'kamar', 'mandi', 'dan', 'musola', 'harga', 'makanan', 'dan', 'minuman', 'sesuai', 'kantong']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['pasir', 'pantai', 'tajam', 'lumayan', 'bersih', 'toilet', 'kamar', 'mandi', 'musola', 'harga', 'makanan', 'minuman', 'sesuai', 'kantong']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
+          <t>pasir pantai tajam lumayan bersih toilet kamar mandi musola harga makan minum sesuai kantong</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1218,12 +1218,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1233,22 +1233,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
+          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
+          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
+          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1265,42 +1265,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
+          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
+          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
+          <t>cocok jalanjalan santai ramai sejuk</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1312,106 +1312,106 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>Accommodating thousands of people, with a nice park and toilet facilities...</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>accommodating thousands of people with a nice park and toilet facilities</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>accommodating thousands of people with a nice park and toilet facilities</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
+          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1421,22 +1421,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
+          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>pake produck gk kecewa kerennnn deh</t>
+          <t>nongki chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1453,42 +1453,44 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>Please kesini bkn baru pertama kalinya, tp kesekian kalinyað¥° and aku kesini bkn d hari weekand tp d hari biasa, so aku lebih suka suasana sepi hehehe, jd lebih nikmat liat sunsetnyað+ð+, dahal setiap kesini pasti d jalan tolnya ujan tp oas â¦</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>please kesini bkn baru pertama kalinya tp kesekian kalinyað and aku kesini bkn d hari weekand tp d hari biasa so aku lebih suka suasana sepi hehehe jd lebih nikmat liat sunsetnyað ð dahal setiap kesini pasti d jalan tolnya ujan tp oas â</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
+          <t>['please', 'kesini', 'bkn', 'baru', 'pertama', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'aku', 'kesini', 'bkn', 'd', 'hari', 'weekand', 'tp', 'd', 'hari', 'biasa', 'so', 'aku', 'lebih', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'lebih', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'setiap', 'kesini', 'pasti', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
+          <t>['please', 'kesini', 'bkn', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'kesini', 'bkn', 'd', 'weekand', 'tp', 'd', 'so', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'kesini', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
+          <t>please kesini bkn kali tp sekian kali and kesini bkn d weekand tp d so suka suasana sepi hehehe jd nikmat liat sunsetnya dahal kesini d jalan tol ujan tp oas</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1500,12 +1502,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
+          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1515,22 +1517,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
+          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
+          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1547,89 +1549,89 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
+          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
+          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
+          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
+          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
+          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Beautiful, neat and clean. Suitable for taking photos for sunset hunters</t>
+          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>beautiful neat and clean suitable for taking photos for sunset hunters</t>
+          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['beautiful', 'neat', 'and', 'clean', 'suitable', 'for', 'taking', 'photos', 'for', 'sunset', 'hunters']</t>
+          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['beautiful', 'neat', 'and', 'clean', 'suitable', 'for', 'taking', 'photos', 'for', 'sunset', 'hunters']</t>
+          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>beautiful neat and clean suitable for taking photos for sunset hunters</t>
+          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1646,37 +1648,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alun Alun Pelabuhan Ratu Sukabumi adalah tempat yang menawan dengan pesona alamnya. Keindahan alun-alun dan pemandangan laut yang menakjubkan membuatnya menjadi tempat yang pas untuk bersantai. Suasana tenang dan sejuk di sekitar area ini â¦</t>
+          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>alun alun pelabuhan ratu sukabumi adalah tempat yang menawan dengan pesona alamnya keindahan alunalun dan pemandangan laut yang menakjubkan membuatnya menjadi tempat yang pas untuk bersantai suasana tenang dan sejuk di sekitar area ini â</t>
+          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['alun', 'alun', 'pelabuhan', 'ratu', 'sukabumi', 'adalah', 'tempat', 'yang', 'menawan', 'dengan', 'pesona', 'alamnya', 'keindahan', 'alunalun', 'dan', 'pemandangan', 'laut', 'yang', 'menakjubkan', 'membuatnya', 'menjadi', 'tempat', 'yang', 'pas', 'untuk', 'bersantai', 'suasana', 'tenang', 'dan', 'sejuk', 'di', 'sekitar', 'area', 'ini', 'â']</t>
+          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['alun', 'alun', 'pelabuhan', 'ratu', 'sukabumi', 'menawan', 'pesona', 'alamnya', 'keindahan', 'alunalun', 'pemandangan', 'laut', 'menakjubkan', 'membuatnya', 'pas', 'bersantai', 'suasana', 'tenang', 'sejuk', 'area', 'â']</t>
+          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>alun alun labuh ratu sukabumi tawan pesona alam indah alunalun pandang laut takjub buat pas santa suasana tenang sejuk area</t>
+          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1688,12 +1690,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Di kelola oleh oknum</t>
+          <t>Pantai nya lumayan cuma banyak pengamenya</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1703,22 +1705,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>di kelola oleh oknum</t>
+          <t>pantai nya lumayan cuma banyak pengamenya</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['di', 'kelola', 'oleh', 'oknum']</t>
+          <t>['pantai', 'nya', 'lumayan', 'cuma', 'banyak', 'pengamenya']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['kelola', 'oknum']</t>
+          <t>['pantai', 'nya', 'lumayan', 'pengamenya']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>kelola oknum</t>
+          <t>pantai nya lumayan pengamenya</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1735,42 +1737,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>Di kelola oleh oknum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>di kelola oleh oknum</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
+          <t>['di', 'kelola', 'oleh', 'oknum']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
+          <t>['kelola', 'oknum']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>mantaps dah olahraga ringan keluarga</t>
+          <t>kelola oknum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1782,42 +1784,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pemandangan baik,bagus,hanya saja tempat ganti pakaian/mandi agak kurang rapih saja</t>
+          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>pemandangan baikbagushanya saja tempat ganti pakaianmandi agak kurang rapih saja</t>
+          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['pemandangan', 'baikbagushanya', 'saja', 'tempat', 'ganti', 'pakaianmandi', 'agak', 'kurang', 'rapih', 'saja']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['pemandangan', 'baikbagushanya', 'ganti', 'pakaianmandi', 'rapih']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>pandang baikbagushanya ganti pakaianmandi rapih</t>
+          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1829,42 +1831,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1876,42 +1878,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tidak nyaman oleh orngÂ² yg menyewakan tempat untuk istirahat/baleÂ² Krn mahal Dan sangat perhitungan...di sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d Carikan tmpt istrht Krn mrk welcome dan baikÂ².</t>
+          <t>A place in Pelabuhan Ratu for families to play, but there are rarely any places to take shelter, a beautiful beach atmosphere, lots of traders, spacious parking, hopefully it will be better maintained and beautified so that the place will be even better.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tidak nyaman oleh orngâ² yg menyewakan tempat untuk istirahatbaleâ² krn mahal dan sangat perhitungandi sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d carikan tmpt istrht krn mrk welcome dan baikâ²</t>
+          <t>a place in pelabuhan ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['tidak', 'nyaman', 'oleh', 'orngâ²', 'yg', 'menyewakan', 'tempat', 'untuk', 'istirahatbaleâ²', 'krn', 'mahal', 'dan', 'sangat', 'perhitungandi', 'sarankan', 'jika', 'berwisata', 'ke', 'sana', 'bisa', 'meminta', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'untuk', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'dan', 'baikâ²']</t>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['nyaman', 'orngâ²', 'yg', 'menyewakan', 'istirahatbaleâ²', 'krn', 'mahal', 'perhitungandi', 'sarankan', 'berwisata', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'baikâ²']</t>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>nyaman orng yg sewa istirahatbale krn mahal perhitungandi saran wisata bantu jasa kpd jaga pintu masuk utama d cari tmpt istrht krn mrk welcome baik</t>
+          <t>a place in labuh ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1923,42 +1925,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A place in Pelabuhan Ratu for families to play, but there are rarely any places to take shelter, a beautiful beach atmosphere, lots of traders, spacious parking, hopefully it will be better maintained and beautified so that the place will be even better.</t>
+          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>a place in pelabuhan ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>a place in labuh ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1970,42 +1972,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
+          <t>Pantainya bersih, yang terpenting harga makanan dan minuman super murah,parkir jg normal..</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
+          <t>pantainya bersih yang terpenting harga makanan dan minuman super murahparkir jg normal</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
+          <t>['pantainya', 'bersih', 'yang', 'terpenting', 'harga', 'makanan', 'dan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
+          <t>['pantainya', 'bersih', 'terpenting', 'harga', 'makanan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
+          <t>pantai bersih penting harga makan minum super murahparkir jg normal</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2017,42 +2019,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2064,12 +2066,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bagus ada masjidnya ada lapangannya dan jualannya juga cuman Memang karena sekarang lagi Corona jadi agak sepi cuman sekarang udah lumayan mulai kembali banyak orang sih ke alun-alun ini tempat pusatnya pelabuhanratu gitu selain pantainya â¦</t>
+          <t>Lapangannya luas,rapih, bersih,di tata dengan sangat bagus,penyuluh sosial masyarakat kab sukabumi,mengikuti upacara hari jadi Sukabumi</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2079,22 +2081,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>bagus ada masjidnya ada lapangannya dan jualannya juga cuman memang karena sekarang lagi corona jadi agak sepi cuman sekarang udah lumayan mulai kembali banyak orang sih ke alunalun ini tempat pusatnya pelabuhanratu gitu selain pantainya â</t>
+          <t>lapangannya luasrapih bersihdi tata dengan sangat baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara hari jadi sukabumi</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['bagus', 'ada', 'masjidnya', 'ada', 'lapangannya', 'dan', 'jualannya', 'juga', 'cuman', 'memang', 'karena', 'sekarang', 'lagi', 'corona', 'jadi', 'agak', 'sepi', 'cuman', 'sekarang', 'udah', 'lumayan', 'mulai', 'kembali', 'banyak', 'orang', 'sih', 'ke', 'alunalun', 'ini', 'tempat', 'pusatnya', 'pelabuhanratu', 'gitu', 'selain', 'pantainya', 'â']</t>
+          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'dengan', 'sangat', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'hari', 'jadi', 'sukabumi']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['bagus', 'masjidnya', 'lapangannya', 'jualannya', 'cuman', 'corona', 'sepi', 'cuman', 'udah', 'lumayan', 'orang', 'sih', 'alunalun', 'pusatnya', 'pelabuhanratu', 'gitu', 'pantainya', 'â']</t>
+          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'sukabumi']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>bagus masjid lapang jual cuman corona sepi cuman udah lumayan orang sih alunalun pusat pelabuhanratu gitu pantai</t>
+          <t>lapang luasrapih bersihdi tata baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara sukabumi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2111,89 +2113,89 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>Alun Alun Pelabuhan Ratu Sukabumi adalah tempat yang menawan dengan pesona alamnya. Keindahan alun-alun dan pemandangan laut yang menakjubkan membuatnya menjadi tempat yang pas untuk bersantai. Suasana tenang dan sejuk di sekitar area ini â¦</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>alun alun pelabuhan ratu sukabumi adalah tempat yang menawan dengan pesona alamnya keindahan alunalun dan pemandangan laut yang menakjubkan membuatnya menjadi tempat yang pas untuk bersantai suasana tenang dan sejuk di sekitar area ini â</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+          <t>['alun', 'alun', 'pelabuhan', 'ratu', 'sukabumi', 'adalah', 'tempat', 'yang', 'menawan', 'dengan', 'pesona', 'alamnya', 'keindahan', 'alunalun', 'dan', 'pemandangan', 'laut', 'yang', 'menakjubkan', 'membuatnya', 'menjadi', 'tempat', 'yang', 'pas', 'untuk', 'bersantai', 'suasana', 'tenang', 'dan', 'sejuk', 'di', 'sekitar', 'area', 'ini', 'â']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+          <t>['alun', 'alun', 'pelabuhan', 'ratu', 'sukabumi', 'menawan', 'pesona', 'alamnya', 'keindahan', 'alunalun', 'pemandangan', 'laut', 'menakjubkan', 'membuatnya', 'pas', 'bersantai', 'suasana', 'tenang', 'sejuk', 'area', 'â']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+          <t>alun alun labuh ratu sukabumi tawan pesona alam indah alunalun pandang laut takjub buat pas santa suasana tenang sejuk area</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Pemandangan baik,bagus,hanya saja tempat ganti pakaian/mandi agak kurang rapih saja</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>pemandangan baikbagushanya saja tempat ganti pakaianmandi agak kurang rapih saja</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['pemandangan', 'baikbagushanya', 'saja', 'tempat', 'ganti', 'pakaianmandi', 'agak', 'kurang', 'rapih', 'saja']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['pemandangan', 'baikbagushanya', 'ganti', 'pakaianmandi', 'rapih']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>pandang baikbagushanya ganti pakaianmandi rapih</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2205,12 +2207,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
+          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2220,22 +2222,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
+          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
+          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
+          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
+          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2245,49 +2247,49 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>It's free, with no entrance fee. The sand is fine and coral-free. Toilet and changing room facilities need to be expanded and their cleanliness monitored.</t>
+          <t>Tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
+          <t>tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
+          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
+          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
+          <t>tugu nyah udah pindahin</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2299,12 +2301,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
+          <t>It's free, with no entrance fee. The sand is fine and coral-free. Toilet and changing room facilities need to be expanded and their cleanliness monitored.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2314,22 +2316,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
+          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
+          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
+          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
+          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2339,19 +2341,19 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SDH tidak terlalu bagus...kalau malam sangat gelap..bnyk lampu yg mati dan tak diperbaiki..Pedagang Kaki lima nya sih lumayan tertata rapi...</t>
+          <t>Available milk, diapers, baby supplies, toiletries and staple foods and smashed chicken</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2361,22 +2363,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>sdh tidak terlalu baguskalau malam sangat gelapbnyk lampu yg mati dan tak diperbaikipedagang kaki lima nya sih lumayan tertata rapi</t>
+          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['sdh', 'tidak', 'terlalu', 'baguskalau', 'malam', 'sangat', 'gelapbnyk', 'lampu', 'yg', 'mati', 'dan', 'tak', 'diperbaikipedagang', 'kaki', 'lima', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
+          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['sdh', 'baguskalau', 'malam', 'gelapbnyk', 'lampu', 'yg', 'mati', 'diperbaikipedagang', 'kaki', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
+          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>sdh baguskalau malam gelapbnyk lampu yg mati diperbaikipedagang kaki nya sih lumayan tata rapi</t>
+          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2393,42 +2395,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tugu nyah udah di pindahin</t>
+          <t>Untuk pantainya seperti pantai kebanyakan, dengan ombak besarnya. Sarana di dipantai tersebut kurang nyaman, lesehan buat nginap terbilang mahal, kurang aman buat anak2 bermain air karena minimnya pengawasan petugas.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tugu nyah udah di pindahin</t>
+          <t>untuk pantainya seperti pantai kebanyakan dengan ombak besarnya sarana di dipantai tersebut kurang nyaman lesehan buat nginap terbilang mahal kurang aman buat anak bermain air karena minimnya pengawasan petugas</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
+          <t>['untuk', 'pantainya', 'seperti', 'pantai', 'kebanyakan', 'dengan', 'ombak', 'besarnya', 'sarana', 'di', 'dipantai', 'tersebut', 'kurang', 'nyaman', 'lesehan', 'buat', 'nginap', 'terbilang', 'mahal', 'kurang', 'aman', 'buat', 'anak', 'bermain', 'air', 'karena', 'minimnya', 'pengawasan', 'petugas']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
+          <t>['pantainya', 'pantai', 'kebanyakan', 'ombak', 'besarnya', 'sarana', 'dipantai', 'nyaman', 'lesehan', 'nginap', 'terbilang', 'mahal', 'aman', 'anak', 'bermain', 'air', 'minimnya', 'pengawasan', 'petugas']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>tugu nyah udah pindahin</t>
+          <t>pantai pantai banyak ombak besar sarana pantai nyaman leseh nginap bilang mahal aman anak main air minim awas tugas</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2445,84 +2447,84 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Buka setiap hari, tiket masuk kisaran 20 ribu. Tempat nyaman,luas ,kolam cukup banyak ,  kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia. â¦</t>
+          <t>Air nya hijau ga terurus banyak bentuknya, gazebo udah pada rusak</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>buka setiap hari tiket masuk kisaran ribu tempat nyamanluas kolam cukup banyak kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia â</t>
+          <t>air nya hijau ga terurus banyak bentuknya gazebo udah pada rusak</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['buka', 'setiap', 'hari', 'tiket', 'masuk', 'kisaran', 'ribu', 'tempat', 'nyamanluas', 'kolam', 'cukup', 'banyak', 'kantin', 'dan', 'tempat', 'sewa', 'ban', 'juga', 'ada', 'tempat', 'berteduh', 'atau', 'bale', 'juga', 'tersedia', 'â']</t>
+          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'banyak', 'bentuknya', 'gazebo', 'udah', 'pada', 'rusak']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['buka', 'tiket', 'masuk', 'kisaran', 'ribu', 'nyamanluas', 'kolam', 'kantin', 'sewa', 'ban', 'berteduh', 'bale', 'tersedia', 'â']</t>
+          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'bentuknya', 'gazebo', 'udah', 'rusak']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>buka tiket masuk kisar ribu nyamanluas kolam kantin sewa ban teduh bale sedia</t>
+          <t>air nya hijau ga urus bentuk gazebo udah rusak</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>A comfortable square for resting and chatting with family. The place is very spacious, you can also enjoy culinary activities. There is a mosque that is very comfortable for worship, clean toilets, many separate ablution areas for brothers â¦</t>
+          <t>Mantap tempat berkumpul dan hangout atau sekedar joging di hari minggu</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers â</t>
+          <t>mantap tempat berkumpul dan hangout atau sekedar joging di hari minggu</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
+          <t>['mantap', 'tempat', 'berkumpul', 'dan', 'hangout', 'atau', 'sekedar', 'joging', 'di', 'hari', 'minggu']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
+          <t>['mantap', 'berkumpul', 'hangout', 'sekedar', 'joging', 'minggu']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers</t>
+          <t>mantap kumpul hangout dar joging minggu</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2534,42 +2536,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The staff are friendly, the beach is nice, but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower... try to take a shower in the toilet near the beach, the toilet near the floor is not suitable â¦</t>
+          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable â</t>
+          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
+          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
+          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable</t>
+          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2581,42 +2583,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
+          <t>Air terlihat agak kotor, pasirnya hitam.. Mungkin bagi yang terbiasa ke pantai wilayah Jawa bagian timur akan merasa kurang nyaman</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
+          <t>air terlihat agak kotor pasirnya hitam mungkin bagi yang terbiasa ke pantai wilayah jawa bagian timur akan merasa kurang nyaman</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['air', 'terlihat', 'agak', 'kotor', 'pasirnya', 'hitam', 'mungkin', 'bagi', 'yang', 'terbiasa', 'ke', 'pantai', 'wilayah', 'jawa', 'bagian', 'timur', 'akan', 'merasa', 'kurang', 'nyaman']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['air', 'kotor', 'pasirnya', 'hitam', 'terbiasa', 'pantai', 'wilayah', 'jawa', 'timur', 'nyaman']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
+          <t>air kotor pasir hitam biasa pantai wilayah jawa timur nyaman</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2628,42 +2630,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Karang Sari Beach. Located before Citepus Beach from the market. The atmosphere is quite nice for photos, and swimming is also possible, but be â¦</t>
+          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>karang sari beach located before citepus beach from the market the atmosphere is quite nice for photos and swimming is also possible but be â</t>
+          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['karang', 'sari', 'beach', 'located', 'before', 'citepus', 'beach', 'from', 'the', 'market', 'the', 'atmosphere', 'is', 'quite', 'nice', 'for', 'photos', 'and', 'swimming', 'is', 'also', 'possible', 'but', 'be', 'â']</t>
+          <t>['skarang', 'lebih', 'sepi', 'dan', 'kebanyakan', 'di', 'pakai', 'oknum', 'pemuda', 'pemudi', 'buat', 'pacaran', 'kadang', 'suka', 'ada', 'yg', 'mabuk', 'atau', 'tawuran', 'anak', 'sekolah']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['karang', 'sari', 'beach', 'located', 'before', 'citepus', 'beach', 'from', 'the', 'market', 'the', 'atmosphere', 'is', 'quite', 'nice', 'for', 'photos', 'and', 'swimming', 'is', 'also', 'possible', 'but', 'be', 'â']</t>
+          <t>['skarang', 'sepi', 'kebanyakan', 'pakai', 'oknum', 'pemuda', 'pemudi', 'pacaran', 'kadang', 'suka', 'yg', 'mabuk', 'tawuran', 'anak', 'sekolah']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>karang sari beach located before citepus beach from the market the atmosphere is quite nice for photos and swimming is also possible but be</t>
+          <t>skarang sepi banyak pakai oknum pemuda pemudi pacar kadang suka yg mabuk tawur anak sekolah</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2675,12 +2677,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
+          <t>Kurang bagus renop nya, saung nya malah jdi gak ada, di ganti jadi lsehan krang nyaman licin banget</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2690,22 +2692,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
+          <t>kurang bagus renop nya saung nya malah jdi gak ada di ganti jadi lsehan krang nyaman licin banget</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['kurang', 'bagus', 'renop', 'nya', 'saung', 'nya', 'malah', 'jdi', 'gak', 'ada', 'di', 'ganti', 'jadi', 'lsehan', 'krang', 'nyaman', 'licin', 'banget']</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['bagus', 'renop', 'nya', 'saung', 'nya', 'jdi', 'gak', 'ganti', 'lsehan', 'krang', 'nyaman', 'licin', 'banget']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>kali lapang cangehgarbagus</t>
+          <t>bagus renop nya saung nya jdi gak ganti lsehan krang nyaman licin banget</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2722,12 +2724,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
+          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2737,22 +2739,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
+          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
+          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2769,42 +2771,42 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>Banyak sampah, kayanya kalo mlm sring dipake buat hal-hal yg tdk sharusnya. Tlg Bapak satpol PP dan Polisi mengawal tempat tsb. Trmksh.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>banyak sampah kayanya kalo mlm sring dipake buat halhal yg tdk sharusnya tlg bapak satpol pp dan polisi mengawal tempat tsb trmksh</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['banyak', 'sampah', 'kayanya', 'kalo', 'mlm', 'sring', 'dipake', 'buat', 'halhal', 'yg', 'tdk', 'sharusnya', 'tlg', 'bapak', 'satpol', 'pp', 'dan', 'polisi', 'mengawal', 'tempat', 'tsb', 'trmksh']</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['sampah', 'kayanya', 'kalo', 'mlm', 'sring', 'dipake', 'halhal', 'yg', 'tdk', 'sharusnya', 'tlg', 'satpol', 'pp', 'polisi', 'mengawal', 'tsb', 'trmksh']</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>sampah kaya kalo mlm sring dipake halhal yg tdk sharusnya tlg satpol pp polisi awal tsb trmksh</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2816,12 +2818,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2831,22 +2833,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2855,335 +2857,6 @@
         </is>
       </c>
       <c r="I52" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Alun - Alun Palabuhanratu</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak  mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang  sebab ada oknum pedagang terutama pedagang  gorengan ada bapa bapa yang menjual /mencampur gorengan sisa hari kemarinnya,yang diangetin lagi hingga  terasa keras dan basi.</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CONF</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang sebab ada oknum pedagang terutama pedagang gorengan ada bapa bapa yang menjual mencampur gorengan sisa hari kemarinnyayang diangetin lagi hingga terasa keras dan basi</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>['nyaman', 'untuk', 'nyari', 'kuliner', 'cuma', 'tolong', 'ditertibkan', 'para', 'pedagangnya', 'supaya', 'tidak', 'mengganggu', 'lalu', 'lintas', 'juga', 'rasanya', 'harus', 'ada', 'pembinaan', 'pada', 'para', 'pedagang', 'sebab', 'ada', 'oknum', 'pedagang', 'terutama', 'pedagang', 'gorengan', 'ada', 'bapa', 'bapa', 'yang', 'menjual', 'mencampur', 'gorengan', 'sisa', 'hari', 'kemarinnyayang', 'diangetin', 'lagi', 'hingga', 'terasa', 'keras', 'dan', 'basi']</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>['nyaman', 'nyari', 'kuliner', 'tolong', 'ditertibkan', 'pedagangnya', 'mengganggu', 'lintas', 'pembinaan', 'pedagang', 'oknum', 'pedagang', 'pedagang', 'gorengan', 'bapa', 'bapa', 'menjual', 'mencampur', 'gorengan', 'sisa', 'kemarinnyayang', 'diangetin', 'keras', 'basi']</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>nyaman nyari kuliner tolong tertib dagang ganggu lintas bina dagang oknum dagang dagang goreng bapa bapa jual campur goreng sisa kemarinnyayang diangetin keras basi</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>CONF</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Pantai Pelabuhan Ratu</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>bagus,,enak buat liburan bersama keluarga</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>bagusenak buat liburan bersama keluarga</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>['bagusenak', 'liburan', 'keluarga']</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>bagusenak libur keluarga</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Alun - Alun Palabuhanratu</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Pantai Batu Bintang</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Lumayan bagus,aman untuk anak2 main dipantainya</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>lumayan bagusaman untuk anak main dipantainya</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>['lumayan', 'bagusaman', 'untuk', 'anak', 'main', 'dipantainya']</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>['lumayan', 'bagusaman', 'anak', 'main', 'dipantainya']</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>lumayan bagusaman anak main pantai</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Pantai Karang Sari</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Kondisi lapang lumayan baik. Track lari sedikit rusak. Lari pagi di hari minggu tidak terlalu padat</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>kondisi lapang lumayan baik track lari sedikit rusak lari pagi di hari minggu tidak terlalu padat</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>['kondisi', 'lapang', 'lumayan', 'baik', 'track', 'lari', 'sedikit', 'rusak', 'lari', 'pagi', 'di', 'hari', 'minggu', 'tidak', 'terlalu', 'padat']</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>['kondisi', 'lapang', 'lumayan', 'track', 'lari', 'rusak', 'lari', 'pagi', 'minggu', 'padat']</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>kondisi lapang lumayan track lari rusak lari pagi minggu padat</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Pantai Batu Bintang</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Pertama ngecamp pinggir pantai tuu rasanya,MasyaAllah.. Pantai ini tu,deket ke warung,deket ke mushola,air untuk mandi lancar.tapi,kalau mau cam di tarif lagi untuk biaya kebersihan 1 tenda 20-25k untuk yang mau ikut â¦</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>pertama ngecamp pinggir pantai tuu rasanyamasyaallah pantai ini tudeket ke warungdeket ke musholaair untuk mandi lancartapikalau mau cam di tarif lagi untuk biaya kebersihan tenda k untuk yang mau ikut â</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>['pertama', 'ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'ini', 'tudeket', 'ke', 'warungdeket', 'ke', 'musholaair', 'untuk', 'mandi', 'lancartapikalau', 'mau', 'cam', 'di', 'tarif', 'lagi', 'untuk', 'biaya', 'kebersihan', 'tenda', 'k', 'untuk', 'yang', 'mau', 'ikut', 'â']</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>['ngecamp', 'pinggir', 'pantai', 'tuu', 'rasanyamasyaallah', 'pantai', 'tudeket', 'warungdeket', 'musholaair', 'mandi', 'lancartapikalau', 'cam', 'tarif', 'biaya', 'kebersihan', 'tenda', 'k', 'â']</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>ngecamp pinggir pantai tuu rasanyamasyaallah pantai tudeket warungdeket musholaair mandi lancartapikalau cam tarif biaya bersih tenda k</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,37 +471,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alhamdulillahasih bersih, indah apalagi di malam hari, tepat nya di depan majid agung palabuahan ratu, banyak tersedia jajanan juga, ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
+          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>alhamdulillahasih bersih indah apalagi di malam hari tepat nya di depan majid agung palabuahan ratu banyak tersedia jajanan juga ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
+          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['alhamdulillahasih', 'bersih', 'indah', 'apalagi', 'di', 'malam', 'hari', 'tepat', 'nya', 'di', 'depan', 'majid', 'agung', 'palabuahan', 'ratu', 'banyak', 'tersedia', 'jajanan', 'juga', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended', 'lah']</t>
+          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['alhamdulillahasih', 'bersih', 'indah', 'malam', 'nya', 'majid', 'agung', 'palabuahan', 'ratu', 'tersedia', 'jajanan', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended']</t>
+          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>alhamdulillahasih bersih indah malam nya majid agung palabuahan ratu sedia jajan ubtuk dar santa denfan keluarga rekomended</t>
+          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -513,12 +513,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
+          <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
+          <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>kali lapang cangehgarbagus</t>
+          <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -607,42 +607,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bagus,,enak buat liburan bersama keluarga</t>
+          <t>Sangat buruk. Pasilitas hampir semua ruksak. Tempat bermain anak, tempatmain skate. Bangunan banyak yang sudah hancur</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>bagusenak buat liburan bersama keluarga</t>
+          <t>sangat buruk pasilitas hampir semua ruksak tempat bermain anak tempatmain skate bangunan banyak yang sudah hancur</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
+          <t>['sangat', 'buruk', 'pasilitas', 'hampir', 'semua', 'ruksak', 'tempat', 'bermain', 'anak', 'tempatmain', 'skate', 'bangunan', 'banyak', 'yang', 'sudah', 'hancur']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['bagusenak', 'liburan', 'keluarga']</t>
+          <t>['buruk', 'pasilitas', 'ruksak', 'bermain', 'anak', 'tempatmain', 'skate', 'bangunan', 'hancur']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>bagusenak libur keluarga</t>
+          <t>buruk pasilitas ruksak main anak tempatmain skate bangun hancur</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -654,12 +654,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -669,22 +669,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
+          <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
+          <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
+          <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
+          <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
+          <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -748,42 +748,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -795,12 +795,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>It's best to come here in the late afternoon, the view is beautiful. It's a shame the toilets are dirty.</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -810,22 +810,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>its best to come here in the late afternoon the view is beautiful its a shame the toilets are dirty</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['its', 'best', 'to', 'come', 'here', 'in', 'the', 'late', 'afternoon', 'the', 'view', 'is', 'beautiful', 'its', 'a', 'shame', 'the', 'toilets', 'are', 'dirty']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['its', 'best', 'to', 'come', 'here', 'in', 'the', 'late', 'afternoon', 'the', 'view', 'is', 'beautiful', 'its', 'a', 'shame', 'the', 'toilets', 'are', 'dirty']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>its best to come here in the late afternoon the view is beautiful its a shame the toilets are dirty</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -842,47 +842,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>Kotor alun alunnya banyak sampah...mampir ke masjid di alun2 bersih dan nyaman</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>kotor alun alunnya banyak sampahmampir ke masjid di alun bersih dan nyaman</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['kotor', 'alun', 'alunnya', 'banyak', 'sampahmampir', 'ke', 'masjid', 'di', 'alun', 'bersih', 'dan', 'nyaman']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['kotor', 'alun', 'alunnya', 'sampahmampir', 'masjid', 'alun', 'bersih', 'nyaman']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>kotor alun alun sampahmampir masjid alun bersih nyaman</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
@@ -894,37 +894,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -936,42 +936,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Ikon kota palabuhanratu......bagus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>ikon kota palabuhanratubagus</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>ikon kota palabuhanratubagus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -983,42 +983,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>A comfortable square for resting and chatting with family. The place is very spacious, you can also enjoy culinary activities. There is a mosque that is very comfortable for worship, clean toilets, many separate ablution areas for brothers â¦</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers â</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1030,42 +1030,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sangat buruk. Pasilitas hampir semua ruksak. Tempat bermain anak, tempatmain skate. Bangunan banyak yang sudah hancur</t>
+          <t>bagus,,enak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>sangat buruk pasilitas hampir semua ruksak tempat bermain anak tempatmain skate bangunan banyak yang sudah hancur</t>
+          <t>bagusenak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['sangat', 'buruk', 'pasilitas', 'hampir', 'semua', 'ruksak', 'tempat', 'bermain', 'anak', 'tempatmain', 'skate', 'bangunan', 'banyak', 'yang', 'sudah', 'hancur']</t>
+          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['buruk', 'pasilitas', 'ruksak', 'bermain', 'anak', 'tempatmain', 'skate', 'bangunan', 'hancur']</t>
+          <t>['bagusenak', 'liburan', 'keluarga']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>buruk pasilitas ruksak main anak tempatmain skate bangun hancur</t>
+          <t>bagusenak libur keluarga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,42 +1077,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>mantaps dah olahraga ringan keluarga</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1124,42 +1124,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kotor alun alunnya banyak sampah...mampir ke masjid di alun2 bersih dan nyaman</t>
+          <t>Susah wf.sama signal.,..</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>kotor alun alunnya banyak sampahmampir ke masjid di alun bersih dan nyaman</t>
+          <t>susah wfsama signal</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['kotor', 'alun', 'alunnya', 'banyak', 'sampahmampir', 'ke', 'masjid', 'di', 'alun', 'bersih', 'dan', 'nyaman']</t>
+          <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['kotor', 'alun', 'alunnya', 'sampahmampir', 'masjid', 'alun', 'bersih', 'nyaman']</t>
+          <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>kotor alun alun sampahmampir masjid alun bersih nyaman</t>
+          <t>susah wfsama signal</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1171,12 +1171,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pasir pantai tidak tajam, lumayan bersih, banyak toilet, kamar mandi dan musola. Harga makanan dan minuman sesuai kantong.</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1186,22 +1186,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>pasir pantai tidak tajam lumayan bersih banyak toilet kamar mandi dan musola harga makanan dan minuman sesuai kantong</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['pasir', 'pantai', 'tidak', 'tajam', 'lumayan', 'bersih', 'banyak', 'toilet', 'kamar', 'mandi', 'dan', 'musola', 'harga', 'makanan', 'dan', 'minuman', 'sesuai', 'kantong']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['pasir', 'pantai', 'tajam', 'lumayan', 'bersih', 'toilet', 'kamar', 'mandi', 'musola', 'harga', 'makanan', 'minuman', 'sesuai', 'kantong']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>pasir pantai tajam lumayan bersih toilet kamar mandi musola harga makan minum sesuai kantong</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1218,42 +1218,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
+          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
+          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
+          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
+          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
+          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1265,42 +1265,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>cocok jalanjalan santai ramai sejuk</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1312,106 +1312,106 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
+          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
+          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
+          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
+          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
+          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Accommodating thousands of people, with a nice park and toilet facilities...</t>
+          <t>Tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luas,mudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>accommodating thousands of people with a nice park and toilet facilities</t>
+          <t>tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luasmudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
+          <t>['tempat', 'di', 'pelabuhan', 'ratu', 'buat', 'main', 'keluarga', 'cuma', 'jarang', 'tempat', 'untuk', 'berteduh', 'suasana', 'pantai', 'indah', 'banyak', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'lebih', 'di', 'pelihara', 'dan', 'di', 'perindah', 'supaya', 'tempat', 'nya', 'makin', 'bagus']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
+          <t>['pelabuhan', 'ratu', 'main', 'keluarga', 'jarang', 'berteduh', 'suasana', 'pantai', 'indah', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'pelihara', 'perindah', 'nya', 'bagus']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>accommodating thousands of people with a nice park and toilet facilities</t>
+          <t>labuh ratu main keluarga jarang teduh suasana pantai indah tukang dagang parkir luasmudah mudah pelihara indah nya bagus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
+          <t>Beautiful, neat and clean. Suitable for taking photos for sunset hunters</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1421,22 +1421,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
+          <t>beautiful neat and clean suitable for taking photos for sunset hunters</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['beautiful', 'neat', 'and', 'clean', 'suitable', 'for', 'taking', 'photos', 'for', 'sunset', 'hunters']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['beautiful', 'neat', 'and', 'clean', 'suitable', 'for', 'taking', 'photos', 'for', 'sunset', 'hunters']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>nongki chill and cheap yg cocok pas sunsetan</t>
+          <t>beautiful neat and clean suitable for taking photos for sunset hunters</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1453,14 +1453,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Please kesini bkn baru pertama kalinya, tp kesekian kalinyað¥° and aku kesini bkn d hari weekand tp d hari biasa, so aku lebih suka suasana sepi hehehe, jd lebih nikmat liat sunsetnyað-ð-, dahal setiap kesini pasti d jalan tolnya ujan tp oas â¦</t>
+          <t>It's well organized and the street vendors are friendly, but the public facilities like the toilets aren't working.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1470,22 +1468,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>please kesini bkn baru pertama kalinya tp kesekian kalinyað and aku kesini bkn d hari weekand tp d hari biasa so aku lebih suka suasana sepi hehehe jd lebih nikmat liat sunsetnyað ð dahal setiap kesini pasti d jalan tolnya ujan tp oas â</t>
+          <t>its well organized and the street vendors are friendly but the public facilities like the toilets arent working</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['please', 'kesini', 'bkn', 'baru', 'pertama', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'aku', 'kesini', 'bkn', 'd', 'hari', 'weekand', 'tp', 'd', 'hari', 'biasa', 'so', 'aku', 'lebih', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'lebih', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'setiap', 'kesini', 'pasti', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
+          <t>['its', 'well', 'organized', 'and', 'the', 'street', 'vendors', 'are', 'friendly', 'but', 'the', 'public', 'facilities', 'like', 'the', 'toilets', 'arent', 'working']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['please', 'kesini', 'bkn', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'kesini', 'bkn', 'd', 'weekand', 'tp', 'd', 'so', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'kesini', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
+          <t>['its', 'well', 'organized', 'and', 'the', 'street', 'vendors', 'are', 'friendly', 'but', 'the', 'public', 'facilities', 'like', 'the', 'toilets', 'arent', 'working']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>please kesini bkn kali tp sekian kali and kesini bkn d weekand tp d so suka suasana sepi hehehe jd nikmat liat sunsetnya dahal kesini d jalan tol ujan tp oas</t>
+          <t>its well organized and the street vendors are friendly but the public facilities like the toilets arent working</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1502,89 +1500,89 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
+          <t>Baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya. Detail bajunya bagus banget</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
+          <t>baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya detail bajunya bagus banget</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
+          <t>['baju', 'baju', 'yg', 'tetsedia', 'untuk', 'di', 'sewakan', 'sangat', 'bagus', 'dan', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'dengan', 'ke', 'inginan', 'saya', 'detail', 'bajunya', 'bagus', 'banget']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
+          <t>['baju', 'baju', 'yg', 'tetsedia', 'sewakan', 'bagus', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'inginan', 'detail', 'bajunya', 'bagus', 'banget']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
+          <t>baju baju yg tetsedia sewa bagus riquesan buat baju nya sesuai banget ingin detail baju bagus banget</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
+          <t>Di kelola oleh oknum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
+          <t>di kelola oleh oknum</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
+          <t>['di', 'kelola', 'oleh', 'oknum']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
+          <t>['kelola', 'oknum']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
+          <t>kelola oknum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1596,42 +1594,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>ga ada pungli tapi kalo mau mesen makanan alangkah baiknya tanya harga dulu soalnya main getok harga</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>ga ada pungli tapi kalo mau mesen makanan alangkah baiknya tanya harga dulu soalnya main getok harga</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
+          <t>['ga', 'ada', 'pungli', 'tapi', 'kalo', 'mau', 'mesen', 'makanan', 'alangkah', 'baiknya', 'tanya', 'harga', 'dulu', 'soalnya', 'main', 'getok', 'harga']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
+          <t>['ga', 'pungli', 'kalo', 'mesen', 'makanan', 'alangkah', 'baiknya', 'harga', 'main', 'getok', 'harga']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
+          <t>ga pungli kalo mesen makan alangkah baik harga main getok harga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1643,42 +1641,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
+          <t>Mantappppp</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
+          <t>mantappppp</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
+          <t>['mantappppp']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
+          <t>['mantappppp']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
+          <t>mantappppp</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1690,42 +1688,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pantai nya lumayan cuma banyak pengamenya</t>
+          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>pantai nya lumayan cuma banyak pengamenya</t>
+          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['pantai', 'nya', 'lumayan', 'cuma', 'banyak', 'pengamenya']</t>
+          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['pantai', 'nya', 'lumayan', 'pengamenya']</t>
+          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>pantai nya lumayan pengamenya</t>
+          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1737,42 +1735,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Di kelola oleh oknum</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>di kelola oleh oknum</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['di', 'kelola', 'oleh', 'oknum']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['kelola', 'oknum']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>kelola oknum</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1784,42 +1782,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
+          <t>Beautiful beach view while waiting for the sunset. For those who want to swim, be careful because large waves and strong currents sometimes come.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
+          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
+          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1878,42 +1876,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A place in Pelabuhan Ratu for families to play, but there are rarely any places to take shelter, a beautiful beach atmosphere, lots of traders, spacious parking, hopefully it will be better maintained and beautified so that the place will be even better.</t>
+          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>a place in pelabuhan ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>a place in labuh ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+          <t>nongki chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1925,42 +1923,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
+          <t>Pantainya bersih, yang terpenting harga makanan dan minuman super murah,parkir jg normal..</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
+          <t>pantainya bersih yang terpenting harga makanan dan minuman super murahparkir jg normal</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
+          <t>['pantainya', 'bersih', 'yang', 'terpenting', 'harga', 'makanan', 'dan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
+          <t>['pantainya', 'bersih', 'terpenting', 'harga', 'makanan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
+          <t>pantai bersih penting harga makan minum super murahparkir jg normal</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1972,42 +1970,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pantainya bersih, yang terpenting harga makanan dan minuman super murah,parkir jg normal..</t>
+          <t>A place in Pelabuhan Ratu for families to play, but there are rarely any places to take shelter, a beautiful beach atmosphere, lots of traders, spacious parking, hopefully it will be better maintained and beautified so that the place will be even better.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>pantainya bersih yang terpenting harga makanan dan minuman super murahparkir jg normal</t>
+          <t>a place in pelabuhan ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersih', 'yang', 'terpenting', 'harga', 'makanan', 'dan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersih', 'terpenting', 'harga', 'makanan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>pantai bersih penting harga makan minum super murahparkir jg normal</t>
+          <t>a place in labuh ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2019,42 +2017,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2071,37 +2069,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lapangannya luas,rapih, bersih,di tata dengan sangat bagus,penyuluh sosial masyarakat kab sukabumi,mengikuti upacara hari jadi Sukabumi</t>
+          <t>Kondisi lapang lumayan baik. Track lari sedikit rusak. Lari pagi di hari minggu tidak terlalu padat</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>lapangannya luasrapih bersihdi tata dengan sangat baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara hari jadi sukabumi</t>
+          <t>kondisi lapang lumayan baik track lari sedikit rusak lari pagi di hari minggu tidak terlalu padat</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'dengan', 'sangat', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'hari', 'jadi', 'sukabumi']</t>
+          <t>['kondisi', 'lapang', 'lumayan', 'baik', 'track', 'lari', 'sedikit', 'rusak', 'lari', 'pagi', 'di', 'hari', 'minggu', 'tidak', 'terlalu', 'padat']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'sukabumi']</t>
+          <t>['kondisi', 'lapang', 'lumayan', 'track', 'lari', 'rusak', 'lari', 'pagi', 'minggu', 'padat']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>lapang luasrapih bersihdi tata baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara sukabumi</t>
+          <t>kondisi lapang lumayan track lari rusak lari pagi minggu padat</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2113,42 +2111,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Alun Alun Pelabuhan Ratu Sukabumi adalah tempat yang menawan dengan pesona alamnya. Keindahan alun-alun dan pemandangan laut yang menakjubkan membuatnya menjadi tempat yang pas untuk bersantai. Suasana tenang dan sejuk di sekitar area ini â¦</t>
+          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>alun alun pelabuhan ratu sukabumi adalah tempat yang menawan dengan pesona alamnya keindahan alunalun dan pemandangan laut yang menakjubkan membuatnya menjadi tempat yang pas untuk bersantai suasana tenang dan sejuk di sekitar area ini â</t>
+          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['alun', 'alun', 'pelabuhan', 'ratu', 'sukabumi', 'adalah', 'tempat', 'yang', 'menawan', 'dengan', 'pesona', 'alamnya', 'keindahan', 'alunalun', 'dan', 'pemandangan', 'laut', 'yang', 'menakjubkan', 'membuatnya', 'menjadi', 'tempat', 'yang', 'pas', 'untuk', 'bersantai', 'suasana', 'tenang', 'dan', 'sejuk', 'di', 'sekitar', 'area', 'ini', 'â']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['alun', 'alun', 'pelabuhan', 'ratu', 'sukabumi', 'menawan', 'pesona', 'alamnya', 'keindahan', 'alunalun', 'pemandangan', 'laut', 'menakjubkan', 'membuatnya', 'pas', 'bersantai', 'suasana', 'tenang', 'sejuk', 'area', 'â']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>alun alun labuh ratu sukabumi tawan pesona alam indah alunalun pandang laut takjub buat pas santa suasana tenang sejuk area</t>
+          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2160,42 +2158,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pemandangan baik,bagus,hanya saja tempat ganti pakaian/mandi agak kurang rapih saja</t>
+          <t>Air nya hijau ga terurus banyak bentuknya, gazebo udah pada rusak</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>pemandangan baikbagushanya saja tempat ganti pakaianmandi agak kurang rapih saja</t>
+          <t>air nya hijau ga terurus banyak bentuknya gazebo udah pada rusak</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['pemandangan', 'baikbagushanya', 'saja', 'tempat', 'ganti', 'pakaianmandi', 'agak', 'kurang', 'rapih', 'saja']</t>
+          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'banyak', 'bentuknya', 'gazebo', 'udah', 'pada', 'rusak']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['pemandangan', 'baikbagushanya', 'ganti', 'pakaianmandi', 'rapih']</t>
+          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'bentuknya', 'gazebo', 'udah', 'rusak']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>pandang baikbagushanya ganti pakaianmandi rapih</t>
+          <t>air nya hijau ga urus bentuk gazebo udah rusak</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2207,59 +2205,59 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
+          <t>Alhamdulillahasih bersih, indah apalagi di malam hari, tepat nya di depan majid agung palabuahan ratu, banyak tersedia jajanan juga, ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
+          <t>alhamdulillahasih bersih indah apalagi di malam hari tepat nya di depan majid agung palabuahan ratu banyak tersedia jajanan juga ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
+          <t>['alhamdulillahasih', 'bersih', 'indah', 'apalagi', 'di', 'malam', 'hari', 'tepat', 'nya', 'di', 'depan', 'majid', 'agung', 'palabuahan', 'ratu', 'banyak', 'tersedia', 'jajanan', 'juga', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended', 'lah']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
+          <t>['alhamdulillahasih', 'bersih', 'indah', 'malam', 'nya', 'majid', 'agung', 'palabuahan', 'ratu', 'tersedia', 'jajanan', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
+          <t>alhamdulillahasih bersih indah malam nya majid agung palabuahan ratu sedia jajan ubtuk dar santa denfan keluarga rekomended</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tugu nyah udah di pindahin</t>
+          <t>Pantai Batu Bintang merupakan salah satu pantai yang terletak di Pelabuhan Ratu, Kabupaten Sukabumi, Jawa Barat. Pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik. â¦</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2269,22 +2267,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tugu nyah udah di pindahin</t>
+          <t>pantai batu bintang merupakan salah satu pantai yang terletak di pelabuhan ratu kabupaten sukabumi jawa barat pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik â</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
+          <t>['pantai', 'batu', 'bintang', 'merupakan', 'salah', 'satu', 'pantai', 'yang', 'terletak', 'di', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'ini', 'terkenal', 'dengan', 'keindahan', 'pantainya', 'yang', 'masih', 'alami', 'dan', 'dihiasi', 'dengan', 'bebatuan', 'yang', 'unik', 'dan', 'menarik', 'â']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
+          <t>['pantai', 'batu', 'bintang', 'salah', 'pantai', 'terletak', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'terkenal', 'keindahan', 'pantainya', 'alami', 'dihiasi', 'bebatuan', 'unik', 'menarik', 'â']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>tugu nyah udah pindahin</t>
+          <t>pantai batu bintang salah pantai letak labuh ratu kabupaten sukabumi jawa barat pantai kenal indah pantai alami hias bebatuan unik tarik</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2301,12 +2299,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>It's free, with no entrance fee. The sand is fine and coral-free. Toilet and changing room facilities need to be expanded and their cleanliness monitored.</t>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2316,22 +2314,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2341,49 +2339,49 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Available milk, diapers, baby supplies, toiletries and staple foods and smashed chicken</t>
+          <t>The place is not as big as other town squares, but the atmosphere is calm and beautiful, the mosque is nice, and the parking is quite good.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
+          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
+          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
+          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
+          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2395,89 +2393,89 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Untuk pantainya seperti pantai kebanyakan, dengan ombak besarnya. Sarana di dipantai tersebut kurang nyaman, lesehan buat nginap terbilang mahal, kurang aman buat anak2 bermain air karena minimnya pengawasan petugas.</t>
+          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>untuk pantainya seperti pantai kebanyakan dengan ombak besarnya sarana di dipantai tersebut kurang nyaman lesehan buat nginap terbilang mahal kurang aman buat anak bermain air karena minimnya pengawasan petugas</t>
+          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['untuk', 'pantainya', 'seperti', 'pantai', 'kebanyakan', 'dengan', 'ombak', 'besarnya', 'sarana', 'di', 'dipantai', 'tersebut', 'kurang', 'nyaman', 'lesehan', 'buat', 'nginap', 'terbilang', 'mahal', 'kurang', 'aman', 'buat', 'anak', 'bermain', 'air', 'karena', 'minimnya', 'pengawasan', 'petugas']</t>
+          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['pantainya', 'pantai', 'kebanyakan', 'ombak', 'besarnya', 'sarana', 'dipantai', 'nyaman', 'lesehan', 'nginap', 'terbilang', 'mahal', 'aman', 'anak', 'bermain', 'air', 'minimnya', 'pengawasan', 'petugas']</t>
+          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>pantai pantai banyak ombak besar sarana pantai nyaman leseh nginap bilang mahal aman anak main air minim awas tugas</t>
+          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Air nya hijau ga terurus banyak bentuknya, gazebo udah pada rusak</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>air nya hijau ga terurus banyak bentuknya gazebo udah pada rusak</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'banyak', 'bentuknya', 'gazebo', 'udah', 'pada', 'rusak']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'bentuknya', 'gazebo', 'udah', 'rusak']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>air nya hijau ga urus bentuk gazebo udah rusak</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2489,89 +2487,89 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mantap tempat berkumpul dan hangout atau sekedar joging di hari minggu</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>mantap tempat berkumpul dan hangout atau sekedar joging di hari minggu</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['mantap', 'tempat', 'berkumpul', 'dan', 'hangout', 'atau', 'sekedar', 'joging', 'di', 'hari', 'minggu']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['mantap', 'berkumpul', 'hangout', 'sekedar', 'joging', 'minggu']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>mantap kumpul hangout dar joging minggu</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
+          <t>Lokasi strategis. Cocok untuk santai cocok untuk anak-anak, cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan, cocok untuk yg tua muda semuanya.. tinggal d jaga bersama sama.. jangan vandalisme dan mengotorinya dgn sampah..okkkk</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
+          <t>lokasi strategis cocok untuk santai cocok untuk anakanak cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan cocok untuk yg tua muda semuanya tinggal d jaga bersama sama jangan vandalisme dan mengotorinya dgn sampahokkkk</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['lokasi', 'strategis', 'cocok', 'untuk', 'santai', 'cocok', 'untuk', 'anakanak', 'cocok', 'untuk', 'olahraga', 'subuh', 'dengan', 'udara', 'yg', 'segar', 'dekat', 'pegunungan', 'cocok', 'untuk', 'yg', 'tua', 'muda', 'semuanya', 'tinggal', 'd', 'jaga', 'bersama', 'sama', 'jangan', 'vandalisme', 'dan', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
+          <t>['lokasi', 'strategis', 'cocok', 'santai', 'cocok', 'anakanak', 'cocok', 'olahraga', 'subuh', 'udara', 'yg', 'segar', 'pegunungan', 'cocok', 'yg', 'tua', 'muda', 'tinggal', 'd', 'jaga', 'vandalisme', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
+          <t>lokasi strategis cocok santai cocok anakanak cocok olahraga subuh udara yg segar gunung cocok yg tua muda tinggal d jaga vandalisme kotor dgn sampahokkkk</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2583,12 +2581,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Air terlihat agak kotor, pasirnya hitam.. Mungkin bagi yang terbiasa ke pantai wilayah Jawa bagian timur akan merasa kurang nyaman</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2598,22 +2596,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>air terlihat agak kotor pasirnya hitam mungkin bagi yang terbiasa ke pantai wilayah jawa bagian timur akan merasa kurang nyaman</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['air', 'terlihat', 'agak', 'kotor', 'pasirnya', 'hitam', 'mungkin', 'bagi', 'yang', 'terbiasa', 'ke', 'pantai', 'wilayah', 'jawa', 'bagian', 'timur', 'akan', 'merasa', 'kurang', 'nyaman']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['air', 'kotor', 'pasirnya', 'hitam', 'terbiasa', 'pantai', 'wilayah', 'jawa', 'timur', 'nyaman']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>air kotor pasir hitam biasa pantai wilayah jawa timur nyaman</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2630,42 +2628,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
+          <t>The place is nice, the waves are not too big, you can see the sunset which is also beautiful accompanied by a pretty good view ð¥°ð¥° â¦</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
+          <t>the place is nice the waves are not too big you can see the sunset which is also beautiful accompanied by a pretty good view ðð â</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['skarang', 'lebih', 'sepi', 'dan', 'kebanyakan', 'di', 'pakai', 'oknum', 'pemuda', 'pemudi', 'buat', 'pacaran', 'kadang', 'suka', 'ada', 'yg', 'mabuk', 'atau', 'tawuran', 'anak', 'sekolah']</t>
+          <t>['the', 'place', 'is', 'nice', 'the', 'waves', 'are', 'not', 'too', 'big', 'you', 'can', 'see', 'the', 'sunset', 'which', 'is', 'also', 'beautiful', 'accompanied', 'by', 'a', 'pretty', 'good', 'view', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['skarang', 'sepi', 'kebanyakan', 'pakai', 'oknum', 'pemuda', 'pemudi', 'pacaran', 'kadang', 'suka', 'yg', 'mabuk', 'tawuran', 'anak', 'sekolah']</t>
+          <t>['the', 'place', 'is', 'nice', 'the', 'waves', 'are', 'not', 'too', 'big', 'you', 'can', 'see', 'the', 'sunset', 'which', 'is', 'also', 'beautiful', 'accompanied', 'by', 'a', 'pretty', 'good', 'view', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>skarang sepi banyak pakai oknum pemuda pemudi pacar kadang suka yg mabuk tawur anak sekolah</t>
+          <t>the place is nice the waves are not too big you can see the sunset which is also beautiful accompanied by a pretty good view</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2677,12 +2675,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kurang bagus renop nya, saung nya malah jdi gak ada, di ganti jadi lsehan krang nyaman licin banget</t>
+          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2692,22 +2690,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>kurang bagus renop nya saung nya malah jdi gak ada di ganti jadi lsehan krang nyaman licin banget</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>['kurang', 'bagus', 'renop', 'nya', 'saung', 'nya', 'malah', 'jdi', 'gak', 'ada', 'di', 'ganti', 'jadi', 'lsehan', 'krang', 'nyaman', 'licin', 'banget']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['bagus', 'renop', 'nya', 'saung', 'nya', 'jdi', 'gak', 'ganti', 'lsehan', 'krang', 'nyaman', 'licin', 'banget']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>bagus renop nya saung nya jdi gak ganti lsehan krang nyaman licin banget</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2724,12 +2722,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2739,22 +2737,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2771,42 +2769,42 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Banyak sampah, kayanya kalo mlm sring dipake buat hal-hal yg tdk sharusnya. Tlg Bapak satpol PP dan Polisi mengawal tempat tsb. Trmksh.</t>
+          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>banyak sampah kayanya kalo mlm sring dipake buat halhal yg tdk sharusnya tlg bapak satpol pp dan polisi mengawal tempat tsb trmksh</t>
+          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>['banyak', 'sampah', 'kayanya', 'kalo', 'mlm', 'sring', 'dipake', 'buat', 'halhal', 'yg', 'tdk', 'sharusnya', 'tlg', 'bapak', 'satpol', 'pp', 'dan', 'polisi', 'mengawal', 'tempat', 'tsb', 'trmksh']</t>
+          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['sampah', 'kayanya', 'kalo', 'mlm', 'sring', 'dipake', 'halhal', 'yg', 'tdk', 'sharusnya', 'tlg', 'satpol', 'pp', 'polisi', 'mengawal', 'tsb', 'trmksh']</t>
+          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>sampah kaya kalo mlm sring dipake halhal yg tdk sharusnya tlg satpol pp polisi awal tsb trmksh</t>
+          <t>kali lapang cangehgarbagus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2818,12 +2816,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Pemandangan baik,bagus,hanya saja tempat ganti pakaian/mandi agak kurang rapih saja</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2833,22 +2831,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>pemandangan baikbagushanya saja tempat ganti pakaianmandi agak kurang rapih saja</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['pemandangan', 'baikbagushanya', 'saja', 'tempat', 'ganti', 'pakaianmandi', 'agak', 'kurang', 'rapih', 'saja']</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['pemandangan', 'baikbagushanya', 'ganti', 'pakaianmandi', 'rapih']</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>pandang baikbagushanya ganti pakaianmandi rapih</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2857,6 +2855,147 @@
         </is>
       </c>
       <c r="I52" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>['mesjid', 'nya', 'bagus', 'tapi', 'sayang', 'banyak', 'itu', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'itu', 'iya', 'itu', 'apa', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>['mesjid', 'nya', 'bagus', 'sayang', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'iya', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>mesjid nya bagus sayang tuh ih ituloh apasih ya iya ih eta tea naon si arana nyaeta be pokonamah</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>A fairly comfortable place to hang out, but there are no supporting facilities, such as stalls, cafes, toilets, etc.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>a fairly comfortable place to hang out but there are no supporting facilities such as stalls cafes toilets etc</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>['a', 'fairly', 'comfortable', 'place', 'to', 'hang', 'out', 'but', 'there', 'are', 'no', 'supporting', 'facilities', 'such', 'as', 'stalls', 'cafes', 'toilets', 'etc']</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>['a', 'fairly', 'comfortable', 'place', 'to', 'hang', 'out', 'but', 'there', 'are', 'no', 'supporting', 'facilities', 'such', 'as', 'stalls', 'cafes', 'toilets', 'etc']</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>a fairly comfortable place to hang out but there are no supporting facilities such as stalls cafes toilets etc</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
+          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
+          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
+          <t>nongki chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -513,42 +513,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -560,89 +560,89 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sangat buruk. Pasilitas hampir semua ruksak. Tempat bermain anak, tempatmain skate. Bangunan banyak yang sudah hancur</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>sangat buruk pasilitas hampir semua ruksak tempat bermain anak tempatmain skate bangunan banyak yang sudah hancur</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['sangat', 'buruk', 'pasilitas', 'hampir', 'semua', 'ruksak', 'tempat', 'bermain', 'anak', 'tempatmain', 'skate', 'bangunan', 'banyak', 'yang', 'sudah', 'hancur']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['buruk', 'pasilitas', 'ruksak', 'bermain', 'anak', 'tempatmain', 'skate', 'bangunan', 'hancur']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>buruk pasilitas ruksak main anak tempatmain skate bangun hancur</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -654,42 +654,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
+          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
+          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
+          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
+          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
+          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -701,42 +701,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
+          <t>Liburan murmer ,,sewa rumah di pinggir pantai murah cuma sayang banyak yg ngamen.. Repot juga tiap 5 menit mah dikira liburan banyak duit...bilang maaf ga pergi2.. Saran siapin receh yg banyak</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
+          <t>liburan murmer sewa rumah di pinggir pantai murah cuma sayang banyak yg ngamen repot juga tiap menit mah dikira liburan banyak duitbilang maaf ga pergi saran siapin receh yg banyak</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
+          <t>['liburan', 'murmer', 'sewa', 'rumah', 'di', 'pinggir', 'pantai', 'murah', 'cuma', 'sayang', 'banyak', 'yg', 'ngamen', 'repot', 'juga', 'tiap', 'menit', 'mah', 'dikira', 'liburan', 'banyak', 'duitbilang', 'maaf', 'ga', 'pergi', 'saran', 'siapin', 'receh', 'yg', 'banyak']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
+          <t>['liburan', 'murmer', 'sewa', 'rumah', 'pinggir', 'pantai', 'murah', 'sayang', 'yg', 'ngamen', 'repot', 'menit', 'mah', 'liburan', 'duitbilang', 'maaf', 'ga', 'pergi', 'saran', 'siapin', 'receh', 'yg']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
+          <t>libur murmer sewa rumah pinggir pantai murah sayang yg ngamen repot menit mah libur duitbilang maaf ga pergi saran siapin receh yg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -748,42 +748,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Bagussss</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -795,42 +795,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -842,12 +842,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Smile hill Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kotor alun alunnya banyak sampah...mampir ke masjid di alun2 bersih dan nyaman</t>
+          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -857,22 +857,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>kotor alun alunnya banyak sampahmampir ke masjid di alun bersih dan nyaman</t>
+          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['kotor', 'alun', 'alunnya', 'banyak', 'sampahmampir', 'ke', 'masjid', 'di', 'alun', 'bersih', 'dan', 'nyaman']</t>
+          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['kotor', 'alun', 'alunnya', 'sampahmampir', 'masjid', 'alun', 'bersih', 'nyaman']</t>
+          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>kotor alun alun sampahmampir masjid alun bersih nyaman</t>
+          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -889,12 +889,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -904,22 +904,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -936,89 +936,89 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ikon kota palabuhanratu......bagus</t>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ikon kota palabuhanratubagus</t>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ikon kota palabuhanratubagus</t>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A comfortable square for resting and chatting with family. The place is very spacious, you can also enjoy culinary activities. There is a mosque that is very comfortable for worship, clean toilets, many separate ablution areas for brothers â¦</t>
+          <t>Pantai Batu Bintang merupakan salah satu pantai yang terletak di Pelabuhan Ratu, Kabupaten Sukabumi, Jawa Barat. Pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik. â¦</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers â</t>
+          <t>pantai batu bintang merupakan salah satu pantai yang terletak di pelabuhan ratu kabupaten sukabumi jawa barat pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik â</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
+          <t>['pantai', 'batu', 'bintang', 'merupakan', 'salah', 'satu', 'pantai', 'yang', 'terletak', 'di', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'ini', 'terkenal', 'dengan', 'keindahan', 'pantainya', 'yang', 'masih', 'alami', 'dan', 'dihiasi', 'dengan', 'bebatuan', 'yang', 'unik', 'dan', 'menarik', 'â']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['a', 'comfortable', 'square', 'for', 'resting', 'and', 'chatting', 'with', 'family', 'the', 'place', 'is', 'very', 'spacious', 'you', 'can', 'also', 'enjoy', 'culinary', 'activities', 'there', 'is', 'a', 'mosque', 'that', 'is', 'very', 'comfortable', 'for', 'worship', 'clean', 'toilets', 'many', 'separate', 'ablution', 'areas', 'for', 'brothers', 'â']</t>
+          <t>['pantai', 'batu', 'bintang', 'salah', 'pantai', 'terletak', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'terkenal', 'keindahan', 'pantainya', 'alami', 'dihiasi', 'bebatuan', 'unik', 'menarik', 'â']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>a comfortable square for resting and chatting with family the place is very spacious you can also enjoy culinary activities there is a mosque that is very comfortable for worship clean toilets many separate ablution areas for brothers</t>
+          <t>pantai batu bintang salah pantai letak labuh ratu kabupaten sukabumi jawa barat pantai kenal indah pantai alami hias bebatuan unik tarik</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1035,37 +1035,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bagus,,enak buat liburan bersama keluarga</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>bagusenak buat liburan bersama keluarga</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['bagusenak', 'liburan', 'keluarga']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>bagusenak libur keluarga</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,89 +1077,89 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>Jalanya mantap</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>jalanya mantap</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>jala mantap</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Susah wf.sama signal.,..</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1171,42 +1171,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>A hidden gem, visit at dusk or dawn to watch the sunrise and sunset. It offers one of the best views for sunsets. However, the place is sparsely populated and poorly maintained. The local government should contribute to maintaining and supporting tourism in the Pelabuhan Ratu area.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the pelabuhan ratu area</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the labuh ratu area</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1218,12 +1218,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1233,22 +1233,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1265,42 +1265,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>cocok jalanjalan santai ramai sejuk</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1312,42 +1312,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
+          <t>The view is quite good for enjoying the sunset with the family, at this location port facilities are also being built</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
+          <t>the view is quite good for enjoying the sunset with the family at this location port facilities are also being built</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
+          <t>['the', 'view', 'is', 'quite', 'good', 'for', 'enjoying', 'the', 'sunset', 'with', 'the', 'family', 'at', 'this', 'location', 'port', 'facilities', 'are', 'also', 'being', 'built']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
+          <t>['the', 'view', 'is', 'quite', 'good', 'for', 'enjoying', 'the', 'sunset', 'with', 'the', 'family', 'at', 'this', 'location', 'port', 'facilities', 'are', 'also', 'being', 'built']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
+          <t>the view is quite good for enjoying the sunset with the family at this location port facilities are also being built</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1359,89 +1359,91 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luas,mudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+          <t>Please kesini bkn baru pertama kalinya, tp kesekian kalinyað¥° and aku kesini bkn d hari weekand tp d hari biasa, so aku lebih suka suasana sepi hehehe, jd lebih nikmat liat sunsetnyað+ð+, dahal setiap kesini pasti d jalan tolnya ujan tp oas â¦</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luasmudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+          <t>please kesini bkn baru pertama kalinya tp kesekian kalinyað and aku kesini bkn d hari weekand tp d hari biasa so aku lebih suka suasana sepi hehehe jd lebih nikmat liat sunsetnyað ð dahal setiap kesini pasti d jalan tolnya ujan tp oas â</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['tempat', 'di', 'pelabuhan', 'ratu', 'buat', 'main', 'keluarga', 'cuma', 'jarang', 'tempat', 'untuk', 'berteduh', 'suasana', 'pantai', 'indah', 'banyak', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'lebih', 'di', 'pelihara', 'dan', 'di', 'perindah', 'supaya', 'tempat', 'nya', 'makin', 'bagus']</t>
+          <t>['please', 'kesini', 'bkn', 'baru', 'pertama', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'aku', 'kesini', 'bkn', 'd', 'hari', 'weekand', 'tp', 'd', 'hari', 'biasa', 'so', 'aku', 'lebih', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'lebih', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'setiap', 'kesini', 'pasti', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['pelabuhan', 'ratu', 'main', 'keluarga', 'jarang', 'berteduh', 'suasana', 'pantai', 'indah', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'pelihara', 'perindah', 'nya', 'bagus']</t>
+          <t>['please', 'kesini', 'bkn', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'kesini', 'bkn', 'd', 'weekand', 'tp', 'd', 'so', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'kesini', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>labuh ratu main keluarga jarang teduh suasana pantai indah tukang dagang parkir luasmudah mudah pelihara indah nya bagus</t>
+          <t>please kesini bkn kali tp sekian kali and kesini bkn d weekand tp d so suka suasana sepi hehehe jd nikmat liat sunsetnya dahal kesini d jalan tol ujan tp oas</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Beautiful, neat and clean. Suitable for taking photos for sunset hunters</t>
+          <t>Accommodating thousands of people, with a nice park and toilet facilities...</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>beautiful neat and clean suitable for taking photos for sunset hunters</t>
+          <t>accommodating thousands of people with a nice park and toilet facilities</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['beautiful', 'neat', 'and', 'clean', 'suitable', 'for', 'taking', 'photos', 'for', 'sunset', 'hunters']</t>
+          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['beautiful', 'neat', 'and', 'clean', 'suitable', 'for', 'taking', 'photos', 'for', 'sunset', 'hunters']</t>
+          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>beautiful neat and clean suitable for taking photos for sunset hunters</t>
+          <t>accommodating thousands of people with a nice park and toilet facilities</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1453,42 +1455,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>It's well organized and the street vendors are friendly, but the public facilities like the toilets aren't working.</t>
+          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>its well organized and the street vendors are friendly but the public facilities like the toilets arent working</t>
+          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['its', 'well', 'organized', 'and', 'the', 'street', 'vendors', 'are', 'friendly', 'but', 'the', 'public', 'facilities', 'like', 'the', 'toilets', 'arent', 'working']</t>
+          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['its', 'well', 'organized', 'and', 'the', 'street', 'vendors', 'are', 'friendly', 'but', 'the', 'public', 'facilities', 'like', 'the', 'toilets', 'arent', 'working']</t>
+          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>its well organized and the street vendors are friendly but the public facilities like the toilets arent working</t>
+          <t>kali lapang cangehgarbagus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1500,47 +1502,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya. Detail bajunya bagus banget</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya detail bajunya bagus banget</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['baju', 'baju', 'yg', 'tetsedia', 'untuk', 'di', 'sewakan', 'sangat', 'bagus', 'dan', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'dengan', 'ke', 'inginan', 'saya', 'detail', 'bajunya', 'bagus', 'banget']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['baju', 'baju', 'yg', 'tetsedia', 'sewakan', 'bagus', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'inginan', 'detail', 'bajunya', 'bagus', 'banget']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>baju baju yg tetsedia sewa bagus riquesan buat baju nya sesuai banget ingin detail baju bagus banget</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
@@ -1594,42 +1596,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ga ada pungli tapi kalo mau mesen makanan alangkah baiknya tanya harga dulu soalnya main getok harga</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ga ada pungli tapi kalo mau mesen makanan alangkah baiknya tanya harga dulu soalnya main getok harga</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['ga', 'ada', 'pungli', 'tapi', 'kalo', 'mau', 'mesen', 'makanan', 'alangkah', 'baiknya', 'tanya', 'harga', 'dulu', 'soalnya', 'main', 'getok', 'harga']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['ga', 'pungli', 'kalo', 'mesen', 'makanan', 'alangkah', 'baiknya', 'harga', 'main', 'getok', 'harga']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ga pungli kalo mesen makan alangkah baik harga main getok harga</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1641,42 +1643,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mantappppp</t>
+          <t>Come here during the durian festival, the atmosphere is nice with a direct view of the mountains</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>mantappppp</t>
+          <t>come here during the durian festival the atmosphere is nice with a direct view of the mountains</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['mantappppp']</t>
+          <t>['come', 'here', 'during', 'the', 'durian', 'festival', 'the', 'atmosphere', 'is', 'nice', 'with', 'a', 'direct', 'view', 'of', 'the', 'mountains']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['mantappppp']</t>
+          <t>['come', 'here', 'during', 'the', 'durian', 'festival', 'the', 'atmosphere', 'is', 'nice', 'with', 'a', 'direct', 'view', 'of', 'the', 'mountains']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>mantappppp</t>
+          <t>come here during the durian festival the atmosphere is nice with a direct view of the mountains</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1688,42 +1690,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1735,42 +1737,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1782,89 +1784,89 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Beautiful beach view while waiting for the sunset. For those who want to swim, be careful because large waves and strong currents sometimes come.</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>Air nya hijau ga terurus banyak bentuknya, gazebo udah pada rusak</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>air nya hijau ga terurus banyak bentuknya gazebo udah pada rusak</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'banyak', 'bentuknya', 'gazebo', 'udah', 'pada', 'rusak']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'bentuknya', 'gazebo', 'udah', 'rusak']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>air nya hijau ga urus bentuk gazebo udah rusak</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1876,12 +1878,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
+          <t>Tampil nasyid tingkat provinsi..mantap cah2 Lanang ð¥°ð¥° â¦</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1891,22 +1893,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
+          <t>tampil nasyid tingkat provinsimantap cah lanang ðð â</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>nongki chill and cheap yg cocok pas sunsetan</t>
+          <t>tampil nasyid tingkat provinsimantap cah lanang</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1923,42 +1925,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pantainya bersih, yang terpenting harga makanan dan minuman super murah,parkir jg normal..</t>
+          <t>bagus,,enak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>pantainya bersih yang terpenting harga makanan dan minuman super murahparkir jg normal</t>
+          <t>bagusenak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersih', 'yang', 'terpenting', 'harga', 'makanan', 'dan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
+          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersih', 'terpenting', 'harga', 'makanan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
+          <t>['bagusenak', 'liburan', 'keluarga']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>pantai bersih penting harga makan minum super murahparkir jg normal</t>
+          <t>bagusenak libur keluarga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1970,42 +1972,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A place in Pelabuhan Ratu for families to play, but there are rarely any places to take shelter, a beautiful beach atmosphere, lots of traders, spacious parking, hopefully it will be better maintained and beautified so that the place will be even better.</t>
+          <t>Bagus,dan penduduk nya ramah dan baik2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>a place in pelabuhan ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+          <t>bagusdan penduduk nya ramah dan baik</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>a place in labuh ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
+          <t>bagusdan duduk nya ramah</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2022,7 +2024,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
+          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2032,22 +2034,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
+          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
+          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2064,12 +2066,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kondisi lapang lumayan baik. Track lari sedikit rusak. Lari pagi di hari minggu tidak terlalu padat</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2079,22 +2081,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>kondisi lapang lumayan baik track lari sedikit rusak lari pagi di hari minggu tidak terlalu padat</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['kondisi', 'lapang', 'lumayan', 'baik', 'track', 'lari', 'sedikit', 'rusak', 'lari', 'pagi', 'di', 'hari', 'minggu', 'tidak', 'terlalu', 'padat']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['kondisi', 'lapang', 'lumayan', 'track', 'lari', 'rusak', 'lari', 'pagi', 'minggu', 'padat']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>kondisi lapang lumayan track lari rusak lari pagi minggu padat</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2116,37 +2118,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2158,12 +2160,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Air nya hijau ga terurus banyak bentuknya, gazebo udah pada rusak</t>
+          <t>Konstruksi banyak yang rusak, terutama yang berbatasan dengan pasir. Mungkin tergerus ombak, sementara konstruksi tidak sesuai kondisi. Harusnya dikasih tiang pancang dan fondasi agak dalam. Tidak ada petugas pengawas, jadi orang bebas. Ada â¦</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2173,22 +2175,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>air nya hijau ga terurus banyak bentuknya gazebo udah pada rusak</t>
+          <t>konstruksi banyak yang rusak terutama yang berbatasan dengan pasir mungkin tergerus ombak sementara konstruksi tidak sesuai kondisi harusnya dikasih tiang pancang dan fondasi agak dalam tidak ada petugas pengawas jadi orang bebas ada â</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'banyak', 'bentuknya', 'gazebo', 'udah', 'pada', 'rusak']</t>
+          <t>['konstruksi', 'banyak', 'yang', 'rusak', 'terutama', 'yang', 'berbatasan', 'dengan', 'pasir', 'mungkin', 'tergerus', 'ombak', 'sementara', 'konstruksi', 'tidak', 'sesuai', 'kondisi', 'harusnya', 'dikasih', 'tiang', 'pancang', 'dan', 'fondasi', 'agak', 'dalam', 'tidak', 'ada', 'petugas', 'pengawas', 'jadi', 'orang', 'bebas', 'ada', 'â']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'bentuknya', 'gazebo', 'udah', 'rusak']</t>
+          <t>['konstruksi', 'rusak', 'berbatasan', 'pasir', 'tergerus', 'ombak', 'konstruksi', 'sesuai', 'kondisi', 'dikasih', 'tiang', 'pancang', 'fondasi', 'petugas', 'pengawas', 'orang', 'bebas', 'â']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>air nya hijau ga urus bentuk gazebo udah rusak</t>
+          <t>konstruksi rusak batas pasir gerus ombak konstruksi sesuai kondisi kasih tiang pancang fondasi tugas awas orang bebas</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2205,89 +2207,89 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Alhamdulillahasih bersih, indah apalagi di malam hari, tepat nya di depan majid agung palabuahan ratu, banyak tersedia jajanan juga, ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
+          <t>Ombak nya cukup aman untuk berenang anak2 asalkan tetap di awasi orang tua, makanan tersedia banyak yang berjualan, penginapan depan pantai pun tersedia</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>alhamdulillahasih bersih indah apalagi di malam hari tepat nya di depan majid agung palabuahan ratu banyak tersedia jajanan juga ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
+          <t>ombak nya cukup aman untuk berenang anak asalkan tetap di awasi orang tua makanan tersedia banyak yang berjualan penginapan depan pantai pun tersedia</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['alhamdulillahasih', 'bersih', 'indah', 'apalagi', 'di', 'malam', 'hari', 'tepat', 'nya', 'di', 'depan', 'majid', 'agung', 'palabuahan', 'ratu', 'banyak', 'tersedia', 'jajanan', 'juga', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended', 'lah']</t>
+          <t>['ombak', 'nya', 'cukup', 'aman', 'untuk', 'berenang', 'anak', 'asalkan', 'tetap', 'di', 'awasi', 'orang', 'tua', 'makanan', 'tersedia', 'banyak', 'yang', 'berjualan', 'penginapan', 'depan', 'pantai', 'pun', 'tersedia']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['alhamdulillahasih', 'bersih', 'indah', 'malam', 'nya', 'majid', 'agung', 'palabuahan', 'ratu', 'tersedia', 'jajanan', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended']</t>
+          <t>['ombak', 'nya', 'aman', 'berenang', 'anak', 'awasi', 'orang', 'tua', 'makanan', 'tersedia', 'berjualan', 'penginapan', 'pantai', 'tersedia']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>alhamdulillahasih bersih indah malam nya majid agung palabuahan ratu sedia jajan ubtuk dar santa denfan keluarga rekomended</t>
+          <t>ombak nya aman renang anak awas orang tua makan sedia jual inap pantai sedia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>ECON</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang merupakan salah satu pantai yang terletak di Pelabuhan Ratu, Kabupaten Sukabumi, Jawa Barat. Pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik. â¦</t>
+          <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>pantai batu bintang merupakan salah satu pantai yang terletak di pelabuhan ratu kabupaten sukabumi jawa barat pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik â</t>
+          <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['pantai', 'batu', 'bintang', 'merupakan', 'salah', 'satu', 'pantai', 'yang', 'terletak', 'di', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'ini', 'terkenal', 'dengan', 'keindahan', 'pantainya', 'yang', 'masih', 'alami', 'dan', 'dihiasi', 'dengan', 'bebatuan', 'yang', 'unik', 'dan', 'menarik', 'â']</t>
+          <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['pantai', 'batu', 'bintang', 'salah', 'pantai', 'terletak', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'terkenal', 'keindahan', 'pantainya', 'alami', 'dihiasi', 'bebatuan', 'unik', 'menarik', 'â']</t>
+          <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>pantai batu bintang salah pantai letak labuh ratu kabupaten sukabumi jawa barat pantai kenal indah pantai alami hias bebatuan unik tarik</t>
+          <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2299,12 +2301,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
+          <t>Saungnya pada kotor ga nyaman..padahal tempatnya adem..tolong di perhatikan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2314,22 +2316,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
+          <t>saungnya pada kotor ga nyamanpadahal tempatnya ademtolong di perhatikan</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
+          <t>['saungnya', 'pada', 'kotor', 'ga', 'nyamanpadahal', 'tempatnya', 'ademtolong', 'di', 'perhatikan']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
+          <t>['saungnya', 'kotor', 'ga', 'nyamanpadahal', 'tempatnya', 'ademtolong', 'perhatikan']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
+          <t>saung kotor ga nyamanpadahal tempat ademtolong perhati</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2339,49 +2341,49 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The place is not as big as other town squares, but the atmosphere is calm and beautiful, the mosque is nice, and the parking is quite good.</t>
+          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
+          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
+          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
+          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
+          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2393,609 +2395,45 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
+          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
+          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
+          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
+          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
+          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Taman Bunga Gunung Sumping</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Pantai Twenty Cipatuguran</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Lokasi strategis. Cocok untuk santai cocok untuk anak-anak, cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan, cocok untuk yg tua muda semuanya.. tinggal d jaga bersama sama.. jangan vandalisme dan mengotorinya dgn sampah..okkkk</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>lokasi strategis cocok untuk santai cocok untuk anakanak cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan cocok untuk yg tua muda semuanya tinggal d jaga bersama sama jangan vandalisme dan mengotorinya dgn sampahokkkk</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>['lokasi', 'strategis', 'cocok', 'untuk', 'santai', 'cocok', 'untuk', 'anakanak', 'cocok', 'untuk', 'olahraga', 'subuh', 'dengan', 'udara', 'yg', 'segar', 'dekat', 'pegunungan', 'cocok', 'untuk', 'yg', 'tua', 'muda', 'semuanya', 'tinggal', 'd', 'jaga', 'bersama', 'sama', 'jangan', 'vandalisme', 'dan', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>['lokasi', 'strategis', 'cocok', 'santai', 'cocok', 'anakanak', 'cocok', 'olahraga', 'subuh', 'udara', 'yg', 'segar', 'pegunungan', 'cocok', 'yg', 'tua', 'muda', 'tinggal', 'd', 'jaga', 'vandalisme', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>lokasi strategis cocok santai cocok anakanak cocok olahraga subuh udara yg segar gunung cocok yg tua muda tinggal d jaga vandalisme kotor dgn sampahokkkk</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Pantai Karang Sari</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Pantai Karang Sari</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>The place is nice, the waves are not too big, you can see the sunset which is also beautiful accompanied by a pretty good view ð¥°ð¥° â¦</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>the place is nice the waves are not too big you can see the sunset which is also beautiful accompanied by a pretty good view ðð â</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>['the', 'place', 'is', 'nice', 'the', 'waves', 'are', 'not', 'too', 'big', 'you', 'can', 'see', 'the', 'sunset', 'which', 'is', 'also', 'beautiful', 'accompanied', 'by', 'a', 'pretty', 'good', 'view', 'ðð', 'â']</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>['the', 'place', 'is', 'nice', 'the', 'waves', 'are', 'not', 'too', 'big', 'you', 'can', 'see', 'the', 'sunset', 'which', 'is', 'also', 'beautiful', 'accompanied', 'by', 'a', 'pretty', 'good', 'view', 'ðð', 'â']</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>the place is nice the waves are not too big you can see the sunset which is also beautiful accompanied by a pretty good view</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Pantai Pelabuhan Ratu</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Pantai Batu Bintang</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>kali lapang cangehgarbagus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>PANTAI CIBANGBAN</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Pemandangan baik,bagus,hanya saja tempat ganti pakaian/mandi agak kurang rapih saja</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>pemandangan baikbagushanya saja tempat ganti pakaianmandi agak kurang rapih saja</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>['pemandangan', 'baikbagushanya', 'saja', 'tempat', 'ganti', 'pakaianmandi', 'agak', 'kurang', 'rapih', 'saja']</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>['pemandangan', 'baikbagushanya', 'ganti', 'pakaianmandi', 'rapih']</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>pandang baikbagushanya ganti pakaianmandi rapih</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Tmpatnya lmayan strategis berada di bibir pantai Citepus,sya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>tmpatnya lmayan strategis berada di bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat terpikirkan klw google maps akan mrekomendasikan</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'berada', 'di', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'akan', 'mrekomendasikan']</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>['tmpatnya', 'lmayan', 'strategis', 'bibir', 'pantai', 'citepussya', 'tdak', 'mmiliki', 'foto', 'bngunanannya', 'krna', 'gk', 'smpat', 'terpikirkan', 'klw', 'google', 'maps', 'mrekomendasikan']</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>tmpatnya lmayan strategis bibir pantai citepussya tdak mmiliki foto bngunanannya krna gk smpat pikir klw google maps mrekomendasikan</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Alun - Alun Palabuhanratu</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>['mesjid', 'nya', 'bagus', 'tapi', 'sayang', 'banyak', 'itu', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'itu', 'iya', 'itu', 'apa', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>['mesjid', 'nya', 'bagus', 'sayang', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'iya', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>mesjid nya bagus sayang tuh ih ituloh apasih ya iya ih eta tea naon si arana nyaeta be pokonamah</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>A fairly comfortable place to hang out, but there are no supporting facilities, such as stalls, cafes, toilets, etc.</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>a fairly comfortable place to hang out but there are no supporting facilities such as stalls cafes toilets etc</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>['a', 'fairly', 'comfortable', 'place', 'to', 'hang', 'out', 'but', 'there', 'are', 'no', 'supporting', 'facilities', 'such', 'as', 'stalls', 'cafes', 'toilets', 'etc']</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>['a', 'fairly', 'comfortable', 'place', 'to', 'hang', 'out', 'but', 'there', 'are', 'no', 'supporting', 'facilities', 'such', 'as', 'stalls', 'cafes', 'toilets', 'etc']</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>a fairly comfortable place to hang out but there are no supporting facilities such as stalls cafes toilets etc</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nongki chill and cheap yg cocok pas sunsetan</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -518,37 +518,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -560,89 +560,89 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
+          <t>Sangat buruk. Pasilitas hampir semua ruksak. Tempat bermain anak, tempatmain skate. Bangunan banyak yang sudah hancur</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
+          <t>sangat buruk pasilitas hampir semua ruksak tempat bermain anak tempatmain skate bangunan banyak yang sudah hancur</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['sangat', 'buruk', 'pasilitas', 'hampir', 'semua', 'ruksak', 'tempat', 'bermain', 'anak', 'tempatmain', 'skate', 'bangunan', 'banyak', 'yang', 'sudah', 'hancur']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['buruk', 'pasilitas', 'ruksak', 'bermain', 'anak', 'tempatmain', 'skate', 'bangunan', 'hancur']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
+          <t>buruk pasilitas ruksak main anak tempatmain skate bangun hancur</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>SDH tidak terlalu bagus...kalau malam sangat gelap..bnyk lampu yg mati dan tak diperbaiki..Pedagang Kaki lima nya sih lumayan tertata rapi...</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>sdh tidak terlalu baguskalau malam sangat gelapbnyk lampu yg mati dan tak diperbaikipedagang kaki lima nya sih lumayan tertata rapi</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['sdh', 'tidak', 'terlalu', 'baguskalau', 'malam', 'sangat', 'gelapbnyk', 'lampu', 'yg', 'mati', 'dan', 'tak', 'diperbaikipedagang', 'kaki', 'lima', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['sdh', 'baguskalau', 'malam', 'gelapbnyk', 'lampu', 'yg', 'mati', 'diperbaikipedagang', 'kaki', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>sdh baguskalau malam gelapbnyk lampu yg mati diperbaikipedagang kaki nya sih lumayan tata rapi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -654,42 +654,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
+          <t>mudik dari bandung, ga berani berenang d pantai, jd k kolam renang aja. kolam udah bagus, cuma perlu penegasan d saung2 u/ pngunjung. sewa jg gppa u/ saung, drpd ga jelas nongkrong dmna.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
+          <t>mudik dari bandung ga berani berenang d pantai jd k kolam renang aja kolam udah bagus cuma perlu penegasan d saung u pngunjung sewa jg gppa u saung drpd ga jelas nongkrong dmna</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
+          <t>['mudik', 'dari', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'cuma', 'perlu', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'jelas', 'nongkrong', 'dmna']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
+          <t>['mudik', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'nongkrong', 'dmna']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
+          <t>mudik bandung ga berani renang d pantai jd k kolam renang aja kolam udah bagus tegas d saung u pngunjung sewa jg gppa u saung drpd ga nongkrong dmna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -701,42 +701,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Liburan murmer ,,sewa rumah di pinggir pantai murah cuma sayang banyak yg ngamen.. Repot juga tiap 5 menit mah dikira liburan banyak duit...bilang maaf ga pergi2.. Saran siapin receh yg banyak</t>
+          <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>liburan murmer sewa rumah di pinggir pantai murah cuma sayang banyak yg ngamen repot juga tiap menit mah dikira liburan banyak duitbilang maaf ga pergi saran siapin receh yg banyak</t>
+          <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['liburan', 'murmer', 'sewa', 'rumah', 'di', 'pinggir', 'pantai', 'murah', 'cuma', 'sayang', 'banyak', 'yg', 'ngamen', 'repot', 'juga', 'tiap', 'menit', 'mah', 'dikira', 'liburan', 'banyak', 'duitbilang', 'maaf', 'ga', 'pergi', 'saran', 'siapin', 'receh', 'yg', 'banyak']</t>
+          <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['liburan', 'murmer', 'sewa', 'rumah', 'pinggir', 'pantai', 'murah', 'sayang', 'yg', 'ngamen', 'repot', 'menit', 'mah', 'liburan', 'duitbilang', 'maaf', 'ga', 'pergi', 'saran', 'siapin', 'receh', 'yg']</t>
+          <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>libur murmer sewa rumah pinggir pantai murah sayang yg ngamen repot menit mah libur duitbilang maaf ga pergi saran siapin receh yg</t>
+          <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -748,42 +748,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bagussss</t>
+          <t>The staff are friendly, the beach is nice, but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower... try to take a shower in the toilet near the beach, the toilet near the floor is not suitable â¦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable â</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -800,37 +800,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
+          <t>The place is not as big as other town squares, but the atmosphere is calm and beautiful, the mosque is nice, and the parking is quite good.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
+          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
+          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
+          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
+          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -842,59 +842,59 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
+          <t>Buka setiap hari, tiket masuk kisaran 20 ribu. Tempat nyaman,luas ,kolam cukup banyak ,  kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia. â¦</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
+          <t>buka setiap hari tiket masuk kisaran ribu tempat nyamanluas kolam cukup banyak kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia â</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
+          <t>['buka', 'setiap', 'hari', 'tiket', 'masuk', 'kisaran', 'ribu', 'tempat', 'nyamanluas', 'kolam', 'cukup', 'banyak', 'kantin', 'dan', 'tempat', 'sewa', 'ban', 'juga', 'ada', 'tempat', 'berteduh', 'atau', 'bale', 'juga', 'tersedia', 'â']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
+          <t>['buka', 'tiket', 'masuk', 'kisaran', 'ribu', 'nyamanluas', 'kolam', 'kantin', 'sewa', 'ban', 'berteduh', 'bale', 'tersedia', 'â']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
+          <t>buka tiket masuk kisar ribu nyamanluas kolam kantin sewa ban teduh bale sedia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>ECON</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
+          <t>Sdh mulai banyak kerusakan. Terutama pada area olahraga. Kurang terawat tidak seperti awal awal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -904,22 +904,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
+          <t>sdh mulai banyak kerusakan terutama pada area olahraga kurang terawat tidak seperti awal awal</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
+          <t>['sdh', 'mulai', 'banyak', 'kerusakan', 'terutama', 'pada', 'area', 'olahraga', 'kurang', 'terawat', 'tidak', 'seperti', 'awal', 'awal']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
+          <t>['sdh', 'kerusakan', 'area', 'olahraga', 'terawat']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
+          <t>sdh rusa area olahraga awat</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -936,59 +936,59 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Smile hill Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang merupakan salah satu pantai yang terletak di Pelabuhan Ratu, Kabupaten Sukabumi, Jawa Barat. Pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik. â¦</t>
+          <t>Alhamdulillahasih bersih, indah apalagi di malam hari, tepat nya di depan majid agung palabuahan ratu, banyak tersedia jajanan juga, ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -998,22 +998,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>pantai batu bintang merupakan salah satu pantai yang terletak di pelabuhan ratu kabupaten sukabumi jawa barat pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik â</t>
+          <t>alhamdulillahasih bersih indah apalagi di malam hari tepat nya di depan majid agung palabuahan ratu banyak tersedia jajanan juga ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['pantai', 'batu', 'bintang', 'merupakan', 'salah', 'satu', 'pantai', 'yang', 'terletak', 'di', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'ini', 'terkenal', 'dengan', 'keindahan', 'pantainya', 'yang', 'masih', 'alami', 'dan', 'dihiasi', 'dengan', 'bebatuan', 'yang', 'unik', 'dan', 'menarik', 'â']</t>
+          <t>['alhamdulillahasih', 'bersih', 'indah', 'apalagi', 'di', 'malam', 'hari', 'tepat', 'nya', 'di', 'depan', 'majid', 'agung', 'palabuahan', 'ratu', 'banyak', 'tersedia', 'jajanan', 'juga', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended', 'lah']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['pantai', 'batu', 'bintang', 'salah', 'pantai', 'terletak', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'terkenal', 'keindahan', 'pantainya', 'alami', 'dihiasi', 'bebatuan', 'unik', 'menarik', 'â']</t>
+          <t>['alhamdulillahasih', 'bersih', 'indah', 'malam', 'nya', 'majid', 'agung', 'palabuahan', 'ratu', 'tersedia', 'jajanan', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>pantai batu bintang salah pantai letak labuh ratu kabupaten sukabumi jawa barat pantai kenal indah pantai alami hias bebatuan unik tarik</t>
+          <t>alhamdulillahasih bersih indah malam nya majid agung palabuahan ratu sedia jajan ubtuk dar santa denfan keluarga rekomended</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1030,42 +1030,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>A fairly comfortable place to hang out, but there are no supporting facilities, such as stalls, cafes, toilets, etc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>a fairly comfortable place to hang out but there are no supporting facilities such as stalls cafes toilets etc</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['a', 'fairly', 'comfortable', 'place', 'to', 'hang', 'out', 'but', 'there', 'are', 'no', 'supporting', 'facilities', 'such', 'as', 'stalls', 'cafes', 'toilets', 'etc']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['a', 'fairly', 'comfortable', 'place', 'to', 'hang', 'out', 'but', 'there', 'are', 'no', 'supporting', 'facilities', 'such', 'as', 'stalls', 'cafes', 'toilets', 'etc']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>a fairly comfortable place to hang out but there are no supporting facilities such as stalls cafes toilets etc</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,89 +1077,89 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jalanya mantap</t>
+          <t>The sunset is really beautiful... If it's a holiday, it's definitely really crowded.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jalanya mantap</t>
+          <t>the sunset is really beautiful if its a holiday its definitely really crowded</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['the', 'sunset', 'is', 'really', 'beautiful', 'if', 'its', 'a', 'holiday', 'its', 'definitely', 'really', 'crowded']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['the', 'sunset', 'is', 'really', 'beautiful', 'if', 'its', 'a', 'holiday', 'its', 'definitely', 'really', 'crowded']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jala mantap</t>
+          <t>the sunset is really beautiful if its a holiday its definitely really crowded</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1171,42 +1171,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A hidden gem, visit at dusk or dawn to watch the sunrise and sunset. It offers one of the best views for sunsets. However, the place is sparsely populated and poorly maintained. The local government should contribute to maintaining and supporting tourism in the Pelabuhan Ratu area.</t>
+          <t>Untuk pantainya seperti pantai kebanyakan, dengan ombak besarnya. Sarana di dipantai tersebut kurang nyaman, lesehan buat nginap terbilang mahal, kurang aman buat anak2 bermain air karena minimnya pengawasan petugas.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the pelabuhan ratu area</t>
+          <t>untuk pantainya seperti pantai kebanyakan dengan ombak besarnya sarana di dipantai tersebut kurang nyaman lesehan buat nginap terbilang mahal kurang aman buat anak bermain air karena minimnya pengawasan petugas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
+          <t>['untuk', 'pantainya', 'seperti', 'pantai', 'kebanyakan', 'dengan', 'ombak', 'besarnya', 'sarana', 'di', 'dipantai', 'tersebut', 'kurang', 'nyaman', 'lesehan', 'buat', 'nginap', 'terbilang', 'mahal', 'kurang', 'aman', 'buat', 'anak', 'bermain', 'air', 'karena', 'minimnya', 'pengawasan', 'petugas']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
+          <t>['pantainya', 'pantai', 'kebanyakan', 'ombak', 'besarnya', 'sarana', 'dipantai', 'nyaman', 'lesehan', 'nginap', 'terbilang', 'mahal', 'aman', 'anak', 'bermain', 'air', 'minimnya', 'pengawasan', 'petugas']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the labuh ratu area</t>
+          <t>pantai pantai banyak ombak besar sarana pantai nyaman leseh nginap bilang mahal aman anak main air minim awas tugas</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1218,12 +1218,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
+          <t>Pantai selatan nan indah.perlu penataan.dan pembenahan dengan ke seriusan pemda setempat.agar bisa menjadi obyek wisata andalan.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1233,22 +1233,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
+          <t>pantai selatan nan indahperlu penataandan pembenahan dengan ke seriusan pemda setempatagar bisa menjadi obyek wisata andalan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'dengan', 'ke', 'seriusan', 'pemda', 'setempatagar', 'bisa', 'menjadi', 'obyek', 'wisata', 'andalan']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'seriusan', 'pemda', 'setempatagar', 'obyek', 'wisata', 'andalan']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
+          <t>pantai selatan nan indahperlu penataandan benah serius pemda setempatagar obyek wisata andal</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1265,42 +1265,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+          <t>Wow, don't ask, of course Pelabuhan Ratu beach is the best, from its beautiful atmosphere to its top-notch culinary delights.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+          <t>wow dont ask of course pelabuhan ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>cocok jalanjalan santai ramai sejuk</t>
+          <t>wow dont ask of course labuh ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1312,420 +1312,420 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The view is quite good for enjoying the sunset with the family, at this location port facilities are also being built</t>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>the view is quite good for enjoying the sunset with the family at this location port facilities are also being built</t>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['the', 'view', 'is', 'quite', 'good', 'for', 'enjoying', 'the', 'sunset', 'with', 'the', 'family', 'at', 'this', 'location', 'port', 'facilities', 'are', 'also', 'being', 'built']</t>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['the', 'view', 'is', 'quite', 'good', 'for', 'enjoying', 'the', 'sunset', 'with', 'the', 'family', 'at', 'this', 'location', 'port', 'facilities', 'are', 'also', 'being', 'built']</t>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>the view is quite good for enjoying the sunset with the family at this location port facilities are also being built</t>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Taman Bunga Gunung Sumping</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Good. Parking is free. Toilets are 2,000 yen. Degan is 15,000 yen. No entrance fee. The waves are quite big. There are horses and ATVs.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>good parking is free toilets are yen degan is yen no entrance fee the waves are quite big there are horses and atvs</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>['good', 'parking', 'is', 'free', 'toilets', 'are', 'yen', 'degan', 'is', 'yen', 'no', 'entrance', 'fee', 'the', 'waves', 'are', 'quite', 'big', 'there', 'are', 'horses', 'and', 'atvs']</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>['good', 'parking', 'is', 'free', 'toilets', 'are', 'yen', 'degan', 'is', 'yen', 'no', 'entrance', 'fee', 'the', 'waves', 'are', 'quite', 'big', 'there', 'are', 'horses', 'and', 'atvs']</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>good parking is free toilets are yen degan is yen no entrance fee the waves are quite big there are horses and atvs</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Pantai Citepus</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pantainya bersih, yang terpenting harga makanan dan minuman super murah,parkir jg normal..</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>pantainya bersih yang terpenting harga makanan dan minuman super murahparkir jg normal</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>['pantainya', 'bersih', 'yang', 'terpenting', 'harga', 'makanan', 'dan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>['pantainya', 'bersih', 'terpenting', 'harga', 'makanan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>pantai bersih penting harga makan minum super murahparkir jg normal</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ALUN ALUN GADOBANGKONG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luas,mudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luasmudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>['tempat', 'di', 'pelabuhan', 'ratu', 'buat', 'main', 'keluarga', 'cuma', 'jarang', 'tempat', 'untuk', 'berteduh', 'suasana', 'pantai', 'indah', 'banyak', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'lebih', 'di', 'pelihara', 'dan', 'di', 'perindah', 'supaya', 'tempat', 'nya', 'makin', 'bagus']</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>['pelabuhan', 'ratu', 'main', 'keluarga', 'jarang', 'berteduh', 'suasana', 'pantai', 'indah', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'pelihara', 'perindah', 'nya', 'bagus']</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>labuh ratu main keluarga jarang teduh suasana pantai indah tukang dagang parkir luasmudah mudah pelihara indah nya bagus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Taman Bunga Gunung Sumping</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>cocok jalanjalan santai ramai sejuk</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Pantai Citepus</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>Please kesini bkn baru pertama kalinya, tp kesekian kalinyað¥° and aku kesini bkn d hari weekand tp d hari biasa, so aku lebih suka suasana sepi hehehe, jd lebih nikmat liat sunsetnyað ð , dahal setiap kesini pasti d jalan tolnya ujan tp oas â¦</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>please kesini bkn baru pertama kalinya tp kesekian kalinyað and aku kesini bkn d hari weekand tp d hari biasa so aku lebih suka suasana sepi hehehe jd lebih nikmat liat sunsetnyað ð dahal setiap kesini pasti d jalan tolnya ujan tp oas â</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>['please', 'kesini', 'bkn', 'baru', 'pertama', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'aku', 'kesini', 'bkn', 'd', 'hari', 'weekand', 'tp', 'd', 'hari', 'biasa', 'so', 'aku', 'lebih', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'lebih', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'setiap', 'kesini', 'pasti', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>['please', 'kesini', 'bkn', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'kesini', 'bkn', 'd', 'weekand', 'tp', 'd', 'so', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'kesini', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>please kesini bkn kali tp sekian kali and kesini bkn d weekand tp d so suka suasana sepi hehehe jd nikmat liat sunsetnya dahal kesini d jalan tol ujan tp oas</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Accommodating thousands of people, with a nice park and toilet facilities...</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>accommodating thousands of people with a nice park and toilet facilities</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>accommodating thousands of people with a nice park and toilet facilities</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>kali lapang cangehgarbagus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Pantai Batu Bintang</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CONF</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>CONF</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Di kelola oleh oknum</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CONF</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>di kelola oleh oknum</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>['di', 'kelola', 'oleh', 'oknum']</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>['kelola', 'oknum']</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>kelola oknum</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>CONF</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Pantai Citepus Sukabumi</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Come here during the durian festival, the atmosphere is nice with a direct view of the mountains</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DIGI</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>come here during the durian festival the atmosphere is nice with a direct view of the mountains</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>['come', 'here', 'during', 'the', 'durian', 'festival', 'the', 'atmosphere', 'is', 'nice', 'with', 'a', 'direct', 'view', 'of', 'the', 'mountains']</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>['come', 'here', 'during', 'the', 'durian', 'festival', 'the', 'atmosphere', 'is', 'nice', 'with', 'a', 'direct', 'view', 'of', 'the', 'mountains']</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>come here during the durian festival the atmosphere is nice with a direct view of the mountains</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>DIGI</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Pantai Citepus Sukabumi</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
-        </is>
-      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1737,12 +1737,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>The place is comfortable, cool, the toilet is always clean. The prayer clothes in the mosque are fragrant and clean. There are many vendors selling unique and cheap snacks, and the taste is also delicious.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1752,22 +1752,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1784,89 +1784,89 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>pake produck gk kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Air nya hijau ga terurus banyak bentuknya, gazebo udah pada rusak</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>air nya hijau ga terurus banyak bentuknya gazebo udah pada rusak</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'banyak', 'bentuknya', 'gazebo', 'udah', 'pada', 'rusak']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['air', 'nya', 'hijau', 'ga', 'terurus', 'bentuknya', 'gazebo', 'udah', 'rusak']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>air nya hijau ga urus bentuk gazebo udah rusak</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1878,42 +1878,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tampil nasyid tingkat provinsi..mantap cah2 Lanang ð¥°ð¥° â¦</t>
+          <t>Di kelola oleh oknum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tampil nasyid tingkat provinsimantap cah lanang ðð â</t>
+          <t>di kelola oleh oknum</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
+          <t>['di', 'kelola', 'oleh', 'oknum']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
+          <t>['kelola', 'oknum']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>tampil nasyid tingkat provinsimantap cah lanang</t>
+          <t>kelola oknum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1925,42 +1925,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>bagus,,enak buat liburan bersama keluarga</t>
+          <t>It's well organized and the street vendors are friendly, but the public facilities like the toilets aren't working.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>bagusenak buat liburan bersama keluarga</t>
+          <t>its well organized and the street vendors are friendly but the public facilities like the toilets arent working</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
+          <t>['its', 'well', 'organized', 'and', 'the', 'street', 'vendors', 'are', 'friendly', 'but', 'the', 'public', 'facilities', 'like', 'the', 'toilets', 'arent', 'working']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['bagusenak', 'liburan', 'keluarga']</t>
+          <t>['its', 'well', 'organized', 'and', 'the', 'street', 'vendors', 'are', 'friendly', 'but', 'the', 'public', 'facilities', 'like', 'the', 'toilets', 'arent', 'working']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>bagusenak libur keluarga</t>
+          <t>its well organized and the street vendors are friendly but the public facilities like the toilets arent working</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1972,42 +1972,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bagus,dan penduduk nya ramah dan baik2</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>bagusdan penduduk nya ramah dan baik</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>bagusdan duduk nya ramah</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
+          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2034,22 +2034,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
+          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
+          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2066,42 +2066,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2113,42 +2113,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2160,136 +2160,136 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Konstruksi banyak yang rusak, terutama yang berbatasan dengan pasir. Mungkin tergerus ombak, sementara konstruksi tidak sesuai kondisi. Harusnya dikasih tiang pancang dan fondasi agak dalam. Tidak ada petugas pengawas, jadi orang bebas. Ada â¦</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>konstruksi banyak yang rusak terutama yang berbatasan dengan pasir mungkin tergerus ombak sementara konstruksi tidak sesuai kondisi harusnya dikasih tiang pancang dan fondasi agak dalam tidak ada petugas pengawas jadi orang bebas ada â</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['konstruksi', 'banyak', 'yang', 'rusak', 'terutama', 'yang', 'berbatasan', 'dengan', 'pasir', 'mungkin', 'tergerus', 'ombak', 'sementara', 'konstruksi', 'tidak', 'sesuai', 'kondisi', 'harusnya', 'dikasih', 'tiang', 'pancang', 'dan', 'fondasi', 'agak', 'dalam', 'tidak', 'ada', 'petugas', 'pengawas', 'jadi', 'orang', 'bebas', 'ada', 'â']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['konstruksi', 'rusak', 'berbatasan', 'pasir', 'tergerus', 'ombak', 'konstruksi', 'sesuai', 'kondisi', 'dikasih', 'tiang', 'pancang', 'fondasi', 'petugas', 'pengawas', 'orang', 'bebas', 'â']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>konstruksi rusak batas pasir gerus ombak konstruksi sesuai kondisi kasih tiang pancang fondasi tugas awas orang bebas</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ombak nya cukup aman untuk berenang anak2 asalkan tetap di awasi orang tua, makanan tersedia banyak yang berjualan, penginapan depan pantai pun tersedia</t>
+          <t>Kotor alun alunnya banyak sampah...mampir ke masjid di alun2 bersih dan nyaman</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ombak nya cukup aman untuk berenang anak asalkan tetap di awasi orang tua makanan tersedia banyak yang berjualan penginapan depan pantai pun tersedia</t>
+          <t>kotor alun alunnya banyak sampahmampir ke masjid di alun bersih dan nyaman</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['ombak', 'nya', 'cukup', 'aman', 'untuk', 'berenang', 'anak', 'asalkan', 'tetap', 'di', 'awasi', 'orang', 'tua', 'makanan', 'tersedia', 'banyak', 'yang', 'berjualan', 'penginapan', 'depan', 'pantai', 'pun', 'tersedia']</t>
+          <t>['kotor', 'alun', 'alunnya', 'banyak', 'sampahmampir', 'ke', 'masjid', 'di', 'alun', 'bersih', 'dan', 'nyaman']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['ombak', 'nya', 'aman', 'berenang', 'anak', 'awasi', 'orang', 'tua', 'makanan', 'tersedia', 'berjualan', 'penginapan', 'pantai', 'tersedia']</t>
+          <t>['kotor', 'alun', 'alunnya', 'sampahmampir', 'masjid', 'alun', 'bersih', 'nyaman']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ombak nya aman renang anak awas orang tua makan sedia jual inap pantai sedia</t>
+          <t>kotor alun alun sampahmampir masjid alun bersih nyaman</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
+          <t>bagus,,enak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
+          <t>bagusenak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
+          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
+          <t>['bagusenak', 'liburan', 'keluarga']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
+          <t>bagusenak libur keluarga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Saungnya pada kotor ga nyaman..padahal tempatnya adem..tolong di perhatikan</t>
+          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2316,22 +2316,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>saungnya pada kotor ga nyamanpadahal tempatnya ademtolong di perhatikan</t>
+          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['saungnya', 'pada', 'kotor', 'ga', 'nyamanpadahal', 'tempatnya', 'ademtolong', 'di', 'perhatikan']</t>
+          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['saungnya', 'kotor', 'ga', 'nyamanpadahal', 'tempatnya', 'ademtolong', 'perhatikan']</t>
+          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>saung kotor ga nyamanpadahal tempat ademtolong perhati</t>
+          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2348,12 +2348,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+          <t>Bagus,dan penduduk nya ramah dan baik2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2363,22 +2363,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+          <t>bagusdan penduduk nya ramah dan baik</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
+          <t>bagusdan duduk nya ramah</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2395,45 +2395,703 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Jangilus Monument</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Tugu nyah udah di pindahin</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>tugu nyah udah di pindahin</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>tugu nyah udah pindahin</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>GEND</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>GEND</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PANTAI CIBANGBAN</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Tidak nyaman oleh orngÂ² yg menyewakan tempat untuk istirahat/baleÂ² Krn mahal Dan sangat perhitungan...di sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d Carikan tmpt istrht Krn mrk welcome dan baikÂ².</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>tidak nyaman oleh orngâ² yg menyewakan tempat untuk istirahatbaleâ² krn mahal dan sangat perhitungandi sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d carikan tmpt istrht krn mrk welcome dan baikâ²</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>['tidak', 'nyaman', 'oleh', 'orngâ²', 'yg', 'menyewakan', 'tempat', 'untuk', 'istirahatbaleâ²', 'krn', 'mahal', 'dan', 'sangat', 'perhitungandi', 'sarankan', 'jika', 'berwisata', 'ke', 'sana', 'bisa', 'meminta', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'untuk', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'dan', 'baikâ²']</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>['nyaman', 'orngâ²', 'yg', 'menyewakan', 'istirahatbaleâ²', 'krn', 'mahal', 'perhitungandi', 'sarankan', 'berwisata', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'baikâ²']</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>nyaman orng yg sewa istirahatbale krn mahal perhitungandi saran wisata bantu jasa kpd jaga pintu masuk utama d cari tmpt istrht krn mrk welcome baik</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Pantai Karang Sari</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>['mesjid', 'nya', 'bagus', 'tapi', 'sayang', 'banyak', 'itu', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'itu', 'iya', 'itu', 'apa', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>['mesjid', 'nya', 'bagus', 'sayang', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'iya', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>mesjid nya bagus sayang tuh ih ituloh apasih ya iya ih eta tea naon si arana nyaeta be pokonamah</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>The 77th HAB ceremony at the Sukabumi Regency Ministry of Religious Affairs Office. Atmosphere in traditional attire.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DIGI</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>DIGI</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ALUN ALUN GADOBANGKONG</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Konstruksi banyak yang rusak, terutama yang berbatasan dengan pasir. Mungkin tergerus ombak, sementara konstruksi tidak sesuai kondisi. Harusnya dikasih tiang pancang dan fondasi agak dalam. Tidak ada petugas pengawas, jadi orang bebas. Ada â¦</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>konstruksi banyak yang rusak terutama yang berbatasan dengan pasir mungkin tergerus ombak sementara konstruksi tidak sesuai kondisi harusnya dikasih tiang pancang dan fondasi agak dalam tidak ada petugas pengawas jadi orang bebas ada â</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>['konstruksi', 'banyak', 'yang', 'rusak', 'terutama', 'yang', 'berbatasan', 'dengan', 'pasir', 'mungkin', 'tergerus', 'ombak', 'sementara', 'konstruksi', 'tidak', 'sesuai', 'kondisi', 'harusnya', 'dikasih', 'tiang', 'pancang', 'dan', 'fondasi', 'agak', 'dalam', 'tidak', 'ada', 'petugas', 'pengawas', 'jadi', 'orang', 'bebas', 'ada', 'â']</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>['konstruksi', 'rusak', 'berbatasan', 'pasir', 'tergerus', 'ombak', 'konstruksi', 'sesuai', 'kondisi', 'dikasih', 'tiang', 'pancang', 'fondasi', 'petugas', 'pengawas', 'orang', 'bebas', 'â']</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>konstruksi rusak batas pasir gerus ombak konstruksi sesuai kondisi kasih tiang pancang fondasi tugas awas orang bebas</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Lokasi yg nyaman, bangunannya salah satu yg tahan gempa dengan rujukan dari BNPB. Mudah di akses dari jalan raya. Bisa menginap dengan harga yg terjangkau. Menjadi pusat penelitian ketahanan gempa.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>lokasi yg nyaman bangunannya salah satu yg tahan gempa dengan rujukan dari bnpb mudah di akses dari jalan raya bisa menginap dengan harga yg terjangkau menjadi pusat penelitian ketahanan gempa</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'satu', 'yg', 'tahan', 'gempa', 'dengan', 'rujukan', 'dari', 'bnpb', 'mudah', 'di', 'akses', 'dari', 'jalan', 'raya', 'bisa', 'menginap', 'dengan', 'harga', 'yg', 'terjangkau', 'menjadi', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'yg', 'tahan', 'gempa', 'rujukan', 'bnpb', 'mudah', 'akses', 'jalan', 'raya', 'menginap', 'harga', 'yg', 'terjangkau', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>lokasi yg nyaman bangun salah yg tahan gempa rujuk bnpb mudah akses jalan raya inap harga yg jangkau pusat teliti tahan gempa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Pantai Citepus</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Pasir pantai tidak tajam, lumayan bersih, banyak toilet, kamar mandi dan musola. Harga makanan dan minuman sesuai kantong.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>pasir pantai tidak tajam lumayan bersih banyak toilet kamar mandi dan musola harga makanan dan minuman sesuai kantong</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>['pasir', 'pantai', 'tidak', 'tajam', 'lumayan', 'bersih', 'banyak', 'toilet', 'kamar', 'mandi', 'dan', 'musola', 'harga', 'makanan', 'dan', 'minuman', 'sesuai', 'kantong']</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>['pasir', 'pantai', 'tajam', 'lumayan', 'bersih', 'toilet', 'kamar', 'mandi', 'musola', 'harga', 'makanan', 'minuman', 'sesuai', 'kantong']</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>pasir pantai tajam lumayan bersih toilet kamar mandi musola harga makan minum sesuai kantong</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Tempat nya strategis untuk istrahat. Setelah solat d mesjid, bisa jajan dan mknan dlu, bnyak tempat jajannya, dekat dgn KFC, ATM dan toserba juga...ð â¦</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DIGI</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>tempat nya strategis untuk istrahat setelah solat d mesjid bisa jajan dan mknan dlu bnyak tempat jajannya dekat dgn kfc atm dan toserba jugað â</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>['tempat', 'nya', 'strategis', 'untuk', 'istrahat', 'setelah', 'solat', 'd', 'mesjid', 'bisa', 'jajan', 'dan', 'mknan', 'dlu', 'bnyak', 'tempat', 'jajannya', 'dekat', 'dgn', 'kfc', 'atm', 'dan', 'toserba', 'jugað', 'â']</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>['nya', 'strategis', 'istrahat', 'solat', 'd', 'mesjid', 'jajan', 'mknan', 'dlu', 'bnyak', 'jajannya', 'dgn', 'kfc', 'atm', 'toserba', 'jugað', 'â']</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>nya strategis istrahat solat d mesjid jajan mknan dlu bnyak jajan dgn kfc atm toserba juga</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>DIGI</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Pantai Karang Sari</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Pantai Batu Bintang</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>NEUT</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>NEUT</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,42 +513,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Available milk, diapers, baby supplies, toiletries and staple foods and smashed chicken</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -560,42 +560,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sangat buruk. Pasilitas hampir semua ruksak. Tempat bermain anak, tempatmain skate. Bangunan banyak yang sudah hancur</t>
+          <t>Nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak  mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang  sebab ada oknum pedagang terutama pedagang  gorengan ada bapa bapa yang menjual /mencampur gorengan sisa hari kemarinnya,yang diangetin lagi hingga  terasa keras dan basi.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sangat buruk pasilitas hampir semua ruksak tempat bermain anak tempatmain skate bangunan banyak yang sudah hancur</t>
+          <t>nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang sebab ada oknum pedagang terutama pedagang gorengan ada bapa bapa yang menjual mencampur gorengan sisa hari kemarinnyayang diangetin lagi hingga terasa keras dan basi</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['sangat', 'buruk', 'pasilitas', 'hampir', 'semua', 'ruksak', 'tempat', 'bermain', 'anak', 'tempatmain', 'skate', 'bangunan', 'banyak', 'yang', 'sudah', 'hancur']</t>
+          <t>['nyaman', 'untuk', 'nyari', 'kuliner', 'cuma', 'tolong', 'ditertibkan', 'para', 'pedagangnya', 'supaya', 'tidak', 'mengganggu', 'lalu', 'lintas', 'juga', 'rasanya', 'harus', 'ada', 'pembinaan', 'pada', 'para', 'pedagang', 'sebab', 'ada', 'oknum', 'pedagang', 'terutama', 'pedagang', 'gorengan', 'ada', 'bapa', 'bapa', 'yang', 'menjual', 'mencampur', 'gorengan', 'sisa', 'hari', 'kemarinnyayang', 'diangetin', 'lagi', 'hingga', 'terasa', 'keras', 'dan', 'basi']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['buruk', 'pasilitas', 'ruksak', 'bermain', 'anak', 'tempatmain', 'skate', 'bangunan', 'hancur']</t>
+          <t>['nyaman', 'nyari', 'kuliner', 'tolong', 'ditertibkan', 'pedagangnya', 'mengganggu', 'lintas', 'pembinaan', 'pedagang', 'oknum', 'pedagang', 'pedagang', 'gorengan', 'bapa', 'bapa', 'menjual', 'mencampur', 'gorengan', 'sisa', 'kemarinnyayang', 'diangetin', 'keras', 'basi']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>buruk pasilitas ruksak main anak tempatmain skate bangun hancur</t>
+          <t>nyaman nyari kuliner tolong tertib dagang ganggu lintas bina dagang oknum dagang dagang goreng bapa bapa jual campur goreng sisa kemarinnyayang diangetin keras basi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SDH tidak terlalu bagus...kalau malam sangat gelap..bnyk lampu yg mati dan tak diperbaiki..Pedagang Kaki lima nya sih lumayan tertata rapi...</t>
+          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -622,22 +622,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>sdh tidak terlalu baguskalau malam sangat gelapbnyk lampu yg mati dan tak diperbaikipedagang kaki lima nya sih lumayan tertata rapi</t>
+          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['sdh', 'tidak', 'terlalu', 'baguskalau', 'malam', 'sangat', 'gelapbnyk', 'lampu', 'yg', 'mati', 'dan', 'tak', 'diperbaikipedagang', 'kaki', 'lima', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
+          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['sdh', 'baguskalau', 'malam', 'gelapbnyk', 'lampu', 'yg', 'mati', 'diperbaikipedagang', 'kaki', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
+          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>sdh baguskalau malam gelapbnyk lampu yg mati diperbaikipedagang kaki nya sih lumayan tata rapi</t>
+          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -647,49 +647,49 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mudik dari bandung, ga berani berenang d pantai, jd k kolam renang aja. kolam udah bagus, cuma perlu penegasan d saung2 u/ pngunjung. sewa jg gppa u/ saung, drpd ga jelas nongkrong dmna.</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>mudik dari bandung ga berani berenang d pantai jd k kolam renang aja kolam udah bagus cuma perlu penegasan d saung u pngunjung sewa jg gppa u saung drpd ga jelas nongkrong dmna</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['mudik', 'dari', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'cuma', 'perlu', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'jelas', 'nongkrong', 'dmna']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['mudik', 'bandung', 'ga', 'berani', 'berenang', 'd', 'pantai', 'jd', 'k', 'kolam', 'renang', 'aja', 'kolam', 'udah', 'bagus', 'penegasan', 'd', 'saung', 'u', 'pngunjung', 'sewa', 'jg', 'gppa', 'u', 'saung', 'drpd', 'ga', 'nongkrong', 'dmna']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>mudik bandung ga berani renang d pantai jd k kolam renang aja kolam udah bagus tegas d saung u pngunjung sewa jg gppa u saung drpd ga nongkrong dmna</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -701,42 +701,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
+          <t>Pagi,siang mlm ramai pedagang smua murah meriah. Buat nongkrong smua usia jgn lupa silakan berkunjung, anda pasti suka....</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
+          <t>pagisiang mlm ramai pedagang smua murah meriah buat nongkrong smua usia jgn lupa silakan berkunjung anda pasti suka</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
+          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'buat', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'anda', 'pasti', 'suka']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
+          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'suka']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
+          <t>pagisiang mlm ramai dagang smua murah riah nongkrong smua usia jgn lupa sila kunjung suka</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -748,12 +748,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The staff are friendly, the beach is nice, but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower... try to take a shower in the toilet near the beach, the toilet near the floor is not suitable â¦</t>
+          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -763,22 +763,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable â</t>
+          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable</t>
+          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -788,49 +788,49 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The place is not as big as other town squares, but the atmosphere is calm and beautiful, the mosque is nice, and the parking is quite good.</t>
+          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
+          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
+          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
+          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
+          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -842,89 +842,89 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Buka setiap hari, tiket masuk kisaran 20 ribu. Tempat nyaman,luas ,kolam cukup banyak ,  kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia. â¦</t>
+          <t>Bagussss</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>buka setiap hari tiket masuk kisaran ribu tempat nyamanluas kolam cukup banyak kantin dan tempat sewa ban juga ada tempat berteduh atau bale juga tersedia â</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['buka', 'setiap', 'hari', 'tiket', 'masuk', 'kisaran', 'ribu', 'tempat', 'nyamanluas', 'kolam', 'cukup', 'banyak', 'kantin', 'dan', 'tempat', 'sewa', 'ban', 'juga', 'ada', 'tempat', 'berteduh', 'atau', 'bale', 'juga', 'tersedia', 'â']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['buka', 'tiket', 'masuk', 'kisaran', 'ribu', 'nyamanluas', 'kolam', 'kantin', 'sewa', 'ban', 'berteduh', 'bale', 'tersedia', 'â']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>buka tiket masuk kisar ribu nyamanluas kolam kantin sewa ban teduh bale sedia</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sdh mulai banyak kerusakan. Terutama pada area olahraga. Kurang terawat tidak seperti awal awal</t>
+          <t>Pantai selatan nan indah.perlu penataan.dan pembenahan dengan ke seriusan pemda setempat.agar bisa menjadi obyek wisata andalan.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>sdh mulai banyak kerusakan terutama pada area olahraga kurang terawat tidak seperti awal awal</t>
+          <t>pantai selatan nan indahperlu penataandan pembenahan dengan ke seriusan pemda setempatagar bisa menjadi obyek wisata andalan</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['sdh', 'mulai', 'banyak', 'kerusakan', 'terutama', 'pada', 'area', 'olahraga', 'kurang', 'terawat', 'tidak', 'seperti', 'awal', 'awal']</t>
+          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'dengan', 'ke', 'seriusan', 'pemda', 'setempatagar', 'bisa', 'menjadi', 'obyek', 'wisata', 'andalan']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['sdh', 'kerusakan', 'area', 'olahraga', 'terawat']</t>
+          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'seriusan', 'pemda', 'setempatagar', 'obyek', 'wisata', 'andalan']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>sdh rusa area olahraga awat</t>
+          <t>pantai selatan nan indahperlu penataandan benah serius pemda setempatagar obyek wisata andal</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -936,42 +936,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
+          <t>Tempat nya strategis untuk istrahat. Setelah solat d mesjid, bisa jajan dan mknan dlu, bnyak tempat jajannya, dekat dgn KFC, ATM dan toserba juga...ð â¦</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
+          <t>tempat nya strategis untuk istrahat setelah solat d mesjid bisa jajan dan mknan dlu bnyak tempat jajannya dekat dgn kfc atm dan toserba jugað â</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
+          <t>['tempat', 'nya', 'strategis', 'untuk', 'istrahat', 'setelah', 'solat', 'd', 'mesjid', 'bisa', 'jajan', 'dan', 'mknan', 'dlu', 'bnyak', 'tempat', 'jajannya', 'dekat', 'dgn', 'kfc', 'atm', 'dan', 'toserba', 'jugað', 'â']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
+          <t>['nya', 'strategis', 'istrahat', 'solat', 'd', 'mesjid', 'jajan', 'mknan', 'dlu', 'bnyak', 'jajannya', 'dgn', 'kfc', 'atm', 'toserba', 'jugað', 'â']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
+          <t>nya strategis istrahat solat d mesjid jajan mknan dlu bnyak jajan dgn kfc atm toserba juga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -983,12 +983,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alhamdulillahasih bersih, indah apalagi di malam hari, tepat nya di depan majid agung palabuahan ratu, banyak tersedia jajanan juga, ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
+          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -998,22 +998,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>alhamdulillahasih bersih indah apalagi di malam hari tepat nya di depan majid agung palabuahan ratu banyak tersedia jajanan juga ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
+          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['alhamdulillahasih', 'bersih', 'indah', 'apalagi', 'di', 'malam', 'hari', 'tepat', 'nya', 'di', 'depan', 'majid', 'agung', 'palabuahan', 'ratu', 'banyak', 'tersedia', 'jajanan', 'juga', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended', 'lah']</t>
+          <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['alhamdulillahasih', 'bersih', 'indah', 'malam', 'nya', 'majid', 'agung', 'palabuahan', 'ratu', 'tersedia', 'jajanan', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended']</t>
+          <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>alhamdulillahasih bersih indah malam nya majid agung palabuahan ratu sedia jajan ubtuk dar santa denfan keluarga rekomended</t>
+          <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1030,42 +1030,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A fairly comfortable place to hang out, but there are no supporting facilities, such as stalls, cafes, toilets, etc.</t>
+          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>a fairly comfortable place to hang out but there are no supporting facilities such as stalls cafes toilets etc</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['a', 'fairly', 'comfortable', 'place', 'to', 'hang', 'out', 'but', 'there', 'are', 'no', 'supporting', 'facilities', 'such', 'as', 'stalls', 'cafes', 'toilets', 'etc']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['a', 'fairly', 'comfortable', 'place', 'to', 'hang', 'out', 'but', 'there', 'are', 'no', 'supporting', 'facilities', 'such', 'as', 'stalls', 'cafes', 'toilets', 'etc']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>a fairly comfortable place to hang out but there are no supporting facilities such as stalls cafes toilets etc</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,42 +1077,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Smile hill Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The sunset is really beautiful... If it's a holiday, it's definitely really crowded.</t>
+          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>the sunset is really beautiful if its a holiday its definitely really crowded</t>
+          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['the', 'sunset', 'is', 'really', 'beautiful', 'if', 'its', 'a', 'holiday', 'its', 'definitely', 'really', 'crowded']</t>
+          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['the', 'sunset', 'is', 'really', 'beautiful', 'if', 'its', 'a', 'holiday', 'its', 'definitely', 'really', 'crowded']</t>
+          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>the sunset is really beautiful if its a holiday its definitely really crowded</t>
+          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1124,12 +1124,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
+          <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1139,22 +1139,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
+          <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
+          <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
+          <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
+          <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1171,42 +1171,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Untuk pantainya seperti pantai kebanyakan, dengan ombak besarnya. Sarana di dipantai tersebut kurang nyaman, lesehan buat nginap terbilang mahal, kurang aman buat anak2 bermain air karena minimnya pengawasan petugas.</t>
+          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>untuk pantainya seperti pantai kebanyakan dengan ombak besarnya sarana di dipantai tersebut kurang nyaman lesehan buat nginap terbilang mahal kurang aman buat anak bermain air karena minimnya pengawasan petugas</t>
+          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['untuk', 'pantainya', 'seperti', 'pantai', 'kebanyakan', 'dengan', 'ombak', 'besarnya', 'sarana', 'di', 'dipantai', 'tersebut', 'kurang', 'nyaman', 'lesehan', 'buat', 'nginap', 'terbilang', 'mahal', 'kurang', 'aman', 'buat', 'anak', 'bermain', 'air', 'karena', 'minimnya', 'pengawasan', 'petugas']</t>
+          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['pantainya', 'pantai', 'kebanyakan', 'ombak', 'besarnya', 'sarana', 'dipantai', 'nyaman', 'lesehan', 'nginap', 'terbilang', 'mahal', 'aman', 'anak', 'bermain', 'air', 'minimnya', 'pengawasan', 'petugas']</t>
+          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>pantai pantai banyak ombak besar sarana pantai nyaman leseh nginap bilang mahal aman anak main air minim awas tugas</t>
+          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1218,42 +1218,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pantai selatan nan indah.perlu penataan.dan pembenahan dengan ke seriusan pemda setempat.agar bisa menjadi obyek wisata andalan.</t>
+          <t>Pantainya bersih, yang terpenting harga makanan dan minuman super murah,parkir jg normal..</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>pantai selatan nan indahperlu penataandan pembenahan dengan ke seriusan pemda setempatagar bisa menjadi obyek wisata andalan</t>
+          <t>pantainya bersih yang terpenting harga makanan dan minuman super murahparkir jg normal</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'dengan', 'ke', 'seriusan', 'pemda', 'setempatagar', 'bisa', 'menjadi', 'obyek', 'wisata', 'andalan']</t>
+          <t>['pantainya', 'bersih', 'yang', 'terpenting', 'harga', 'makanan', 'dan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'seriusan', 'pemda', 'setempatagar', 'obyek', 'wisata', 'andalan']</t>
+          <t>['pantainya', 'bersih', 'terpenting', 'harga', 'makanan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>pantai selatan nan indahperlu penataandan benah serius pemda setempatagar obyek wisata andal</t>
+          <t>pantai bersih penting harga makan minum super murahparkir jg normal</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1265,94 +1265,94 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wow, don't ask, of course Pelabuhan Ratu beach is the best, from its beautiful atmosphere to its top-notch culinary delights.</t>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>wow dont ask of course pelabuhan ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>wow dont ask of course labuh ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>Pantai Batu Bintang merupakan salah satu pantai yang terletak di Pelabuhan Ratu, Kabupaten Sukabumi, Jawa Barat. Pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik. â¦</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>pantai batu bintang merupakan salah satu pantai yang terletak di pelabuhan ratu kabupaten sukabumi jawa barat pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik â</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+          <t>['pantai', 'batu', 'bintang', 'merupakan', 'salah', 'satu', 'pantai', 'yang', 'terletak', 'di', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'ini', 'terkenal', 'dengan', 'keindahan', 'pantainya', 'yang', 'masih', 'alami', 'dan', 'dihiasi', 'dengan', 'bebatuan', 'yang', 'unik', 'dan', 'menarik', 'â']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+          <t>['pantai', 'batu', 'bintang', 'salah', 'pantai', 'terletak', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'terkenal', 'keindahan', 'pantainya', 'alami', 'dihiasi', 'bebatuan', 'unik', 'menarik', 'â']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+          <t>pantai batu bintang salah pantai letak labuh ratu kabupaten sukabumi jawa barat pantai kenal indah pantai alami hias bebatuan unik tarik</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
@@ -1406,42 +1406,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>Wow, don't ask, of course Pelabuhan Ratu beach is the best, from its beautiful atmosphere to its top-notch culinary delights.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>wow dont ask of course pelabuhan ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>wow dont ask of course labuh ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1453,12 +1453,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Good. Parking is free. Toilets are 2,000 yen. Degan is 15,000 yen. No entrance fee. The waves are quite big. There are horses and ATVs.</t>
+          <t>The toilets are dirty and only want money and almost every location is full of rubbish, even though it's a shame that the place is as neat as this but it's not well maintained.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1468,22 +1468,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>good parking is free toilets are yen degan is yen no entrance fee the waves are quite big there are horses and atvs</t>
+          <t>the toilets are dirty and only want money and almost every location is full of rubbish even though its a shame that the place is as neat as this but its not well maintained</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['good', 'parking', 'is', 'free', 'toilets', 'are', 'yen', 'degan', 'is', 'yen', 'no', 'entrance', 'fee', 'the', 'waves', 'are', 'quite', 'big', 'there', 'are', 'horses', 'and', 'atvs']</t>
+          <t>['the', 'toilets', 'are', 'dirty', 'and', 'only', 'want', 'money', 'and', 'almost', 'every', 'location', 'is', 'full', 'of', 'rubbish', 'even', 'though', 'its', 'a', 'shame', 'that', 'the', 'place', 'is', 'as', 'neat', 'as', 'this', 'but', 'its', 'not', 'well', 'maintained']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['good', 'parking', 'is', 'free', 'toilets', 'are', 'yen', 'degan', 'is', 'yen', 'no', 'entrance', 'fee', 'the', 'waves', 'are', 'quite', 'big', 'there', 'are', 'horses', 'and', 'atvs']</t>
+          <t>['the', 'toilets', 'are', 'dirty', 'and', 'only', 'want', 'money', 'and', 'almost', 'every', 'location', 'is', 'full', 'of', 'rubbish', 'even', 'though', 'its', 'a', 'shame', 'that', 'the', 'place', 'is', 'as', 'neat', 'as', 'this', 'but', 'its', 'not', 'well', 'maintained']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>good parking is free toilets are yen degan is yen no entrance fee the waves are quite big there are horses and atvs</t>
+          <t>the toilets are dirty and only want money and almost every location is full of rubbish even though its a shame that the place is as neat as this but its not well maintained</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1500,42 +1500,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pantainya bersih, yang terpenting harga makanan dan minuman super murah,parkir jg normal..</t>
+          <t>Lebih rapih dan tertata, untuk saat ini belum dibuka masih dipagar seng</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>pantainya bersih yang terpenting harga makanan dan minuman super murahparkir jg normal</t>
+          <t>lebih rapih dan tertata untuk saat ini belum dibuka masih dipagar seng</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersih', 'yang', 'terpenting', 'harga', 'makanan', 'dan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
+          <t>['lebih', 'rapih', 'dan', 'tertata', 'untuk', 'saat', 'ini', 'belum', 'dibuka', 'masih', 'dipagar', 'seng']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersih', 'terpenting', 'harga', 'makanan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
+          <t>['rapih', 'tertata', 'dibuka', 'dipagar', 'seng']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>pantai bersih penting harga makan minum super murahparkir jg normal</t>
+          <t>rapih tata buka pagar seng</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1547,59 +1547,59 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luas,mudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+          <t>Karang Pamulang Beach, Bunga Ayu Seaside Resort Is a friendly, beautiful beach</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luasmudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+          <t>karang pamulang beach bunga ayu seaside resort is a friendly beautiful beach</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['tempat', 'di', 'pelabuhan', 'ratu', 'buat', 'main', 'keluarga', 'cuma', 'jarang', 'tempat', 'untuk', 'berteduh', 'suasana', 'pantai', 'indah', 'banyak', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'lebih', 'di', 'pelihara', 'dan', 'di', 'perindah', 'supaya', 'tempat', 'nya', 'makin', 'bagus']</t>
+          <t>['karang', 'pamulang', 'beach', 'bunga', 'ayu', 'seaside', 'resort', 'is', 'a', 'friendly', 'beautiful', 'beach']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['pelabuhan', 'ratu', 'main', 'keluarga', 'jarang', 'berteduh', 'suasana', 'pantai', 'indah', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'pelihara', 'perindah', 'nya', 'bagus']</t>
+          <t>['karang', 'pamulang', 'beach', 'bunga', 'ayu', 'seaside', 'resort', 'is', 'a', 'friendly', 'beautiful', 'beach']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>labuh ratu main keluarga jarang teduh suasana pantai indah tukang dagang parkir luasmudah mudah pelihara indah nya bagus</t>
+          <t>karang pamulang beach bunga ayu seaside resort is a friendly beautiful beach</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
+          <t>Tampil nasyid tingkat provinsi..mantap cah2 Lanang ð¥°ð¥° â¦</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1609,22 +1609,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
+          <t>tampil nasyid tingkat provinsimantap cah lanang ðð â</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
+          <t>tampil nasyid tingkat provinsimantap cah lanang</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1641,42 +1641,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+          <t>Inhale the comfortable atmosphere of Sukabumi's southern coast for just a day off</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+          <t>inhale the comfortable atmosphere of sukabumis southern coast for just a day off</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+          <t>['inhale', 'the', 'comfortable', 'atmosphere', 'of', 'sukabumis', 'southern', 'coast', 'for', 'just', 'a', 'day', 'off']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+          <t>['inhale', 'the', 'comfortable', 'atmosphere', 'of', 'sukabumis', 'southern', 'coast', 'for', 'just', 'a', 'day', 'off']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>cocok jalanjalan santai ramai sejuk</t>
+          <t>inhale the comfortable atmosphere of sukabumis southern coast for just a day off</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1688,44 +1688,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Please kesini bkn baru pertama kalinya, tp kesekian kalinyað¥° and aku kesini bkn d hari weekand tp d hari biasa, so aku lebih suka suasana sepi hehehe, jd lebih nikmat liat sunsetnyað-ð-, dahal setiap kesini pasti d jalan tolnya ujan tp oas â¦</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>please kesini bkn baru pertama kalinya tp kesekian kalinyað and aku kesini bkn d hari weekand tp d hari biasa so aku lebih suka suasana sepi hehehe jd lebih nikmat liat sunsetnyað ð dahal setiap kesini pasti d jalan tolnya ujan tp oas â</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['please', 'kesini', 'bkn', 'baru', 'pertama', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'aku', 'kesini', 'bkn', 'd', 'hari', 'weekand', 'tp', 'd', 'hari', 'biasa', 'so', 'aku', 'lebih', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'lebih', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'setiap', 'kesini', 'pasti', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['please', 'kesini', 'bkn', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'kesini', 'bkn', 'd', 'weekand', 'tp', 'd', 'so', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'kesini', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>please kesini bkn kali tp sekian kali and kesini bkn d weekand tp d so suka suasana sepi hehehe jd nikmat liat sunsetnya dahal kesini d jalan tol ujan tp oas</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1737,42 +1735,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The place is comfortable, cool, the toilet is always clean. The prayer clothes in the mosque are fragrant and clean. There are many vendors selling unique and cheap snacks, and the taste is also delicious.</t>
+          <t>Di kelola oleh oknum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
+          <t>di kelola oleh oknum</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
+          <t>['di', 'kelola', 'oleh', 'oknum']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'comfortable', 'cool', 'the', 'toilet', 'is', 'always', 'clean', 'the', 'prayer', 'clothes', 'in', 'the', 'mosque', 'are', 'fragrant', 'and', 'clean', 'there', 'are', 'many', 'vendors', 'selling', 'unique', 'and', 'cheap', 'snacks', 'and', 'the', 'taste', 'is', 'also', 'delicious']</t>
+          <t>['kelola', 'oknum']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>the place is comfortable cool the toilet is always clean the prayer clothes in the mosque are fragrant and clean there are many vendors selling unique and cheap snacks and the taste is also delicious</t>
+          <t>kelola oknum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1784,42 +1782,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
+          <t>The beach is definitely hot but it is helped by the presence of tents, a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere, the people are also friendly, there are many vendors here and there are many â¦</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
+          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many â</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>pake produck gk kecewa kerennnn deh</t>
+          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1831,42 +1829,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1878,42 +1876,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Di kelola oleh oknum</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>di kelola oleh oknum</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['di', 'kelola', 'oleh', 'oknum']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['kelola', 'oknum']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>kelola oknum</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1925,12 +1923,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>It's well organized and the street vendors are friendly, but the public facilities like the toilets aren't working.</t>
+          <t>Lokasi strategis. Cocok untuk santai cocok untuk anak-anak, cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan, cocok untuk yg tua muda semuanya.. tinggal d jaga bersama sama.. jangan vandalisme dan mengotorinya dgn sampah..okkkk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1940,22 +1938,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>its well organized and the street vendors are friendly but the public facilities like the toilets arent working</t>
+          <t>lokasi strategis cocok untuk santai cocok untuk anakanak cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan cocok untuk yg tua muda semuanya tinggal d jaga bersama sama jangan vandalisme dan mengotorinya dgn sampahokkkk</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['its', 'well', 'organized', 'and', 'the', 'street', 'vendors', 'are', 'friendly', 'but', 'the', 'public', 'facilities', 'like', 'the', 'toilets', 'arent', 'working']</t>
+          <t>['lokasi', 'strategis', 'cocok', 'untuk', 'santai', 'cocok', 'untuk', 'anakanak', 'cocok', 'untuk', 'olahraga', 'subuh', 'dengan', 'udara', 'yg', 'segar', 'dekat', 'pegunungan', 'cocok', 'untuk', 'yg', 'tua', 'muda', 'semuanya', 'tinggal', 'd', 'jaga', 'bersama', 'sama', 'jangan', 'vandalisme', 'dan', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['its', 'well', 'organized', 'and', 'the', 'street', 'vendors', 'are', 'friendly', 'but', 'the', 'public', 'facilities', 'like', 'the', 'toilets', 'arent', 'working']</t>
+          <t>['lokasi', 'strategis', 'cocok', 'santai', 'cocok', 'anakanak', 'cocok', 'olahraga', 'subuh', 'udara', 'yg', 'segar', 'pegunungan', 'cocok', 'yg', 'tua', 'muda', 'tinggal', 'd', 'jaga', 'vandalisme', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>its well organized and the street vendors are friendly but the public facilities like the toilets arent working</t>
+          <t>lokasi strategis cocok santai cocok anakanak cocok olahraga subuh udara yg segar gunung cocok yg tua muda tinggal d jaga vandalisme kotor dgn sampahokkkk</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1972,42 +1970,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>The atmosphere is comfortable and pleasant. You can play in the sand on the beach, making it perfect for family outings.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2019,12 +2017,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2034,22 +2032,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2066,42 +2064,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2113,106 +2111,106 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>bagus,,enak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>bagusenak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['bagusenak', 'liburan', 'keluarga']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>bagusenak libur keluarga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kotor alun alunnya banyak sampah...mampir ke masjid di alun2 bersih dan nyaman</t>
+          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2222,22 +2220,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>kotor alun alunnya banyak sampahmampir ke masjid di alun bersih dan nyaman</t>
+          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['kotor', 'alun', 'alunnya', 'banyak', 'sampahmampir', 'ke', 'masjid', 'di', 'alun', 'bersih', 'dan', 'nyaman']</t>
+          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['kotor', 'alun', 'alunnya', 'sampahmampir', 'masjid', 'alun', 'bersih', 'nyaman']</t>
+          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>kotor alun alun sampahmampir masjid alun bersih nyaman</t>
+          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2254,12 +2252,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>bagus,,enak buat liburan bersama keluarga</t>
+          <t>Beautiful beach view while waiting for the sunset. For those who want to swim, be careful because large waves and strong currents sometimes come.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2269,22 +2267,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>bagusenak buat liburan bersama keluarga</t>
+          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
+          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['bagusenak', 'liburan', 'keluarga']</t>
+          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>bagusenak libur keluarga</t>
+          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2301,42 +2299,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
+          <t>Bagus,dan penduduk nya ramah dan baik2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
+          <t>bagusdan penduduk nya ramah dan baik</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
+          <t>bagusdan duduk nya ramah</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2348,42 +2346,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bagus,dan penduduk nya ramah dan baik2</t>
+          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>bagusdan penduduk nya ramah dan baik</t>
+          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
+          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
+          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>bagusdan duduk nya ramah</t>
+          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2442,42 +2440,42 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tugu nyah udah di pindahin</t>
+          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tugu nyah udah di pindahin</t>
+          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>tugu nyah udah pindahin</t>
+          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2489,89 +2487,89 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
+          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
+          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
+          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
+          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
+          <t>cocok jalanjalan santai ramai sejuk</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tidak nyaman oleh orngÂ² yg menyewakan tempat untuk istirahat/baleÂ² Krn mahal Dan sangat perhitungan...di sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d Carikan tmpt istrht Krn mrk welcome dan baikÂ².</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tidak nyaman oleh orngâ² yg menyewakan tempat untuk istirahatbaleâ² krn mahal dan sangat perhitungandi sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d carikan tmpt istrht krn mrk welcome dan baikâ²</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['tidak', 'nyaman', 'oleh', 'orngâ²', 'yg', 'menyewakan', 'tempat', 'untuk', 'istirahatbaleâ²', 'krn', 'mahal', 'dan', 'sangat', 'perhitungandi', 'sarankan', 'jika', 'berwisata', 'ke', 'sana', 'bisa', 'meminta', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'untuk', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'dan', 'baikâ²']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['nyaman', 'orngâ²', 'yg', 'menyewakan', 'istirahatbaleâ²', 'krn', 'mahal', 'perhitungandi', 'sarankan', 'berwisata', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'baikâ²']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>nyaman orng yg sewa istirahatbale krn mahal perhitungandi saran wisata bantu jasa kpd jaga pintu masuk utama d cari tmpt istrht krn mrk welcome baik</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2583,12 +2581,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>It's best to come here in the late afternoon, the view is beautiful. It's a shame the toilets are dirty.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2598,22 +2596,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>its best to come here in the late afternoon the view is beautiful its a shame the toilets are dirty</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+          <t>['its', 'best', 'to', 'come', 'here', 'in', 'the', 'late', 'afternoon', 'the', 'view', 'is', 'beautiful', 'its', 'a', 'shame', 'the', 'toilets', 'are', 'dirty']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+          <t>['its', 'best', 'to', 'come', 'here', 'in', 'the', 'late', 'afternoon', 'the', 'view', 'is', 'beautiful', 'its', 'a', 'shame', 'the', 'toilets', 'are', 'dirty']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+          <t>its best to come here in the late afternoon the view is beautiful its a shame the toilets are dirty</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2630,42 +2628,42 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2677,42 +2675,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
+          <t>Good. Parking is free. Toilets are 2,000 yen. Degan is 15,000 yen. No entrance fee. The waves are quite big. There are horses and ATVs.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
+          <t>good parking is free toilets are yen degan is yen no entrance fee the waves are quite big there are horses and atvs</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>['mesjid', 'nya', 'bagus', 'tapi', 'sayang', 'banyak', 'itu', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'itu', 'iya', 'itu', 'apa', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
+          <t>['good', 'parking', 'is', 'free', 'toilets', 'are', 'yen', 'degan', 'is', 'yen', 'no', 'entrance', 'fee', 'the', 'waves', 'are', 'quite', 'big', 'there', 'are', 'horses', 'and', 'atvs']</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['mesjid', 'nya', 'bagus', 'sayang', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'iya', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
+          <t>['good', 'parking', 'is', 'free', 'toilets', 'are', 'yen', 'degan', 'is', 'yen', 'no', 'entrance', 'fee', 'the', 'waves', 'are', 'quite', 'big', 'there', 'are', 'horses', 'and', 'atvs']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>mesjid nya bagus sayang tuh ih ituloh apasih ya iya ih eta tea naon si arana nyaeta be pokonamah</t>
+          <t>good parking is free toilets are yen degan is yen no entrance fee the waves are quite big there are horses and atvs</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2724,42 +2722,42 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The 77th HAB ceremony at the Sukabumi Regency Ministry of Religious Affairs Office. Atmosphere in traditional attire.</t>
+          <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
+          <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
+          <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
+          <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
+          <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2771,12 +2769,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2786,22 +2784,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2818,42 +2816,42 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Konstruksi banyak yang rusak, terutama yang berbatasan dengan pasir. Mungkin tergerus ombak, sementara konstruksi tidak sesuai kondisi. Harusnya dikasih tiang pancang dan fondasi agak dalam. Tidak ada petugas pengawas, jadi orang bebas. Ada â¦</t>
+          <t>Susah wf.sama signal.,..</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>konstruksi banyak yang rusak terutama yang berbatasan dengan pasir mungkin tergerus ombak sementara konstruksi tidak sesuai kondisi harusnya dikasih tiang pancang dan fondasi agak dalam tidak ada petugas pengawas jadi orang bebas ada â</t>
+          <t>susah wfsama signal</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>['konstruksi', 'banyak', 'yang', 'rusak', 'terutama', 'yang', 'berbatasan', 'dengan', 'pasir', 'mungkin', 'tergerus', 'ombak', 'sementara', 'konstruksi', 'tidak', 'sesuai', 'kondisi', 'harusnya', 'dikasih', 'tiang', 'pancang', 'dan', 'fondasi', 'agak', 'dalam', 'tidak', 'ada', 'petugas', 'pengawas', 'jadi', 'orang', 'bebas', 'ada', 'â']</t>
+          <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['konstruksi', 'rusak', 'berbatasan', 'pasir', 'tergerus', 'ombak', 'konstruksi', 'sesuai', 'kondisi', 'dikasih', 'tiang', 'pancang', 'fondasi', 'petugas', 'pengawas', 'orang', 'bebas', 'â']</t>
+          <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>konstruksi rusak batas pasir gerus ombak konstruksi sesuai kondisi kasih tiang pancang fondasi tugas awas orang bebas</t>
+          <t>susah wfsama signal</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2865,42 +2863,42 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lokasi yg nyaman, bangunannya salah satu yg tahan gempa dengan rujukan dari BNPB. Mudah di akses dari jalan raya. Bisa menginap dengan harga yg terjangkau. Menjadi pusat penelitian ketahanan gempa.</t>
+          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>lokasi yg nyaman bangunannya salah satu yg tahan gempa dengan rujukan dari bnpb mudah di akses dari jalan raya bisa menginap dengan harga yg terjangkau menjadi pusat penelitian ketahanan gempa</t>
+          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'satu', 'yg', 'tahan', 'gempa', 'dengan', 'rujukan', 'dari', 'bnpb', 'mudah', 'di', 'akses', 'dari', 'jalan', 'raya', 'bisa', 'menginap', 'dengan', 'harga', 'yg', 'terjangkau', 'menjadi', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
+          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'yg', 'tahan', 'gempa', 'rujukan', 'bnpb', 'mudah', 'akses', 'jalan', 'raya', 'menginap', 'harga', 'yg', 'terjangkau', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
+          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>lokasi yg nyaman bangun salah yg tahan gempa rujuk bnpb mudah akses jalan raya inap harga yg jangkau pusat teliti tahan gempa</t>
+          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2912,42 +2910,42 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pasir pantai tidak tajam, lumayan bersih, banyak toilet, kamar mandi dan musola. Harga makanan dan minuman sesuai kantong.</t>
+          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>pasir pantai tidak tajam lumayan bersih banyak toilet kamar mandi dan musola harga makanan dan minuman sesuai kantong</t>
+          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>['pasir', 'pantai', 'tidak', 'tajam', 'lumayan', 'bersih', 'banyak', 'toilet', 'kamar', 'mandi', 'dan', 'musola', 'harga', 'makanan', 'dan', 'minuman', 'sesuai', 'kantong']</t>
+          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>['pasir', 'pantai', 'tajam', 'lumayan', 'bersih', 'toilet', 'kamar', 'mandi', 'musola', 'harga', 'makanan', 'minuman', 'sesuai', 'kantong']</t>
+          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>pasir pantai tajam lumayan bersih toilet kamar mandi musola harga makan minum sesuai kantong</t>
+          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2959,139 +2957,45 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tempat nya strategis untuk istrahat. Setelah solat d mesjid, bisa jajan dan mknan dlu, bnyak tempat jajannya, dekat dgn KFC, ATM dan toserba juga...ð â¦</t>
+          <t>Pasir pantai tidak tajam, lumayan bersih, banyak toilet, kamar mandi dan musola. Harga makanan dan minuman sesuai kantong.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tempat nya strategis untuk istrahat setelah solat d mesjid bisa jajan dan mknan dlu bnyak tempat jajannya dekat dgn kfc atm dan toserba jugað â</t>
+          <t>pasir pantai tidak tajam lumayan bersih banyak toilet kamar mandi dan musola harga makanan dan minuman sesuai kantong</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'strategis', 'untuk', 'istrahat', 'setelah', 'solat', 'd', 'mesjid', 'bisa', 'jajan', 'dan', 'mknan', 'dlu', 'bnyak', 'tempat', 'jajannya', 'dekat', 'dgn', 'kfc', 'atm', 'dan', 'toserba', 'jugað', 'â']</t>
+          <t>['pasir', 'pantai', 'tidak', 'tajam', 'lumayan', 'bersih', 'banyak', 'toilet', 'kamar', 'mandi', 'dan', 'musola', 'harga', 'makanan', 'dan', 'minuman', 'sesuai', 'kantong']</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>['nya', 'strategis', 'istrahat', 'solat', 'd', 'mesjid', 'jajan', 'mknan', 'dlu', 'bnyak', 'jajannya', 'dgn', 'kfc', 'atm', 'toserba', 'jugað', 'â']</t>
+          <t>['pasir', 'pantai', 'tajam', 'lumayan', 'bersih', 'toilet', 'kamar', 'mandi', 'musola', 'harga', 'makanan', 'minuman', 'sesuai', 'kantong']</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>nya strategis istrahat solat d mesjid jajan mknan dlu bnyak jajan dgn kfc atm toserba juga</t>
+          <t>pasir pantai tajam lumayan bersih toilet kamar mandi musola harga makan minum sesuai kantong</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Pantai Karang Sari</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Pantai Batu Bintang</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -513,42 +513,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Available milk, diapers, baby supplies, toiletries and staple foods and smashed chicken</t>
+          <t>Jajahannya banyak pilihan dan enak ð Tahu crispy juara, sate padang juga mantul, cilok lumayan, cilor enak, pisang keju enak, sate2 an enak, waduh kalap pokoknya â¦</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
+          <t>jajahannya banyak pilihan dan enak ð tahu crispy juara sate padang juga mantul cilok lumayan cilor enak pisang keju enak sate an enak waduh kalap pokoknya â</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
+          <t>['jajahannya', 'banyak', 'pilihan', 'dan', 'enak', 'ð', 'tahu', 'crispy', 'juara', 'sate', 'padang', 'juga', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'waduh', 'kalap', 'pokoknya', 'â']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
+          <t>['jajahannya', 'pilihan', 'enak', 'ð', 'crispy', 'juara', 'sate', 'padang', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'kalap', 'pokoknya', 'â']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
+          <t>jajah pilih enak crispy juara sate padang mantul cilok lumayan cilor enak pisang keju enak sate an enak kalap pokok</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -560,42 +560,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak  mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang  sebab ada oknum pedagang terutama pedagang  gorengan ada bapa bapa yang menjual /mencampur gorengan sisa hari kemarinnya,yang diangetin lagi hingga  terasa keras dan basi.</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang sebab ada oknum pedagang terutama pedagang gorengan ada bapa bapa yang menjual mencampur gorengan sisa hari kemarinnyayang diangetin lagi hingga terasa keras dan basi</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['nyaman', 'untuk', 'nyari', 'kuliner', 'cuma', 'tolong', 'ditertibkan', 'para', 'pedagangnya', 'supaya', 'tidak', 'mengganggu', 'lalu', 'lintas', 'juga', 'rasanya', 'harus', 'ada', 'pembinaan', 'pada', 'para', 'pedagang', 'sebab', 'ada', 'oknum', 'pedagang', 'terutama', 'pedagang', 'gorengan', 'ada', 'bapa', 'bapa', 'yang', 'menjual', 'mencampur', 'gorengan', 'sisa', 'hari', 'kemarinnyayang', 'diangetin', 'lagi', 'hingga', 'terasa', 'keras', 'dan', 'basi']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['nyaman', 'nyari', 'kuliner', 'tolong', 'ditertibkan', 'pedagangnya', 'mengganggu', 'lintas', 'pembinaan', 'pedagang', 'oknum', 'pedagang', 'pedagang', 'gorengan', 'bapa', 'bapa', 'menjual', 'mencampur', 'gorengan', 'sisa', 'kemarinnyayang', 'diangetin', 'keras', 'basi']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>nyaman nyari kuliner tolong tertib dagang ganggu lintas bina dagang oknum dagang dagang goreng bapa bapa jual campur goreng sisa kemarinnyayang diangetin keras basi</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -607,89 +607,89 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
+          <t>Keren nih tempatnya, sambil istirahat trus pesen kelapa muda , duh di seruput, alamak hati senang , ingat kerjaan nya setelah di jakarta aja ya, â¦</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
+          <t>keren nih tempatnya sambil istirahat trus pesen kelapa muda duh di seruput alamak hati senang ingat kerjaan nya setelah di jakarta aja ya â</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['keren', 'nih', 'tempatnya', 'sambil', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'di', 'seruput', 'alamak', 'hati', 'senang', 'ingat', 'kerjaan', 'nya', 'setelah', 'di', 'jakarta', 'aja', 'ya', 'â']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['keren', 'nih', 'tempatnya', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'seruput', 'alamak', 'hati', 'senang', 'kerjaan', 'nya', 'jakarta', 'aja', 'ya', 'â']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
+          <t>keren nih tempat istirahat trus sen kelapa muda duh seruput alamak hati senang kerja nya jakarta aja ya</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Tempat nya strategis untuk istrahat. Setelah solat d mesjid, bisa jajan dan mknan dlu, bnyak tempat jajannya, dekat dgn KFC, ATM dan toserba juga...ð â¦</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>tempat nya strategis untuk istrahat setelah solat d mesjid bisa jajan dan mknan dlu bnyak tempat jajannya dekat dgn kfc atm dan toserba jugað â</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['tempat', 'nya', 'strategis', 'untuk', 'istrahat', 'setelah', 'solat', 'd', 'mesjid', 'bisa', 'jajan', 'dan', 'mknan', 'dlu', 'bnyak', 'tempat', 'jajannya', 'dekat', 'dgn', 'kfc', 'atm', 'dan', 'toserba', 'jugað', 'â']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['nya', 'strategis', 'istrahat', 'solat', 'd', 'mesjid', 'jajan', 'mknan', 'dlu', 'bnyak', 'jajannya', 'dgn', 'kfc', 'atm', 'toserba', 'jugað', 'â']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>nya strategis istrahat solat d mesjid jajan mknan dlu bnyak jajan dgn kfc atm toserba juga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -701,42 +701,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pagi,siang mlm ramai pedagang smua murah meriah. Buat nongkrong smua usia jgn lupa silakan berkunjung, anda pasti suka....</t>
+          <t>Lokasi strategis. Cocok untuk santai cocok untuk anak-anak, cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan, cocok untuk yg tua muda semuanya.. tinggal d jaga bersama sama.. jangan vandalisme dan mengotorinya dgn sampah..okkkk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>pagisiang mlm ramai pedagang smua murah meriah buat nongkrong smua usia jgn lupa silakan berkunjung anda pasti suka</t>
+          <t>lokasi strategis cocok untuk santai cocok untuk anakanak cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan cocok untuk yg tua muda semuanya tinggal d jaga bersama sama jangan vandalisme dan mengotorinya dgn sampahokkkk</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'buat', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'anda', 'pasti', 'suka']</t>
+          <t>['lokasi', 'strategis', 'cocok', 'untuk', 'santai', 'cocok', 'untuk', 'anakanak', 'cocok', 'untuk', 'olahraga', 'subuh', 'dengan', 'udara', 'yg', 'segar', 'dekat', 'pegunungan', 'cocok', 'untuk', 'yg', 'tua', 'muda', 'semuanya', 'tinggal', 'd', 'jaga', 'bersama', 'sama', 'jangan', 'vandalisme', 'dan', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'suka']</t>
+          <t>['lokasi', 'strategis', 'cocok', 'santai', 'cocok', 'anakanak', 'cocok', 'olahraga', 'subuh', 'udara', 'yg', 'segar', 'pegunungan', 'cocok', 'yg', 'tua', 'muda', 'tinggal', 'd', 'jaga', 'vandalisme', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>pagisiang mlm ramai dagang smua murah riah nongkrong smua usia jgn lupa sila kunjung suka</t>
+          <t>lokasi strategis cocok santai cocok anakanak cocok olahraga subuh udara yg segar gunung cocok yg tua muda tinggal d jaga vandalisme kotor dgn sampahokkkk</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -748,89 +748,89 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
+          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
+          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
+          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
+          <t>Sdh mulai banyak kerusakan. Terutama pada area olahraga. Kurang terawat tidak seperti awal awal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
+          <t>sdh mulai banyak kerusakan terutama pada area olahraga kurang terawat tidak seperti awal awal</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
+          <t>['sdh', 'mulai', 'banyak', 'kerusakan', 'terutama', 'pada', 'area', 'olahraga', 'kurang', 'terawat', 'tidak', 'seperti', 'awal', 'awal']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
+          <t>['sdh', 'kerusakan', 'area', 'olahraga', 'terawat']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
+          <t>sdh rusa area olahraga awat</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -842,59 +842,59 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bagussss</t>
+          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pantai selatan nan indah.perlu penataan.dan pembenahan dengan ke seriusan pemda setempat.agar bisa menjadi obyek wisata andalan.</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -904,22 +904,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>pantai selatan nan indahperlu penataandan pembenahan dengan ke seriusan pemda setempatagar bisa menjadi obyek wisata andalan</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'dengan', 'ke', 'seriusan', 'pemda', 'setempatagar', 'bisa', 'menjadi', 'obyek', 'wisata', 'andalan']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'seriusan', 'pemda', 'setempatagar', 'obyek', 'wisata', 'andalan']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>pantai selatan nan indahperlu penataandan benah serius pemda setempatagar obyek wisata andal</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -936,42 +936,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tempat nya strategis untuk istrahat. Setelah solat d mesjid, bisa jajan dan mknan dlu, bnyak tempat jajannya, dekat dgn KFC, ATM dan toserba juga...ð â¦</t>
+          <t>The view is quite good for enjoying the sunset with the family, at this location port facilities are also being built</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>tempat nya strategis untuk istrahat setelah solat d mesjid bisa jajan dan mknan dlu bnyak tempat jajannya dekat dgn kfc atm dan toserba jugað â</t>
+          <t>the view is quite good for enjoying the sunset with the family at this location port facilities are also being built</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'strategis', 'untuk', 'istrahat', 'setelah', 'solat', 'd', 'mesjid', 'bisa', 'jajan', 'dan', 'mknan', 'dlu', 'bnyak', 'tempat', 'jajannya', 'dekat', 'dgn', 'kfc', 'atm', 'dan', 'toserba', 'jugað', 'â']</t>
+          <t>['the', 'view', 'is', 'quite', 'good', 'for', 'enjoying', 'the', 'sunset', 'with', 'the', 'family', 'at', 'this', 'location', 'port', 'facilities', 'are', 'also', 'being', 'built']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['nya', 'strategis', 'istrahat', 'solat', 'd', 'mesjid', 'jajan', 'mknan', 'dlu', 'bnyak', 'jajannya', 'dgn', 'kfc', 'atm', 'toserba', 'jugað', 'â']</t>
+          <t>['the', 'view', 'is', 'quite', 'good', 'for', 'enjoying', 'the', 'sunset', 'with', 'the', 'family', 'at', 'this', 'location', 'port', 'facilities', 'are', 'also', 'being', 'built']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>nya strategis istrahat solat d mesjid jajan mknan dlu bnyak jajan dgn kfc atm toserba juga</t>
+          <t>the view is quite good for enjoying the sunset with the family at this location port facilities are also being built</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -983,12 +983,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
+          <t>Pantai selatan nan indah.perlu penataan.dan pembenahan dengan ke seriusan pemda setempat.agar bisa menjadi obyek wisata andalan.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -998,22 +998,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
+          <t>pantai selatan nan indahperlu penataandan pembenahan dengan ke seriusan pemda setempatagar bisa menjadi obyek wisata andalan</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
+          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'dengan', 'ke', 'seriusan', 'pemda', 'setempatagar', 'bisa', 'menjadi', 'obyek', 'wisata', 'andalan']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
+          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'seriusan', 'pemda', 'setempatagar', 'obyek', 'wisata', 'andalan']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
+          <t>pantai selatan nan indahperlu penataandan benah serius pemda setempatagar obyek wisata andal</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1030,12 +1030,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
+          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
+          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
+          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1077,12 +1077,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
+          <t>It's free, with no entrance fee. The sand is fine and coral-free. Toilet and changing room facilities need to be expanded and their cleanliness monitored.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1092,22 +1092,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
+          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
+          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
+          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
+          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1124,42 +1124,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
+          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
+          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
+          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
+          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
+          <t>kali lapang cangehgarbagus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1171,42 +1171,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
+          <t>Transit sebelum ke Geopark Ciletuh bs di sini. Shalat di mesjid Agung, makan ada warung Padang enak murah. Jajanan kakilimanya jg banyak.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
+          <t>transit sebelum ke geopark ciletuh bs di sini shalat di mesjid agung makan ada warung padang enak murah jajanan kakilimanya jg banyak</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
+          <t>['transit', 'sebelum', 'ke', 'geopark', 'ciletuh', 'bs', 'di', 'sini', 'shalat', 'di', 'mesjid', 'agung', 'makan', 'ada', 'warung', 'padang', 'enak', 'murah', 'jajanan', 'kakilimanya', 'jg', 'banyak']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
+          <t>['transit', 'geopark', 'ciletuh', 'bs', 'shalat', 'mesjid', 'agung', 'makan', 'warung', 'padang', 'enak', 'murah', 'jajanan', 'kakilimanya', 'jg']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
+          <t>transit geopark ciletuh bs shalat mesjid agung makan warung padang enak murah jajan kakilimanya jg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1218,42 +1218,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pantainya bersih, yang terpenting harga makanan dan minuman super murah,parkir jg normal..</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>pantainya bersih yang terpenting harga makanan dan minuman super murahparkir jg normal</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersih', 'yang', 'terpenting', 'harga', 'makanan', 'dan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersih', 'terpenting', 'harga', 'makanan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>pantai bersih penting harga makan minum super murahparkir jg normal</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1265,12 +1265,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1280,22 +1280,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1312,42 +1312,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang merupakan salah satu pantai yang terletak di Pelabuhan Ratu, Kabupaten Sukabumi, Jawa Barat. Pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik. â¦</t>
+          <t>Lebih rapih dan tertata, untuk saat ini belum dibuka masih dipagar seng</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>pantai batu bintang merupakan salah satu pantai yang terletak di pelabuhan ratu kabupaten sukabumi jawa barat pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik â</t>
+          <t>lebih rapih dan tertata untuk saat ini belum dibuka masih dipagar seng</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['pantai', 'batu', 'bintang', 'merupakan', 'salah', 'satu', 'pantai', 'yang', 'terletak', 'di', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'ini', 'terkenal', 'dengan', 'keindahan', 'pantainya', 'yang', 'masih', 'alami', 'dan', 'dihiasi', 'dengan', 'bebatuan', 'yang', 'unik', 'dan', 'menarik', 'â']</t>
+          <t>['lebih', 'rapih', 'dan', 'tertata', 'untuk', 'saat', 'ini', 'belum', 'dibuka', 'masih', 'dipagar', 'seng']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['pantai', 'batu', 'bintang', 'salah', 'pantai', 'terletak', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'terkenal', 'keindahan', 'pantainya', 'alami', 'dihiasi', 'bebatuan', 'unik', 'menarik', 'â']</t>
+          <t>['rapih', 'tertata', 'dibuka', 'dipagar', 'seng']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>pantai batu bintang salah pantai letak labuh ratu kabupaten sukabumi jawa barat pantai kenal indah pantai alami hias bebatuan unik tarik</t>
+          <t>rapih tata buka pagar seng</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1359,89 +1359,89 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wow, don't ask, of course Pelabuhan Ratu beach is the best, from its beautiful atmosphere to its top-notch culinary delights.</t>
+          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>wow dont ask of course pelabuhan ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
+          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
+          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
+          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>wow dont ask of course labuh ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
+          <t>nongki chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1453,42 +1453,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The toilets are dirty and only want money and almost every location is full of rubbish, even though it's a shame that the place is as neat as this but it's not well maintained.</t>
+          <t>Pantai Batu Bintang merupakan salah satu pantai yang terletak di Pelabuhan Ratu, Kabupaten Sukabumi, Jawa Barat. Pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik. â¦</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>the toilets are dirty and only want money and almost every location is full of rubbish even though its a shame that the place is as neat as this but its not well maintained</t>
+          <t>pantai batu bintang merupakan salah satu pantai yang terletak di pelabuhan ratu kabupaten sukabumi jawa barat pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik â</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['the', 'toilets', 'are', 'dirty', 'and', 'only', 'want', 'money', 'and', 'almost', 'every', 'location', 'is', 'full', 'of', 'rubbish', 'even', 'though', 'its', 'a', 'shame', 'that', 'the', 'place', 'is', 'as', 'neat', 'as', 'this', 'but', 'its', 'not', 'well', 'maintained']</t>
+          <t>['pantai', 'batu', 'bintang', 'merupakan', 'salah', 'satu', 'pantai', 'yang', 'terletak', 'di', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'ini', 'terkenal', 'dengan', 'keindahan', 'pantainya', 'yang', 'masih', 'alami', 'dan', 'dihiasi', 'dengan', 'bebatuan', 'yang', 'unik', 'dan', 'menarik', 'â']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['the', 'toilets', 'are', 'dirty', 'and', 'only', 'want', 'money', 'and', 'almost', 'every', 'location', 'is', 'full', 'of', 'rubbish', 'even', 'though', 'its', 'a', 'shame', 'that', 'the', 'place', 'is', 'as', 'neat', 'as', 'this', 'but', 'its', 'not', 'well', 'maintained']</t>
+          <t>['pantai', 'batu', 'bintang', 'salah', 'pantai', 'terletak', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'terkenal', 'keindahan', 'pantainya', 'alami', 'dihiasi', 'bebatuan', 'unik', 'menarik', 'â']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>the toilets are dirty and only want money and almost every location is full of rubbish even though its a shame that the place is as neat as this but its not well maintained</t>
+          <t>pantai batu bintang salah pantai letak labuh ratu kabupaten sukabumi jawa barat pantai kenal indah pantai alami hias bebatuan unik tarik</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1500,42 +1500,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lebih rapih dan tertata, untuk saat ini belum dibuka masih dipagar seng</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>lebih rapih dan tertata untuk saat ini belum dibuka masih dipagar seng</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['lebih', 'rapih', 'dan', 'tertata', 'untuk', 'saat', 'ini', 'belum', 'dibuka', 'masih', 'dipagar', 'seng']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['rapih', 'tertata', 'dibuka', 'dipagar', 'seng']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>rapih tata buka pagar seng</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1547,42 +1547,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Karang Pamulang Beach, Bunga Ayu Seaside Resort Is a friendly, beautiful beach</t>
+          <t>Ikon kota palabuhanratu......bagus</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>karang pamulang beach bunga ayu seaside resort is a friendly beautiful beach</t>
+          <t>ikon kota palabuhanratubagus</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['karang', 'pamulang', 'beach', 'bunga', 'ayu', 'seaside', 'resort', 'is', 'a', 'friendly', 'beautiful', 'beach']</t>
+          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['karang', 'pamulang', 'beach', 'bunga', 'ayu', 'seaside', 'resort', 'is', 'a', 'friendly', 'beautiful', 'beach']</t>
+          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>karang pamulang beach bunga ayu seaside resort is a friendly beautiful beach</t>
+          <t>ikon kota palabuhanratubagus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1594,42 +1594,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tampil nasyid tingkat provinsi..mantap cah2 Lanang ð¥°ð¥° â¦</t>
+          <t>Wow, don't ask, of course Pelabuhan Ratu beach is the best, from its beautiful atmosphere to its top-notch culinary delights.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tampil nasyid tingkat provinsimantap cah lanang ðð â</t>
+          <t>wow dont ask of course pelabuhan ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
+          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['tampil', 'nasyid', 'tingkat', 'provinsimantap', 'cah', 'lanang', 'ðð', 'â']</t>
+          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tampil nasyid tingkat provinsimantap cah lanang</t>
+          <t>wow dont ask of course labuh ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1641,42 +1641,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Inhale the comfortable atmosphere of Sukabumi's southern coast for just a day off</t>
+          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>inhale the comfortable atmosphere of sukabumis southern coast for just a day off</t>
+          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['inhale', 'the', 'comfortable', 'atmosphere', 'of', 'sukabumis', 'southern', 'coast', 'for', 'just', 'a', 'day', 'off']</t>
+          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['inhale', 'the', 'comfortable', 'atmosphere', 'of', 'sukabumis', 'southern', 'coast', 'for', 'just', 'a', 'day', 'off']</t>
+          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>inhale the comfortable atmosphere of sukabumis southern coast for just a day off</t>
+          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1688,42 +1688,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Pasir pantai tidak tajam, lumayan bersih, banyak toilet, kamar mandi dan musola. Harga makanan dan minuman sesuai kantong.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>pasir pantai tidak tajam lumayan bersih banyak toilet kamar mandi dan musola harga makanan dan minuman sesuai kantong</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['pasir', 'pantai', 'tidak', 'tajam', 'lumayan', 'bersih', 'banyak', 'toilet', 'kamar', 'mandi', 'dan', 'musola', 'harga', 'makanan', 'dan', 'minuman', 'sesuai', 'kantong']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['pasir', 'pantai', 'tajam', 'lumayan', 'bersih', 'toilet', 'kamar', 'mandi', 'musola', 'harga', 'makanan', 'minuman', 'sesuai', 'kantong']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>pasir pantai tajam lumayan bersih toilet kamar mandi musola harga makan minum sesuai kantong</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1735,89 +1735,89 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Di kelola oleh oknum</t>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>di kelola oleh oknum</t>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['di', 'kelola', 'oleh', 'oknum']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['kelola', 'oknum']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>kelola oknum</t>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The beach is definitely hot but it is helped by the presence of tents, a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere, the people are also friendly, there are many vendors here and there are many â¦</t>
+          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many â</t>
+          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
+          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'definitely', 'hot', 'but', 'it', 'is', 'helped', 'by', 'the', 'presence', 'of', 'tents', 'a', 'pleasant', 'place', 'with', 'the', 'sound', 'of', 'the', 'waves', 'and', 'the', 'sea', 'breeze', 'creating', 'a', 'calm', 'atmosphere', 'the', 'people', 'are', 'also', 'friendly', 'there', 'are', 'many', 'vendors', 'here', 'and', 'there', 'are', 'many', 'â']</t>
+          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>the beach is definitely hot but it is helped by the presence of tents a pleasant place with the sound of the waves and the sea breeze creating a calm atmosphere the people are also friendly there are many vendors here and there are many</t>
+          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1829,89 +1829,89 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>Tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luas,mudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luasmudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['tempat', 'di', 'pelabuhan', 'ratu', 'buat', 'main', 'keluarga', 'cuma', 'jarang', 'tempat', 'untuk', 'berteduh', 'suasana', 'pantai', 'indah', 'banyak', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'lebih', 'di', 'pelihara', 'dan', 'di', 'perindah', 'supaya', 'tempat', 'nya', 'makin', 'bagus']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['pelabuhan', 'ratu', 'main', 'keluarga', 'jarang', 'berteduh', 'suasana', 'pantai', 'indah', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'pelihara', 'perindah', 'nya', 'bagus']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>labuh ratu main keluarga jarang teduh suasana pantai indah tukang dagang parkir luasmudah mudah pelihara indah nya bagus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1923,42 +1923,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lokasi strategis. Cocok untuk santai cocok untuk anak-anak, cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan, cocok untuk yg tua muda semuanya.. tinggal d jaga bersama sama.. jangan vandalisme dan mengotorinya dgn sampah..okkkk</t>
+          <t>bagus,,enak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>lokasi strategis cocok untuk santai cocok untuk anakanak cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan cocok untuk yg tua muda semuanya tinggal d jaga bersama sama jangan vandalisme dan mengotorinya dgn sampahokkkk</t>
+          <t>bagusenak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['lokasi', 'strategis', 'cocok', 'untuk', 'santai', 'cocok', 'untuk', 'anakanak', 'cocok', 'untuk', 'olahraga', 'subuh', 'dengan', 'udara', 'yg', 'segar', 'dekat', 'pegunungan', 'cocok', 'untuk', 'yg', 'tua', 'muda', 'semuanya', 'tinggal', 'd', 'jaga', 'bersama', 'sama', 'jangan', 'vandalisme', 'dan', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
+          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['lokasi', 'strategis', 'cocok', 'santai', 'cocok', 'anakanak', 'cocok', 'olahraga', 'subuh', 'udara', 'yg', 'segar', 'pegunungan', 'cocok', 'yg', 'tua', 'muda', 'tinggal', 'd', 'jaga', 'vandalisme', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
+          <t>['bagusenak', 'liburan', 'keluarga']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>lokasi strategis cocok santai cocok anakanak cocok olahraga subuh udara yg segar gunung cocok yg tua muda tinggal d jaga vandalisme kotor dgn sampahokkkk</t>
+          <t>bagusenak libur keluarga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1975,37 +1975,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The atmosphere is comfortable and pleasant. You can play in the sand on the beach, making it perfect for family outings.</t>
+          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2017,42 +2017,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2064,12 +2064,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
+          <t>Di kelola oleh oknum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
+          <t>di kelola oleh oknum</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
+          <t>['di', 'kelola', 'oleh', 'oknum']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
+          <t>['kelola', 'oknum']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
+          <t>kelola oknum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2111,59 +2111,59 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>bagus,,enak buat liburan bersama keluarga</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2173,22 +2173,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>bagusenak buat liburan bersama keluarga</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['bagusenak', 'liburan', 'keluarga']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>bagusenak libur keluarga</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
+          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2220,22 +2220,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
+          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
+          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
+          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
+          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2252,42 +2252,42 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Beautiful beach view while waiting for the sunset. For those who want to swim, be careful because large waves and strong currents sometimes come.</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2299,42 +2299,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bagus,dan penduduk nya ramah dan baik2</t>
+          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>bagusdan penduduk nya ramah dan baik</t>
+          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
+          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
+          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>bagusdan duduk nya ramah</t>
+          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2346,42 +2346,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
+          <t>Bagus,dan penduduk nya ramah dan baik2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
+          <t>bagusdan penduduk nya ramah dan baik</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
+          <t>bagusdan duduk nya ramah</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2393,12 +2393,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
+          <t>Jalanya mantap</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2408,22 +2408,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
+          <t>jalanya mantap</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
+          <t>jala mantap</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2433,49 +2433,49 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
+          <t>Tempat nya nongkrong anak plara,keren pokonya tmpat nya asik...bnyk hiburn dan permainan anak</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
+          <t>tempat nya nongkrong anak plarakeren pokonya tmpat nya asikbnyk hiburn dan permainan anak</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
+          <t>['tempat', 'nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'dan', 'permainan', 'anak']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
+          <t>['nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'permainan', 'anak']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
+          <t>nya nongkrong anak plarakeren poko tmpat nya asikbnyk hiburn main anak</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2487,42 +2487,42 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+          <t>Parkir bayar, tapi ada barang yg hilang. Pas dicek di pantai barang bwaan berkurang. Krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+          <t>parkir bayar tapi ada barang yg hilang pas dicek di pantai barang bwaan berkurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+          <t>['parkir', 'bayar', 'tapi', 'ada', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'di', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+          <t>['parkir', 'bayar', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>cocok jalanjalan santai ramai sejuk</t>
+          <t>parkir bayar barang yg hilang pas cek pantai barang bwaan kurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2534,59 +2534,59 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>Pantainya kurang bagus kotor terus parkiranya gaboleh didepan warung sama yg punya warung</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>pantainya kurang bagus kotor terus parkiranya gaboleh didepan warung sama yg punya warung</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+          <t>['pantainya', 'kurang', 'bagus', 'kotor', 'terus', 'parkiranya', 'gaboleh', 'didepan', 'warung', 'sama', 'yg', 'punya', 'warung']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+          <t>['pantainya', 'bagus', 'kotor', 'parkiranya', 'gaboleh', 'didepan', 'warung', 'yg', 'warung']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+          <t>pantai bagus kotor parkiranya gaboleh depan warung yg warung</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>It's best to come here in the late afternoon, the view is beautiful. It's a shame the toilets are dirty.</t>
+          <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>its best to come here in the late afternoon the view is beautiful its a shame the toilets are dirty</t>
+          <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['its', 'best', 'to', 'come', 'here', 'in', 'the', 'late', 'afternoon', 'the', 'view', 'is', 'beautiful', 'its', 'a', 'shame', 'the', 'toilets', 'are', 'dirty']</t>
+          <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['its', 'best', 'to', 'come', 'here', 'in', 'the', 'late', 'afternoon', 'the', 'view', 'is', 'beautiful', 'its', 'a', 'shame', 'the', 'toilets', 'are', 'dirty']</t>
+          <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>its best to come here in the late afternoon the view is beautiful its a shame the toilets are dirty</t>
+          <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2628,12 +2628,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Beautiful beach view while waiting for the sunset. For those who want to swim, be careful because large waves and strong currents sometimes come.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2643,22 +2643,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2675,42 +2675,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Good. Parking is free. Toilets are 2,000 yen. Degan is 15,000 yen. No entrance fee. The waves are quite big. There are horses and ATVs.</t>
+          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>good parking is free toilets are yen degan is yen no entrance fee the waves are quite big there are horses and atvs</t>
+          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>['good', 'parking', 'is', 'free', 'toilets', 'are', 'yen', 'degan', 'is', 'yen', 'no', 'entrance', 'fee', 'the', 'waves', 'are', 'quite', 'big', 'there', 'are', 'horses', 'and', 'atvs']</t>
+          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['good', 'parking', 'is', 'free', 'toilets', 'are', 'yen', 'degan', 'is', 'yen', 'no', 'entrance', 'fee', 'the', 'waves', 'are', 'quite', 'big', 'there', 'are', 'horses', 'and', 'atvs']</t>
+          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>good parking is free toilets are yen degan is yen no entrance fee the waves are quite big there are horses and atvs</t>
+          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2727,37 +2727,37 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
+          <t>Pantainya bersih, yang terpenting harga makanan dan minuman super murah,parkir jg normal..</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
+          <t>pantainya bersih yang terpenting harga makanan dan minuman super murahparkir jg normal</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
+          <t>['pantainya', 'bersih', 'yang', 'terpenting', 'harga', 'makanan', 'dan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
+          <t>['pantainya', 'bersih', 'terpenting', 'harga', 'makanan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
+          <t>pantai bersih penting harga makan minum super murahparkir jg normal</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2769,42 +2769,42 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>The atmosphere is comfortable and pleasant. You can play in the sand on the beach, making it perfect for family outings.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2816,42 +2816,42 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Susah wf.sama signal.,..</t>
+          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2863,12 +2863,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+          <t>Alhamdulillahasih bersih, indah apalagi di malam hari, tepat nya di depan majid agung palabuahan ratu, banyak tersedia jajanan juga, ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2878,22 +2878,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+          <t>alhamdulillahasih bersih indah apalagi di malam hari tepat nya di depan majid agung palabuahan ratu banyak tersedia jajanan juga ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
+          <t>['alhamdulillahasih', 'bersih', 'indah', 'apalagi', 'di', 'malam', 'hari', 'tepat', 'nya', 'di', 'depan', 'majid', 'agung', 'palabuahan', 'ratu', 'banyak', 'tersedia', 'jajanan', 'juga', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended', 'lah']</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
+          <t>['alhamdulillahasih', 'bersih', 'indah', 'malam', 'nya', 'majid', 'agung', 'palabuahan', 'ratu', 'tersedia', 'jajanan', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended']</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
+          <t>alhamdulillahasih bersih indah malam nya majid agung palabuahan ratu sedia jajan ubtuk dar santa denfan keluarga rekomended</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2949,53 +2949,6 @@
         </is>
       </c>
       <c r="I54" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Pantai Citepus</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Pasir pantai tidak tajam, lumayan bersih, banyak toilet, kamar mandi dan musola. Harga makanan dan minuman sesuai kantong.</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>pasir pantai tidak tajam lumayan bersih banyak toilet kamar mandi dan musola harga makanan dan minuman sesuai kantong</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>['pasir', 'pantai', 'tidak', 'tajam', 'lumayan', 'bersih', 'banyak', 'toilet', 'kamar', 'mandi', 'dan', 'musola', 'harga', 'makanan', 'dan', 'minuman', 'sesuai', 'kantong']</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>['pasir', 'pantai', 'tajam', 'lumayan', 'bersih', 'toilet', 'kamar', 'mandi', 'musola', 'harga', 'makanan', 'minuman', 'sesuai', 'kantong']</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>pasir pantai tajam lumayan bersih toilet kamar mandi musola harga makan minum sesuai kantong</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
+          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
+          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
+          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
+          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
+          <t>pake produck gk kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -513,42 +513,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jajahannya banyak pilihan dan enak ð Tahu crispy juara, sate padang juga mantul, cilok lumayan, cilor enak, pisang keju enak, sate2 an enak, waduh kalap pokoknya â¦</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>jajahannya banyak pilihan dan enak ð tahu crispy juara sate padang juga mantul cilok lumayan cilor enak pisang keju enak sate an enak waduh kalap pokoknya â</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['jajahannya', 'banyak', 'pilihan', 'dan', 'enak', 'ð', 'tahu', 'crispy', 'juara', 'sate', 'padang', 'juga', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'waduh', 'kalap', 'pokoknya', 'â']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['jajahannya', 'pilihan', 'enak', 'ð', 'crispy', 'juara', 'sate', 'padang', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'kalap', 'pokoknya', 'â']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>jajah pilih enak crispy juara sate padang mantul cilok lumayan cilor enak pisang keju enak sate an enak kalap pokok</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -560,42 +560,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -607,89 +607,89 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Keren nih tempatnya, sambil istirahat trus pesen kelapa muda , duh di seruput, alamak hati senang , ingat kerjaan nya setelah di jakarta aja ya, â¦</t>
+          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>keren nih tempatnya sambil istirahat trus pesen kelapa muda duh di seruput alamak hati senang ingat kerjaan nya setelah di jakarta aja ya â</t>
+          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['keren', 'nih', 'tempatnya', 'sambil', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'di', 'seruput', 'alamak', 'hati', 'senang', 'ingat', 'kerjaan', 'nya', 'setelah', 'di', 'jakarta', 'aja', 'ya', 'â']</t>
+          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['keren', 'nih', 'tempatnya', 'istirahat', 'trus', 'pesen', 'kelapa', 'muda', 'duh', 'seruput', 'alamak', 'hati', 'senang', 'kerjaan', 'nya', 'jakarta', 'aja', 'ya', 'â']</t>
+          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>keren nih tempat istirahat trus sen kelapa muda duh seruput alamak hati senang kerja nya jakarta aja ya</t>
+          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tempat nya strategis untuk istrahat. Setelah solat d mesjid, bisa jajan dan mknan dlu, bnyak tempat jajannya, dekat dgn KFC, ATM dan toserba juga...ð â¦</t>
+          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>tempat nya strategis untuk istrahat setelah solat d mesjid bisa jajan dan mknan dlu bnyak tempat jajannya dekat dgn kfc atm dan toserba jugað â</t>
+          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'strategis', 'untuk', 'istrahat', 'setelah', 'solat', 'd', 'mesjid', 'bisa', 'jajan', 'dan', 'mknan', 'dlu', 'bnyak', 'tempat', 'jajannya', 'dekat', 'dgn', 'kfc', 'atm', 'dan', 'toserba', 'jugað', 'â']</t>
+          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['nya', 'strategis', 'istrahat', 'solat', 'd', 'mesjid', 'jajan', 'mknan', 'dlu', 'bnyak', 'jajannya', 'dgn', 'kfc', 'atm', 'toserba', 'jugað', 'â']</t>
+          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nya strategis istrahat solat d mesjid jajan mknan dlu bnyak jajan dgn kfc atm toserba juga</t>
+          <t>nongki chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lokasi strategis. Cocok untuk santai cocok untuk anak-anak, cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan, cocok untuk yg tua muda semuanya.. tinggal d jaga bersama sama.. jangan vandalisme dan mengotorinya dgn sampah..okkkk</t>
+          <t>Kotor alun alunnya banyak sampah...mampir ke masjid di alun2 bersih dan nyaman</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>lokasi strategis cocok untuk santai cocok untuk anakanak cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan cocok untuk yg tua muda semuanya tinggal d jaga bersama sama jangan vandalisme dan mengotorinya dgn sampahokkkk</t>
+          <t>kotor alun alunnya banyak sampahmampir ke masjid di alun bersih dan nyaman</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['lokasi', 'strategis', 'cocok', 'untuk', 'santai', 'cocok', 'untuk', 'anakanak', 'cocok', 'untuk', 'olahraga', 'subuh', 'dengan', 'udara', 'yg', 'segar', 'dekat', 'pegunungan', 'cocok', 'untuk', 'yg', 'tua', 'muda', 'semuanya', 'tinggal', 'd', 'jaga', 'bersama', 'sama', 'jangan', 'vandalisme', 'dan', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
+          <t>['kotor', 'alun', 'alunnya', 'banyak', 'sampahmampir', 'ke', 'masjid', 'di', 'alun', 'bersih', 'dan', 'nyaman']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['lokasi', 'strategis', 'cocok', 'santai', 'cocok', 'anakanak', 'cocok', 'olahraga', 'subuh', 'udara', 'yg', 'segar', 'pegunungan', 'cocok', 'yg', 'tua', 'muda', 'tinggal', 'd', 'jaga', 'vandalisme', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
+          <t>['kotor', 'alun', 'alunnya', 'sampahmampir', 'masjid', 'alun', 'bersih', 'nyaman']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lokasi strategis cocok santai cocok anakanak cocok olahraga subuh udara yg segar gunung cocok yg tua muda tinggal d jaga vandalisme kotor dgn sampahokkkk</t>
+          <t>kotor alun alun sampahmampir masjid alun bersih nyaman</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -748,12 +748,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
+          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -763,22 +763,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
+          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
+          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -795,42 +795,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sdh mulai banyak kerusakan. Terutama pada area olahraga. Kurang terawat tidak seperti awal awal</t>
+          <t>The sunset is really beautiful... If it's a holiday, it's definitely really crowded.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sdh mulai banyak kerusakan terutama pada area olahraga kurang terawat tidak seperti awal awal</t>
+          <t>the sunset is really beautiful if its a holiday its definitely really crowded</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['sdh', 'mulai', 'banyak', 'kerusakan', 'terutama', 'pada', 'area', 'olahraga', 'kurang', 'terawat', 'tidak', 'seperti', 'awal', 'awal']</t>
+          <t>['the', 'sunset', 'is', 'really', 'beautiful', 'if', 'its', 'a', 'holiday', 'its', 'definitely', 'really', 'crowded']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['sdh', 'kerusakan', 'area', 'olahraga', 'terawat']</t>
+          <t>['the', 'sunset', 'is', 'really', 'beautiful', 'if', 'its', 'a', 'holiday', 'its', 'definitely', 'really', 'crowded']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>sdh rusa area olahraga awat</t>
+          <t>the sunset is really beautiful if its a holiday its definitely really crowded</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -847,54 +847,54 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
+          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
+          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
+          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -904,22 +904,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>mantaps dah olahraga ringan keluarga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -936,42 +936,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The view is quite good for enjoying the sunset with the family, at this location port facilities are also being built</t>
+          <t>Lokasi yg nyaman, bangunannya salah satu yg tahan gempa dengan rujukan dari BNPB. Mudah di akses dari jalan raya. Bisa menginap dengan harga yg terjangkau. Menjadi pusat penelitian ketahanan gempa.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>the view is quite good for enjoying the sunset with the family at this location port facilities are also being built</t>
+          <t>lokasi yg nyaman bangunannya salah satu yg tahan gempa dengan rujukan dari bnpb mudah di akses dari jalan raya bisa menginap dengan harga yg terjangkau menjadi pusat penelitian ketahanan gempa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['the', 'view', 'is', 'quite', 'good', 'for', 'enjoying', 'the', 'sunset', 'with', 'the', 'family', 'at', 'this', 'location', 'port', 'facilities', 'are', 'also', 'being', 'built']</t>
+          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'satu', 'yg', 'tahan', 'gempa', 'dengan', 'rujukan', 'dari', 'bnpb', 'mudah', 'di', 'akses', 'dari', 'jalan', 'raya', 'bisa', 'menginap', 'dengan', 'harga', 'yg', 'terjangkau', 'menjadi', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['the', 'view', 'is', 'quite', 'good', 'for', 'enjoying', 'the', 'sunset', 'with', 'the', 'family', 'at', 'this', 'location', 'port', 'facilities', 'are', 'also', 'being', 'built']</t>
+          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'yg', 'tahan', 'gempa', 'rujukan', 'bnpb', 'mudah', 'akses', 'jalan', 'raya', 'menginap', 'harga', 'yg', 'terjangkau', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>the view is quite good for enjoying the sunset with the family at this location port facilities are also being built</t>
+          <t>lokasi yg nyaman bangun salah yg tahan gempa rujuk bnpb mudah akses jalan raya inap harga yg jangkau pusat teliti tahan gempa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -983,42 +983,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pantai selatan nan indah.perlu penataan.dan pembenahan dengan ke seriusan pemda setempat.agar bisa menjadi obyek wisata andalan.</t>
+          <t>Accommodating thousands of people, with a nice park and toilet facilities...</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>pantai selatan nan indahperlu penataandan pembenahan dengan ke seriusan pemda setempatagar bisa menjadi obyek wisata andalan</t>
+          <t>accommodating thousands of people with a nice park and toilet facilities</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'dengan', 'ke', 'seriusan', 'pemda', 'setempatagar', 'bisa', 'menjadi', 'obyek', 'wisata', 'andalan']</t>
+          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'seriusan', 'pemda', 'setempatagar', 'obyek', 'wisata', 'andalan']</t>
+          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>pantai selatan nan indahperlu penataandan benah serius pemda setempatagar obyek wisata andal</t>
+          <t>accommodating thousands of people with a nice park and toilet facilities</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1030,42 +1030,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
+          <t>Saungnya pada kotor ga nyaman..padahal tempatnya adem..tolong di perhatikan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
+          <t>saungnya pada kotor ga nyamanpadahal tempatnya ademtolong di perhatikan</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['saungnya', 'pada', 'kotor', 'ga', 'nyamanpadahal', 'tempatnya', 'ademtolong', 'di', 'perhatikan']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['saungnya', 'kotor', 'ga', 'nyamanpadahal', 'tempatnya', 'ademtolong', 'perhatikan']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
+          <t>saung kotor ga nyamanpadahal tempat ademtolong perhati</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,42 +1077,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>It's free, with no entrance fee. The sand is fine and coral-free. Toilet and changing room facilities need to be expanded and their cleanliness monitored.</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['its', 'free', 'with', 'no', 'entrance', 'fee', 'the', 'sand', 'is', 'fine', 'and', 'coralfree', 'toilet', 'and', 'changing', 'room', 'facilities', 'need', 'to', 'be', 'expanded', 'and', 'their', 'cleanliness', 'monitored']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>its free with no entrance fee the sand is fine and coralfree toilet and changing room facilities need to be expanded and their cleanliness monitored</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1124,12 +1124,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
+          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1139,22 +1139,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
+          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>kali lapang cangehgarbagus</t>
+          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1171,42 +1171,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Transit sebelum ke Geopark Ciletuh bs di sini. Shalat di mesjid Agung, makan ada warung Padang enak murah. Jajanan kakilimanya jg banyak.</t>
+          <t>Wow, don't ask, of course Pelabuhan Ratu beach is the best, from its beautiful atmosphere to its top-notch culinary delights.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>transit sebelum ke geopark ciletuh bs di sini shalat di mesjid agung makan ada warung padang enak murah jajanan kakilimanya jg banyak</t>
+          <t>wow dont ask of course pelabuhan ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['transit', 'sebelum', 'ke', 'geopark', 'ciletuh', 'bs', 'di', 'sini', 'shalat', 'di', 'mesjid', 'agung', 'makan', 'ada', 'warung', 'padang', 'enak', 'murah', 'jajanan', 'kakilimanya', 'jg', 'banyak']</t>
+          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['transit', 'geopark', 'ciletuh', 'bs', 'shalat', 'mesjid', 'agung', 'makan', 'warung', 'padang', 'enak', 'murah', 'jajanan', 'kakilimanya', 'jg']</t>
+          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>transit geopark ciletuh bs shalat mesjid agung makan warung padang enak murah jajan kakilimanya jg</t>
+          <t>wow dont ask of course labuh ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1218,12 +1218,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Pantai selatan nan indah.perlu penataan.dan pembenahan dengan ke seriusan pemda setempat.agar bisa menjadi obyek wisata andalan.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1233,22 +1233,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>pantai selatan nan indahperlu penataandan pembenahan dengan ke seriusan pemda setempatagar bisa menjadi obyek wisata andalan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'dengan', 'ke', 'seriusan', 'pemda', 'setempatagar', 'bisa', 'menjadi', 'obyek', 'wisata', 'andalan']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'seriusan', 'pemda', 'setempatagar', 'obyek', 'wisata', 'andalan']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>pantai selatan nan indahperlu penataandan benah serius pemda setempatagar obyek wisata andal</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1265,183 +1265,183 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>Bagussss</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lebih rapih dan tertata, untuk saat ini belum dibuka masih dipagar seng</t>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>lebih rapih dan tertata untuk saat ini belum dibuka masih dipagar seng</t>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['lebih', 'rapih', 'dan', 'tertata', 'untuk', 'saat', 'ini', 'belum', 'dibuka', 'masih', 'dipagar', 'seng']</t>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['rapih', 'tertata', 'dibuka', 'dipagar', 'seng']</t>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>rapih tata buka pagar seng</t>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>Jalanya mantap</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>jalanya mantap</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+          <t>jala mantap</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>nongki chill and cheap yg cocok pas sunsetan</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1453,42 +1453,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang merupakan salah satu pantai yang terletak di Pelabuhan Ratu, Kabupaten Sukabumi, Jawa Barat. Pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik. â¦</t>
+          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>pantai batu bintang merupakan salah satu pantai yang terletak di pelabuhan ratu kabupaten sukabumi jawa barat pantai ini terkenal dengan keindahan pantainya yang masih alami dan dihiasi dengan bebatuan yang unik dan menarik â</t>
+          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['pantai', 'batu', 'bintang', 'merupakan', 'salah', 'satu', 'pantai', 'yang', 'terletak', 'di', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'ini', 'terkenal', 'dengan', 'keindahan', 'pantainya', 'yang', 'masih', 'alami', 'dan', 'dihiasi', 'dengan', 'bebatuan', 'yang', 'unik', 'dan', 'menarik', 'â']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['pantai', 'batu', 'bintang', 'salah', 'pantai', 'terletak', 'pelabuhan', 'ratu', 'kabupaten', 'sukabumi', 'jawa', 'barat', 'pantai', 'terkenal', 'keindahan', 'pantainya', 'alami', 'dihiasi', 'bebatuan', 'unik', 'menarik', 'â']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>pantai batu bintang salah pantai letak labuh ratu kabupaten sukabumi jawa barat pantai kenal indah pantai alami hias bebatuan unik tarik</t>
+          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1505,37 +1505,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1547,42 +1547,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ikon kota palabuhanratu......bagus</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ikon kota palabuhanratubagus</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ikon kota palabuhanratubagus</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1594,42 +1594,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wow, don't ask, of course Pelabuhan Ratu beach is the best, from its beautiful atmosphere to its top-notch culinary delights.</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>wow dont ask of course pelabuhan ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>wow dont ask of course labuh ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1641,89 +1641,89 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pasir pantai tidak tajam, lumayan bersih, banyak toilet, kamar mandi dan musola. Harga makanan dan minuman sesuai kantong.</t>
+          <t>Susah wf.sama signal.,..</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>pasir pantai tidak tajam lumayan bersih banyak toilet kamar mandi dan musola harga makanan dan minuman sesuai kantong</t>
+          <t>susah wfsama signal</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['pasir', 'pantai', 'tidak', 'tajam', 'lumayan', 'bersih', 'banyak', 'toilet', 'kamar', 'mandi', 'dan', 'musola', 'harga', 'makanan', 'dan', 'minuman', 'sesuai', 'kantong']</t>
+          <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['pasir', 'pantai', 'tajam', 'lumayan', 'bersih', 'toilet', 'kamar', 'mandi', 'musola', 'harga', 'makanan', 'minuman', 'sesuai', 'kantong']</t>
+          <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>pasir pantai tajam lumayan bersih toilet kamar mandi musola harga makan minum sesuai kantong</t>
+          <t>susah wfsama signal</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1735,12 +1735,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
+          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1750,22 +1750,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
+          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
+          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1775,49 +1775,49 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
+          <t>bagus,,enak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
+          <t>bagusenak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
+          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
+          <t>['bagusenak', 'liburan', 'keluarga']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
+          <t>bagusenak libur keluarga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1829,59 +1829,59 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luas,mudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+          <t>Di kelola oleh oknum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luasmudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
+          <t>di kelola oleh oknum</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['tempat', 'di', 'pelabuhan', 'ratu', 'buat', 'main', 'keluarga', 'cuma', 'jarang', 'tempat', 'untuk', 'berteduh', 'suasana', 'pantai', 'indah', 'banyak', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'lebih', 'di', 'pelihara', 'dan', 'di', 'perindah', 'supaya', 'tempat', 'nya', 'makin', 'bagus']</t>
+          <t>['di', 'kelola', 'oleh', 'oknum']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['pelabuhan', 'ratu', 'main', 'keluarga', 'jarang', 'berteduh', 'suasana', 'pantai', 'indah', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'pelihara', 'perindah', 'nya', 'bagus']</t>
+          <t>['kelola', 'oknum']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>labuh ratu main keluarga jarang teduh suasana pantai indah tukang dagang parkir luasmudah mudah pelihara indah nya bagus</t>
+          <t>kelola oknum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1891,22 +1891,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>bagus,,enak buat liburan bersama keluarga</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1938,22 +1938,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>bagusenak buat liburan bersama keluarga</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['bagusenak', 'liburan', 'keluarga']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>bagusenak libur keluarga</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1970,42 +1970,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2017,42 +2017,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2064,42 +2064,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Di kelola oleh oknum</t>
+          <t>Mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>di kelola oleh oknum</t>
+          <t>mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['di', 'kelola', 'oleh', 'oknum']</t>
+          <t>['mesjid', 'nya', 'bagus', 'tapi', 'sayang', 'banyak', 'itu', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'itu', 'iya', 'itu', 'apa', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['kelola', 'oknum']</t>
+          <t>['mesjid', 'nya', 'bagus', 'sayang', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'iya', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>kelola oknum</t>
+          <t>mesjid nya bagus sayang tuh ih ituloh apasih ya iya ih eta tea naon si arana nyaeta be pokonamah</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2111,12 +2111,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2158,12 +2158,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>Bagus,dan penduduk nya ramah dan baik2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2173,22 +2173,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>bagusdan penduduk nya ramah dan baik</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>bagusdan duduk nya ramah</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2210,37 +2210,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2252,42 +2252,42 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>The place is not as big as other town squares, but the atmosphere is calm and beautiful, the mosque is nice, and the parking is quite good.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2299,42 +2299,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
+          <t>Pagi,siang mlm ramai pedagang smua murah meriah. Buat nongkrong smua usia jgn lupa silakan berkunjung, anda pasti suka....</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
+          <t>pagisiang mlm ramai pedagang smua murah meriah buat nongkrong smua usia jgn lupa silakan berkunjung anda pasti suka</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
+          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'buat', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'anda', 'pasti', 'suka']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
+          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'suka']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
+          <t>pagisiang mlm ramai dagang smua murah riah nongkrong smua usia jgn lupa sila kunjung suka</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2346,42 +2346,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bagus,dan penduduk nya ramah dan baik2</t>
+          <t>The mosque is spacious, the toilets and ablution area are clean. There are many variations of snacks around the town square, but some of them don't really suit my taste. They're a bit strange, different from what I usually eat.. hehehee</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>bagusdan penduduk nya ramah dan baik</t>
+          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
+          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
+          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>bagusdan duduk nya ramah</t>
+          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2393,12 +2393,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jalanya mantap</t>
+          <t>Available milk, diapers, baby supplies, toiletries and staple foods and smashed chicken</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2408,22 +2408,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jalanya mantap</t>
+          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>jala mantap</t>
+          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2433,522 +2433,99 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tempat nya nongkrong anak plara,keren pokonya tmpat nya asik...bnyk hiburn dan permainan anak</t>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tempat nya nongkrong anak plarakeren pokonya tmpat nya asikbnyk hiburn dan permainan anak</t>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'dan', 'permainan', 'anak']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'permainan', 'anak']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>nya nongkrong anak plarakeren poko tmpat nya asikbnyk hiburn main anak</t>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Parkir bayar, tapi ada barang yg hilang. Pas dicek di pantai barang bwaan berkurang. Krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>parkir bayar tapi ada barang yg hilang pas dicek di pantai barang bwaan berkurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['parkir', 'bayar', 'tapi', 'ada', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'di', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
+          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['parkir', 'bayar', 'barang', 'yg', 'hilang', 'pas', 'dicek', 'pantai', 'barang', 'bwaan', 'berkurang', 'krna', 'gbs', 'ngsh', 'bukti', 'jdinya', 'gbs', 'judge', 'jukir', 'nya']</t>
+          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>parkir bayar barang yg hilang pas cek pantai barang bwaan kurang krna gbs ngsh bukti jdinya gbs judge jukir nya</t>
+          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>PANTAI CIBANGBAN</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Pantainya kurang bagus kotor terus parkiranya gaboleh didepan warung sama yg punya warung</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>pantainya kurang bagus kotor terus parkiranya gaboleh didepan warung sama yg punya warung</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>['pantainya', 'kurang', 'bagus', 'kotor', 'terus', 'parkiranya', 'gaboleh', 'didepan', 'warung', 'sama', 'yg', 'punya', 'warung']</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'kotor', 'parkiranya', 'gaboleh', 'didepan', 'warung', 'yg', 'warung']</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>pantai bagus kotor parkiranya gaboleh depan warung yg warung</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Jangilus Monument</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratu..letak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu.</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>tugu jangilus terletak dalam kota kabupaten sukabumi atau terkenal dengan kota kabupaten palabuhan ratuletak yg strategis di perapatan dalam alun alun palabuhan ratu dan depan masjid raya palabuhan ratu tepatnya di pinggir jalan raya palabuhan ratu</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>['tugu', 'jangilus', 'terletak', 'dalam', 'kota', 'kabupaten', 'sukabumi', 'atau', 'terkenal', 'dengan', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'di', 'perapatan', 'dalam', 'alun', 'alun', 'palabuhan', 'ratu', 'dan', 'depan', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'di', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>['tugu', 'jangilus', 'terletak', 'kota', 'kabupaten', 'sukabumi', 'terkenal', 'kota', 'kabupaten', 'palabuhan', 'ratuletak', 'yg', 'strategis', 'perapatan', 'alun', 'alun', 'palabuhan', 'ratu', 'masjid', 'raya', 'palabuhan', 'ratu', 'tepatnya', 'pinggir', 'jalan', 'raya', 'palabuhan', 'ratu']</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>tugu jangilus letak kota kabupaten sukabumi kenal kota kabupaten palabuhan ratuletak yg strategis rapat alun alun palabuhan ratu masjid raya palabuhan ratu tepat pinggir jalan raya palabuhan ratu</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Pantai Karang Sari</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Beautiful beach view while waiting for the sunset. For those who want to swim, be careful because large waves and strong currents sometimes come.</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Pantai Karang Sari</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Pantai Citepus</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Pantainya bersih, yang terpenting harga makanan dan minuman super murah,parkir jg normal..</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>pantainya bersih yang terpenting harga makanan dan minuman super murahparkir jg normal</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bersih', 'yang', 'terpenting', 'harga', 'makanan', 'dan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bersih', 'terpenting', 'harga', 'makanan', 'minuman', 'super', 'murahparkir', 'jg', 'normal']</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>pantai bersih penting harga makan minum super murahparkir jg normal</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Pantai Pelabuhan Ratu</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>The atmosphere is comfortable and pleasant. You can play in the sand on the beach, making it perfect for family outings.</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>DIGI</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>DIGI</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Alun - Alun Palabuhanratu</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Alun - Alun Palabuhanratu</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Alhamdulillahasih bersih, indah apalagi di malam hari, tepat nya di depan majid agung palabuahan ratu, banyak tersedia jajanan juga, ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>alhamdulillahasih bersih indah apalagi di malam hari tepat nya di depan majid agung palabuahan ratu banyak tersedia jajanan juga ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>['alhamdulillahasih', 'bersih', 'indah', 'apalagi', 'di', 'malam', 'hari', 'tepat', 'nya', 'di', 'depan', 'majid', 'agung', 'palabuahan', 'ratu', 'banyak', 'tersedia', 'jajanan', 'juga', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended', 'lah']</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>['alhamdulillahasih', 'bersih', 'indah', 'malam', 'nya', 'majid', 'agung', 'palabuahan', 'ratu', 'tersedia', 'jajanan', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended']</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>alhamdulillahasih bersih indah malam nya majid agung palabuahan ratu sedia jajan ubtuk dar santa denfan keluarga rekomended</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Pantai Batu Bintang</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
+          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
+          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>pake produck gk kecewa kerennnn deh</t>
+          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -513,42 +513,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -560,42 +560,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -607,106 +607,106 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
+          <t>Susah wf.sama signal.,..</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
+          <t>susah wfsama signal</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['susah', 'wfsama', 'signal']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
+          <t>susah wfsama signal</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
+          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
+          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nongki chill and cheap yg cocok pas sunsetan</t>
+          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kotor alun alunnya banyak sampah...mampir ke masjid di alun2 bersih dan nyaman</t>
+          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>kotor alun alunnya banyak sampahmampir ke masjid di alun bersih dan nyaman</t>
+          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['kotor', 'alun', 'alunnya', 'banyak', 'sampahmampir', 'ke', 'masjid', 'di', 'alun', 'bersih', 'dan', 'nyaman']</t>
+          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['kotor', 'alun', 'alunnya', 'sampahmampir', 'masjid', 'alun', 'bersih', 'nyaman']</t>
+          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>kotor alun alun sampahmampir masjid alun bersih nyaman</t>
+          <t>cocok jalanjalan santai ramai sejuk</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -748,42 +748,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
+          <t>A hidden gem, visit at dusk or dawn to watch the sunrise and sunset. It offers one of the best views for sunsets. However, the place is sparsely populated and poorly maintained. The local government should contribute to maintaining and supporting tourism in the Pelabuhan Ratu area.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
+          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the pelabuhan ratu area</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
+          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
+          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
+          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the labuh ratu area</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -795,59 +795,59 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The sunset is really beautiful... If it's a holiday, it's definitely really crowded.</t>
+          <t>Kekayaan alam sukabumi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>the sunset is really beautiful if its a holiday its definitely really crowded</t>
+          <t>kekayaan alam sukabumi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['the', 'sunset', 'is', 'really', 'beautiful', 'if', 'its', 'a', 'holiday', 'its', 'definitely', 'really', 'crowded']</t>
+          <t>['kekayaan', 'alam', 'sukabumi']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['the', 'sunset', 'is', 'really', 'beautiful', 'if', 'its', 'a', 'holiday', 'its', 'definitely', 'really', 'crowded']</t>
+          <t>['kekayaan', 'alam', 'sukabumi']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>the sunset is really beautiful if its a holiday its definitely really crowded</t>
+          <t>kaya alam sukabumi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -857,22 +857,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -889,42 +889,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>The mosque is spacious, the toilets and ablution area are clean. There are many variations of snacks around the town square, but some of them don't really suit my taste. They're a bit strange, different from what I usually eat.. hehehee</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
+          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
+          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>mantaps dah olahraga ringan keluarga</t>
+          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -936,42 +936,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lokasi yg nyaman, bangunannya salah satu yg tahan gempa dengan rujukan dari BNPB. Mudah di akses dari jalan raya. Bisa menginap dengan harga yg terjangkau. Menjadi pusat penelitian ketahanan gempa.</t>
+          <t>The location is comfortable for hanging out waiting for the sunset while drinking pure coconut.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>lokasi yg nyaman bangunannya salah satu yg tahan gempa dengan rujukan dari bnpb mudah di akses dari jalan raya bisa menginap dengan harga yg terjangkau menjadi pusat penelitian ketahanan gempa</t>
+          <t>the location is comfortable for hanging out waiting for the sunset while drinking pure coconut</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'satu', 'yg', 'tahan', 'gempa', 'dengan', 'rujukan', 'dari', 'bnpb', 'mudah', 'di', 'akses', 'dari', 'jalan', 'raya', 'bisa', 'menginap', 'dengan', 'harga', 'yg', 'terjangkau', 'menjadi', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
+          <t>['the', 'location', 'is', 'comfortable', 'for', 'hanging', 'out', 'waiting', 'for', 'the', 'sunset', 'while', 'drinking', 'pure', 'coconut']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'yg', 'tahan', 'gempa', 'rujukan', 'bnpb', 'mudah', 'akses', 'jalan', 'raya', 'menginap', 'harga', 'yg', 'terjangkau', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
+          <t>['the', 'location', 'is', 'comfortable', 'for', 'hanging', 'out', 'waiting', 'for', 'the', 'sunset', 'while', 'drinking', 'pure', 'coconut']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lokasi yg nyaman bangun salah yg tahan gempa rujuk bnpb mudah akses jalan raya inap harga yg jangkau pusat teliti tahan gempa</t>
+          <t>the location is comfortable for hanging out waiting for the sunset while drinking pure coconut</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -983,12 +983,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Accommodating thousands of people, with a nice park and toilet facilities...</t>
+          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -998,22 +998,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>accommodating thousands of people with a nice park and toilet facilities</t>
+          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
+          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['accommodating', 'thousands', 'of', 'people', 'with', 'a', 'nice', 'park', 'and', 'toilet', 'facilities']</t>
+          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>accommodating thousands of people with a nice park and toilet facilities</t>
+          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1030,42 +1030,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Saungnya pada kotor ga nyaman..padahal tempatnya adem..tolong di perhatikan</t>
+          <t>Tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>saungnya pada kotor ga nyamanpadahal tempatnya ademtolong di perhatikan</t>
+          <t>tugu nyah udah di pindahin</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['saungnya', 'pada', 'kotor', 'ga', 'nyamanpadahal', 'tempatnya', 'ademtolong', 'di', 'perhatikan']</t>
+          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['saungnya', 'kotor', 'ga', 'nyamanpadahal', 'tempatnya', 'ademtolong', 'perhatikan']</t>
+          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>saung kotor ga nyamanpadahal tempat ademtolong perhati</t>
+          <t>tugu nyah udah pindahin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,12 +1077,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1092,22 +1092,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1124,42 +1124,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+          <t>Palabuhanratu Square is the center of Palabuhanratu City. It is characterized by a large plot of land. Surrounding it are functional buildings. This square is located in Palabuhanratu Village, Palabuhanratu City District, precisely on Jalan Siliwangi Palabuhanratu, to the east of the Great Mosque of Palabuhanratu.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
+          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
+          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
+          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1171,42 +1171,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wow, don't ask, of course Pelabuhan Ratu beach is the best, from its beautiful atmosphere to its top-notch culinary delights.</t>
+          <t>Alhamdulillahasih bersih, indah apalagi di malam hari, tepat nya di depan majid agung palabuahan ratu, banyak tersedia jajanan juga, ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>wow dont ask of course pelabuhan ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
+          <t>alhamdulillahasih bersih indah apalagi di malam hari tepat nya di depan majid agung palabuahan ratu banyak tersedia jajanan juga ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
+          <t>['alhamdulillahasih', 'bersih', 'indah', 'apalagi', 'di', 'malam', 'hari', 'tepat', 'nya', 'di', 'depan', 'majid', 'agung', 'palabuahan', 'ratu', 'banyak', 'tersedia', 'jajanan', 'juga', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended', 'lah']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['wow', 'dont', 'ask', 'of', 'course', 'pelabuhan', 'ratu', 'beach', 'is', 'the', 'best', 'from', 'its', 'beautiful', 'atmosphere', 'to', 'its', 'topnotch', 'culinary', 'delights']</t>
+          <t>['alhamdulillahasih', 'bersih', 'indah', 'malam', 'nya', 'majid', 'agung', 'palabuahan', 'ratu', 'tersedia', 'jajanan', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>wow dont ask of course labuh ratu beach is the best from its beautiful atmosphere to its topnotch culinary delights</t>
+          <t>alhamdulillahasih bersih indah malam nya majid agung palabuahan ratu sedia jajan ubtuk dar santa denfan keluarga rekomended</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1218,12 +1218,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pantai selatan nan indah.perlu penataan.dan pembenahan dengan ke seriusan pemda setempat.agar bisa menjadi obyek wisata andalan.</t>
+          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1233,22 +1233,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>pantai selatan nan indahperlu penataandan pembenahan dengan ke seriusan pemda setempatagar bisa menjadi obyek wisata andalan</t>
+          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'dengan', 'ke', 'seriusan', 'pemda', 'setempatagar', 'bisa', 'menjadi', 'obyek', 'wisata', 'andalan']</t>
+          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['pantai', 'selatan', 'nan', 'indahperlu', 'penataandan', 'pembenahan', 'seriusan', 'pemda', 'setempatagar', 'obyek', 'wisata', 'andalan']</t>
+          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>pantai selatan nan indahperlu penataandan benah serius pemda setempatagar obyek wisata andal</t>
+          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1265,106 +1265,108 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bagussss</t>
+          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>Please kesini bkn baru pertama kalinya, tp kesekian kalinyað¥° and aku kesini bkn d hari weekand tp d hari biasa, so aku lebih suka suasana sepi hehehe, jd lebih nikmat liat sunsetnyað+ð+, dahal setiap kesini pasti d jalan tolnya ujan tp oas â¦</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>please kesini bkn baru pertama kalinya tp kesekian kalinyað and aku kesini bkn d hari weekand tp d hari biasa so aku lebih suka suasana sepi hehehe jd lebih nikmat liat sunsetnyað ð dahal setiap kesini pasti d jalan tolnya ujan tp oas â</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+          <t>['please', 'kesini', 'bkn', 'baru', 'pertama', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'aku', 'kesini', 'bkn', 'd', 'hari', 'weekand', 'tp', 'd', 'hari', 'biasa', 'so', 'aku', 'lebih', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'lebih', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'setiap', 'kesini', 'pasti', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+          <t>['please', 'kesini', 'bkn', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'kesini', 'bkn', 'd', 'weekand', 'tp', 'd', 'so', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'kesini', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+          <t>please kesini bkn kali tp sekian kali and kesini bkn d weekand tp d so suka suasana sepi hehehe jd nikmat liat sunsetnya dahal kesini d jalan tol ujan tp oas</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jalanya mantap</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1374,22 +1376,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jalanya mantap</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jala mantap</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1399,19 +1401,19 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1421,22 +1423,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1453,42 +1455,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
+          <t>BRI KCP PALABUHAN RATU. Alhamdulillah pelayanan bagus, tempat ramah difabel.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
+          <t>bri kcp palabuhan ratu alhamdulillah pelayanan bagus tempat ramah difabel</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['bri', 'kcp', 'palabuhan', 'ratu', 'alhamdulillah', 'pelayanan', 'bagus', 'tempat', 'ramah', 'difabel']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['bri', 'kcp', 'palabuhan', 'ratu', 'alhamdulillah', 'pelayanan', 'bagus', 'ramah', 'difabel']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
+          <t>bri kcp palabuhan ratu alhamdulillah layan bagus ramah difabel</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1500,59 +1502,59 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Smile hill Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1562,22 +1564,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1594,12 +1596,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1609,22 +1611,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1641,89 +1643,89 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>bagus,,enak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>bagusenak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['bagusenak', 'liburan', 'keluarga']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>bagusenak libur keluarga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Susah wf.sama signal.,..</t>
+          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1735,12 +1737,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
+          <t>Lokasi yg nyaman, bangunannya salah satu yg tahan gempa dengan rujukan dari BNPB. Mudah di akses dari jalan raya. Bisa menginap dengan harga yg terjangkau. Menjadi pusat penelitian ketahanan gempa.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1750,22 +1752,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
+          <t>lokasi yg nyaman bangunannya salah satu yg tahan gempa dengan rujukan dari bnpb mudah di akses dari jalan raya bisa menginap dengan harga yg terjangkau menjadi pusat penelitian ketahanan gempa</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
+          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'satu', 'yg', 'tahan', 'gempa', 'dengan', 'rujukan', 'dari', 'bnpb', 'mudah', 'di', 'akses', 'dari', 'jalan', 'raya', 'bisa', 'menginap', 'dengan', 'harga', 'yg', 'terjangkau', 'menjadi', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
+          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'yg', 'tahan', 'gempa', 'rujukan', 'bnpb', 'mudah', 'akses', 'jalan', 'raya', 'menginap', 'harga', 'yg', 'terjangkau', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
+          <t>lokasi yg nyaman bangun salah yg tahan gempa rujuk bnpb mudah akses jalan raya inap harga yg jangkau pusat teliti tahan gempa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1782,42 +1784,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>bagus,,enak buat liburan bersama keluarga</t>
+          <t>Pagi,siang mlm ramai pedagang smua murah meriah. Buat nongkrong smua usia jgn lupa silakan berkunjung, anda pasti suka....</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>bagusenak buat liburan bersama keluarga</t>
+          <t>pagisiang mlm ramai pedagang smua murah meriah buat nongkrong smua usia jgn lupa silakan berkunjung anda pasti suka</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
+          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'buat', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'anda', 'pasti', 'suka']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['bagusenak', 'liburan', 'keluarga']</t>
+          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'suka']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>bagusenak libur keluarga</t>
+          <t>pagisiang mlm ramai dagang smua murah riah nongkrong smua usia jgn lupa sila kunjung suka</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1834,37 +1836,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Di kelola oleh oknum</t>
+          <t>The beach is clean, and the photo spots are beautiful, with lots of coral reefs. Swimming is also fun and safe. There are also gazebos along the shore that can be rented for resting. However, the toilets here are not very good.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>di kelola oleh oknum</t>
+          <t>the beach is clean and the photo spots are beautiful with lots of coral reefs swimming is also fun and safe there are also gazebos along the shore that can be rented for resting however the toilets here are not very good</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['di', 'kelola', 'oleh', 'oknum']</t>
+          <t>['the', 'beach', 'is', 'clean', 'and', 'the', 'photo', 'spots', 'are', 'beautiful', 'with', 'lots', 'of', 'coral', 'reefs', 'swimming', 'is', 'also', 'fun', 'and', 'safe', 'there', 'are', 'also', 'gazebos', 'along', 'the', 'shore', 'that', 'can', 'be', 'rented', 'for', 'resting', 'however', 'the', 'toilets', 'here', 'are', 'not', 'very', 'good']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['kelola', 'oknum']</t>
+          <t>['the', 'beach', 'is', 'clean', 'and', 'the', 'photo', 'spots', 'are', 'beautiful', 'with', 'lots', 'of', 'coral', 'reefs', 'swimming', 'is', 'also', 'fun', 'and', 'safe', 'there', 'are', 'also', 'gazebos', 'along', 'the', 'shore', 'that', 'can', 'be', 'rented', 'for', 'resting', 'however', 'the', 'toilets', 'here', 'are', 'not', 'very', 'good']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>kelola oknum</t>
+          <t>the beach is clean and the photo spots are beautiful with lots of coral reefs swimming is also fun and safe there are also gazebos along the shore that can be rented for resting however the toilets here are not very good</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1876,42 +1878,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>Jajahannya banyak pilihan dan enak ð Tahu crispy juara, sate padang juga mantul, cilok lumayan, cilor enak, pisang keju enak, sate2 an enak, waduh kalap pokoknya â¦</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>jajahannya banyak pilihan dan enak ð tahu crispy juara sate padang juga mantul cilok lumayan cilor enak pisang keju enak sate an enak waduh kalap pokoknya â</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['jajahannya', 'banyak', 'pilihan', 'dan', 'enak', 'ð', 'tahu', 'crispy', 'juara', 'sate', 'padang', 'juga', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'waduh', 'kalap', 'pokoknya', 'â']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['jajahannya', 'pilihan', 'enak', 'ð', 'crispy', 'juara', 'sate', 'padang', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'kalap', 'pokoknya', 'â']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>jajah pilih enak crispy juara sate padang mantul cilok lumayan cilor enak pisang keju enak sate an enak kalap pokok</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1923,12 +1925,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>The sunset is really beautiful... If it's a holiday, it's definitely really crowded.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1938,22 +1940,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>the sunset is really beautiful if its a holiday its definitely really crowded</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['the', 'sunset', 'is', 'really', 'beautiful', 'if', 'its', 'a', 'holiday', 'its', 'definitely', 'really', 'crowded']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['the', 'sunset', 'is', 'really', 'beautiful', 'if', 'its', 'a', 'holiday', 'its', 'definitely', 'really', 'crowded']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>the sunset is really beautiful if its a holiday its definitely really crowded</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1970,12 +1972,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Sdh mulai banyak kerusakan. Terutama pada area olahraga. Kurang terawat tidak seperti awal awal</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1985,22 +1987,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>sdh mulai banyak kerusakan terutama pada area olahraga kurang terawat tidak seperti awal awal</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['sdh', 'mulai', 'banyak', 'kerusakan', 'terutama', 'pada', 'area', 'olahraga', 'kurang', 'terawat', 'tidak', 'seperti', 'awal', 'awal']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['sdh', 'kerusakan', 'area', 'olahraga', 'terawat']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>sdh rusa area olahraga awat</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2017,12 +2019,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
+          <t>Pasir pantai tidak tajam, lumayan bersih, banyak toilet, kamar mandi dan musola. Harga makanan dan minuman sesuai kantong.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2032,22 +2034,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
+          <t>pasir pantai tidak tajam lumayan bersih banyak toilet kamar mandi dan musola harga makanan dan minuman sesuai kantong</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
+          <t>['pasir', 'pantai', 'tidak', 'tajam', 'lumayan', 'bersih', 'banyak', 'toilet', 'kamar', 'mandi', 'dan', 'musola', 'harga', 'makanan', 'dan', 'minuman', 'sesuai', 'kantong']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
+          <t>['pasir', 'pantai', 'tajam', 'lumayan', 'bersih', 'toilet', 'kamar', 'mandi', 'musola', 'harga', 'makanan', 'minuman', 'sesuai', 'kantong']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
+          <t>pasir pantai tajam lumayan bersih toilet kamar mandi musola harga makan minum sesuai kantong</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2064,42 +2066,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
+          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
+          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['mesjid', 'nya', 'bagus', 'tapi', 'sayang', 'banyak', 'itu', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'itu', 'iya', 'itu', 'apa', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['mesjid', 'nya', 'bagus', 'sayang', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'iya', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>mesjid nya bagus sayang tuh ih ituloh apasih ya iya ih eta tea naon si arana nyaeta be pokonamah</t>
+          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2111,42 +2113,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
+          <t>Nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak  mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang  sebab ada oknum pedagang terutama pedagang  gorengan ada bapa bapa yang menjual /mencampur gorengan sisa hari kemarinnya,yang diangetin lagi hingga  terasa keras dan basi.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
+          <t>nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang sebab ada oknum pedagang terutama pedagang gorengan ada bapa bapa yang menjual mencampur gorengan sisa hari kemarinnyayang diangetin lagi hingga terasa keras dan basi</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
+          <t>['nyaman', 'untuk', 'nyari', 'kuliner', 'cuma', 'tolong', 'ditertibkan', 'para', 'pedagangnya', 'supaya', 'tidak', 'mengganggu', 'lalu', 'lintas', 'juga', 'rasanya', 'harus', 'ada', 'pembinaan', 'pada', 'para', 'pedagang', 'sebab', 'ada', 'oknum', 'pedagang', 'terutama', 'pedagang', 'gorengan', 'ada', 'bapa', 'bapa', 'yang', 'menjual', 'mencampur', 'gorengan', 'sisa', 'hari', 'kemarinnyayang', 'diangetin', 'lagi', 'hingga', 'terasa', 'keras', 'dan', 'basi']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
+          <t>['nyaman', 'nyari', 'kuliner', 'tolong', 'ditertibkan', 'pedagangnya', 'mengganggu', 'lintas', 'pembinaan', 'pedagang', 'oknum', 'pedagang', 'pedagang', 'gorengan', 'bapa', 'bapa', 'menjual', 'mencampur', 'gorengan', 'sisa', 'kemarinnyayang', 'diangetin', 'keras', 'basi']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
+          <t>nyaman nyari kuliner tolong tertib dagang ganggu lintas bina dagang oknum dagang dagang goreng bapa bapa jual campur goreng sisa kemarinnyayang diangetin keras basi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2163,37 +2165,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bagus,dan penduduk nya ramah dan baik2</t>
+          <t>Di kelola oleh oknum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>bagusdan penduduk nya ramah dan baik</t>
+          <t>di kelola oleh oknum</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
+          <t>['di', 'kelola', 'oleh', 'oknum']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
+          <t>['kelola', 'oknum']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>bagusdan duduk nya ramah</t>
+          <t>kelola oknum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2205,42 +2207,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>Bagussss</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['bagussss']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>bagussss</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2252,42 +2254,42 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The place is not as big as other town squares, but the atmosphere is calm and beautiful, the mosque is nice, and the parking is quite good.</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2299,42 +2301,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pagi,siang mlm ramai pedagang smua murah meriah. Buat nongkrong smua usia jgn lupa silakan berkunjung, anda pasti suka....</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>pagisiang mlm ramai pedagang smua murah meriah buat nongkrong smua usia jgn lupa silakan berkunjung anda pasti suka</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'buat', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'anda', 'pasti', 'suka']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'suka']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>pagisiang mlm ramai dagang smua murah riah nongkrong smua usia jgn lupa sila kunjung suka</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2346,12 +2348,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The mosque is spacious, the toilets and ablution area are clean. There are many variations of snacks around the town square, but some of them don't really suit my taste. They're a bit strange, different from what I usually eat.. hehehee</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2361,22 +2363,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2393,12 +2395,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Available milk, diapers, baby supplies, toiletries and staple foods and smashed chicken</t>
+          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2408,22 +2410,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
+          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['available', 'milk', 'diapers', 'baby', 'supplies', 'toiletries', 'and', 'staple', 'foods', 'and', 'smashed', 'chicken']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>available milk diapers baby supplies toiletries and staple foods and smashed chicken</t>
+          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2440,92 +2442,609 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
+          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
+          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
+          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
+          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
+          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Wisata Alam Pantai Sukawayana</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Bagus,dan penduduk nya ramah dan baik2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>bagusdan penduduk nya ramah dan baik</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>bagusdan duduk nya ramah</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Tempat nya nongkrong anak plara,keren pokonya tmpat nya asik...bnyk hiburn dan permainan anak</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>tempat nya nongkrong anak plarakeren pokonya tmpat nya asikbnyk hiburn dan permainan anak</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>['tempat', 'nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'dan', 'permainan', 'anak']</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>['nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'permainan', 'anak']</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>nya nongkrong anak plarakeren poko tmpat nya asikbnyk hiburn main anak</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PANTAI CIBANGBAN</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>untuk  harga masuk motor 10k, mobil 20k, mobil travel 30k bis kecil 50k, bis besar 100k menurutku dengan harga segini udah worth it banget sih karna pantai dan pemandangannya ga mainmain bener2 sekeren itu bikin betah seharian</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>untuk harga masuk motor k mobil k mobil travel k bis kecil k bis besar k menurutku dengan harga segini udah worth it banget sih karna pantai dan pemandangannya ga mainmain bener sekeren itu bikin betah seharian</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>['untuk', 'harga', 'masuk', 'motor', 'k', 'mobil', 'k', 'mobil', 'travel', 'k', 'bis', 'kecil', 'k', 'bis', 'besar', 'k', 'menurutku', 'dengan', 'harga', 'segini', 'udah', 'worth', 'it', 'banget', 'sih', 'karna', 'pantai', 'dan', 'pemandangannya', 'ga', 'mainmain', 'bener', 'sekeren', 'itu', 'bikin', 'betah', 'seharian']</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>['harga', 'masuk', 'motor', 'k', 'mobil', 'k', 'mobil', 'travel', 'k', 'bis', 'k', 'bis', 'k', 'menurutku', 'harga', 'segini', 'udah', 'worth', 'it', 'banget', 'sih', 'karna', 'pantai', 'pemandangannya', 'ga', 'mainmain', 'bener', 'sekeren', 'bikin', 'betah', 'seharian']</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>harga masuk motor k mobil k mobil travel k bis k bis k turut harga gin udah worth it banget sih karna pantai pandang ga mainmain bener keren bikin betah hari</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Kondisi lapang lumayan baik. Track lari sedikit rusak. Lari pagi di hari minggu tidak terlalu padat</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>kondisi lapang lumayan baik track lari sedikit rusak lari pagi di hari minggu tidak terlalu padat</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>['kondisi', 'lapang', 'lumayan', 'baik', 'track', 'lari', 'sedikit', 'rusak', 'lari', 'pagi', 'di', 'hari', 'minggu', 'tidak', 'terlalu', 'padat']</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>['kondisi', 'lapang', 'lumayan', 'track', 'lari', 'rusak', 'lari', 'pagi', 'minggu', 'padat']</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>kondisi lapang lumayan track lari rusak lari pagi minggu padat</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Alun - Alun Palabuhanratu</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Bagus ada masjidnya ada lapangannya dan jualannya juga cuman Memang karena sekarang lagi Corona jadi agak sepi cuman sekarang udah lumayan mulai kembali banyak orang sih ke alun-alun ini tempat pusatnya pelabuhanratu gitu selain pantainya â¦</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>bagus ada masjidnya ada lapangannya dan jualannya juga cuman memang karena sekarang lagi corona jadi agak sepi cuman sekarang udah lumayan mulai kembali banyak orang sih ke alunalun ini tempat pusatnya pelabuhanratu gitu selain pantainya â</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>['bagus', 'ada', 'masjidnya', 'ada', 'lapangannya', 'dan', 'jualannya', 'juga', 'cuman', 'memang', 'karena', 'sekarang', 'lagi', 'corona', 'jadi', 'agak', 'sepi', 'cuman', 'sekarang', 'udah', 'lumayan', 'mulai', 'kembali', 'banyak', 'orang', 'sih', 'ke', 'alunalun', 'ini', 'tempat', 'pusatnya', 'pelabuhanratu', 'gitu', 'selain', 'pantainya', 'â']</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>['bagus', 'masjidnya', 'lapangannya', 'jualannya', 'cuman', 'corona', 'sepi', 'cuman', 'udah', 'lumayan', 'orang', 'sih', 'alunalun', 'pusatnya', 'pelabuhanratu', 'gitu', 'pantainya', 'â']</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>bagus masjid lapang jual cuman corona sepi cuman udah lumayan orang sih alunalun pusat pelabuhanratu gitu pantai</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Pantai Karang Sari</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Beautiful beach view while waiting for the sunset. For those who want to swim, be careful because large waves and strong currents sometimes come.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PANTAI CIBANGBAN</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Pantainya kurang bagus kotor terus parkiranya gaboleh didepan warung sama yg punya warung</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>pantainya kurang bagus kotor terus parkiranya gaboleh didepan warung sama yg punya warung</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>['pantainya', 'kurang', 'bagus', 'kotor', 'terus', 'parkiranya', 'gaboleh', 'didepan', 'warung', 'sama', 'yg', 'punya', 'warung']</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>['pantainya', 'bagus', 'kotor', 'parkiranya', 'gaboleh', 'didepan', 'warung', 'yg', 'warung']</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>pantai bagus kotor parkiranya gaboleh depan warung yg warung</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Pantai Karang Sari</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Pantai Batu Bintang</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
+          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
+          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
+          <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
+          <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
+          <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -513,12 +513,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -560,42 +560,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Good. Parking is free. Toilets are 2,000 yen. Degan is 15,000 yen. No entrance fee. The waves are quite big. There are horses and ATVs.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>good parking is free toilets are yen degan is yen no entrance fee the waves are quite big there are horses and atvs</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['good', 'parking', 'is', 'free', 'toilets', 'are', 'yen', 'degan', 'is', 'yen', 'no', 'entrance', 'fee', 'the', 'waves', 'are', 'quite', 'big', 'there', 'are', 'horses', 'and', 'atvs']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['good', 'parking', 'is', 'free', 'toilets', 'are', 'yen', 'degan', 'is', 'yen', 'no', 'entrance', 'fee', 'the', 'waves', 'are', 'quite', 'big', 'there', 'are', 'horses', 'and', 'atvs']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>good parking is free toilets are yen degan is yen no entrance fee the waves are quite big there are horses and atvs</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -607,42 +607,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Susah wf.sama signal.,..</t>
+          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['susah', 'wfsama', 'signal']</t>
+          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>susah wfsama signal</t>
+          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -654,59 +654,59 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
+          <t>Di kelola oleh oknum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
+          <t>di kelola oleh oknum</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['di', 'kelola', 'oleh', 'oknum']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['kelola', 'oknum']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
+          <t>kelola oknum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>cocok jalanjalan santai ramai sejuk</t>
+          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -741,49 +741,49 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A hidden gem, visit at dusk or dawn to watch the sunrise and sunset. It offers one of the best views for sunsets. However, the place is sparsely populated and poorly maintained. The local government should contribute to maintaining and supporting tourism in the Pelabuhan Ratu area.</t>
+          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the pelabuhan ratu area</t>
+          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
+          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
+          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the labuh ratu area</t>
+          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -795,47 +795,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kekayaan alam sukabumi</t>
+          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>kekayaan alam sukabumi</t>
+          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['kekayaan', 'alam', 'sukabumi']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['kekayaan', 'alam', 'sukabumi']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>kaya alam sukabumi</t>
+          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
@@ -889,42 +889,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The mosque is spacious, the toilets and ablution area are clean. There are many variations of snacks around the town square, but some of them don't really suit my taste. They're a bit strange, different from what I usually eat.. hehehee</t>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -936,12 +936,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The location is comfortable for hanging out waiting for the sunset while drinking pure coconut.</t>
+          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -951,22 +951,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>the location is comfortable for hanging out waiting for the sunset while drinking pure coconut</t>
+          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['the', 'location', 'is', 'comfortable', 'for', 'hanging', 'out', 'waiting', 'for', 'the', 'sunset', 'while', 'drinking', 'pure', 'coconut']</t>
+          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['the', 'location', 'is', 'comfortable', 'for', 'hanging', 'out', 'waiting', 'for', 'the', 'sunset', 'while', 'drinking', 'pure', 'coconut']</t>
+          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>the location is comfortable for hanging out waiting for the sunset while drinking pure coconut</t>
+          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -983,42 +983,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
+          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
+          <t>mantaps dah buat olahraga ringan sama keluarga</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
+          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
+          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
+          <t>mantaps dah olahraga ringan keluarga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1030,42 +1030,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tugu nyah udah di pindahin</t>
+          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>tugu nyah udah di pindahin</t>
+          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
+          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
+          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tugu nyah udah pindahin</t>
+          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,12 +1077,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
+          <t>bagus,,enak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1092,22 +1092,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
+          <t>bagusenak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
+          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
+          <t>['bagusenak', 'liburan', 'keluarga']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
+          <t>bagusenak libur keluarga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1124,12 +1124,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Palabuhanratu Square is the center of Palabuhanratu City. It is characterized by a large plot of land. Surrounding it are functional buildings. This square is located in Palabuhanratu Village, Palabuhanratu City District, precisely on Jalan Siliwangi Palabuhanratu, to the east of the Great Mosque of Palabuhanratu.</t>
+          <t>The beach is clean, and the photo spots are beautiful, with lots of coral reefs. Swimming is also fun and safe. There are also gazebos along the shore that can be rented for resting. However, the toilets here are not very good.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1139,22 +1139,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
+          <t>the beach is clean and the photo spots are beautiful with lots of coral reefs swimming is also fun and safe there are also gazebos along the shore that can be rented for resting however the toilets here are not very good</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
+          <t>['the', 'beach', 'is', 'clean', 'and', 'the', 'photo', 'spots', 'are', 'beautiful', 'with', 'lots', 'of', 'coral', 'reefs', 'swimming', 'is', 'also', 'fun', 'and', 'safe', 'there', 'are', 'also', 'gazebos', 'along', 'the', 'shore', 'that', 'can', 'be', 'rented', 'for', 'resting', 'however', 'the', 'toilets', 'here', 'are', 'not', 'very', 'good']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
+          <t>['the', 'beach', 'is', 'clean', 'and', 'the', 'photo', 'spots', 'are', 'beautiful', 'with', 'lots', 'of', 'coral', 'reefs', 'swimming', 'is', 'also', 'fun', 'and', 'safe', 'there', 'are', 'also', 'gazebos', 'along', 'the', 'shore', 'that', 'can', 'be', 'rented', 'for', 'resting', 'however', 'the', 'toilets', 'here', 'are', 'not', 'very', 'good']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
+          <t>the beach is clean and the photo spots are beautiful with lots of coral reefs swimming is also fun and safe there are also gazebos along the shore that can be rented for resting however the toilets here are not very good</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1171,12 +1171,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alhamdulillahasih bersih, indah apalagi di malam hari, tepat nya di depan majid agung palabuahan ratu, banyak tersedia jajanan juga, ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
+          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1186,22 +1186,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>alhamdulillahasih bersih indah apalagi di malam hari tepat nya di depan majid agung palabuahan ratu banyak tersedia jajanan juga ubtuk sekedar bersantai denfan keluarga rekomended lah</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['alhamdulillahasih', 'bersih', 'indah', 'apalagi', 'di', 'malam', 'hari', 'tepat', 'nya', 'di', 'depan', 'majid', 'agung', 'palabuahan', 'ratu', 'banyak', 'tersedia', 'jajanan', 'juga', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended', 'lah']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['alhamdulillahasih', 'bersih', 'indah', 'malam', 'nya', 'majid', 'agung', 'palabuahan', 'ratu', 'tersedia', 'jajanan', 'ubtuk', 'sekedar', 'bersantai', 'denfan', 'keluarga', 'rekomended']</t>
+          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>alhamdulillahasih bersih indah malam nya majid agung palabuahan ratu sedia jajan ubtuk dar santa denfan keluarga rekomended</t>
+          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1218,138 +1218,136 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
+          <t>Baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya. Detail bajunya bagus banget</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
+          <t>baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya detail bajunya bagus banget</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['baju', 'baju', 'yg', 'tetsedia', 'untuk', 'di', 'sewakan', 'sangat', 'bagus', 'dan', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'dengan', 'ke', 'inginan', 'saya', 'detail', 'bajunya', 'bagus', 'banget']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['baju', 'baju', 'yg', 'tetsedia', 'sewakan', 'bagus', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'inginan', 'detail', 'bajunya', 'bagus', 'banget']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
+          <t>baju baju yg tetsedia sewa bagus riquesan buat baju nya sesuai banget ingin detail baju bagus banget</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lumayan bagus dibanding pantai lain dijabar. Sedikit agak bersih dibanding pangandaran yg banyak sampah. Semoga kedepan nya semakin tambah bagus</t>
+          <t>Alun Alun Pelabuhan Ratu Sukabumi adalah tempat yang menawan dengan pesona alamnya. Keindahan alun-alun dan pemandangan laut yang menakjubkan membuatnya menjadi tempat yang pas untuk bersantai. Suasana tenang dan sejuk di sekitar area ini â¦</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>lumayan bagus dibanding pantai lain dijabar sedikit agak bersih dibanding pangandaran yg banyak sampah semoga kedepan nya semakin tambah bagus</t>
+          <t>alun alun pelabuhan ratu sukabumi adalah tempat yang menawan dengan pesona alamnya keindahan alunalun dan pemandangan laut yang menakjubkan membuatnya menjadi tempat yang pas untuk bersantai suasana tenang dan sejuk di sekitar area ini â</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'lain', 'dijabar', 'sedikit', 'agak', 'bersih', 'dibanding', 'pangandaran', 'yg', 'banyak', 'sampah', 'semoga', 'kedepan', 'nya', 'semakin', 'tambah', 'bagus']</t>
+          <t>['alun', 'alun', 'pelabuhan', 'ratu', 'sukabumi', 'adalah', 'tempat', 'yang', 'menawan', 'dengan', 'pesona', 'alamnya', 'keindahan', 'alunalun', 'dan', 'pemandangan', 'laut', 'yang', 'menakjubkan', 'membuatnya', 'menjadi', 'tempat', 'yang', 'pas', 'untuk', 'bersantai', 'suasana', 'tenang', 'dan', 'sejuk', 'di', 'sekitar', 'area', 'ini', 'â']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['lumayan', 'bagus', 'dibanding', 'pantai', 'dijabar', 'bersih', 'dibanding', 'pangandaran', 'yg', 'sampah', 'semoga', 'kedepan', 'nya', 'bagus']</t>
+          <t>['alun', 'alun', 'pelabuhan', 'ratu', 'sukabumi', 'menawan', 'pesona', 'alamnya', 'keindahan', 'alunalun', 'pemandangan', 'laut', 'menakjubkan', 'membuatnya', 'pas', 'bersantai', 'suasana', 'tenang', 'sejuk', 'area', 'â']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>lumayan bagus banding pantai jabar bersih banding pangandaran yg sampah moga depan nya bagus</t>
+          <t>alun alun labuh ratu sukabumi tawan pesona alam indah alunalun pandang laut takjub buat pas santa suasana tenang sejuk area</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Please kesini bkn baru pertama kalinya, tp kesekian kalinyað¥° and aku kesini bkn d hari weekand tp d hari biasa, so aku lebih suka suasana sepi hehehe, jd lebih nikmat liat sunsetnyað-ð-, dahal setiap kesini pasti d jalan tolnya ujan tp oas â¦</t>
+          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>please kesini bkn baru pertama kalinya tp kesekian kalinyað and aku kesini bkn d hari weekand tp d hari biasa so aku lebih suka suasana sepi hehehe jd lebih nikmat liat sunsetnyað ð dahal setiap kesini pasti d jalan tolnya ujan tp oas â</t>
+          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['please', 'kesini', 'bkn', 'baru', 'pertama', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'aku', 'kesini', 'bkn', 'd', 'hari', 'weekand', 'tp', 'd', 'hari', 'biasa', 'so', 'aku', 'lebih', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'lebih', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'setiap', 'kesini', 'pasti', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
+          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['please', 'kesini', 'bkn', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'kesini', 'bkn', 'd', 'weekand', 'tp', 'd', 'so', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'kesini', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
+          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>please kesini bkn kali tp sekian kali and kesini bkn d weekand tp d so suka suasana sepi hehehe jd nikmat liat sunsetnya dahal kesini d jalan tol ujan tp oas</t>
+          <t>nongki chill and cheap yg cocok pas sunsetan</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1361,42 +1359,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1408,42 +1406,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>Bagus ada masjidnya ada lapangannya dan jualannya juga cuman Memang karena sekarang lagi Corona jadi agak sepi cuman sekarang udah lumayan mulai kembali banyak orang sih ke alun-alun ini tempat pusatnya pelabuhanratu gitu selain pantainya â¦</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+          <t>bagus ada masjidnya ada lapangannya dan jualannya juga cuman memang karena sekarang lagi corona jadi agak sepi cuman sekarang udah lumayan mulai kembali banyak orang sih ke alunalun ini tempat pusatnya pelabuhanratu gitu selain pantainya â</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+          <t>['bagus', 'ada', 'masjidnya', 'ada', 'lapangannya', 'dan', 'jualannya', 'juga', 'cuman', 'memang', 'karena', 'sekarang', 'lagi', 'corona', 'jadi', 'agak', 'sepi', 'cuman', 'sekarang', 'udah', 'lumayan', 'mulai', 'kembali', 'banyak', 'orang', 'sih', 'ke', 'alunalun', 'ini', 'tempat', 'pusatnya', 'pelabuhanratu', 'gitu', 'selain', 'pantainya', 'â']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+          <t>['bagus', 'masjidnya', 'lapangannya', 'jualannya', 'cuman', 'corona', 'sepi', 'cuman', 'udah', 'lumayan', 'orang', 'sih', 'alunalun', 'pusatnya', 'pelabuhanratu', 'gitu', 'pantainya', 'â']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+          <t>bagus masjid lapang jual cuman corona sepi cuman udah lumayan orang sih alunalun pusat pelabuhanratu gitu pantai</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1455,42 +1453,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BRI KCP PALABUHAN RATU. Alhamdulillah pelayanan bagus, tempat ramah difabel.</t>
+          <t>Visited on September 24th, 2022 at 7 AM, it was still quiet, free admission, car parking 10,000 Rupiah, toilets 5,000 Rupiah. The view is great, especially if you go up to Batu Bintang Hydroelectric Power Plant, the waves are not as big as at Karanghawu, children can still get wet with supervision.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>bri kcp palabuhan ratu alhamdulillah pelayanan bagus tempat ramah difabel</t>
+          <t>visited on september th at am it was still quiet free admission car parking rupiah toilets rupiah the view is great especially if you go up to batu bintang hydroelectric power plant the waves are not as big as at karanghawu children can still get wet with supervision</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['bri', 'kcp', 'palabuhan', 'ratu', 'alhamdulillah', 'pelayanan', 'bagus', 'tempat', 'ramah', 'difabel']</t>
+          <t>['visited', 'on', 'september', 'th', 'at', 'am', 'it', 'was', 'still', 'quiet', 'free', 'admission', 'car', 'parking', 'rupiah', 'toilets', 'rupiah', 'the', 'view', 'is', 'great', 'especially', 'if', 'you', 'go', 'up', 'to', 'batu', 'bintang', 'hydroelectric', 'power', 'plant', 'the', 'waves', 'are', 'not', 'as', 'big', 'as', 'at', 'karanghawu', 'children', 'can', 'still', 'get', 'wet', 'with', 'supervision']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['bri', 'kcp', 'palabuhan', 'ratu', 'alhamdulillah', 'pelayanan', 'bagus', 'ramah', 'difabel']</t>
+          <t>['visited', 'on', 'september', 'th', 'at', 'am', 'it', 'was', 'still', 'quiet', 'free', 'admission', 'car', 'parking', 'rupiah', 'toilets', 'rupiah', 'the', 'view', 'is', 'great', 'especially', 'if', 'you', 'go', 'up', 'to', 'batu', 'bintang', 'hydroelectric', 'power', 'plant', 'the', 'waves', 'are', 'not', 'as', 'big', 'as', 'at', 'karanghawu', 'children', 'can', 'still', 'get', 'wet', 'with', 'supervision']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>bri kcp palabuhan ratu alhamdulillah layan bagus ramah difabel</t>
+          <t>visited on september th at am it was still quiet free admission car parking rupiah toilets rupiah the view is great especially if you go up to batu bintang hydroelectric power plant the waves are not as big as at karanghawu children can still get wet with supervision</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1502,89 +1500,89 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>Ikon kota palabuhanratu......bagus</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>ikon kota palabuhanratubagus</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+          <t>ikon kota palabuhanratubagus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
+          <t>Pantai nya lumayan cuma banyak pengamenya</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
+          <t>pantai nya lumayan cuma banyak pengamenya</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
+          <t>['pantai', 'nya', 'lumayan', 'cuma', 'banyak', 'pengamenya']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
+          <t>['pantai', 'nya', 'lumayan', 'pengamenya']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
+          <t>pantai nya lumayan pengamenya</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1596,89 +1594,89 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bagus,,enak buat liburan bersama keluarga</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>bagusenak buat liburan bersama keluarga</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['bagusenak', 'liburan', 'keluarga']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>bagusenak libur keluarga</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1690,42 +1688,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
+          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
+          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
+          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1737,89 +1735,89 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lokasi yg nyaman, bangunannya salah satu yg tahan gempa dengan rujukan dari BNPB. Mudah di akses dari jalan raya. Bisa menginap dengan harga yg terjangkau. Menjadi pusat penelitian ketahanan gempa.</t>
+          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>lokasi yg nyaman bangunannya salah satu yg tahan gempa dengan rujukan dari bnpb mudah di akses dari jalan raya bisa menginap dengan harga yg terjangkau menjadi pusat penelitian ketahanan gempa</t>
+          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'satu', 'yg', 'tahan', 'gempa', 'dengan', 'rujukan', 'dari', 'bnpb', 'mudah', 'di', 'akses', 'dari', 'jalan', 'raya', 'bisa', 'menginap', 'dengan', 'harga', 'yg', 'terjangkau', 'menjadi', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
+          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['lokasi', 'yg', 'nyaman', 'bangunannya', 'salah', 'yg', 'tahan', 'gempa', 'rujukan', 'bnpb', 'mudah', 'akses', 'jalan', 'raya', 'menginap', 'harga', 'yg', 'terjangkau', 'pusat', 'penelitian', 'ketahanan', 'gempa']</t>
+          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>lokasi yg nyaman bangun salah yg tahan gempa rujuk bnpb mudah akses jalan raya inap harga yg jangkau pusat teliti tahan gempa</t>
+          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pagi,siang mlm ramai pedagang smua murah meriah. Buat nongkrong smua usia jgn lupa silakan berkunjung, anda pasti suka....</t>
+          <t>Lapangannya luas,rapih, bersih,di tata dengan sangat bagus,penyuluh sosial masyarakat kab sukabumi,mengikuti upacara hari jadi Sukabumi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>pagisiang mlm ramai pedagang smua murah meriah buat nongkrong smua usia jgn lupa silakan berkunjung anda pasti suka</t>
+          <t>lapangannya luasrapih bersihdi tata dengan sangat baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara hari jadi sukabumi</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'buat', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'anda', 'pasti', 'suka']</t>
+          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'dengan', 'sangat', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'hari', 'jadi', 'sukabumi']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'suka']</t>
+          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'sukabumi']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>pagisiang mlm ramai dagang smua murah riah nongkrong smua usia jgn lupa sila kunjung suka</t>
+          <t>lapang luasrapih bersihdi tata baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara sukabumi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1831,42 +1829,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The beach is clean, and the photo spots are beautiful, with lots of coral reefs. Swimming is also fun and safe. There are also gazebos along the shore that can be rented for resting. However, the toilets here are not very good.</t>
+          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>the beach is clean and the photo spots are beautiful with lots of coral reefs swimming is also fun and safe there are also gazebos along the shore that can be rented for resting however the toilets here are not very good</t>
+          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'clean', 'and', 'the', 'photo', 'spots', 'are', 'beautiful', 'with', 'lots', 'of', 'coral', 'reefs', 'swimming', 'is', 'also', 'fun', 'and', 'safe', 'there', 'are', 'also', 'gazebos', 'along', 'the', 'shore', 'that', 'can', 'be', 'rented', 'for', 'resting', 'however', 'the', 'toilets', 'here', 'are', 'not', 'very', 'good']</t>
+          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'clean', 'and', 'the', 'photo', 'spots', 'are', 'beautiful', 'with', 'lots', 'of', 'coral', 'reefs', 'swimming', 'is', 'also', 'fun', 'and', 'safe', 'there', 'are', 'also', 'gazebos', 'along', 'the', 'shore', 'that', 'can', 'be', 'rented', 'for', 'resting', 'however', 'the', 'toilets', 'here', 'are', 'not', 'very', 'good']</t>
+          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>the beach is clean and the photo spots are beautiful with lots of coral reefs swimming is also fun and safe there are also gazebos along the shore that can be rented for resting however the toilets here are not very good</t>
+          <t>pake produck gk kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1878,42 +1876,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jajahannya banyak pilihan dan enak ð Tahu crispy juara, sate padang juga mantul, cilok lumayan, cilor enak, pisang keju enak, sate2 an enak, waduh kalap pokoknya â¦</t>
+          <t>Sdh mulai banyak kerusakan. Terutama pada area olahraga. Kurang terawat tidak seperti awal awal</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jajahannya banyak pilihan dan enak ð tahu crispy juara sate padang juga mantul cilok lumayan cilor enak pisang keju enak sate an enak waduh kalap pokoknya â</t>
+          <t>sdh mulai banyak kerusakan terutama pada area olahraga kurang terawat tidak seperti awal awal</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['jajahannya', 'banyak', 'pilihan', 'dan', 'enak', 'ð', 'tahu', 'crispy', 'juara', 'sate', 'padang', 'juga', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'waduh', 'kalap', 'pokoknya', 'â']</t>
+          <t>['sdh', 'mulai', 'banyak', 'kerusakan', 'terutama', 'pada', 'area', 'olahraga', 'kurang', 'terawat', 'tidak', 'seperti', 'awal', 'awal']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['jajahannya', 'pilihan', 'enak', 'ð', 'crispy', 'juara', 'sate', 'padang', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'kalap', 'pokoknya', 'â']</t>
+          <t>['sdh', 'kerusakan', 'area', 'olahraga', 'terawat']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>jajah pilih enak crispy juara sate padang mantul cilok lumayan cilor enak pisang keju enak sate an enak kalap pokok</t>
+          <t>sdh rusa area olahraga awat</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1925,42 +1923,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The sunset is really beautiful... If it's a holiday, it's definitely really crowded.</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>the sunset is really beautiful if its a holiday its definitely really crowded</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['the', 'sunset', 'is', 'really', 'beautiful', 'if', 'its', 'a', 'holiday', 'its', 'definitely', 'really', 'crowded']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['the', 'sunset', 'is', 'really', 'beautiful', 'if', 'its', 'a', 'holiday', 'its', 'definitely', 'really', 'crowded']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>the sunset is really beautiful if its a holiday its definitely really crowded</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1972,12 +1970,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Smile hill Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sdh mulai banyak kerusakan. Terutama pada area olahraga. Kurang terawat tidak seperti awal awal</t>
+          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1987,22 +1985,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>sdh mulai banyak kerusakan terutama pada area olahraga kurang terawat tidak seperti awal awal</t>
+          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['sdh', 'mulai', 'banyak', 'kerusakan', 'terutama', 'pada', 'area', 'olahraga', 'kurang', 'terawat', 'tidak', 'seperti', 'awal', 'awal']</t>
+          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['sdh', 'kerusakan', 'area', 'olahraga', 'terawat']</t>
+          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>sdh rusa area olahraga awat</t>
+          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2019,42 +2017,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pasir pantai tidak tajam, lumayan bersih, banyak toilet, kamar mandi dan musola. Harga makanan dan minuman sesuai kantong.</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>pasir pantai tidak tajam lumayan bersih banyak toilet kamar mandi dan musola harga makanan dan minuman sesuai kantong</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['pasir', 'pantai', 'tidak', 'tajam', 'lumayan', 'bersih', 'banyak', 'toilet', 'kamar', 'mandi', 'dan', 'musola', 'harga', 'makanan', 'dan', 'minuman', 'sesuai', 'kantong']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['pasir', 'pantai', 'tajam', 'lumayan', 'bersih', 'toilet', 'kamar', 'mandi', 'musola', 'harga', 'makanan', 'minuman', 'sesuai', 'kantong']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>pasir pantai tajam lumayan bersih toilet kamar mandi musola harga makan minum sesuai kantong</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2066,42 +2064,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2113,12 +2111,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak  mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang  sebab ada oknum pedagang terutama pedagang  gorengan ada bapa bapa yang menjual /mencampur gorengan sisa hari kemarinnya,yang diangetin lagi hingga  terasa keras dan basi.</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2128,22 +2126,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang sebab ada oknum pedagang terutama pedagang gorengan ada bapa bapa yang menjual mencampur gorengan sisa hari kemarinnyayang diangetin lagi hingga terasa keras dan basi</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['nyaman', 'untuk', 'nyari', 'kuliner', 'cuma', 'tolong', 'ditertibkan', 'para', 'pedagangnya', 'supaya', 'tidak', 'mengganggu', 'lalu', 'lintas', 'juga', 'rasanya', 'harus', 'ada', 'pembinaan', 'pada', 'para', 'pedagang', 'sebab', 'ada', 'oknum', 'pedagang', 'terutama', 'pedagang', 'gorengan', 'ada', 'bapa', 'bapa', 'yang', 'menjual', 'mencampur', 'gorengan', 'sisa', 'hari', 'kemarinnyayang', 'diangetin', 'lagi', 'hingga', 'terasa', 'keras', 'dan', 'basi']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['nyaman', 'nyari', 'kuliner', 'tolong', 'ditertibkan', 'pedagangnya', 'mengganggu', 'lintas', 'pembinaan', 'pedagang', 'oknum', 'pedagang', 'pedagang', 'gorengan', 'bapa', 'bapa', 'menjual', 'mencampur', 'gorengan', 'sisa', 'kemarinnyayang', 'diangetin', 'keras', 'basi']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>nyaman nyari kuliner tolong tertib dagang ganggu lintas bina dagang oknum dagang dagang goreng bapa bapa jual campur goreng sisa kemarinnyayang diangetin keras basi</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2153,49 +2151,49 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Di kelola oleh oknum</t>
+          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>di kelola oleh oknum</t>
+          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['di', 'kelola', 'oleh', 'oknum']</t>
+          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['kelola', 'oknum']</t>
+          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>kelola oknum</t>
+          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2207,42 +2205,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bagussss</t>
+          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['skarang', 'lebih', 'sepi', 'dan', 'kebanyakan', 'di', 'pakai', 'oknum', 'pemuda', 'pemudi', 'buat', 'pacaran', 'kadang', 'suka', 'ada', 'yg', 'mabuk', 'atau', 'tawuran', 'anak', 'sekolah']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['bagussss']</t>
+          <t>['skarang', 'sepi', 'kebanyakan', 'pakai', 'oknum', 'pemuda', 'pemudi', 'pacaran', 'kadang', 'suka', 'yg', 'mabuk', 'tawuran', 'anak', 'sekolah']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>bagussss</t>
+          <t>skarang sepi banyak pakai oknum pemuda pemudi pacar kadang suka yg mabuk tawur anak sekolah</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2254,42 +2252,42 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>Bagus,dan penduduk nya ramah dan baik2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>bagusdan penduduk nya ramah dan baik</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>bagusdan duduk nya ramah</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2301,42 +2299,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2348,42 +2346,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Batu Bintang is indeed beautiful, suitable for people who like to see sunsets/sunrises, and in the evening, sometimes we can also see lots of swiftlets flying around, it is really recommended.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2395,12 +2393,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
+          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2410,22 +2408,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
+          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
+          <t>cocok jalanjalan santai ramai sejuk</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2447,7 +2445,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
+          <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2457,22 +2455,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
+          <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
+          <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
+          <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
+          <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2489,12 +2487,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
+          <t>The mosque is spacious, the toilets and ablution area are clean. There are many variations of snacks around the town square, but some of them don't really suit my taste. They're a bit strange, different from what I usually eat.. hehehee</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2504,22 +2502,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
+          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
+          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
+          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
+          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2536,42 +2534,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>Pemandangan baik,bagus,hanya saja tempat ganti pakaian/mandi agak kurang rapih saja</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>pemandangan baikbagushanya saja tempat ganti pakaianmandi agak kurang rapih saja</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['pemandangan', 'baikbagushanya', 'saja', 'tempat', 'ganti', 'pakaianmandi', 'agak', 'kurang', 'rapih', 'saja']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['pemandangan', 'baikbagushanya', 'ganti', 'pakaianmandi', 'rapih']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>pandang baikbagushanya ganti pakaianmandi rapih</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2583,42 +2581,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bagus,dan penduduk nya ramah dan baik2</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>bagusdan penduduk nya ramah dan baik</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>bagusdan duduk nya ramah</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2630,12 +2628,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tempat nya nongkrong anak plara,keren pokonya tmpat nya asik...bnyk hiburn dan permainan anak</t>
+          <t>Pamulang coral beach, will now become a regional pier, and this is a place for local residents to watch the sunset because it is very beautiful.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2645,22 +2643,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tempat nya nongkrong anak plarakeren pokonya tmpat nya asikbnyk hiburn dan permainan anak</t>
+          <t>pamulang coral beach will now become a regional pier and this is a place for local residents to watch the sunset because it is very beautiful</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'dan', 'permainan', 'anak']</t>
+          <t>['pamulang', 'coral', 'beach', 'will', 'now', 'become', 'a', 'regional', 'pier', 'and', 'this', 'is', 'a', 'place', 'for', 'local', 'residents', 'to', 'watch', 'the', 'sunset', 'because', 'it', 'is', 'very', 'beautiful']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['nya', 'nongkrong', 'anak', 'plarakeren', 'pokonya', 'tmpat', 'nya', 'asikbnyk', 'hiburn', 'permainan', 'anak']</t>
+          <t>['pamulang', 'coral', 'beach', 'will', 'now', 'become', 'a', 'regional', 'pier', 'and', 'this', 'is', 'a', 'place', 'for', 'local', 'residents', 'to', 'watch', 'the', 'sunset', 'because', 'it', 'is', 'very', 'beautiful']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>nya nongkrong anak plarakeren poko tmpat nya asikbnyk hiburn main anak</t>
+          <t>pamulang coral beach will now become a regional pier and this is a place for local residents to watch the sunset because it is very beautiful</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2677,47 +2675,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>untuk  harga masuk motor 10k, mobil 20k, mobil travel 30k bis kecil 50k, bis besar 100k menurutku dengan harga segini udah worth it banget sih karna pantai dan pemandangannya ga mainmain bener2 sekeren itu bikin betah seharian</t>
+          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>untuk harga masuk motor k mobil k mobil travel k bis kecil k bis besar k menurutku dengan harga segini udah worth it banget sih karna pantai dan pemandangannya ga mainmain bener sekeren itu bikin betah seharian</t>
+          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>['untuk', 'harga', 'masuk', 'motor', 'k', 'mobil', 'k', 'mobil', 'travel', 'k', 'bis', 'kecil', 'k', 'bis', 'besar', 'k', 'menurutku', 'dengan', 'harga', 'segini', 'udah', 'worth', 'it', 'banget', 'sih', 'karna', 'pantai', 'dan', 'pemandangannya', 'ga', 'mainmain', 'bener', 'sekeren', 'itu', 'bikin', 'betah', 'seharian']</t>
+          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['harga', 'masuk', 'motor', 'k', 'mobil', 'k', 'mobil', 'travel', 'k', 'bis', 'k', 'bis', 'k', 'menurutku', 'harga', 'segini', 'udah', 'worth', 'it', 'banget', 'sih', 'karna', 'pantai', 'pemandangannya', 'ga', 'mainmain', 'bener', 'sekeren', 'bikin', 'betah', 'seharian']</t>
+          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>harga masuk motor k mobil k mobil travel k bis k bis k turut harga gin udah worth it banget sih karna pantai pandang ga mainmain bener keren bikin betah hari</t>
+          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2727,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kondisi lapang lumayan baik. Track lari sedikit rusak. Lari pagi di hari minggu tidak terlalu padat</t>
+          <t>Lokasi strategis. Cocok untuk santai cocok untuk anak-anak, cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan, cocok untuk yg tua muda semuanya.. tinggal d jaga bersama sama.. jangan vandalisme dan mengotorinya dgn sampah..okkkk</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2739,22 +2737,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>kondisi lapang lumayan baik track lari sedikit rusak lari pagi di hari minggu tidak terlalu padat</t>
+          <t>lokasi strategis cocok untuk santai cocok untuk anakanak cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan cocok untuk yg tua muda semuanya tinggal d jaga bersama sama jangan vandalisme dan mengotorinya dgn sampahokkkk</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>['kondisi', 'lapang', 'lumayan', 'baik', 'track', 'lari', 'sedikit', 'rusak', 'lari', 'pagi', 'di', 'hari', 'minggu', 'tidak', 'terlalu', 'padat']</t>
+          <t>['lokasi', 'strategis', 'cocok', 'untuk', 'santai', 'cocok', 'untuk', 'anakanak', 'cocok', 'untuk', 'olahraga', 'subuh', 'dengan', 'udara', 'yg', 'segar', 'dekat', 'pegunungan', 'cocok', 'untuk', 'yg', 'tua', 'muda', 'semuanya', 'tinggal', 'd', 'jaga', 'bersama', 'sama', 'jangan', 'vandalisme', 'dan', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['kondisi', 'lapang', 'lumayan', 'track', 'lari', 'rusak', 'lari', 'pagi', 'minggu', 'padat']</t>
+          <t>['lokasi', 'strategis', 'cocok', 'santai', 'cocok', 'anakanak', 'cocok', 'olahraga', 'subuh', 'udara', 'yg', 'segar', 'pegunungan', 'cocok', 'yg', 'tua', 'muda', 'tinggal', 'd', 'jaga', 'vandalisme', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>kondisi lapang lumayan track lari rusak lari pagi minggu padat</t>
+          <t>lokasi strategis cocok santai cocok anakanak cocok olahraga subuh udara yg segar gunung cocok yg tua muda tinggal d jaga vandalisme kotor dgn sampahokkkk</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2763,288 +2761,6 @@
         </is>
       </c>
       <c r="I50" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Alun - Alun Palabuhanratu</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Bagus ada masjidnya ada lapangannya dan jualannya juga cuman Memang karena sekarang lagi Corona jadi agak sepi cuman sekarang udah lumayan mulai kembali banyak orang sih ke alun-alun ini tempat pusatnya pelabuhanratu gitu selain pantainya â¦</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>bagus ada masjidnya ada lapangannya dan jualannya juga cuman memang karena sekarang lagi corona jadi agak sepi cuman sekarang udah lumayan mulai kembali banyak orang sih ke alunalun ini tempat pusatnya pelabuhanratu gitu selain pantainya â</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>['bagus', 'ada', 'masjidnya', 'ada', 'lapangannya', 'dan', 'jualannya', 'juga', 'cuman', 'memang', 'karena', 'sekarang', 'lagi', 'corona', 'jadi', 'agak', 'sepi', 'cuman', 'sekarang', 'udah', 'lumayan', 'mulai', 'kembali', 'banyak', 'orang', 'sih', 'ke', 'alunalun', 'ini', 'tempat', 'pusatnya', 'pelabuhanratu', 'gitu', 'selain', 'pantainya', 'â']</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>['bagus', 'masjidnya', 'lapangannya', 'jualannya', 'cuman', 'corona', 'sepi', 'cuman', 'udah', 'lumayan', 'orang', 'sih', 'alunalun', 'pusatnya', 'pelabuhanratu', 'gitu', 'pantainya', 'â']</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>bagus masjid lapang jual cuman corona sepi cuman udah lumayan orang sih alunalun pusat pelabuhanratu gitu pantai</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Pantai Karang Sari</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Beautiful beach view while waiting for the sunset. For those who want to swim, be careful because large waves and strong currents sometimes come.</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>['beautiful', 'beach', 'view', 'while', 'waiting', 'for', 'the', 'sunset', 'for', 'those', 'who', 'want', 'to', 'swim', 'be', 'careful', 'because', 'large', 'waves', 'and', 'strong', 'currents', 'sometimes', 'come']</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>beautiful beach view while waiting for the sunset for those who want to swim be careful because large waves and strong currents sometimes come</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>PANTAI CIBANGBAN</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Pantainya kurang bagus kotor terus parkiranya gaboleh didepan warung sama yg punya warung</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>pantainya kurang bagus kotor terus parkiranya gaboleh didepan warung sama yg punya warung</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>['pantainya', 'kurang', 'bagus', 'kotor', 'terus', 'parkiranya', 'gaboleh', 'didepan', 'warung', 'sama', 'yg', 'punya', 'warung']</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'kotor', 'parkiranya', 'gaboleh', 'didepan', 'warung', 'yg', 'warung']</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>pantai bagus kotor parkiranya gaboleh depan warung yg warung</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Pantai Karang Sari</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Pantai Batu Bintang</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Pantainya bagus. Banyak gajebo. Gajebonya nyaman. Posisinya nangkring di atas. Jd puas liat laut yg luas. Ikan bakarnya enak. Wort it buat family gathering. Btw ini aku lg acara 17san ya gaes.</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>pantainya bagus banyak gajebo gajebonya nyaman posisinya nangkring di atas jd puas liat laut yg luas ikan bakarnya enak wort it buat family gathering btw ini aku lg acara san ya gaes</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'banyak', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'di', 'atas', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'buat', 'family', 'gathering', 'btw', 'ini', 'aku', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'gajebo', 'gajebonya', 'nyaman', 'posisinya', 'nangkring', 'jd', 'puas', 'liat', 'laut', 'yg', 'luas', 'ikan', 'bakarnya', 'enak', 'wort', 'it', 'family', 'gathering', 'btw', 'lg', 'acara', 'san', 'ya', 'gaes']</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>pantai bagus gajebo gajebonya nyaman posisi nangkring jd puas liat laut yg luas ikan bakar enak wort it family gathering btw lg acara san ya gaes</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,22 +481,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -513,12 +513,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>kali lapang cangehgarbagus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -560,42 +560,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Good. Parking is free. Toilets are 2,000 yen. Degan is 15,000 yen. No entrance fee. The waves are quite big. There are horses and ATVs.</t>
+          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>good parking is free toilets are yen degan is yen no entrance fee the waves are quite big there are horses and atvs</t>
+          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['good', 'parking', 'is', 'free', 'toilets', 'are', 'yen', 'degan', 'is', 'yen', 'no', 'entrance', 'fee', 'the', 'waves', 'are', 'quite', 'big', 'there', 'are', 'horses', 'and', 'atvs']</t>
+          <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['good', 'parking', 'is', 'free', 'toilets', 'are', 'yen', 'degan', 'is', 'yen', 'no', 'entrance', 'fee', 'the', 'waves', 'are', 'quite', 'big', 'there', 'are', 'horses', 'and', 'atvs']</t>
+          <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>good parking is free toilets are yen degan is yen no entrance fee the waves are quite big there are horses and atvs</t>
+          <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -607,42 +607,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
+          <t>Mantap tempat berkumpul dan hangout atau sekedar joging di hari minggu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
+          <t>mantap tempat berkumpul dan hangout atau sekedar joging di hari minggu</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
+          <t>['mantap', 'tempat', 'berkumpul', 'dan', 'hangout', 'atau', 'sekedar', 'joging', 'di', 'hari', 'minggu']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
+          <t>['mantap', 'berkumpul', 'hangout', 'sekedar', 'joging', 'minggu']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
+          <t>mantap kumpul hangout dar joging minggu</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -654,42 +654,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Di kelola oleh oknum</t>
+          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>di kelola oleh oknum</t>
+          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['di', 'kelola', 'oleh', 'oknum']</t>
+          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['kelola', 'oknum']</t>
+          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>kelola oknum</t>
+          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -701,89 +701,89 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
+          <t>The place is beautiful at sunset..that's the best time to take pictures hehe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
+          <t>the place is beautiful at sunsetthats the best time to take pictures hehe</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['the', 'place', 'is', 'beautiful', 'at', 'sunsetthats', 'the', 'best', 'time', 'to', 'take', 'pictures', 'hehe']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['the', 'place', 'is', 'beautiful', 'at', 'sunsetthats', 'the', 'best', 'time', 'to', 'take', 'pictures', 'hehe']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
+          <t>the place is beautiful at sunsetthats the best time to take pictures hehe</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
+          <t>It's the most suitable place to drink coffee while watching the sunset, the tourist facilities are neatly arranged and quite complete, there are ATV rentals, banana boat rentals, and even mini soccer. Continued success for the management of Jayanti Village.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
+          <t>its the most suitable place to drink coffee while watching the sunset the tourist facilities are neatly arranged and quite complete there are atv rentals banana boat rentals and even mini soccer continued success for the management of jayanti village</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
+          <t>['its', 'the', 'most', 'suitable', 'place', 'to', 'drink', 'coffee', 'while', 'watching', 'the', 'sunset', 'the', 'tourist', 'facilities', 'are', 'neatly', 'arranged', 'and', 'quite', 'complete', 'there', 'are', 'atv', 'rentals', 'banana', 'boat', 'rentals', 'and', 'even', 'mini', 'soccer', 'continued', 'success', 'for', 'the', 'management', 'of', 'jayanti', 'village']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
+          <t>['its', 'the', 'most', 'suitable', 'place', 'to', 'drink', 'coffee', 'while', 'watching', 'the', 'sunset', 'the', 'tourist', 'facilities', 'are', 'neatly', 'arranged', 'and', 'quite', 'complete', 'there', 'are', 'atv', 'rentals', 'banana', 'boat', 'rentals', 'and', 'even', 'mini', 'soccer', 'continued', 'success', 'for', 'the', 'management', 'of', 'jayanti', 'village']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
+          <t>its the most suitable place to drink coffee while watching the sunset the tourist facilities are neatly arranged and quite complete there are atv rentals banana boat rentals and even mini soccer continued success for the management of jayanti village</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -795,42 +795,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
+          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
+          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
+          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -842,89 +842,89 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
+          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+          <t>Lokasi strategis. Cocok untuk santai cocok untuk anak-anak, cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan, cocok untuk yg tua muda semuanya.. tinggal d jaga bersama sama.. jangan vandalisme dan mengotorinya dgn sampah..okkkk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+          <t>lokasi strategis cocok untuk santai cocok untuk anakanak cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan cocok untuk yg tua muda semuanya tinggal d jaga bersama sama jangan vandalisme dan mengotorinya dgn sampahokkkk</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['lokasi', 'strategis', 'cocok', 'untuk', 'santai', 'cocok', 'untuk', 'anakanak', 'cocok', 'untuk', 'olahraga', 'subuh', 'dengan', 'udara', 'yg', 'segar', 'dekat', 'pegunungan', 'cocok', 'untuk', 'yg', 'tua', 'muda', 'semuanya', 'tinggal', 'd', 'jaga', 'bersama', 'sama', 'jangan', 'vandalisme', 'dan', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+          <t>['lokasi', 'strategis', 'cocok', 'santai', 'cocok', 'anakanak', 'cocok', 'olahraga', 'subuh', 'udara', 'yg', 'segar', 'pegunungan', 'cocok', 'yg', 'tua', 'muda', 'tinggal', 'd', 'jaga', 'vandalisme', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+          <t>lokasi strategis cocok santai cocok anakanak cocok olahraga subuh udara yg segar gunung cocok yg tua muda tinggal d jaga vandalisme kotor dgn sampahokkkk</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -936,89 +936,89 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>mantaps dah buat olahraga ringan sama keluarga</t>
+          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'buat', 'olahraga', 'ringan', 'sama', 'keluarga']</t>
+          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['mantaps', 'dah', 'olahraga', 'ringan', 'keluarga']</t>
+          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>mantaps dah olahraga ringan keluarga</t>
+          <t>cocok jalanjalan santai ramai sejuk</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1035,37 +1035,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lokasinya cukup strategi cuma sayang tidak ada tempat parkir,bangku-bangku sangat minim,pasilitas pendukung tidak ada,kebersihan kurang diperhatikan</t>
+          <t>A fairly comfortable place to hang out, but there are no supporting facilities, such as stalls, cafes, toilets, etc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>lokasinya cukup strategi cuma sayang tidak ada tempat parkirbangkubangku sangat minimpasilitas pendukung tidak adakebersihan kurang diperhatikan</t>
+          <t>a fairly comfortable place to hang out but there are no supporting facilities such as stalls cafes toilets etc</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['lokasinya', 'cukup', 'strategi', 'cuma', 'sayang', 'tidak', 'ada', 'tempat', 'parkirbangkubangku', 'sangat', 'minimpasilitas', 'pendukung', 'tidak', 'adakebersihan', 'kurang', 'diperhatikan']</t>
+          <t>['a', 'fairly', 'comfortable', 'place', 'to', 'hang', 'out', 'but', 'there', 'are', 'no', 'supporting', 'facilities', 'such', 'as', 'stalls', 'cafes', 'toilets', 'etc']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['lokasinya', 'strategi', 'sayang', 'parkirbangkubangku', 'minimpasilitas', 'pendukung', 'adakebersihan', 'diperhatikan']</t>
+          <t>['a', 'fairly', 'comfortable', 'place', 'to', 'hang', 'out', 'but', 'there', 'are', 'no', 'supporting', 'facilities', 'such', 'as', 'stalls', 'cafes', 'toilets', 'etc']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>lokasi strategi sayang parkirbangkubangku minimpasilitas dukung adakebersihan perhati</t>
+          <t>a fairly comfortable place to hang out but there are no supporting facilities such as stalls cafes toilets etc</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,42 +1077,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bagus,,enak buat liburan bersama keluarga</t>
+          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>bagusenak buat liburan bersama keluarga</t>
+          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
+          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['bagusenak', 'liburan', 'keluarga']</t>
+          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>bagusenak libur keluarga</t>
+          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1129,37 +1129,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The beach is clean, and the photo spots are beautiful, with lots of coral reefs. Swimming is also fun and safe. There are also gazebos along the shore that can be rented for resting. However, the toilets here are not very good.</t>
+          <t>Di kelola oleh oknum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>the beach is clean and the photo spots are beautiful with lots of coral reefs swimming is also fun and safe there are also gazebos along the shore that can be rented for resting however the toilets here are not very good</t>
+          <t>di kelola oleh oknum</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'clean', 'and', 'the', 'photo', 'spots', 'are', 'beautiful', 'with', 'lots', 'of', 'coral', 'reefs', 'swimming', 'is', 'also', 'fun', 'and', 'safe', 'there', 'are', 'also', 'gazebos', 'along', 'the', 'shore', 'that', 'can', 'be', 'rented', 'for', 'resting', 'however', 'the', 'toilets', 'here', 'are', 'not', 'very', 'good']</t>
+          <t>['di', 'kelola', 'oleh', 'oknum']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['the', 'beach', 'is', 'clean', 'and', 'the', 'photo', 'spots', 'are', 'beautiful', 'with', 'lots', 'of', 'coral', 'reefs', 'swimming', 'is', 'also', 'fun', 'and', 'safe', 'there', 'are', 'also', 'gazebos', 'along', 'the', 'shore', 'that', 'can', 'be', 'rented', 'for', 'resting', 'however', 'the', 'toilets', 'here', 'are', 'not', 'very', 'good']</t>
+          <t>['kelola', 'oknum']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>the beach is clean and the photo spots are beautiful with lots of coral reefs swimming is also fun and safe there are also gazebos along the shore that can be rented for resting however the toilets here are not very good</t>
+          <t>kelola oknum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1171,136 +1171,136 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A relaxing beach. Plenty of shade while enjoying coffee and instant food. If you're lucky, you can even get a massage at a negotiable price. Sunset spots are easy to find, with accommodations located on the beach and along the roadside. â¦</t>
+          <t>Jalanya mantap</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside â</t>
+          <t>jalanya mantap</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['a', 'relaxing', 'beach', 'plenty', 'of', 'shade', 'while', 'enjoying', 'coffee', 'and', 'instant', 'food', 'if', 'youre', 'lucky', 'you', 'can', 'even', 'get', 'a', 'massage', 'at', 'a', 'negotiable', 'price', 'sunset', 'spots', 'are', 'easy', 'to', 'find', 'with', 'accommodations', 'located', 'on', 'the', 'beach', 'and', 'along', 'the', 'roadside', 'â']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>a relaxing beach plenty of shade while enjoying coffee and instant food if youre lucky you can even get a massage at a negotiable price sunset spots are easy to find with accommodations located on the beach and along the roadside</t>
+          <t>jala mantap</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya. Detail bajunya bagus banget</t>
+          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya detail bajunya bagus banget</t>
+          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['baju', 'baju', 'yg', 'tetsedia', 'untuk', 'di', 'sewakan', 'sangat', 'bagus', 'dan', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'dengan', 'ke', 'inginan', 'saya', 'detail', 'bajunya', 'bagus', 'banget']</t>
+          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['baju', 'baju', 'yg', 'tetsedia', 'sewakan', 'bagus', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'inginan', 'detail', 'bajunya', 'bagus', 'banget']</t>
+          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>baju baju yg tetsedia sewa bagus riquesan buat baju nya sesuai banget ingin detail baju bagus banget</t>
+          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alun Alun Pelabuhan Ratu Sukabumi adalah tempat yang menawan dengan pesona alamnya. Keindahan alun-alun dan pemandangan laut yang menakjubkan membuatnya menjadi tempat yang pas untuk bersantai. Suasana tenang dan sejuk di sekitar area ini â¦</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>alun alun pelabuhan ratu sukabumi adalah tempat yang menawan dengan pesona alamnya keindahan alunalun dan pemandangan laut yang menakjubkan membuatnya menjadi tempat yang pas untuk bersantai suasana tenang dan sejuk di sekitar area ini â</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['alun', 'alun', 'pelabuhan', 'ratu', 'sukabumi', 'adalah', 'tempat', 'yang', 'menawan', 'dengan', 'pesona', 'alamnya', 'keindahan', 'alunalun', 'dan', 'pemandangan', 'laut', 'yang', 'menakjubkan', 'membuatnya', 'menjadi', 'tempat', 'yang', 'pas', 'untuk', 'bersantai', 'suasana', 'tenang', 'dan', 'sejuk', 'di', 'sekitar', 'area', 'ini', 'â']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['alun', 'alun', 'pelabuhan', 'ratu', 'sukabumi', 'menawan', 'pesona', 'alamnya', 'keindahan', 'alunalun', 'pemandangan', 'laut', 'menakjubkan', 'membuatnya', 'pas', 'bersantai', 'suasana', 'tenang', 'sejuk', 'area', 'â']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>alun alun labuh ratu sukabumi tawan pesona alam indah alunalun pandang laut takjub buat pas santa suasana tenang sejuk area</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1312,42 +1312,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tempat nongki paling chill and cheap yg cocok pas sunset'an</t>
+          <t>A comfortable and easy-to-find spot. Hehe, the only fee is for parking. You can enjoy the beach atmosphere, and there are also great selfie spots. Snacks can be purchased around the beach. And if you're curious about riding a horse, you can pay just Rp 10,000.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tempat nongki paling chill and cheap yg cocok pas sunsetan</t>
+          <t>a comfortable and easytofind spot hehe the only fee is for parking you can enjoy the beach atmosphere and there are also great selfie spots snacks can be purchased around the beach and if youre curious about riding a horse you can pay just rp</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['tempat', 'nongki', 'paling', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['a', 'comfortable', 'and', 'easytofind', 'spot', 'hehe', 'the', 'only', 'fee', 'is', 'for', 'parking', 'you', 'can', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'also', 'great', 'selfie', 'spots', 'snacks', 'can', 'be', 'purchased', 'around', 'the', 'beach', 'and', 'if', 'youre', 'curious', 'about', 'riding', 'a', 'horse', 'you', 'can', 'pay', 'just', 'rp']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['nongki', 'chill', 'and', 'cheap', 'yg', 'cocok', 'pas', 'sunsetan']</t>
+          <t>['a', 'comfortable', 'and', 'easytofind', 'spot', 'hehe', 'the', 'only', 'fee', 'is', 'for', 'parking', 'you', 'can', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'also', 'great', 'selfie', 'spots', 'snacks', 'can', 'be', 'purchased', 'around', 'the', 'beach', 'and', 'if', 'youre', 'curious', 'about', 'riding', 'a', 'horse', 'you', 'can', 'pay', 'just', 'rp']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>nongki chill and cheap yg cocok pas sunsetan</t>
+          <t>a comfortable and easytofind spot hehe the only fee is for parking you can enjoy the beach atmosphere and there are also great selfie spots snacks can be purchased around the beach and if youre curious about riding a horse you can pay just rp</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1359,42 +1359,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
+          <t>The place is not as big as other town squares, but the atmosphere is calm and beautiful, the mosque is nice, and the parking is quite good.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
+          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
+          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1406,42 +1406,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bagus ada masjidnya ada lapangannya dan jualannya juga cuman Memang karena sekarang lagi Corona jadi agak sepi cuman sekarang udah lumayan mulai kembali banyak orang sih ke alun-alun ini tempat pusatnya pelabuhanratu gitu selain pantainya â¦</t>
+          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>bagus ada masjidnya ada lapangannya dan jualannya juga cuman memang karena sekarang lagi corona jadi agak sepi cuman sekarang udah lumayan mulai kembali banyak orang sih ke alunalun ini tempat pusatnya pelabuhanratu gitu selain pantainya â</t>
+          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['bagus', 'ada', 'masjidnya', 'ada', 'lapangannya', 'dan', 'jualannya', 'juga', 'cuman', 'memang', 'karena', 'sekarang', 'lagi', 'corona', 'jadi', 'agak', 'sepi', 'cuman', 'sekarang', 'udah', 'lumayan', 'mulai', 'kembali', 'banyak', 'orang', 'sih', 'ke', 'alunalun', 'ini', 'tempat', 'pusatnya', 'pelabuhanratu', 'gitu', 'selain', 'pantainya', 'â']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['bagus', 'masjidnya', 'lapangannya', 'jualannya', 'cuman', 'corona', 'sepi', 'cuman', 'udah', 'lumayan', 'orang', 'sih', 'alunalun', 'pusatnya', 'pelabuhanratu', 'gitu', 'pantainya', 'â']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>bagus masjid lapang jual cuman corona sepi cuman udah lumayan orang sih alunalun pusat pelabuhanratu gitu pantai</t>
+          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1453,12 +1453,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Visited on September 24th, 2022 at 7 AM, it was still quiet, free admission, car parking 10,000 Rupiah, toilets 5,000 Rupiah. The view is great, especially if you go up to Batu Bintang Hydroelectric Power Plant, the waves are not as big as at Karanghawu, children can still get wet with supervision.</t>
+          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1468,22 +1468,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>visited on september th at am it was still quiet free admission car parking rupiah toilets rupiah the view is great especially if you go up to batu bintang hydroelectric power plant the waves are not as big as at karanghawu children can still get wet with supervision</t>
+          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['visited', 'on', 'september', 'th', 'at', 'am', 'it', 'was', 'still', 'quiet', 'free', 'admission', 'car', 'parking', 'rupiah', 'toilets', 'rupiah', 'the', 'view', 'is', 'great', 'especially', 'if', 'you', 'go', 'up', 'to', 'batu', 'bintang', 'hydroelectric', 'power', 'plant', 'the', 'waves', 'are', 'not', 'as', 'big', 'as', 'at', 'karanghawu', 'children', 'can', 'still', 'get', 'wet', 'with', 'supervision']</t>
+          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['visited', 'on', 'september', 'th', 'at', 'am', 'it', 'was', 'still', 'quiet', 'free', 'admission', 'car', 'parking', 'rupiah', 'toilets', 'rupiah', 'the', 'view', 'is', 'great', 'especially', 'if', 'you', 'go', 'up', 'to', 'batu', 'bintang', 'hydroelectric', 'power', 'plant', 'the', 'waves', 'are', 'not', 'as', 'big', 'as', 'at', 'karanghawu', 'children', 'can', 'still', 'get', 'wet', 'with', 'supervision']</t>
+          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>visited on september th at am it was still quiet free admission car parking rupiah toilets rupiah the view is great especially if you go up to batu bintang hydroelectric power plant the waves are not as big as at karanghawu children can still get wet with supervision</t>
+          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1500,12 +1500,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ikon kota palabuhanratu......bagus</t>
+          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1515,22 +1515,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ikon kota palabuhanratubagus</t>
+          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ikon kota palabuhanratubagus</t>
+          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1547,42 +1547,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pesanggrahan Tenjo Resmi Pelabuhan Ratu</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pantai nya lumayan cuma banyak pengamenya</t>
+          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>pantai nya lumayan cuma banyak pengamenya</t>
+          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['pantai', 'nya', 'lumayan', 'cuma', 'banyak', 'pengamenya']</t>
+          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['pantai', 'nya', 'lumayan', 'pengamenya']</t>
+          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>pantai nya lumayan pengamenya</t>
+          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1594,89 +1594,89 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>Ikon kota palabuhanratu......bagus</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>ikon kota palabuhanratubagus</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+          <t>ikon kota palabuhanratubagus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>The view is quite good for enjoying the sunset with the family, at this location port facilities are also being built</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>the view is quite good for enjoying the sunset with the family at this location port facilities are also being built</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['the', 'view', 'is', 'quite', 'good', 'for', 'enjoying', 'the', 'sunset', 'with', 'the', 'family', 'at', 'this', 'location', 'port', 'facilities', 'are', 'also', 'being', 'built']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['the', 'view', 'is', 'quite', 'good', 'for', 'enjoying', 'the', 'sunset', 'with', 'the', 'family', 'at', 'this', 'location', 'port', 'facilities', 'are', 'also', 'being', 'built']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>the view is quite good for enjoying the sunset with the family at this location port facilities are also being built</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1688,42 +1688,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
+          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
+          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
+          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1735,89 +1735,89 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lapangannya luas,rapih, bersih,di tata dengan sangat bagus,penyuluh sosial masyarakat kab sukabumi,mengikuti upacara hari jadi Sukabumi</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>lapangannya luasrapih bersihdi tata dengan sangat baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara hari jadi sukabumi</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'dengan', 'sangat', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'hari', 'jadi', 'sukabumi']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'sukabumi']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>lapang luasrapih bersihdi tata baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara sukabumi</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1829,42 +1829,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
+          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
+          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
+          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>pake produck gk kecewa kerennnn deh</t>
+          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1876,42 +1876,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sdh mulai banyak kerusakan. Terutama pada area olahraga. Kurang terawat tidak seperti awal awal</t>
+          <t>The atmosphere is comfortable and pleasant. You can play in the sand on the beach, making it perfect for family outings.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>sdh mulai banyak kerusakan terutama pada area olahraga kurang terawat tidak seperti awal awal</t>
+          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['sdh', 'mulai', 'banyak', 'kerusakan', 'terutama', 'pada', 'area', 'olahraga', 'kurang', 'terawat', 'tidak', 'seperti', 'awal', 'awal']</t>
+          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['sdh', 'kerusakan', 'area', 'olahraga', 'terawat']</t>
+          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>sdh rusa area olahraga awat</t>
+          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>The staff are friendly, the beach is nice, but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower... try to take a shower in the toilet near the beach, the toilet near the floor is not suitable â¦</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1938,22 +1938,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable â</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1970,12 +1970,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Smile hill Pelabuhan Ratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
+          <t>Konstruksi banyak yang rusak, terutama yang berbatasan dengan pasir. Mungkin tergerus ombak, sementara konstruksi tidak sesuai kondisi. Harusnya dikasih tiang pancang dan fondasi agak dalam. Tidak ada petugas pengawas, jadi orang bebas. Ada â¦</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1985,22 +1985,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
+          <t>konstruksi banyak yang rusak terutama yang berbatasan dengan pasir mungkin tergerus ombak sementara konstruksi tidak sesuai kondisi harusnya dikasih tiang pancang dan fondasi agak dalam tidak ada petugas pengawas jadi orang bebas ada â</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
+          <t>['konstruksi', 'banyak', 'yang', 'rusak', 'terutama', 'yang', 'berbatasan', 'dengan', 'pasir', 'mungkin', 'tergerus', 'ombak', 'sementara', 'konstruksi', 'tidak', 'sesuai', 'kondisi', 'harusnya', 'dikasih', 'tiang', 'pancang', 'dan', 'fondasi', 'agak', 'dalam', 'tidak', 'ada', 'petugas', 'pengawas', 'jadi', 'orang', 'bebas', 'ada', 'â']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
+          <t>['konstruksi', 'rusak', 'berbatasan', 'pasir', 'tergerus', 'ombak', 'konstruksi', 'sesuai', 'kondisi', 'dikasih', 'tiang', 'pancang', 'fondasi', 'petugas', 'pengawas', 'orang', 'bebas', 'â']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
+          <t>konstruksi rusak batas pasir gerus ombak konstruksi sesuai kondisi kasih tiang pancang fondasi tugas awas orang bebas</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2017,42 +2017,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>The toilets are dirty and only want money and almost every location is full of rubbish, even though it's a shame that the place is as neat as this but it's not well maintained.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>the toilets are dirty and only want money and almost every location is full of rubbish even though its a shame that the place is as neat as this but its not well maintained</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['the', 'toilets', 'are', 'dirty', 'and', 'only', 'want', 'money', 'and', 'almost', 'every', 'location', 'is', 'full', 'of', 'rubbish', 'even', 'though', 'its', 'a', 'shame', 'that', 'the', 'place', 'is', 'as', 'neat', 'as', 'this', 'but', 'its', 'not', 'well', 'maintained']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['the', 'toilets', 'are', 'dirty', 'and', 'only', 'want', 'money', 'and', 'almost', 'every', 'location', 'is', 'full', 'of', 'rubbish', 'even', 'though', 'its', 'a', 'shame', 'that', 'the', 'place', 'is', 'as', 'neat', 'as', 'this', 'but', 'its', 'not', 'well', 'maintained']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>the toilets are dirty and only want money and almost every location is full of rubbish even though its a shame that the place is as neat as this but its not well maintained</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2064,42 +2064,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2111,89 +2111,89 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>Pagi,siang mlm ramai pedagang smua murah meriah. Buat nongkrong smua usia jgn lupa silakan berkunjung, anda pasti suka....</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>pagisiang mlm ramai pedagang smua murah meriah buat nongkrong smua usia jgn lupa silakan berkunjung anda pasti suka</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'buat', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'anda', 'pasti', 'suka']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'suka']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>pagisiang mlm ramai dagang smua murah riah nongkrong smua usia jgn lupa sila kunjung suka</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
+          <t>Jajahannya banyak pilihan dan enak ð Tahu crispy juara, sate padang juga mantul, cilok lumayan, cilor enak, pisang keju enak, sate2 an enak, waduh kalap pokoknya â¦</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
+          <t>jajahannya banyak pilihan dan enak ð tahu crispy juara sate padang juga mantul cilok lumayan cilor enak pisang keju enak sate an enak waduh kalap pokoknya â</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
+          <t>['jajahannya', 'banyak', 'pilihan', 'dan', 'enak', 'ð', 'tahu', 'crispy', 'juara', 'sate', 'padang', 'juga', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'waduh', 'kalap', 'pokoknya', 'â']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
+          <t>['jajahannya', 'pilihan', 'enak', 'ð', 'crispy', 'juara', 'sate', 'padang', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'kalap', 'pokoknya', 'â']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
+          <t>jajah pilih enak crispy juara sate padang mantul cilok lumayan cilor enak pisang keju enak sate an enak kalap pokok</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2205,42 +2205,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>skarang lebih sepi dan kebanyakan di pakai oknum pemuda pemudi buat pacaran kadang suka ada yg mabuk atau tawuran anak sekolah</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['skarang', 'lebih', 'sepi', 'dan', 'kebanyakan', 'di', 'pakai', 'oknum', 'pemuda', 'pemudi', 'buat', 'pacaran', 'kadang', 'suka', 'ada', 'yg', 'mabuk', 'atau', 'tawuran', 'anak', 'sekolah']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['skarang', 'sepi', 'kebanyakan', 'pakai', 'oknum', 'pemuda', 'pemudi', 'pacaran', 'kadang', 'suka', 'yg', 'mabuk', 'tawuran', 'anak', 'sekolah']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>skarang sepi banyak pakai oknum pemuda pemudi pacar kadang suka yg mabuk tawur anak sekolah</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2252,12 +2252,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bagus,dan penduduk nya ramah dan baik2</t>
+          <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2267,22 +2267,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>bagusdan penduduk nya ramah dan baik</t>
+          <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
+          <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
+          <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>bagusdan duduk nya ramah</t>
+          <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2299,42 +2299,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2346,42 +2346,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Batu Bintang is indeed beautiful, suitable for people who like to see sunsets/sunrises, and in the evening, sometimes we can also see lots of swiftlets flying around, it is really recommended.</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['batu', 'bintang', 'is', 'indeed', 'beautiful', 'suitable', 'for', 'people', 'who', 'like', 'to', 'see', 'sunsetssunrises', 'and', 'in', 'the', 'evening', 'sometimes', 'we', 'can', 'also', 'see', 'lots', 'of', 'swiftlets', 'flying', 'around', 'it', 'is', 'really', 'recommended']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>batu bintang is indeed beautiful suitable for people who like to see sunsetssunrises and in the evening sometimes we can also see lots of swiftlets flying around it is really recommended</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2393,42 +2393,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+          <t>Transit sebelum ke Geopark Ciletuh bs di sini. Shalat di mesjid Agung, makan ada warung Padang enak murah. Jajanan kakilimanya jg banyak.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+          <t>transit sebelum ke geopark ciletuh bs di sini shalat di mesjid agung makan ada warung padang enak murah jajanan kakilimanya jg banyak</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+          <t>['transit', 'sebelum', 'ke', 'geopark', 'ciletuh', 'bs', 'di', 'sini', 'shalat', 'di', 'mesjid', 'agung', 'makan', 'ada', 'warung', 'padang', 'enak', 'murah', 'jajanan', 'kakilimanya', 'jg', 'banyak']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+          <t>['transit', 'geopark', 'ciletuh', 'bs', 'shalat', 'mesjid', 'agung', 'makan', 'warung', 'padang', 'enak', 'murah', 'jajanan', 'kakilimanya', 'jg']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>cocok jalanjalan santai ramai sejuk</t>
+          <t>transit geopark ciletuh bs shalat mesjid agung makan warung padang enak murah jajan kakilimanya jg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2440,47 +2440,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
@@ -2492,84 +2492,84 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The mosque is spacious, the toilets and ablution area are clean. There are many variations of snacks around the town square, but some of them don't really suit my taste. They're a bit strange, different from what I usually eat.. hehehee</t>
+          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
+          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
+          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['the', 'mosque', 'is', 'spacious', 'the', 'toilets', 'and', 'ablution', 'area', 'are', 'clean', 'there', 'are', 'many', 'variations', 'of', 'snacks', 'around', 'the', 'town', 'square', 'but', 'some', 'of', 'them', 'dont', 'really', 'suit', 'my', 'taste', 'theyre', 'a', 'bit', 'strange', 'different', 'from', 'what', 'i', 'usually', 'eat', 'hehehee']</t>
+          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>the mosque is spacious the toilets and ablution area are clean there are many variations of snacks around the town square but some of them dont really suit my taste theyre a bit strange different from what i usually eat hehehee</t>
+          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PANTAI CIBANGBAN</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pemandangan baik,bagus,hanya saja tempat ganti pakaian/mandi agak kurang rapih saja</t>
+          <t>SDH tidak terlalu bagus...kalau malam sangat gelap..bnyk lampu yg mati dan tak diperbaiki..Pedagang Kaki lima nya sih lumayan tertata rapi...</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>pemandangan baikbagushanya saja tempat ganti pakaianmandi agak kurang rapih saja</t>
+          <t>sdh tidak terlalu baguskalau malam sangat gelapbnyk lampu yg mati dan tak diperbaikipedagang kaki lima nya sih lumayan tertata rapi</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['pemandangan', 'baikbagushanya', 'saja', 'tempat', 'ganti', 'pakaianmandi', 'agak', 'kurang', 'rapih', 'saja']</t>
+          <t>['sdh', 'tidak', 'terlalu', 'baguskalau', 'malam', 'sangat', 'gelapbnyk', 'lampu', 'yg', 'mati', 'dan', 'tak', 'diperbaikipedagang', 'kaki', 'lima', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['pemandangan', 'baikbagushanya', 'ganti', 'pakaianmandi', 'rapih']</t>
+          <t>['sdh', 'baguskalau', 'malam', 'gelapbnyk', 'lampu', 'yg', 'mati', 'diperbaikipedagang', 'kaki', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>pandang baikbagushanya ganti pakaianmandi rapih</t>
+          <t>sdh baguskalau malam gelapbnyk lampu yg mati diperbaikipedagang kaki nya sih lumayan tata rapi</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2581,42 +2581,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2628,12 +2628,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pantai Karang Sari</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pamulang coral beach, will now become a regional pier, and this is a place for local residents to watch the sunset because it is very beautiful.</t>
+          <t>Bagus,dan penduduk nya ramah dan baik2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2643,22 +2643,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>pamulang coral beach will now become a regional pier and this is a place for local residents to watch the sunset because it is very beautiful</t>
+          <t>bagusdan penduduk nya ramah dan baik</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['pamulang', 'coral', 'beach', 'will', 'now', 'become', 'a', 'regional', 'pier', 'and', 'this', 'is', 'a', 'place', 'for', 'local', 'residents', 'to', 'watch', 'the', 'sunset', 'because', 'it', 'is', 'very', 'beautiful']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['pamulang', 'coral', 'beach', 'will', 'now', 'become', 'a', 'regional', 'pier', 'and', 'this', 'is', 'a', 'place', 'for', 'local', 'residents', 'to', 'watch', 'the', 'sunset', 'because', 'it', 'is', 'very', 'beautiful']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>pamulang coral beach will now become a regional pier and this is a place for local residents to watch the sunset because it is very beautiful</t>
+          <t>bagusdan duduk nya ramah</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2675,92 +2675,609 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
+          <t>Tempat nya strategis untuk istrahat. Setelah solat d mesjid, bisa jajan dan mknan dlu, bnyak tempat jajannya, dekat dgn KFC, ATM dan toserba juga...ð â¦</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
+          <t>tempat nya strategis untuk istrahat setelah solat d mesjid bisa jajan dan mknan dlu bnyak tempat jajannya dekat dgn kfc atm dan toserba jugað â</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
+          <t>['tempat', 'nya', 'strategis', 'untuk', 'istrahat', 'setelah', 'solat', 'd', 'mesjid', 'bisa', 'jajan', 'dan', 'mknan', 'dlu', 'bnyak', 'tempat', 'jajannya', 'dekat', 'dgn', 'kfc', 'atm', 'dan', 'toserba', 'jugað', 'â']</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
+          <t>['nya', 'strategis', 'istrahat', 'solat', 'd', 'mesjid', 'jajan', 'mknan', 'dlu', 'bnyak', 'jajannya', 'dgn', 'kfc', 'atm', 'toserba', 'jugað', 'â']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
+          <t>nya strategis istrahat solat d mesjid jajan mknan dlu bnyak jajan dgn kfc atm toserba juga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Smile hill Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Pantai Karang Sari</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Taman Bunga Gunung Sumping</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Lokasi strategis. Cocok untuk santai cocok untuk anak-anak, cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan, cocok untuk yg tua muda semuanya.. tinggal d jaga bersama sama.. jangan vandalisme dan mengotorinya dgn sampah..okkkk</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>lokasi strategis cocok untuk santai cocok untuk anakanak cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan cocok untuk yg tua muda semuanya tinggal d jaga bersama sama jangan vandalisme dan mengotorinya dgn sampahokkkk</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>['lokasi', 'strategis', 'cocok', 'untuk', 'santai', 'cocok', 'untuk', 'anakanak', 'cocok', 'untuk', 'olahraga', 'subuh', 'dengan', 'udara', 'yg', 'segar', 'dekat', 'pegunungan', 'cocok', 'untuk', 'yg', 'tua', 'muda', 'semuanya', 'tinggal', 'd', 'jaga', 'bersama', 'sama', 'jangan', 'vandalisme', 'dan', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>['lokasi', 'strategis', 'cocok', 'santai', 'cocok', 'anakanak', 'cocok', 'olahraga', 'subuh', 'udara', 'yg', 'segar', 'pegunungan', 'cocok', 'yg', 'tua', 'muda', 'tinggal', 'd', 'jaga', 'vandalisme', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>lokasi strategis cocok santai cocok anakanak cocok olahraga subuh udara yg segar gunung cocok yg tua muda tinggal d jaga vandalisme kotor dgn sampahokkkk</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>pake produck gk kecewa kerennnn deh</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Pantai Citepus</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PANTAI CIBANGBAN</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Tidak nyaman oleh orngÂ² yg menyewakan tempat untuk istirahat/baleÂ² Krn mahal Dan sangat perhitungan...di sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d Carikan tmpt istrht Krn mrk welcome dan baikÂ².</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>tidak nyaman oleh orngâ² yg menyewakan tempat untuk istirahatbaleâ² krn mahal dan sangat perhitungandi sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d carikan tmpt istrht krn mrk welcome dan baikâ²</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>['tidak', 'nyaman', 'oleh', 'orngâ²', 'yg', 'menyewakan', 'tempat', 'untuk', 'istirahatbaleâ²', 'krn', 'mahal', 'dan', 'sangat', 'perhitungandi', 'sarankan', 'jika', 'berwisata', 'ke', 'sana', 'bisa', 'meminta', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'untuk', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'dan', 'baikâ²']</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>['nyaman', 'orngâ²', 'yg', 'menyewakan', 'istirahatbaleâ²', 'krn', 'mahal', 'perhitungandi', 'sarankan', 'berwisata', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'baikâ²']</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>nyaman orng yg sewa istirahatbale krn mahal perhitungandi saran wisata bantu jasa kpd jaga pintu masuk utama d cari tmpt istrht krn mrk welcome baik</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ECON</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>bagus,,enak buat liburan bersama keluarga</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>bagusenak buat liburan bersama keluarga</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>['bagusenak', 'liburan', 'keluarga']</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>bagusenak libur keluarga</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Jangilus Monument</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Tugu nyah udah di pindahin</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>tugu nyah udah di pindahin</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>tugu nyah udah pindahin</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Pantai Pelabuhan Ratu</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>NEUT</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Sdh mulai banyak kerusakan. Terutama pada area olahraga. Kurang terawat tidak seperti awal awal</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>sdh mulai banyak kerusakan terutama pada area olahraga kurang terawat tidak seperti awal awal</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>['sdh', 'mulai', 'banyak', 'kerusakan', 'terutama', 'pada', 'area', 'olahraga', 'kurang', 'terawat', 'tidak', 'seperti', 'awal', 'awal']</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>['sdh', 'kerusakan', 'area', 'olahraga', 'terawat']</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>sdh rusa area olahraga awat</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>IRREL</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Pantai Karang Sari</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,22 +481,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['mesjid', 'nya', 'bagus', 'tapi', 'sayang', 'banyak', 'itu', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'itu', 'iya', 'itu', 'apa', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['mesjid', 'nya', 'bagus', 'sayang', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'iya', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>mesjid nya bagus sayang tuh ih ituloh apasih ya iya ih eta tea naon si arana nyaeta be pokonamah</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -513,12 +513,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Baru pertama kali ke lapangan cangehgar...bagus ð â¦</t>
+          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>baru pertama kali ke lapangan cangehgarbagus ð â</t>
+          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['baru', 'pertama', 'kali', 'ke', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['kali', 'lapangan', 'cangehgarbagus', 'ð', 'â']</t>
+          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>kali lapang cangehgarbagus</t>
+          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -560,42 +560,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Waterpark Citepus Pelabuhanratu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
+          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
+          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'besar', 'semoga', 'dinas', 'parawisata', 'memberi', 'penambahan', 'akses', 'penerangan', 'apalagi', 'disana', 'ada', 'sumber', 'besar', 'pltu']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'ombaknya', 'semoga', 'dinas', 'parawisata', 'penambahan', 'akses', 'penerangan', 'disana', 'sumber', 'pltu']</t>
+          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pantai bagus ombak moga dinas parawisata tambah akses terang sana sumber pltu</t>
+          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -607,42 +607,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mantap tempat berkumpul dan hangout atau sekedar joging di hari minggu</t>
+          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>mantap tempat berkumpul dan hangout atau sekedar joging di hari minggu</t>
+          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['mantap', 'tempat', 'berkumpul', 'dan', 'hangout', 'atau', 'sekedar', 'joging', 'di', 'hari', 'minggu']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['mantap', 'berkumpul', 'hangout', 'sekedar', 'joging', 'minggu']</t>
+          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>mantap kumpul hangout dar joging minggu</t>
+          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -654,12 +654,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lapangannya gelap, banyak siih tukang dagangnya. Coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman.</t>
+          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -669,22 +669,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>lapangannya gelap banyak siih tukang dagangnya coba kalo yg jualan itu ada di dalem lapangan terus di sediain terpal untuk bisa duduk duduk nongkrong sambil makan jajanan tersebut pasti lebih enak dan nyaman</t>
+          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'banyak', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'itu', 'ada', 'di', 'dalem', 'lapangan', 'terus', 'di', 'sediain', 'terpal', 'untuk', 'bisa', 'duduk', 'duduk', 'nongkrong', 'sambil', 'makan', 'jajanan', 'tersebut', 'pasti', 'lebih', 'enak', 'dan', 'nyaman']</t>
+          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['lapangannya', 'gelap', 'siih', 'tukang', 'dagangnya', 'coba', 'kalo', 'yg', 'jualan', 'dalem', 'lapangan', 'sediain', 'terpal', 'duduk', 'duduk', 'nongkrong', 'makan', 'jajanan', 'enak', 'nyaman']</t>
+          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lapang gelap siih tukang dagang coba kalo yg jual dalem lapang ain terpal duduk duduk nongkrong makan jajan enak nyaman</t>
+          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -701,59 +701,59 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The place is beautiful at sunset..that's the best time to take pictures hehe</t>
+          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>the place is beautiful at sunsetthats the best time to take pictures hehe</t>
+          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'beautiful', 'at', 'sunsetthats', 'the', 'best', 'time', 'to', 'take', 'pictures', 'hehe']</t>
+          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'beautiful', 'at', 'sunsetthats', 'the', 'best', 'time', 'to', 'take', 'pictures', 'hehe']</t>
+          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>the place is beautiful at sunsetthats the best time to take pictures hehe</t>
+          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>It's the most suitable place to drink coffee while watching the sunset, the tourist facilities are neatly arranged and quite complete, there are ATV rentals, banana boat rentals, and even mini soccer. Continued success for the management of Jayanti Village.</t>
+          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -763,22 +763,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>its the most suitable place to drink coffee while watching the sunset the tourist facilities are neatly arranged and quite complete there are atv rentals banana boat rentals and even mini soccer continued success for the management of jayanti village</t>
+          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['its', 'the', 'most', 'suitable', 'place', 'to', 'drink', 'coffee', 'while', 'watching', 'the', 'sunset', 'the', 'tourist', 'facilities', 'are', 'neatly', 'arranged', 'and', 'quite', 'complete', 'there', 'are', 'atv', 'rentals', 'banana', 'boat', 'rentals', 'and', 'even', 'mini', 'soccer', 'continued', 'success', 'for', 'the', 'management', 'of', 'jayanti', 'village']</t>
+          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['its', 'the', 'most', 'suitable', 'place', 'to', 'drink', 'coffee', 'while', 'watching', 'the', 'sunset', 'the', 'tourist', 'facilities', 'are', 'neatly', 'arranged', 'and', 'quite', 'complete', 'there', 'are', 'atv', 'rentals', 'banana', 'boat', 'rentals', 'and', 'even', 'mini', 'soccer', 'continued', 'success', 'for', 'the', 'management', 'of', 'jayanti', 'village']</t>
+          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>its the most suitable place to drink coffee while watching the sunset the tourist facilities are neatly arranged and quite complete there are atv rentals banana boat rentals and even mini soccer continued success for the management of jayanti village</t>
+          <t>pake produck gk kecewa kerennnn deh</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -795,42 +795,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ada saung yg bisa disewa di bibir pantai, bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ada saung yg bisa disewa di bibir pantai bisa nikmatin angin nya sambil ngopi hehe</t>
+          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['ada', 'saung', 'yg', 'bisa', 'disewa', 'di', 'bibir', 'pantai', 'bisa', 'nikmatin', 'angin', 'nya', 'sambil', 'ngopi', 'hehe']</t>
+          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['saung', 'yg', 'disewa', 'bibir', 'pantai', 'nikmatin', 'angin', 'nya', 'ngopi', 'hehe']</t>
+          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>saung yg sewa bibir pantai nikmatin angin nya ngopi hehe</t>
+          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -842,89 +842,89 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pagi pagi sudah sampai sini dr yang tadi nya sepi terus rame...ke sini lewat jalur cikidang... Mantap perjalanan nya..pas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â¦</t>
+          <t>Lapangannya luas,rapih, bersih,di tata dengan sangat bagus,penyuluh sosial masyarakat kab sukabumi,mengikuti upacara hari jadi Sukabumi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>pagi pagi sudah sampai sini dr yang tadi nya sepi terus rameke sini lewat jalur cikidang mantap perjalanan nyapas sampe di suguhkan dengan pantai yang eksotis ombak nya gede tapi cuaca lagi syahdu jadi mendung mendung gimana â</t>
+          <t>lapangannya luasrapih bersihdi tata dengan sangat baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara hari jadi sukabumi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'sudah', 'sampai', 'sini', 'dr', 'yang', 'tadi', 'nya', 'sepi', 'terus', 'rameke', 'sini', 'lewat', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'di', 'suguhkan', 'dengan', 'pantai', 'yang', 'eksotis', 'ombak', 'nya', 'gede', 'tapi', 'cuaca', 'lagi', 'syahdu', 'jadi', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'dengan', 'sangat', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'hari', 'jadi', 'sukabumi']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['pagi', 'pagi', 'dr', 'nya', 'sepi', 'rameke', 'jalur', 'cikidang', 'mantap', 'perjalanan', 'nyapas', 'sampe', 'suguhkan', 'pantai', 'eksotis', 'ombak', 'nya', 'gede', 'cuaca', 'syahdu', 'mendung', 'mendung', 'gimana', 'â']</t>
+          <t>['lapangannya', 'luasrapih', 'bersihdi', 'tata', 'baguspenyuluh', 'sosial', 'masyarakat', 'kab', 'sukabumimengikuti', 'upacara', 'sukabumi']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>pagi pagi dr nya sepi rameke jalur cikidang mantap jalan nyapas sampe suguh pantai eksotis ombak nya gede cuaca syahdu mendung mendung gimana</t>
+          <t>lapang luasrapih bersihdi tata baguspenyuluh sosial masyarakat kab sukabumimengikuti upacara sukabumi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Taman Bunga Gunung Sumping</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lokasi strategis. Cocok untuk santai cocok untuk anak-anak, cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan, cocok untuk yg tua muda semuanya.. tinggal d jaga bersama sama.. jangan vandalisme dan mengotorinya dgn sampah..okkkk</t>
+          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>lokasi strategis cocok untuk santai cocok untuk anakanak cocok untuk olahraga subuh dengan udara yg segar dekat pegunungan cocok untuk yg tua muda semuanya tinggal d jaga bersama sama jangan vandalisme dan mengotorinya dgn sampahokkkk</t>
+          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['lokasi', 'strategis', 'cocok', 'untuk', 'santai', 'cocok', 'untuk', 'anakanak', 'cocok', 'untuk', 'olahraga', 'subuh', 'dengan', 'udara', 'yg', 'segar', 'dekat', 'pegunungan', 'cocok', 'untuk', 'yg', 'tua', 'muda', 'semuanya', 'tinggal', 'd', 'jaga', 'bersama', 'sama', 'jangan', 'vandalisme', 'dan', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
+          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['lokasi', 'strategis', 'cocok', 'santai', 'cocok', 'anakanak', 'cocok', 'olahraga', 'subuh', 'udara', 'yg', 'segar', 'pegunungan', 'cocok', 'yg', 'tua', 'muda', 'tinggal', 'd', 'jaga', 'vandalisme', 'mengotorinya', 'dgn', 'sampahokkkk']</t>
+          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lokasi strategis cocok santai cocok anakanak cocok olahraga subuh udara yg segar gunung cocok yg tua muda tinggal d jaga vandalisme kotor dgn sampahokkkk</t>
+          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -936,89 +936,89 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pantai Twenty Cipatuguran</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
+          <t>The toilets are dirty and only want money and almost every location is full of rubbish, even though it's a shame that the place is as neat as this but it's not well maintained.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
+          <t>the toilets are dirty and only want money and almost every location is full of rubbish even though its a shame that the place is as neat as this but its not well maintained</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
+          <t>['the', 'toilets', 'are', 'dirty', 'and', 'only', 'want', 'money', 'and', 'almost', 'every', 'location', 'is', 'full', 'of', 'rubbish', 'even', 'though', 'its', 'a', 'shame', 'that', 'the', 'place', 'is', 'as', 'neat', 'as', 'this', 'but', 'its', 'not', 'well', 'maintained']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
+          <t>['the', 'toilets', 'are', 'dirty', 'and', 'only', 'want', 'money', 'and', 'almost', 'every', 'location', 'is', 'full', 'of', 'rubbish', 'even', 'though', 'its', 'a', 'shame', 'that', 'the', 'place', 'is', 'as', 'neat', 'as', 'this', 'but', 'its', 'not', 'well', 'maintained']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
+          <t>the toilets are dirty and only want money and almost every location is full of rubbish even though its a shame that the place is as neat as this but its not well maintained</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cocok untuk jalan-jalan santai, tidak terlalu ramai, sejuk</t>
+          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>cocok untuk jalanjalan santai tidak terlalu ramai sejuk</t>
+          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['cocok', 'untuk', 'jalanjalan', 'santai', 'tidak', 'terlalu', 'ramai', 'sejuk']</t>
+          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['cocok', 'jalanjalan', 'santai', 'ramai', 'sejuk']</t>
+          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>cocok jalanjalan santai ramai sejuk</t>
+          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1030,42 +1030,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A fairly comfortable place to hang out, but there are no supporting facilities, such as stalls, cafes, toilets, etc.</t>
+          <t>Di kelola oleh oknum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>a fairly comfortable place to hang out but there are no supporting facilities such as stalls cafes toilets etc</t>
+          <t>di kelola oleh oknum</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['a', 'fairly', 'comfortable', 'place', 'to', 'hang', 'out', 'but', 'there', 'are', 'no', 'supporting', 'facilities', 'such', 'as', 'stalls', 'cafes', 'toilets', 'etc']</t>
+          <t>['di', 'kelola', 'oleh', 'oknum']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['a', 'fairly', 'comfortable', 'place', 'to', 'hang', 'out', 'but', 'there', 'are', 'no', 'supporting', 'facilities', 'such', 'as', 'stalls', 'cafes', 'toilets', 'etc']</t>
+          <t>['kelola', 'oknum']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>a fairly comfortable place to hang out but there are no supporting facilities such as stalls cafes toilets etc</t>
+          <t>kelola oknum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1082,84 +1082,84 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
+          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
+          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
+          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
+          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
+          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>LAND</t>
+          <t>GEND</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Di kelola oleh oknum</t>
+          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>di kelola oleh oknum</t>
+          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['di', 'kelola', 'oleh', 'oknum']</t>
+          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['kelola', 'oknum']</t>
+          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>kelola oknum</t>
+          <t>cocok libur pekan rekomendasi libur pantai</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1171,89 +1171,89 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jalanya mantap</t>
+          <t>A hidden gem, visit at dusk or dawn to watch the sunrise and sunset. It offers one of the best views for sunsets. However, the place is sparsely populated and poorly maintained. The local government should contribute to maintaining and supporting tourism in the Pelabuhan Ratu area.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jalanya mantap</t>
+          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the pelabuhan ratu area</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['jalanya', 'mantap']</t>
+          <t>['a', 'hidden', 'gem', 'visit', 'at', 'dusk', 'or', 'dawn', 'to', 'watch', 'the', 'sunrise', 'and', 'sunset', 'it', 'offers', 'one', 'of', 'the', 'best', 'views', 'for', 'sunsets', 'however', 'the', 'place', 'is', 'sparsely', 'populated', 'and', 'poorly', 'maintained', 'the', 'local', 'government', 'should', 'contribute', 'to', 'maintaining', 'and', 'supporting', 'tourism', 'in', 'the', 'pelabuhan', 'ratu', 'area']</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jala mantap</t>
+          <t>a hidden gem visit at dusk or dawn to watch the sunrise and sunset it offers one of the best views for sunsets however the place is sparsely populated and poorly maintained the local government should contribute to maintaining and supporting tourism in the labuh ratu area</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Taman Bunga Gunung Sumping</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Saya suka dgn tempat nya.. nyaman untuk bermain anak2.. tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>saya suka dgn tempat nya nyaman untuk bermain anak tp saya gk nyaman sama anak remaja yg sering kali menjadikan tempat pacaran</t>
+          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['saya', 'suka', 'dgn', 'tempat', 'nya', 'nyaman', 'untuk', 'bermain', 'anak', 'tp', 'saya', 'gk', 'nyaman', 'sama', 'anak', 'remaja', 'yg', 'sering', 'kali', 'menjadikan', 'tempat', 'pacaran']</t>
+          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['suka', 'dgn', 'nya', 'nyaman', 'bermain', 'anak', 'tp', 'gk', 'nyaman', 'anak', 'remaja', 'yg', 'kali', 'menjadikan', 'pacaran']</t>
+          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>suka dgn nya nyaman main anak tp gk nyaman anak remaja yg kali jadi pacar</t>
+          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1265,42 +1265,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya, ada warung jajanan d sekitar dan para pengamen, pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â¦</t>
+          <t>Pagi,siang mlm ramai pedagang smua murah meriah. Buat nongkrong smua usia jgn lupa silakan berkunjung, anda pasti suka....</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>saat ini di posting suasana pantai begitu sepi terlihat beberapa pengunjung sedang menikmati liburan pantainya ada warung jajanan d sekitar dan para pengamen pantai yg begitu kurang kesadaran pengunjungnya terhadap kebersihan pantai masih â</t>
+          <t>pagisiang mlm ramai pedagang smua murah meriah buat nongkrong smua usia jgn lupa silakan berkunjung anda pasti suka</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['saat', 'ini', 'di', 'posting', 'suasana', 'pantai', 'begitu', 'sepi', 'terlihat', 'beberapa', 'pengunjung', 'sedang', 'menikmati', 'liburan', 'pantainya', 'ada', 'warung', 'jajanan', 'd', 'sekitar', 'dan', 'para', 'pengamen', 'pantai', 'yg', 'begitu', 'kurang', 'kesadaran', 'pengunjungnya', 'terhadap', 'kebersihan', 'pantai', 'masih', 'â']</t>
+          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'buat', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'anda', 'pasti', 'suka']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['posting', 'suasana', 'pantai', 'sepi', 'pengunjung', 'menikmati', 'liburan', 'pantainya', 'warung', 'jajanan', 'd', 'pengamen', 'pantai', 'yg', 'kesadaran', 'pengunjungnya', 'kebersihan', 'pantai', 'â']</t>
+          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'suka']</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>posting suasana pantai sepi unjung nikmat libur pantai warung jajan d amen pantai yg sadar unjung bersih pantai</t>
+          <t>pagisiang mlm ramai dagang smua murah riah nongkrong smua usia jgn lupa sila kunjung suka</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1312,42 +1312,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A comfortable and easy-to-find spot. Hehe, the only fee is for parking. You can enjoy the beach atmosphere, and there are also great selfie spots. Snacks can be purchased around the beach. And if you're curious about riding a horse, you can pay just Rp 10,000.</t>
+          <t>Pantai nya bagus. Tapi ada vila yang bermasalah dsni.  Banyak maling nya. Dan vila tidak punya penanggungjawab keaman.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>a comfortable and easytofind spot hehe the only fee is for parking you can enjoy the beach atmosphere and there are also great selfie spots snacks can be purchased around the beach and if youre curious about riding a horse you can pay just rp</t>
+          <t>pantai nya bagus tapi ada vila yang bermasalah dsni banyak maling nya dan vila tidak punya penanggungjawab keaman</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['a', 'comfortable', 'and', 'easytofind', 'spot', 'hehe', 'the', 'only', 'fee', 'is', 'for', 'parking', 'you', 'can', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'also', 'great', 'selfie', 'spots', 'snacks', 'can', 'be', 'purchased', 'around', 'the', 'beach', 'and', 'if', 'youre', 'curious', 'about', 'riding', 'a', 'horse', 'you', 'can', 'pay', 'just', 'rp']</t>
+          <t>['pantai', 'nya', 'bagus', 'tapi', 'ada', 'vila', 'yang', 'bermasalah', 'dsni', 'banyak', 'maling', 'nya', 'dan', 'vila', 'tidak', 'punya', 'penanggungjawab', 'keaman']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['a', 'comfortable', 'and', 'easytofind', 'spot', 'hehe', 'the', 'only', 'fee', 'is', 'for', 'parking', 'you', 'can', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'also', 'great', 'selfie', 'spots', 'snacks', 'can', 'be', 'purchased', 'around', 'the', 'beach', 'and', 'if', 'youre', 'curious', 'about', 'riding', 'a', 'horse', 'you', 'can', 'pay', 'just', 'rp']</t>
+          <t>['pantai', 'nya', 'bagus', 'vila', 'bermasalah', 'dsni', 'maling', 'nya', 'vila', 'penanggungjawab', 'keaman']</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>a comfortable and easytofind spot hehe the only fee is for parking you can enjoy the beach atmosphere and there are also great selfie spots snacks can be purchased around the beach and if youre curious about riding a horse you can pay just rp</t>
+          <t>pantai nya bagus vila masalah dsni maling nya vila penanggungjawab aman</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1359,42 +1359,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The place is not as big as other town squares, but the atmosphere is calm and beautiful, the mosque is nice, and the parking is quite good.</t>
+          <t>Lapangan nya  luas &amp; bersih lgi pokonya mantapp</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
+          <t>lapangan nya luas bersih lgi pokonya mantapp</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
+          <t>['lapangan', 'nya', 'luas', 'bersih', 'lgi', 'pokonya', 'mantapp']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['the', 'place', 'is', 'not', 'as', 'big', 'as', 'other', 'town', 'squares', 'but', 'the', 'atmosphere', 'is', 'calm', 'and', 'beautiful', 'the', 'mosque', 'is', 'nice', 'and', 'the', 'parking', 'is', 'quite', 'good']</t>
+          <t>['lapangan', 'nya', 'luas', 'bersih', 'lgi', 'pokonya', 'mantapp']</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>the place is not as big as other town squares but the atmosphere is calm and beautiful the mosque is nice and the parking is quite good</t>
+          <t>lapang nya luas bersih lgi poko mantapp</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1406,42 +1406,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>PANTAI CIBANGBAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
+          <t>Pemandangan baik,bagus,hanya saja tempat ganti pakaian/mandi agak kurang rapih saja</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
+          <t>pemandangan baikbagushanya saja tempat ganti pakaianmandi agak kurang rapih saja</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['pemandangan', 'baikbagushanya', 'saja', 'tempat', 'ganti', 'pakaianmandi', 'agak', 'kurang', 'rapih', 'saja']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'mengisi', 'liburan', 'keluarga', 'teman', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'angkutan', 'terletak', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['pemandangan', 'baikbagushanya', 'ganti', 'pakaianmandi', 'rapih']</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok isi libur keluarga teman praktek renang tiket murah riah letak nya strategis jangkau angkut letak sebrang pantai citepus palabuan ratu</t>
+          <t>pandang baikbagushanya ganti pakaianmandi rapih</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1453,136 +1453,136 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tujuan utama transit, hingga persiapan jalan mengunjungi objekÂ² wisata Pantai yang ada, hingga kembali untuk persiapan pulang lagi ke Kota asal Saya (Bogor). "AAPR lokasi multi kenangan penuh kekeluargaan..."</t>
+          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tujuan utama transit hingga persiapan jalan mengunjungi objekâ² wisata pantai yang ada hingga kembali untuk persiapan pulang lagi ke kota asal saya bogor aapr lokasi multi kenangan penuh kekeluargaan</t>
+          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'hingga', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'yang', 'ada', 'hingga', 'kembali', 'untuk', 'persiapan', 'pulang', 'lagi', 'ke', 'kota', 'asal', 'saya', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['tujuan', 'utama', 'transit', 'persiapan', 'jalan', 'mengunjungi', 'objekâ²', 'wisata', 'pantai', 'persiapan', 'pulang', 'kota', 'bogor', 'aapr', 'lokasi', 'multi', 'kenangan', 'penuh', 'kekeluargaan']</t>
+          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tuju utama transit siap jalan unjung objek wisata pantai siap pulang kota bogor aapr lokasi multi kenang penuh keluarga</t>
+          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>Jangilus Monument</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alhamdulillah bisa berkesempatan berkunjung ke Istana Presiden di Sukabumi. Sederhana tapi keren. View tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan.</t>
+          <t>Jalanya mantap</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>alhamdulillah bisa berkesempatan berkunjung ke istana presiden di sukabumi sederhana tapi keren view tepi pantainya dgn sjmlh karang bagian bawah istan sgt menakjubkan</t>
+          <t>jalanya mantap</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'bisa', 'berkesempatan', 'berkunjung', 'ke', 'istana', 'presiden', 'di', 'sukabumi', 'sederhana', 'tapi', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'bagian', 'bawah', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['alhamdulillah', 'berkesempatan', 'berkunjung', 'istana', 'presiden', 'sukabumi', 'sederhana', 'keren', 'view', 'tepi', 'pantainya', 'dgn', 'sjmlh', 'karang', 'istan', 'sgt', 'menakjubkan']</t>
+          <t>['jalanya', 'mantap']</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>alhamdulillah sempat kunjung istana presiden sukabumi sederhana keren view tepi pantai dgn sjmlh karang istan sgt takjub</t>
+          <t>jala mantap</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sekarang pantainya bersih,jadinya nyaman untuk dijadikan tempat wisata,masyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagus,dan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
+          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>sekarang pantainya bersihjadinya nyaman untuk dijadikan tempat wisatamasyarakat sukabumi akan semakin bangga karena mempunyai tempat wisata yang sangat bagusdan itu akan menambah dan memajukan roda perekonomian masyarakat sekitar</t>
+          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['sekarang', 'pantainya', 'bersihjadinya', 'nyaman', 'untuk', 'dijadikan', 'tempat', 'wisatamasyarakat', 'sukabumi', 'akan', 'semakin', 'bangga', 'karena', 'mempunyai', 'tempat', 'wisata', 'yang', 'sangat', 'bagusdan', 'itu', 'akan', 'menambah', 'dan', 'memajukan', 'roda', 'perekonomian', 'masyarakat', 'sekitar']</t>
+          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['pantainya', 'bersihjadinya', 'nyaman', 'dijadikan', 'wisatamasyarakat', 'sukabumi', 'bangga', 'wisata', 'bagusdan', 'menambah', 'memajukan', 'roda', 'perekonomian', 'masyarakat']</t>
+          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>pantai bersihjadinya nyaman jadi wisatamasyarakat sukabumi bangga wisata bagusdan tambah maju roda ekonomi masyarakat</t>
+          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1594,42 +1594,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jangilus Monument</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ikon kota palabuhanratu......bagus</t>
+          <t>A comfortable and easy-to-find spot. Hehe, the only fee is for parking. You can enjoy the beach atmosphere, and there are also great selfie spots. Snacks can be purchased around the beach. And if you're curious about riding a horse, you can pay just Rp 10,000.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ikon kota palabuhanratubagus</t>
+          <t>a comfortable and easytofind spot hehe the only fee is for parking you can enjoy the beach atmosphere and there are also great selfie spots snacks can be purchased around the beach and if youre curious about riding a horse you can pay just rp</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+          <t>['a', 'comfortable', 'and', 'easytofind', 'spot', 'hehe', 'the', 'only', 'fee', 'is', 'for', 'parking', 'you', 'can', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'also', 'great', 'selfie', 'spots', 'snacks', 'can', 'be', 'purchased', 'around', 'the', 'beach', 'and', 'if', 'youre', 'curious', 'about', 'riding', 'a', 'horse', 'you', 'can', 'pay', 'just', 'rp']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['ikon', 'kota', 'palabuhanratubagus']</t>
+          <t>['a', 'comfortable', 'and', 'easytofind', 'spot', 'hehe', 'the', 'only', 'fee', 'is', 'for', 'parking', 'you', 'can', 'enjoy', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'also', 'great', 'selfie', 'spots', 'snacks', 'can', 'be', 'purchased', 'around', 'the', 'beach', 'and', 'if', 'youre', 'curious', 'about', 'riding', 'a', 'horse', 'you', 'can', 'pay', 'just', 'rp']</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ikon kota palabuhanratubagus</t>
+          <t>a comfortable and easytofind spot hehe the only fee is for parking you can enjoy the beach atmosphere and there are also great selfie spots snacks can be purchased around the beach and if youre curious about riding a horse you can pay just rp</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1646,84 +1646,84 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The view is quite good for enjoying the sunset with the family, at this location port facilities are also being built</t>
+          <t>tempatnya bagus, view bagus pasir masih bersih. untuk masuk memang agak jauh dari jalan raya masuknya sekitar 800 meter, jika menggunakan ojek biaya sekitar 25k dan untuk jasa guide lengkap sekitar 100-120k lengkap dengan tiket masuk.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>the view is quite good for enjoying the sunset with the family at this location port facilities are also being built</t>
+          <t>tempatnya bagus view bagus pasir masih bersih untuk masuk memang agak jauh dari jalan raya masuknya sekitar meter jika menggunakan ojek biaya sekitar k dan untuk jasa guide lengkap sekitar k lengkap dengan tiket masuk</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['the', 'view', 'is', 'quite', 'good', 'for', 'enjoying', 'the', 'sunset', 'with', 'the', 'family', 'at', 'this', 'location', 'port', 'facilities', 'are', 'also', 'being', 'built']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'masih', 'bersih', 'untuk', 'masuk', 'memang', 'agak', 'jauh', 'dari', 'jalan', 'raya', 'masuknya', 'sekitar', 'meter', 'jika', 'menggunakan', 'ojek', 'biaya', 'sekitar', 'k', 'dan', 'untuk', 'jasa', 'guide', 'lengkap', 'sekitar', 'k', 'lengkap', 'dengan', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['the', 'view', 'is', 'quite', 'good', 'for', 'enjoying', 'the', 'sunset', 'with', 'the', 'family', 'at', 'this', 'location', 'port', 'facilities', 'are', 'also', 'being', 'built']</t>
+          <t>['tempatnya', 'bagus', 'view', 'bagus', 'pasir', 'bersih', 'masuk', 'jalan', 'raya', 'masuknya', 'meter', 'ojek', 'biaya', 'k', 'jasa', 'guide', 'lengkap', 'k', 'lengkap', 'tiket', 'masuk']</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>the view is quite good for enjoying the sunset with the family at this location port facilities are also being built</t>
+          <t>tempat bagus view bagus pasir bersih masuk jalan raya masuk meter ojek biaya k jasa guide lengkap k lengkap tiket masuk</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pantainya jorok..Ada sampah diapers di pinggir pantai... jijik... ga terurus.. pemerintah daerahnya bobo yaaa... hahaha</t>
+          <t>Jajahannya banyak pilihan dan enak ð Tahu crispy juara, sate padang juga mantul, cilok lumayan, cilor enak, pisang keju enak, sate2 an enak, waduh kalap pokoknya â¦</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>pantainya jorokada sampah diapers di pinggir pantai jijik ga terurus pemerintah daerahnya bobo yaaa hahaha</t>
+          <t>jajahannya banyak pilihan dan enak ð tahu crispy juara sate padang juga mantul cilok lumayan cilor enak pisang keju enak sate an enak waduh kalap pokoknya â</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'di', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['jajahannya', 'banyak', 'pilihan', 'dan', 'enak', 'ð', 'tahu', 'crispy', 'juara', 'sate', 'padang', 'juga', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'waduh', 'kalap', 'pokoknya', 'â']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['pantainya', 'jorokada', 'sampah', 'diapers', 'pinggir', 'pantai', 'jijik', 'ga', 'terurus', 'pemerintah', 'daerahnya', 'bobo', 'yaaa', 'hahaha']</t>
+          <t>['jajahannya', 'pilihan', 'enak', 'ð', 'crispy', 'juara', 'sate', 'padang', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'kalap', 'pokoknya', 'â']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>pantai jorokada sampah diapers pinggir pantai jijik ga urus perintah daerah bobo yaaa hahaha</t>
+          <t>jajah pilih enak crispy juara sate padang mantul cilok lumayan cilor enak pisang keju enak sate an enak kalap pokok</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1735,89 +1735,89 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pantai alami yang cukup nyaman buat melepas penat. Namun karena tidak ditata oleh pemerintah setempat, terlalu banyak pungli untuk fasilitas setempat. Duduk di balai kena tiba2 ada warga setempat yang nagih uang, kamar mandi 5.000, dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>Baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya. Detail bajunya bagus banget</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>pantai alami yang cukup nyaman buat melepas penat namun karena tidak ditata oleh pemerintah setempat terlalu banyak pungli untuk fasilitas setempat duduk di balai kena tiba ada warga setempat yang nagih uang kamar mandi dan fasilitas untuk buang sampah yang minim sehingga orang lebih sering buat sembarangan</t>
+          <t>baju baju yg tetsedia untuk di sewakan sangat bagus dan riquesan pembuatan baju nya sesuai banget dengan ke inginan saya detail bajunya bagus banget</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'yang', 'cukup', 'nyaman', 'buat', 'melepas', 'penat', 'namun', 'karena', 'tidak', 'ditata', 'oleh', 'pemerintah', 'setempat', 'terlalu', 'banyak', 'pungli', 'untuk', 'fasilitas', 'setempat', 'duduk', 'di', 'balai', 'kena', 'tiba', 'ada', 'warga', 'setempat', 'yang', 'nagih', 'uang', 'kamar', 'mandi', 'dan', 'fasilitas', 'untuk', 'buang', 'sampah', 'yang', 'minim', 'sehingga', 'orang', 'lebih', 'sering', 'buat', 'sembarangan']</t>
+          <t>['baju', 'baju', 'yg', 'tetsedia', 'untuk', 'di', 'sewakan', 'sangat', 'bagus', 'dan', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'dengan', 'ke', 'inginan', 'saya', 'detail', 'bajunya', 'bagus', 'banget']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['pantai', 'alami', 'nyaman', 'melepas', 'penat', 'ditata', 'pemerintah', 'pungli', 'fasilitas', 'duduk', 'balai', 'kena', 'warga', 'nagih', 'uang', 'kamar', 'mandi', 'fasilitas', 'buang', 'sampah', 'minim', 'orang', 'sembarangan']</t>
+          <t>['baju', 'baju', 'yg', 'tetsedia', 'sewakan', 'bagus', 'riquesan', 'pembuatan', 'baju', 'nya', 'sesuai', 'banget', 'inginan', 'detail', 'bajunya', 'bagus', 'banget']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>pantai alami nyaman lepas penat tata perintah pungli fasilitas duduk balai kena warga nagih uang kamar mandi fasilitas buang sampah minim orang sembarang</t>
+          <t>baju baju yg tetsedia sewa bagus riquesan buat baju nya sesuai banget ingin detail baju bagus banget</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>Kecil alun alunnya tidak ada tempat sewa bermain anak. Hanya jajanan kaki lima saja. Buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>pantainya agak kotor dan pinggir pantai kebanyakan saung saung udah kaya kontrakan saling nempel jadi malah view lautnya kehalangan</t>
+          <t>kecil alun alunnya tidak ada tempat sewa bermain anak hanya jajanan kaki lima saja buat nongkrong pun kurang menarik menurit saya</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['pantainya', 'agak', 'kotor', 'dan', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'saling', 'nempel', 'jadi', 'malah', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['kecil', 'alun', 'alunnya', 'tidak', 'ada', 'tempat', 'sewa', 'bermain', 'anak', 'hanya', 'jajanan', 'kaki', 'lima', 'saja', 'buat', 'nongkrong', 'pun', 'kurang', 'menarik', 'menurit', 'saya']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['pantainya', 'kotor', 'pinggir', 'pantai', 'kebanyakan', 'saung', 'saung', 'udah', 'kaya', 'kontrakan', 'nempel', 'view', 'lautnya', 'kehalangan']</t>
+          <t>['alun', 'alunnya', 'sewa', 'bermain', 'anak', 'jajanan', 'kaki', 'nongkrong', 'menarik', 'menurit']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>pantai kotor pinggir pantai banyak saung saung udah kaya kontra nempel view laut halang</t>
+          <t>alun alun sewa main anak jajan kaki nongkrong tarik menurit</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>LAND</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1829,42 +1829,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Smile hill Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pengamen parah..... Tiap menit... Tolong pihak terkait....biar masyarakat aman dan tenang...</t>
+          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>pengamen parah tiap menit tolong pihak terkaitbiar masyarakat aman dan tenang</t>
+          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'tiap', 'menit', 'tolong', 'pihak', 'terkaitbiar', 'masyarakat', 'aman', 'dan', 'tenang']</t>
+          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['pengamen', 'parah', 'menit', 'tolong', 'terkaitbiar', 'masyarakat', 'aman', 'tenang']</t>
+          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>amen parah menit tolong terkaitbiar masyarakat aman tenang</t>
+          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1876,42 +1876,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pantai Pelabuhan Ratu</t>
+          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The atmosphere is comfortable and pleasant. You can play in the sand on the beach, making it perfect for family outings.</t>
+          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
+          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['the', 'atmosphere', 'is', 'comfortable', 'and', 'pleasant', 'you', 'can', 'play', 'in', 'the', 'sand', 'on', 'the', 'beach', 'making', 'it', 'perfect', 'for', 'family', 'outings']</t>
+          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>the atmosphere is comfortable and pleasant you can play in the sand on the beach making it perfect for family outings</t>
+          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>DIGI</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Alun - Alun Palabuhanratu</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The staff are friendly, the beach is nice, but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower... try to take a shower in the toilet near the beach, the toilet near the floor is not suitable â¦</t>
+          <t>Palabuhanratu Square is the center of Palabuhanratu City. It is characterized by a large plot of land. Surrounding it are functional buildings. This square is located in Palabuhanratu Village, Palabuhanratu City District, precisely on Jalan Siliwangi Palabuhanratu, to the east of the Great Mosque of Palabuhanratu.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1938,22 +1938,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable â</t>
+          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
+          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['the', 'staff', 'are', 'friendly', 'the', 'beach', 'is', 'nice', 'but', 'unfortunately', 'there', 'is', 'a', 'lot', 'of', 'trash', 'and', 'you', 'have', 'to', 'go', 'to', 'the', 'mosque', 'across', 'to', 'take', 'a', 'shower', 'try', 'to', 'take', 'a', 'shower', 'in', 'the', 'toilet', 'near', 'the', 'beach', 'the', 'toilet', 'near', 'the', 'floor', 'is', 'not', 'suitable', 'â']</t>
+          <t>['palabuhanratu', 'square', 'is', 'the', 'center', 'of', 'palabuhanratu', 'city', 'it', 'is', 'characterized', 'by', 'a', 'large', 'plot', 'of', 'land', 'surrounding', 'it', 'are', 'functional', 'buildings', 'this', 'square', 'is', 'located', 'in', 'palabuhanratu', 'village', 'palabuhanratu', 'city', 'district', 'precisely', 'on', 'jalan', 'siliwangi', 'palabuhanratu', 'to', 'the', 'east', 'of', 'the', 'great', 'mosque', 'of', 'palabuhanratu']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>the staff are friendly the beach is nice but unfortunately there is a lot of trash and you have to go to the mosque across to take a shower try to take a shower in the toilet near the beach the toilet near the floor is not suitable</t>
+          <t>palabuhanratu square is the center of palabuhanratu city it is characterized by a large plot of land surrounding it are functional buildings this square is located in palabuhanratu village palabuhanratu city district precisely on jalan siliwangi palabuhanratu to the east of the great mosque of palabuhanratu</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1970,12 +1970,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ALUN ALUN GADOBANGKONG</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Konstruksi banyak yang rusak, terutama yang berbatasan dengan pasir. Mungkin tergerus ombak, sementara konstruksi tidak sesuai kondisi. Harusnya dikasih tiang pancang dan fondasi agak dalam. Tidak ada petugas pengawas, jadi orang bebas. Ada â¦</t>
+          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1985,22 +1985,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>konstruksi banyak yang rusak terutama yang berbatasan dengan pasir mungkin tergerus ombak sementara konstruksi tidak sesuai kondisi harusnya dikasih tiang pancang dan fondasi agak dalam tidak ada petugas pengawas jadi orang bebas ada â</t>
+          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['konstruksi', 'banyak', 'yang', 'rusak', 'terutama', 'yang', 'berbatasan', 'dengan', 'pasir', 'mungkin', 'tergerus', 'ombak', 'sementara', 'konstruksi', 'tidak', 'sesuai', 'kondisi', 'harusnya', 'dikasih', 'tiang', 'pancang', 'dan', 'fondasi', 'agak', 'dalam', 'tidak', 'ada', 'petugas', 'pengawas', 'jadi', 'orang', 'bebas', 'ada', 'â']</t>
+          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['konstruksi', 'rusak', 'berbatasan', 'pasir', 'tergerus', 'ombak', 'konstruksi', 'sesuai', 'kondisi', 'dikasih', 'tiang', 'pancang', 'fondasi', 'petugas', 'pengawas', 'orang', 'bebas', 'â']</t>
+          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>konstruksi rusak batas pasir gerus ombak konstruksi sesuai kondisi kasih tiang pancang fondasi tugas awas orang bebas</t>
+          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2022,37 +2022,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The toilets are dirty and only want money and almost every location is full of rubbish, even though it's a shame that the place is as neat as this but it's not well maintained.</t>
+          <t>I feel comfortable when I take my family on vacation to see the beach atmosphere, and there are quite a lot of choices of places for children to play.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>the toilets are dirty and only want money and almost every location is full of rubbish even though its a shame that the place is as neat as this but its not well maintained</t>
+          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>['the', 'toilets', 'are', 'dirty', 'and', 'only', 'want', 'money', 'and', 'almost', 'every', 'location', 'is', 'full', 'of', 'rubbish', 'even', 'though', 'its', 'a', 'shame', 'that', 'the', 'place', 'is', 'as', 'neat', 'as', 'this', 'but', 'its', 'not', 'well', 'maintained']</t>
+          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['the', 'toilets', 'are', 'dirty', 'and', 'only', 'want', 'money', 'and', 'almost', 'every', 'location', 'is', 'full', 'of', 'rubbish', 'even', 'though', 'its', 'a', 'shame', 'that', 'the', 'place', 'is', 'as', 'neat', 'as', 'this', 'but', 'its', 'not', 'well', 'maintained']</t>
+          <t>['i', 'feel', 'comfortable', 'when', 'i', 'take', 'my', 'family', 'on', 'vacation', 'to', 'see', 'the', 'beach', 'atmosphere', 'and', 'there', 'are', 'quite', 'a', 'lot', 'of', 'choices', 'of', 'places', 'for', 'children', 'to', 'play']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>the toilets are dirty and only want money and almost every location is full of rubbish even though its a shame that the place is as neat as this but its not well maintained</t>
+          <t>i feel comfortable when i take my family on vacation to see the beach atmosphere and there are quite a lot of choices of places for children to play</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2064,12 +2064,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Taman Citepus (Ruang Terbuka Hijau) RTH</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Indah bnget kampung kelahiran sy..udh 3 tahun blum nginjak kampung kelahiran..</t>
+          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>indah bnget kampung kelahiran syudh tahun blum nginjak kampung kelahiran</t>
+          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'tahun', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['indah', 'bnget', 'kampung', 'kelahiran', 'syudh', 'blum', 'nginjak', 'kampung', 'kelahiran']</t>
+          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>indah bnget kampung lahir syudh blum nginjak kampung lahir</t>
+          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2111,42 +2111,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Citepus Sukabumi</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pagi,siang mlm ramai pedagang smua murah meriah. Buat nongkrong smua usia jgn lupa silakan berkunjung, anda pasti suka....</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>pagisiang mlm ramai pedagang smua murah meriah buat nongkrong smua usia jgn lupa silakan berkunjung anda pasti suka</t>
+          <t>kamar mandinya gelap</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'buat', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'anda', 'pasti', 'suka']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['pagisiang', 'mlm', 'ramai', 'pedagang', 'smua', 'murah', 'meriah', 'nongkrong', 'smua', 'usia', 'jgn', 'lupa', 'silakan', 'berkunjung', 'suka']</t>
+          <t>['kamar', 'mandinya', 'gelap']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>pagisiang mlm ramai dagang smua murah riah nongkrong smua usia jgn lupa sila kunjung suka</t>
+          <t>kamar mandi gelap</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2158,59 +2158,59 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Batu Bintang</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jajahannya banyak pilihan dan enak ð Tahu crispy juara, sate padang juga mantul, cilok lumayan, cilor enak, pisang keju enak, sate2 an enak, waduh kalap pokoknya â¦</t>
+          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jajahannya banyak pilihan dan enak ð tahu crispy juara sate padang juga mantul cilok lumayan cilor enak pisang keju enak sate an enak waduh kalap pokoknya â</t>
+          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>['jajahannya', 'banyak', 'pilihan', 'dan', 'enak', 'ð', 'tahu', 'crispy', 'juara', 'sate', 'padang', 'juga', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'waduh', 'kalap', 'pokoknya', 'â']</t>
+          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['jajahannya', 'pilihan', 'enak', 'ð', 'crispy', 'juara', 'sate', 'padang', 'mantul', 'cilok', 'lumayan', 'cilor', 'enak', 'pisang', 'keju', 'enak', 'sate', 'an', 'enak', 'kalap', 'pokoknya', 'â']</t>
+          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>jajah pilih enak crispy juara sate padang mantul cilok lumayan cilor enak pisang keju enak sate an enak kalap pokok</t>
+          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kalau malam .. gelap bangettt  kurang pencahayaan nya .. apalagi tulisan citepusnya .. matiii</t>
+          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2220,22 +2220,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>kalau malam gelap bangettt kurang pencahayaan nya apalagi tulisan citepusnya matiii</t>
+          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>['kalau', 'malam', 'gelap', 'bangettt', 'kurang', 'pencahayaan', 'nya', 'apalagi', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['malam', 'gelap', 'bangettt', 'pencahayaan', 'nya', 'tulisan', 'citepusnya', 'matiii']</t>
+          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>malam gelap bangettt cahaya nya tulis citepusnya matiii</t>
+          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2252,42 +2252,42 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pantai Citepus</t>
+          <t>Lapang Cangehgar Pelabuhanratu</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tempatnya nyaman dan untuk fasilitasnya lumayan menunjang, untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama.</t>
+          <t>The 77th HAB ceremony at the Sukabumi Regency Ministry of Religious Affairs Office. Atmosphere in traditional attire.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tempatnya nyaman dan untuk fasilitasnya lumayan menunjang untuk para degang juga ramah jadi saya rekomendasi untuk yang mau liburan dengan membawa keluarga sangat cocok menghabiskan waktunya bersama</t>
+          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'dan', 'untuk', 'fasilitasnya', 'lumayan', 'menunjang', 'untuk', 'para', 'degang', 'juga', 'ramah', 'jadi', 'saya', 'rekomendasi', 'untuk', 'yang', 'mau', 'liburan', 'dengan', 'membawa', 'keluarga', 'sangat', 'cocok', 'menghabiskan', 'waktunya', 'bersama']</t>
+          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['tempatnya', 'nyaman', 'fasilitasnya', 'lumayan', 'menunjang', 'degang', 'ramah', 'rekomendasi', 'liburan', 'membawa', 'keluarga', 'cocok', 'menghabiskan']</t>
+          <t>['the', 'th', 'hab', 'ceremony', 'at', 'the', 'sukabumi', 'regency', 'ministry', 'of', 'religious', 'affairs', 'office', 'atmosphere', 'in', 'traditional', 'attire']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>tempat nyaman fasilitas lumayan tunjang degang ramah rekomendasi libur bawa keluarga cocok habis</t>
+          <t>the th hab ceremony at the sukabumi regency ministry of religious affairs office atmosphere in traditional attire</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2299,12 +2299,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Wisata Alam Pantai Sukawayana</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Buat yang butuh liburan dengan suasana pantai, tempat yang bergitu tertata, pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>Bagus,dan penduduk nya ramah dan baik2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2314,22 +2314,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>buat yang butuh liburan dengan suasana pantai tempat yang bergitu tertata pantai yang bersih bisa jadi slah satu pantai yang di rekomendasikean buat berlibur dengan keluarga maupun santai dengan pasangan nya</t>
+          <t>bagusdan penduduk nya ramah dan baik</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>['buat', 'yang', 'butuh', 'liburan', 'dengan', 'suasana', 'pantai', 'tempat', 'yang', 'bergitu', 'tertata', 'pantai', 'yang', 'bersih', 'bisa', 'jadi', 'slah', 'satu', 'pantai', 'yang', 'di', 'rekomendasikean', 'buat', 'berlibur', 'dengan', 'keluarga', 'maupun', 'santai', 'dengan', 'pasangan', 'nya']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['butuh', 'liburan', 'suasana', 'pantai', 'bergitu', 'tertata', 'pantai', 'bersih', 'slah', 'pantai', 'rekomendasikean', 'berlibur', 'keluarga', 'santai', 'pasangan', 'nya']</t>
+          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>butuh libur suasana pantai bergitu tata pantai bersih slah pantai rekomendasikean libur keluarga santai pasang nya</t>
+          <t>bagusdan duduk nya ramah</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2346,12 +2346,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>Please kesini bkn baru pertama kalinya, tp kesekian kalinyað¥° and aku kesini bkn d hari weekand tp d hari biasa, so aku lebih suka suasana sepi hehehe, jd lebih nikmat liat sunsetnyað+ð+, dahal setiap kesini pasti d jalan tolnya ujan tp oas â¦</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2361,22 +2363,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>kamar mandinya gelap</t>
+          <t>please kesini bkn baru pertama kalinya tp kesekian kalinyað and aku kesini bkn d hari weekand tp d hari biasa so aku lebih suka suasana sepi hehehe jd lebih nikmat liat sunsetnyað ð dahal setiap kesini pasti d jalan tolnya ujan tp oas â</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['please', 'kesini', 'bkn', 'baru', 'pertama', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'aku', 'kesini', 'bkn', 'd', 'hari', 'weekand', 'tp', 'd', 'hari', 'biasa', 'so', 'aku', 'lebih', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'lebih', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'setiap', 'kesini', 'pasti', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['kamar', 'mandinya', 'gelap']</t>
+          <t>['please', 'kesini', 'bkn', 'kalinya', 'tp', 'kesekian', 'kalinyað', 'and', 'kesini', 'bkn', 'd', 'weekand', 'tp', 'd', 'so', 'suka', 'suasana', 'sepi', 'hehehe', 'jd', 'nikmat', 'liat', 'sunsetnyað', 'ð', 'dahal', 'kesini', 'd', 'jalan', 'tolnya', 'ujan', 'tp', 'oas', 'â']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>kamar mandi gelap</t>
+          <t>please kesini bkn kali tp sekian kali and kesini bkn d weekand tp d so suka suasana sepi hehehe jd nikmat liat sunsetnya dahal kesini d jalan tol ujan tp oas</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2393,42 +2395,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Karang Sari</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Transit sebelum ke Geopark Ciletuh bs di sini. Shalat di mesjid Agung, makan ada warung Padang enak murah. Jajanan kakilimanya jg banyak.</t>
+          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>transit sebelum ke geopark ciletuh bs di sini shalat di mesjid agung makan ada warung padang enak murah jajanan kakilimanya jg banyak</t>
+          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>['transit', 'sebelum', 'ke', 'geopark', 'ciletuh', 'bs', 'di', 'sini', 'shalat', 'di', 'mesjid', 'agung', 'makan', 'ada', 'warung', 'padang', 'enak', 'murah', 'jajanan', 'kakilimanya', 'jg', 'banyak']</t>
+          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['transit', 'geopark', 'ciletuh', 'bs', 'shalat', 'mesjid', 'agung', 'makan', 'warung', 'padang', 'enak', 'murah', 'jajanan', 'kakilimanya', 'jg']</t>
+          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>transit geopark ciletuh bs shalat mesjid agung makan warung padang enak murah jajan kakilimanya jg</t>
+          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2440,47 +2442,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pantai Batu Bintang</t>
+          <t>Pantai Citepus</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pantainya bagus, dekat dengan lokasi PLTU Pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke PLTU. Tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame.</t>
+          <t>pegel bgt perjalanan nya,sampe pantat panas,akirnya kebanyakan istirahat,tp pas sampe cakep bgt,pemandangannya bagus,sukak love bgtt,next ke pantai sukabumi lain nyað«¶ð»ð«¶ð»ð«¶ð»ð«¶ð» â¦</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>pantainya bagus dekat dengan lokasi pltu pelabuhanratu dan apabila beruntung akan melihat kapal tongkang batu bara yang akan melintas ke pltu tetapi sebenarnya untuk para pengunjung dilarang untuk naik ke batu bintangnya hal ini sesuai dengan peraturan yanv tertera didalam papan reklame</t>
+          <t>pegel bgt perjalanan nyasampe pantat panasakirnya kebanyakan istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext ke pantai sukabumi lain nyaðððððððð â</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'dekat', 'dengan', 'lokasi', 'pltu', 'pelabuhanratu', 'dan', 'apabila', 'beruntung', 'akan', 'melihat', 'kapal', 'tongkang', 'batu', 'bara', 'yang', 'akan', 'melintas', 'ke', 'pltu', 'tetapi', 'sebenarnya', 'untuk', 'para', 'pengunjung', 'dilarang', 'untuk', 'naik', 'ke', 'batu', 'bintangnya', 'hal', 'ini', 'sesuai', 'dengan', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'ke', 'pantai', 'sukabumi', 'lain', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['pantainya', 'bagus', 'lokasi', 'pltu', 'pelabuhanratu', 'beruntung', 'kapal', 'tongkang', 'batu', 'bara', 'melintas', 'pltu', 'pengunjung', 'dilarang', 'batu', 'bintangnya', 'sesuai', 'peraturan', 'yanv', 'tertera', 'didalam', 'papan', 'reklame']</t>
+          <t>['pegel', 'bgt', 'perjalanan', 'nyasampe', 'pantat', 'panasakirnya', 'kebanyakan', 'istirahattp', 'pas', 'sampe', 'cakep', 'bgtpemandangannya', 'bagussukak', 'love', 'bgttnext', 'pantai', 'sukabumi', 'nyaðððððððð', 'â']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>pantai bagus lokasi pltu pelabuhanratu untung kapal tongkang batu bara lintas pltu unjung larang batu bintang sesuai atur yanv tera dalam papan reklame</t>
+          <t>gel bgt jalan nyasampe pantat panasakirnya banyak istirahattp pas sampe cakep bgtpemandangannya bagussukak love bgttnext pantai sukabumi nya</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CONF</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
@@ -2492,131 +2494,131 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sebenarnya bagus tempatnya  tapi terlalu banyak pedagang kaki lima .di tambah bnyak tangan panjang ny..tidak aman kalau mau sholat di masjid agung nya..harus hati hati klau mau shalat di masjid agungnya.</t>
+          <t>Nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak  mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang  sebab ada oknum pedagang terutama pedagang  gorengan ada bapa bapa yang menjual /mencampur gorengan sisa hari kemarinnya,yang diangetin lagi hingga  terasa keras dan basi.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>sebenarnya bagus tempatnya tapi terlalu banyak pedagang kaki lima di tambah bnyak tangan panjang nytidak aman kalau mau sholat di masjid agung nyaharus hati hati klau mau shalat di masjid agungnya</t>
+          <t>nyaman untuk nyari kuliner cuma tolong ditertibkan para pedagangnya supaya tidak mengganggu lalu lintas juga rasanya harus ada pembinaan pada para pedagang sebab ada oknum pedagang terutama pedagang gorengan ada bapa bapa yang menjual mencampur gorengan sisa hari kemarinnyayang diangetin lagi hingga terasa keras dan basi</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>['sebenarnya', 'bagus', 'tempatnya', 'tapi', 'terlalu', 'banyak', 'pedagang', 'kaki', 'lima', 'di', 'tambah', 'bnyak', 'tangan', 'panjang', 'nytidak', 'aman', 'kalau', 'mau', 'sholat', 'di', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'mau', 'shalat', 'di', 'masjid', 'agungnya']</t>
+          <t>['nyaman', 'untuk', 'nyari', 'kuliner', 'cuma', 'tolong', 'ditertibkan', 'para', 'pedagangnya', 'supaya', 'tidak', 'mengganggu', 'lalu', 'lintas', 'juga', 'rasanya', 'harus', 'ada', 'pembinaan', 'pada', 'para', 'pedagang', 'sebab', 'ada', 'oknum', 'pedagang', 'terutama', 'pedagang', 'gorengan', 'ada', 'bapa', 'bapa', 'yang', 'menjual', 'mencampur', 'gorengan', 'sisa', 'hari', 'kemarinnyayang', 'diangetin', 'lagi', 'hingga', 'terasa', 'keras', 'dan', 'basi']</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['bagus', 'tempatnya', 'pedagang', 'kaki', 'bnyak', 'tangan', 'nytidak', 'aman', 'sholat', 'masjid', 'agung', 'nyaharus', 'hati', 'hati', 'klau', 'shalat', 'masjid', 'agungnya']</t>
+          <t>['nyaman', 'nyari', 'kuliner', 'tolong', 'ditertibkan', 'pedagangnya', 'mengganggu', 'lintas', 'pembinaan', 'pedagang', 'oknum', 'pedagang', 'pedagang', 'gorengan', 'bapa', 'bapa', 'menjual', 'mencampur', 'gorengan', 'sisa', 'kemarinnyayang', 'diangetin', 'keras', 'basi']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>bagus tempat dagang kaki bnyak tangan nytidak aman sholat masjid agung nyaharus hati hati klau shalat masjid agung</t>
+          <t>nyaman nyari kuliner tolong tertib dagang ganggu lintas bina dagang oknum dagang dagang goreng bapa bapa jual campur goreng sisa kemarinnyayang diangetin keras basi</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>GEND</t>
+          <t>CONF</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>IRREL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SDH tidak terlalu bagus...kalau malam sangat gelap..bnyk lampu yg mati dan tak diperbaiki..Pedagang Kaki lima nya sih lumayan tertata rapi...</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>sdh tidak terlalu baguskalau malam sangat gelapbnyk lampu yg mati dan tak diperbaikipedagang kaki lima nya sih lumayan tertata rapi</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>['sdh', 'tidak', 'terlalu', 'baguskalau', 'malam', 'sangat', 'gelapbnyk', 'lampu', 'yg', 'mati', 'dan', 'tak', 'diperbaikipedagang', 'kaki', 'lima', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['sdh', 'baguskalau', 'malam', 'gelapbnyk', 'lampu', 'yg', 'mati', 'diperbaikipedagang', 'kaki', 'nya', 'sih', 'lumayan', 'tertata', 'rapi']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>sdh baguskalau malam gelapbnyk lampu yg mati diperbaikipedagang kaki nya sih lumayan tata rapi</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pantai Istana Presiden Pelabuhanratu</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tempat cantik.. relatif aman dr ombak krn ada karang alami peredam ombak... Cm spt biasa .. sampah yg kurang terkelola jg budaya pengunjung yg gitu lah... HATI2 BANYAK LANDAK LAUT/BULU BABI DI KARANG â¦</t>
+          <t>A place in Pelabuhan Ratu for families to play, but there are rarely any places to take shelter, a beautiful beach atmosphere, lots of traders, spacious parking, hopefully it will be better maintained and beautified so that the place will be even better.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tempat cantik relatif aman dr ombak krn ada karang alami peredam ombak cm spt biasa sampah yg kurang terkelola jg budaya pengunjung yg gitu lah hati banyak landak lautbulu babi di karang â</t>
+          <t>a place in pelabuhan ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>['tempat', 'cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'ada', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'biasa', 'sampah', 'yg', 'kurang', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'lah', 'hati', 'banyak', 'landak', 'lautbulu', 'babi', 'di', 'karang', 'â']</t>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['cantik', 'relatif', 'aman', 'dr', 'ombak', 'krn', 'karang', 'alami', 'peredam', 'ombak', 'cm', 'spt', 'sampah', 'yg', 'terkelola', 'jg', 'budaya', 'pengunjung', 'yg', 'gitu', 'hati', 'landak', 'lautbulu', 'babi', 'karang', 'â']</t>
+          <t>['a', 'place', 'in', 'pelabuhan', 'ratu', 'for', 'families', 'to', 'play', 'but', 'there', 'are', 'rarely', 'any', 'places', 'to', 'take', 'shelter', 'a', 'beautiful', 'beach', 'atmosphere', 'lots', 'of', 'traders', 'spacious', 'parking', 'hopefully', 'it', 'will', 'be', 'better', 'maintained', 'and', 'beautified', 'so', 'that', 'the', 'place', 'will', 'be', 'even', 'better']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>cantik relatif aman dr ombak krn karang alami redam ombak cm spt sampah yg kelola jg budaya unjung yg gitu hati landak lautbulu babi karang</t>
+          <t>a place in labuh ratu for families to play but there are rarely any places to take shelter a beautiful beach atmosphere lots of traders spacious parking hopefully it will be better maintained and beautified so that the place will be even better</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>DIGI</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2628,12 +2630,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Wisata Alam Pantai Sukawayana</t>
+          <t>Pantai Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bagus,dan penduduk nya ramah dan baik2</t>
+          <t>bagus,,enak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2643,22 +2645,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>bagusdan penduduk nya ramah dan baik</t>
+          <t>bagusenak buat liburan bersama keluarga</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah', 'dan', 'baik']</t>
+          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['bagusdan', 'penduduk', 'nya', 'ramah']</t>
+          <t>['bagusenak', 'liburan', 'keluarga']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>bagusdan duduk nya ramah</t>
+          <t>bagusenak libur keluarga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2667,617 +2669,6 @@
         </is>
       </c>
       <c r="I48" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Alun - Alun Palabuhanratu</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Tempat nya strategis untuk istrahat. Setelah solat d mesjid, bisa jajan dan mknan dlu, bnyak tempat jajannya, dekat dgn KFC, ATM dan toserba juga...ð â¦</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>DIGI</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>tempat nya strategis untuk istrahat setelah solat d mesjid bisa jajan dan mknan dlu bnyak tempat jajannya dekat dgn kfc atm dan toserba jugað â</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>['tempat', 'nya', 'strategis', 'untuk', 'istrahat', 'setelah', 'solat', 'd', 'mesjid', 'bisa', 'jajan', 'dan', 'mknan', 'dlu', 'bnyak', 'tempat', 'jajannya', 'dekat', 'dgn', 'kfc', 'atm', 'dan', 'toserba', 'jugað', 'â']</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>['nya', 'strategis', 'istrahat', 'solat', 'd', 'mesjid', 'jajan', 'mknan', 'dlu', 'bnyak', 'jajannya', 'dgn', 'kfc', 'atm', 'toserba', 'jugað', 'â']</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>nya strategis istrahat solat d mesjid jajan mknan dlu bnyak jajan dgn kfc atm toserba juga</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>DIGI</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Smile hill Pelabuhan Ratu</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantai,,,karena ketika kita sampai di bukit senyum,rasa lelah selama perjalanan kita,akan dibayar lunas,dengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indah,hembusan angin,birunya laut,dan kapa2,yg seakan akan berada di atas kita,,,wooooowwqq</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>tempat ini yg paling berkesan untuk siapa saja yg menuju ke pantaikarena ketika kita sampai di bukit senyumrasa lelah selama perjalanan kitaakan dibayar lunasdengan mata kita yg akan dimanjakan dengan pemandangan yg sangaatt indahhembusan anginbirunya lautdan kapayg seakan akan berada di atas kitawooooowwqq</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>['tempat', 'ini', 'yg', 'paling', 'berkesan', 'untuk', 'siapa', 'saja', 'yg', 'menuju', 'ke', 'pantaikarena', 'ketika', 'kita', 'sampai', 'di', 'bukit', 'senyumrasa', 'lelah', 'selama', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'kita', 'yg', 'akan', 'dimanjakan', 'dengan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'akan', 'berada', 'di', 'atas', 'kitawooooowwqq']</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>['yg', 'berkesan', 'yg', 'pantaikarena', 'bukit', 'senyumrasa', 'lelah', 'perjalanan', 'kitaakan', 'dibayar', 'lunasdengan', 'mata', 'yg', 'dimanjakan', 'pemandangan', 'yg', 'sangaatt', 'indahhembusan', 'anginbirunya', 'lautdan', 'kapayg', 'seakan', 'kitawooooowwqq']</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>yg kesan yg pantaikarena bukit senyumrasa lelah jalan kitaakan bayar lunasdengan mata yg manja pandang yg sangaatt indahhembusan anginbirunya lautdan kapayg akan kitawooooowwqq</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Pantai Pelabuhan Ratu</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Ada beberapa point' saya ke plara : 1. Silaturahmi ke kakak kandung 2. Jalan-jalan sebelum masuk ramadhan. â¦</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>ada beberapa point saya ke plara silaturahmi ke kakak kandung jalanjalan sebelum masuk ramadhan â</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>['ada', 'beberapa', 'point', 'saya', 'ke', 'plara', 'silaturahmi', 'ke', 'kakak', 'kandung', 'jalanjalan', 'sebelum', 'masuk', 'ramadhan', 'â']</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>['point', 'plara', 'silaturahmi', 'kakak', 'kandung', 'jalanjalan', 'masuk', 'ramadhan', 'â']</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>point plara silaturahmi kakak kandung jalanjalan masuk ramadhan</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Pantai Karang Sari</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Lebih mantap kalau cari penginapan yang beach view, jadi buka pintu kamar langsung akses beranda menuju pantai</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>lebih mantap kalau cari penginapan yang beach view jadi buka pintu kamar langsung akses beranda menuju pantai</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>['lebih', 'mantap', 'kalau', 'cari', 'penginapan', 'yang', 'beach', 'view', 'jadi', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'menuju', 'pantai']</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>['mantap', 'cari', 'penginapan', 'beach', 'view', 'buka', 'pintu', 'kamar', 'langsung', 'akses', 'beranda', 'pantai']</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>mantap cari inap beach view buka pintu kamar langsung akses beranda pantai</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Taman Bunga Gunung Sumping</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Jauh2 dateng ksini karna liat poto2 yang review bagus,haduh kok gini pas nyampe..ð­ â¦</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>jauh dateng ksini karna liat poto yang review bagushaduh kok gini pas nyampeð â</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>['jauh', 'dateng', 'ksini', 'karna', 'liat', 'poto', 'yang', 'review', 'bagushaduh', 'kok', 'gini', 'pas', 'nyampeð', 'â']</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>['dateng', 'ksini', 'karna', 'liat', 'poto', 'review', 'bagushaduh', 'gini', 'pas', 'nyampeð', 'â']</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>dateng ksini karna liat poto review bagushaduh gin pas nyampe</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Selama pake produck ini.. gk pernah kecewa!! Kerennnn deh</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>selama pake produck ini gk pernah kecewa kerennnn deh</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>['selama', 'pake', 'produck', 'ini', 'gk', 'pernah', 'kecewa', 'kerennnn', 'deh']</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>['pake', 'produck', 'gk', 'kecewa', 'kerennnn', 'deh']</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>pake produck gk kecewa kerennnn deh</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Pantai Citepus</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Pantainya bagus dengan hamparan pasir yg luas dan panjang, untuk anak anak tetap dijaga karna ombaknya lumyan besar, untuk kebersihan pantai  dari sampah sudah cukup bagus, tapi harus ditingkatkan lagi, â¦</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>pantainya bagus dengan hamparan pasir yg luas dan panjang untuk anak anak tetap dijaga karna ombaknya lumyan besar untuk kebersihan pantai dari sampah sudah cukup bagus tapi harus ditingkatkan lagi â</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'dengan', 'hamparan', 'pasir', 'yg', 'luas', 'dan', 'panjang', 'untuk', 'anak', 'anak', 'tetap', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'besar', 'untuk', 'kebersihan', 'pantai', 'dari', 'sampah', 'sudah', 'cukup', 'bagus', 'tapi', 'harus', 'ditingkatkan', 'lagi', 'â']</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>['pantainya', 'bagus', 'hamparan', 'pasir', 'yg', 'luas', 'anak', 'anak', 'dijaga', 'karna', 'ombaknya', 'lumyan', 'kebersihan', 'pantai', 'sampah', 'bagus', 'ditingkatkan', 'â']</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>pantai bagus hampar pasir yg luas anak anak jaga karna ombak lumyan bersih pantai sampah bagus tingkat</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>PANTAI CIBANGBAN</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Tidak nyaman oleh orngÂ² yg menyewakan tempat untuk istirahat/baleÂ² Krn mahal Dan sangat perhitungan...di sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d Carikan tmpt istrht Krn mrk welcome dan baikÂ².</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>tidak nyaman oleh orngâ² yg menyewakan tempat untuk istirahatbaleâ² krn mahal dan sangat perhitungandi sarankan jika berwisata ke sana bisa meminta bantuan jasa kpd penjaga pintu masuk utama untuk d carikan tmpt istrht krn mrk welcome dan baikâ²</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>['tidak', 'nyaman', 'oleh', 'orngâ²', 'yg', 'menyewakan', 'tempat', 'untuk', 'istirahatbaleâ²', 'krn', 'mahal', 'dan', 'sangat', 'perhitungandi', 'sarankan', 'jika', 'berwisata', 'ke', 'sana', 'bisa', 'meminta', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'untuk', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'dan', 'baikâ²']</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>['nyaman', 'orngâ²', 'yg', 'menyewakan', 'istirahatbaleâ²', 'krn', 'mahal', 'perhitungandi', 'sarankan', 'berwisata', 'bantuan', 'jasa', 'kpd', 'penjaga', 'pintu', 'masuk', 'utama', 'd', 'carikan', 'tmpt', 'istrht', 'krn', 'mrk', 'welcome', 'baikâ²']</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>nyaman orng yg sewa istirahatbale krn mahal perhitungandi saran wisata bantu jasa kpd jaga pintu masuk utama d cari tmpt istrht krn mrk welcome baik</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>ECON</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Pantai Pelabuhan Ratu</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>bagus,,enak buat liburan bersama keluarga</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>bagusenak buat liburan bersama keluarga</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>['bagusenak', 'buat', 'liburan', 'bersama', 'keluarga']</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>['bagusenak', 'liburan', 'keluarga']</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>bagusenak libur keluarga</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Jangilus Monument</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Tugu nyah udah di pindahin</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>tugu nyah udah di pindahin</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>['tugu', 'nyah', 'udah', 'di', 'pindahin']</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>['tugu', 'nyah', 'udah', 'pindahin']</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>tugu nyah udah pindahin</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Pantai Pelabuhan Ratu</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Cocok untuk liburan di akhir pekan. Rekomendasi untuk liburan ke pantai.</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>cocok untuk liburan di akhir pekan rekomendasi untuk liburan ke pantai</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>['cocok', 'untuk', 'liburan', 'di', 'akhir', 'pekan', 'rekomendasi', 'untuk', 'liburan', 'ke', 'pantai']</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>['cocok', 'liburan', 'pekan', 'rekomendasi', 'liburan', 'pantai']</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>cocok libur pekan rekomendasi libur pantai</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>NEUT</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Lapang Cangehgar Pelabuhanratu</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Sdh mulai banyak kerusakan. Terutama pada area olahraga. Kurang terawat tidak seperti awal awal</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>sdh mulai banyak kerusakan terutama pada area olahraga kurang terawat tidak seperti awal awal</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>['sdh', 'mulai', 'banyak', 'kerusakan', 'terutama', 'pada', 'area', 'olahraga', 'kurang', 'terawat', 'tidak', 'seperti', 'awal', 'awal']</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>['sdh', 'kerusakan', 'area', 'olahraga', 'terawat']</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>sdh rusa area olahraga awat</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>IRREL</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Pantai Karang Sari</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Cocok buat bersantai sore hari .. tegah hari pun baguss cmn panasss luar biasaa .. jga sama sampahhh nya tolong pihak2 yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>cocok buat bersantai sore hari tegah hari pun baguss cmn panasss luar biasaa jga sama sampahhh nya tolong pihak yg bertangung jawab atw pengelola bisa di perhatikan soal kebersihanya</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>['cocok', 'buat', 'bersantai', 'sore', 'hari', 'tegah', 'hari', 'pun', 'baguss', 'cmn', 'panasss', 'luar', 'biasaa', 'jga', 'sama', 'sampahhh', 'nya', 'tolong', 'pihak', 'yg', 'bertangung', 'jawab', 'atw', 'pengelola', 'bisa', 'di', 'perhatikan', 'soal', 'kebersihanya']</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>['cocok', 'bersantai', 'sore', 'tegah', 'baguss', 'cmn', 'panasss', 'biasaa', 'jga', 'sampahhh', 'nya', 'tolong', 'yg', 'bertangung', 'atw', 'pengelola', 'perhatikan', 'kebersihanya']</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>cocok santa sore tegah baguss cmn panasss biasaa jga sampahhh nya tolong yg bertangung atw kelola perhati kebersihanya</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
         <is>
           <t>IRREL</t>
         </is>

--- a/data/output/error_analysis.xlsx
+++ b/data/output/error_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,136 +466,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alun - Alun Palabuhanratu</t>
+          <t>Pantai Twenty Cipatuguran</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
+          <t>Pantai asri tapi sampahnya berserakan, walaupun tidak menggunung. Alhamdulillah tidak ada pungli ð â¦</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mesjid nya bagus tapi sayang banyak itu tuh ih ituloh apasih ya itu iya itu apa ih eta tea naon si arana nyaeta be pokonamah</t>
+          <t>pantai asri tapi sampahnya berserakan walaupun tidak menggunung alhamdulillah tidak ada pungli ð â</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['mesjid', 'nya', 'bagus', 'tapi', 'sayang', 'banyak', 'itu', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'itu', 'iya', 'itu', 'apa', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
+          <t>['pantai', 'asri', 'tapi', 'sampahnya', 'berserakan', 'walaupun', 'tidak', 'menggunung', 'alhamdulillah', 'tidak', 'ada', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['mesjid', 'nya', 'bagus', 'sayang', 'tuh', 'ih', 'ituloh', 'apasih', 'ya', 'iya', 'ih', 'eta', 'tea', 'naon', 'si', 'arana', 'nyaeta', 'be', 'pokonamah']</t>
+          <t>['pantai', 'asri', 'sampahnya', 'berserakan', 'menggunung', 'alhamdulillah', 'pungli', 'ð', 'â']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>mesjid nya bagus sayang tuh ih ituloh apasih ya iya ih eta tea naon si arana nyaeta be pokonamah</t>
+          <t>pantai asri sampah sera gunung alhamdulillah pungli</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>INFRA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pantai Citepus Sukabumi</t>
+          <t>ALUN ALUN GADOBANGKONG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tempat nya bagusss, asri bikin betah aja..ga usah ke mana2 di citepus juga oke deechhh...</t>
+          <t>Tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luas,mudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>tempat nya bagusss asri bikin betah ajaga usah ke mana di citepus juga oke deechhh</t>
+          <t>tempat di pelabuhan ratu buat main keluarga cuma jarang tempat untuk berteduh suasana pantai indah banyak tukang dagang parkiran luasmudah mudahan lebih di pelihara dan di perindah supaya tempat nya makin bagus</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['tempat', 'nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'usah', 'ke', 'mana', 'di', 'citepus', 'juga', 'oke', 'deechhh']</t>
+          <t>['tempat', 'di', 'pelabuhan', 'ratu', 'buat', 'main', 'keluarga', 'cuma', 'jarang', 'tempat', 'untuk', 'berteduh', 'suasana', 'pantai', 'indah', 'banyak', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'lebih', 'di', 'pelihara', 'dan', 'di', 'perindah', 'supaya', 'tempat', 'nya', 'makin', 'bagus']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['nya', 'bagusss', 'asri', 'bikin', 'betah', 'ajaga', 'citepus', 'oke', 'deechhh']</t>
+          <t>['pelabuhan', 'ratu', 'main', 'keluarga', 'jarang', 'berteduh', 'suasana', 'pantai', 'indah', 'tukang', 'dagang', 'parkiran', 'luasmudah', 'mudahan', 'pelihara', 'perindah', 'nya', 'bagus']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>nya bagusss asri bikin betah ajaga citepus oke deechhh</t>
+          <t>labuh ratu main keluarga jarang teduh suasana pantai indah tukang dagang parkir luasmudah mudah pelihara indah nya bagus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NEUT</t>
+          <t>ECON</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IRREL</t>
+          <t>NEUT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Waterpark Citepus Pelabuhanratu</t>
+          <t>Pantai Istana Presiden Pelabuhanratu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tmpat rekreasi yg happy fun, cocok untuk mengisi liburan bersama keluarga dan teman. Bisa juga untuk praktek renang. Tiketnya murah meriah. Letak nya strategis terjangkau oleh angkutan umum. Terletak di sebrang pantai citepus palabuan ratu.</t>
+          <t>Pantainya bagus. Ombaknya besar. Semoga dinas parawisata memberi penambahan akses penerangan. Apalagi disana ada sumber besar PLTU</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ECON</t>
+          <t>NEUT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>tmpat rekreasi yg happy fun cocok untuk mengisi liburan bersama keluarga dan teman bisa juga untuk praktek renang tiketnya murah meriah letak nya strategis terjangkau oleh angkutan umum terletak di sebrang pantai citepus palabuan ratu</t>
+          <t>pantainya bagus ombaknya besar semoga dinas parawisata memberi penambahan akses penerangan apalagi disana ada sumber besar pltu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['tmpat', 'rekreasi', 'yg', 'happy', 'fun', 'cocok', 'untuk', 'mengisi', 'liburan', 'bersama', 'keluarga', 'dan', 'teman', 'bisa', 'juga', 'untuk', 'praktek', 'renang', 'tiketnya', 'murah', 'meriah', 'letak', 'nya', 'strategis', 'terjangkau', 'oleh', 'angkutan', 'umum', 'terletak', 'di', 'sebrang', 'pantai', 'citepus', 'palabuan', 'ratu']</t>
+          <t>['pantainya